--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -3603,7 +3603,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -4119,7 +4118,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -6445,7 +6443,6 @@
       <c r="G5" s="127" t="n"/>
     </row>
     <row r="6" ht="40.5" customHeight="1" s="203"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="136" t="inlineStr">
         <is>
@@ -8072,10 +8069,6 @@
       <c r="E3" s="131" t="n"/>
       <c r="F3" s="127" t="n"/>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -8572,7 +8565,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: 2026 라인업 반영·Screen Move는 OLED 포함, Gaming GNB 미노출</t>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8595,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>Screen Move 문항 포함</t>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8625,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>Screen Move 문항 포함</t>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8655,7 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: 2026 라인업·Screen Move 반영 완료</t>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
@@ -8677,22 +8670,18 @@
           <t>https://www.lg.com/es/monitores/monitores-ultragear-gaming/</t>
         </is>
       </c>
-      <c r="D13" s="278" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E13" s="123" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="D13" s="279" t="inlineStr">
+        <is>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E13" s="123" t="n"/>
       <c r="F13" s="123" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: 라이브 확인 — 단 2026 답변 갱신 미반영(구버전 FAQ)</t>
+          <t>2026 답변 갱신 미반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8707,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: Gaming 완료(2026 갱신 미반영) · OLED PLP 미개설(404, 진행표 URL 무효)</t>
+          <t>2026 답변 갱신 미반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
@@ -8748,7 +8737,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: 2026 라인업·Screen Move 반영 완료</t>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8767,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: 2026 라인업·Screen Move 반영 완료</t>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8797,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>완료 07/06, Screen Move 포함</t>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8827,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>완료 06/22, Screen Move 포함</t>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8857,7 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>2026 라인업 반영, Gaming GNB 미노출·OLED Y</t>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
@@ -8956,7 +8945,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -10005,7 +9993,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -10555,7 +10542,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -595,7 +595,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="287">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1160,6 +1160,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1765,41 +1768,13 @@
           <t>https://www.lg.com/uk/appliances/buying-guide/fridge-freezers/type/</t>
         </is>
       </c>
-      <c r="H10" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/appliances/buying-guide/fridge-freezers/feature-performance/</t>
-        </is>
-      </c>
-      <c r="I10" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/appliances/buying-guide/fridge-freezers/size-volume/</t>
-        </is>
-      </c>
-      <c r="J10" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/appliances/buying-guide/washing-machines/type/</t>
-        </is>
-      </c>
-      <c r="K10" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/appliances/buying-guide/washing-machines/feature-performance/</t>
-        </is>
-      </c>
-      <c r="L10" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/appliances/buying-guide/washing-machines/size-capacity/</t>
-        </is>
-      </c>
-      <c r="M10" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/appliances/installation-guide/fridge-freezer/</t>
-        </is>
-      </c>
-      <c r="N10" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/appliances/installation-guide/washing-machine/</t>
-        </is>
-      </c>
+      <c r="H10" s="209" t="n"/>
+      <c r="I10" s="209" t="n"/>
+      <c r="J10" s="209" t="n"/>
+      <c r="K10" s="209" t="n"/>
+      <c r="L10" s="209" t="n"/>
+      <c r="M10" s="209" t="n"/>
+      <c r="N10" s="209" t="n"/>
       <c r="O10" s="0" t="inlineStr"/>
       <c r="P10" s="0" t="inlineStr"/>
       <c r="Q10" s="6" t="inlineStr"/>
@@ -1842,31 +1817,11 @@
           <t>https://www.lg.com/fr/electromenager/guide-d-achat/refrigerateur-congelateur-type/</t>
         </is>
       </c>
-      <c r="H11" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/electromenager/guide-d-achat/refrigerateur-congelateur-fonctionnalite/</t>
-        </is>
-      </c>
-      <c r="I11" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/electromenager/guide-d-achat/refrigerateur-congelateur-taille-et-capacite/</t>
-        </is>
-      </c>
-      <c r="J11" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/electromenager/guide-d-achat/machines-a-laver-type/</t>
-        </is>
-      </c>
-      <c r="K11" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/electromenager/guide-d-achat/machines-a-laver-fonctionnalite/</t>
-        </is>
-      </c>
-      <c r="L11" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/electromenager/guide-d-achat/machines-a-laver-taille-et-capacite/</t>
-        </is>
-      </c>
+      <c r="H11" s="209" t="n"/>
+      <c r="I11" s="209" t="n"/>
+      <c r="J11" s="209" t="n"/>
+      <c r="K11" s="209" t="n"/>
+      <c r="L11" s="209" t="n"/>
       <c r="M11" s="210" t="inlineStr"/>
       <c r="N11" s="210" t="inlineStr"/>
       <c r="O11" s="0" t="inlineStr"/>
@@ -1909,27 +1864,11 @@
       <c r="G12" s="210" t="inlineStr"/>
       <c r="H12" s="210" t="inlineStr"/>
       <c r="I12" s="210" t="inlineStr"/>
-      <c r="J12" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/de/buying-guide/washing-machines-type/</t>
-        </is>
-      </c>
+      <c r="J12" s="209" t="n"/>
       <c r="K12" s="210" t="inlineStr"/>
-      <c r="L12" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/de/buying-guide/washing-machines-size-capacity/</t>
-        </is>
-      </c>
-      <c r="M12" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/de/installation-guide/kuhlschranke/</t>
-        </is>
-      </c>
-      <c r="N12" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/de/installation-guide/waschgeraete/</t>
-        </is>
-      </c>
+      <c r="L12" s="209" t="n"/>
+      <c r="M12" s="209" t="n"/>
+      <c r="N12" s="209" t="n"/>
       <c r="O12" s="0" t="inlineStr"/>
       <c r="P12" s="0" t="inlineStr"/>
       <c r="Q12" s="6" t="inlineStr"/>
@@ -1972,31 +1911,11 @@
           <t>https://www.lg.com/it/elettrodomestici/buying-guide/fridge-freezer-type/</t>
         </is>
       </c>
-      <c r="H13" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/elettrodomestici/buying-guide/fridge-freezer-feature/</t>
-        </is>
-      </c>
-      <c r="I13" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/elettrodomestici/buying-guide/fridge-freezer-size-capacity/</t>
-        </is>
-      </c>
-      <c r="J13" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/elettrodomestici/buying-guide/washing-machines-type/</t>
-        </is>
-      </c>
-      <c r="K13" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/elettrodomestici/buying-guide/washing-machines-feature/</t>
-        </is>
-      </c>
-      <c r="L13" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/elettrodomestici/buying-guide/washing-machines-size-capacity/</t>
-        </is>
-      </c>
+      <c r="H13" s="209" t="n"/>
+      <c r="I13" s="209" t="n"/>
+      <c r="J13" s="209" t="n"/>
+      <c r="K13" s="209" t="n"/>
+      <c r="L13" s="209" t="n"/>
       <c r="M13" s="210" t="inlineStr"/>
       <c r="N13" s="210" t="inlineStr"/>
       <c r="O13" s="0" t="inlineStr"/>
@@ -2086,41 +2005,13 @@
           <t>https://www.lg.com/th/appliances/buying-guide/fridge-freezers/type/</t>
         </is>
       </c>
-      <c r="H15" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/th/appliances/buying-guide/fridge-freezers/feature/</t>
-        </is>
-      </c>
-      <c r="I15" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/th/appliances/buying-guide/fridge-freezers/size-capacity/</t>
-        </is>
-      </c>
-      <c r="J15" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/th/appliances/buying-guide/washing-machine/type/</t>
-        </is>
-      </c>
-      <c r="K15" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/th/appliances/buying-guide/washing-machine/feature-performance/</t>
-        </is>
-      </c>
-      <c r="L15" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/th/appliances/buying-guide/washing-machine/size-capacity/</t>
-        </is>
-      </c>
-      <c r="M15" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/th/appliances/installation-guide/fridge-freezer</t>
-        </is>
-      </c>
-      <c r="N15" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/th/appliances/installation-guide/washing-machine/</t>
-        </is>
-      </c>
+      <c r="H15" s="209" t="n"/>
+      <c r="I15" s="209" t="n"/>
+      <c r="J15" s="209" t="n"/>
+      <c r="K15" s="209" t="n"/>
+      <c r="L15" s="209" t="n"/>
+      <c r="M15" s="209" t="n"/>
+      <c r="N15" s="209" t="n"/>
       <c r="O15" s="0" t="inlineStr"/>
       <c r="P15" s="0" t="inlineStr"/>
       <c r="Q15" s="6" t="inlineStr"/>
@@ -2163,41 +2054,13 @@
           <t>https://www.lg.com/tw/appliance/buying-guide/kitchen/type/</t>
         </is>
       </c>
-      <c r="H16" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/appliance/buying-guide/kitchen/feature/</t>
-        </is>
-      </c>
-      <c r="I16" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/appliance/buying-guide/kitchen/size-capacity/</t>
-        </is>
-      </c>
-      <c r="J16" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/appliance/buying-guide/laundry/type/</t>
-        </is>
-      </c>
-      <c r="K16" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/appliance/buying-guide/laundry/feature/</t>
-        </is>
-      </c>
-      <c r="L16" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/appliance/buying-guide/laundry/size-capacity/</t>
-        </is>
-      </c>
-      <c r="M16" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/appliance/buying-guide/kitchen/installation/</t>
-        </is>
-      </c>
-      <c r="N16" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/appliance/buying-guide/kitchen/installation/</t>
-        </is>
-      </c>
+      <c r="H16" s="209" t="n"/>
+      <c r="I16" s="209" t="n"/>
+      <c r="J16" s="209" t="n"/>
+      <c r="K16" s="209" t="n"/>
+      <c r="L16" s="209" t="n"/>
+      <c r="M16" s="209" t="n"/>
+      <c r="N16" s="209" t="n"/>
       <c r="O16" s="0" t="inlineStr"/>
       <c r="P16" s="0" t="inlineStr"/>
       <c r="Q16" s="6" t="inlineStr"/>
@@ -2240,41 +2103,13 @@
           <t>https://www.lg.com/ph/appliances/buying-guide/fridge-freezers/type/</t>
         </is>
       </c>
-      <c r="H17" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ph/appliances/buying-guide/fridge-freezers/feature/</t>
-        </is>
-      </c>
-      <c r="I17" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ph/appliances/buying-guide/fridge-freezers/size-capacity/</t>
-        </is>
-      </c>
-      <c r="J17" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ph/appliances/buying-guide/washing-machines/type/</t>
-        </is>
-      </c>
-      <c r="K17" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ph/appliances/buying-guide/washing-machines/feature</t>
-        </is>
-      </c>
-      <c r="L17" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ph/appliances/buying-guide/washing-machines/size-capacity/</t>
-        </is>
-      </c>
-      <c r="M17" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ph/appliances/installation-guide/fridge-freezer/</t>
-        </is>
-      </c>
-      <c r="N17" s="209" t="inlineStr">
-        <is>
-          <t>http://lg.com/ph/appliances/installation-guide/washing-machine/</t>
-        </is>
-      </c>
+      <c r="H17" s="209" t="n"/>
+      <c r="I17" s="209" t="n"/>
+      <c r="J17" s="209" t="n"/>
+      <c r="K17" s="209" t="n"/>
+      <c r="L17" s="209" t="n"/>
+      <c r="M17" s="209" t="n"/>
+      <c r="N17" s="209" t="n"/>
       <c r="O17" s="0" t="inlineStr"/>
       <c r="P17" s="0" t="inlineStr"/>
       <c r="Q17" s="6" t="inlineStr"/>
@@ -2317,41 +2152,13 @@
           <t>https://www.lg.com/vn/thiet-bi-dien-gia-dung/huong-dan-mua-hang/tu-lanh/loai-tu-lanh/</t>
         </is>
       </c>
-      <c r="H18" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn/thiet-bi-dien-gia-dung/huong-dan-mua-hang/tu-lanh/tinh-nang/</t>
-        </is>
-      </c>
-      <c r="I18" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn/thiet-bi-dien-gia-dung/huong-dan-mua-hang/tu-lanh/kich-thuoc-dung-tich/</t>
-        </is>
-      </c>
-      <c r="J18" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn/thiet-bi-dien-gia-dung/huong-dan-mua-hang/giat-say/loai-giat-say/</t>
-        </is>
-      </c>
-      <c r="K18" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn/thiet-bi-dien-gia-dung/huong-dan-mua-hang/giat-say/tinh-nang/</t>
-        </is>
-      </c>
-      <c r="L18" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn/thiet-bi-dien-gia-dung/huong-dan-mua-hang/giat-say/kich-thuoc-cong-suat/</t>
-        </is>
-      </c>
-      <c r="M18" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn/thiet-bi-dien-gia-dung/huong-dan-lap-dat/tu-lanh/</t>
-        </is>
-      </c>
-      <c r="N18" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn/thiet-bi-dien-gia-dung/huong-dan-lap-dat/giat-say/</t>
-        </is>
-      </c>
+      <c r="H18" s="209" t="n"/>
+      <c r="I18" s="209" t="n"/>
+      <c r="J18" s="209" t="n"/>
+      <c r="K18" s="209" t="n"/>
+      <c r="L18" s="209" t="n"/>
+      <c r="M18" s="209" t="n"/>
+      <c r="N18" s="209" t="n"/>
       <c r="O18" s="0" t="inlineStr"/>
       <c r="P18" s="0" t="inlineStr"/>
       <c r="Q18" s="6" t="inlineStr"/>
@@ -2394,41 +2201,13 @@
           <t>https://www.lg.com/au/appliances/buying-guide/fridge-freezers/type/</t>
         </is>
       </c>
-      <c r="H19" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/appliances/buying-guide/fridge-freezers/feature-performance/</t>
-        </is>
-      </c>
-      <c r="I19" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/appliances/buying-guide/fridge-freezers/size-volume/</t>
-        </is>
-      </c>
-      <c r="J19" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/appliances/buying-guide/washing-machines/type/</t>
-        </is>
-      </c>
-      <c r="K19" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/appliances/buying-guide/washing-machines/feature-performance/</t>
-        </is>
-      </c>
-      <c r="L19" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/appliances/buying-guide/washing-machines/size-capacity/</t>
-        </is>
-      </c>
-      <c r="M19" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/appliances/installation-guide/fridge-freezer/</t>
-        </is>
-      </c>
-      <c r="N19" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/appliances/installation-guide/washing-machines/</t>
-        </is>
-      </c>
+      <c r="H19" s="209" t="n"/>
+      <c r="I19" s="209" t="n"/>
+      <c r="J19" s="209" t="n"/>
+      <c r="K19" s="209" t="n"/>
+      <c r="L19" s="209" t="n"/>
+      <c r="M19" s="209" t="n"/>
+      <c r="N19" s="209" t="n"/>
       <c r="O19" s="0" t="inlineStr"/>
       <c r="P19" s="0" t="inlineStr"/>
       <c r="Q19" s="6" t="inlineStr"/>
@@ -2471,41 +2250,13 @@
           <t>https://www.lg.com/mx/home-appliances/buying-guide/fridge-freezer/type/</t>
         </is>
       </c>
-      <c r="H20" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/mx/home-appliances/buying-guide/fridge-freezer/feature-performance/</t>
-        </is>
-      </c>
-      <c r="I20" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/mx/home-appliances/buying-guide/fridge-freezer/size-volume/</t>
-        </is>
-      </c>
-      <c r="J20" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/mx/home-appliances/buying-guide/washing-machine/type/</t>
-        </is>
-      </c>
-      <c r="K20" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/mx/home-appliances/buying-guide/washing-machine/feature-performance/</t>
-        </is>
-      </c>
-      <c r="L20" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/mx/home-appliances/buying-guide/washing-machine/size-capacity/</t>
-        </is>
-      </c>
-      <c r="M20" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/mx/home-appliances/installlation-guide/refrigerators</t>
-        </is>
-      </c>
-      <c r="N20" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/mx/home-appliances/installlation-guide/washing-machine/</t>
-        </is>
-      </c>
+      <c r="H20" s="209" t="n"/>
+      <c r="I20" s="209" t="n"/>
+      <c r="J20" s="209" t="n"/>
+      <c r="K20" s="209" t="n"/>
+      <c r="L20" s="209" t="n"/>
+      <c r="M20" s="209" t="n"/>
+      <c r="N20" s="209" t="n"/>
       <c r="O20" s="0" t="inlineStr"/>
       <c r="P20" s="0" t="inlineStr"/>
       <c r="Q20" s="6" t="inlineStr"/>
@@ -2548,41 +2299,13 @@
           <t>https://www.lg.com/co/home-appliances/buying-guide/fridge-freezer/type/</t>
         </is>
       </c>
-      <c r="H21" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/co/home-appliances/buying-guide/fridge-freezer/feature-performance/</t>
-        </is>
-      </c>
-      <c r="I21" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/co/home-appliances/buying-guide/fridge-freezer/size-volume/</t>
-        </is>
-      </c>
-      <c r="J21" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/co/home-appliances/buying-guide/washing-machine/type/</t>
-        </is>
-      </c>
-      <c r="K21" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/co/home-appliances/buying-guide/washing-machine/feature-performance/</t>
-        </is>
-      </c>
-      <c r="L21" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/co/home-appliances/buying-guide/washing-machine/size-capacity/</t>
-        </is>
-      </c>
-      <c r="M21" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/co/home-appliances/installlation-guide/refrigerators/</t>
-        </is>
-      </c>
-      <c r="N21" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/co/home-appliances/installlation-guide/washing-machine/</t>
-        </is>
-      </c>
+      <c r="H21" s="209" t="n"/>
+      <c r="I21" s="209" t="n"/>
+      <c r="J21" s="209" t="n"/>
+      <c r="K21" s="209" t="n"/>
+      <c r="L21" s="209" t="n"/>
+      <c r="M21" s="209" t="n"/>
+      <c r="N21" s="209" t="n"/>
       <c r="O21" s="0" t="inlineStr"/>
       <c r="P21" s="0" t="inlineStr"/>
       <c r="Q21" s="6" t="inlineStr"/>
@@ -2670,41 +2393,13 @@
           <t>https://www.lg.com/cl/home-appliances/buying-guide/fridge-freezer/type/</t>
         </is>
       </c>
-      <c r="H23" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cl/home-appliances/buying-guide/fridge-freezer/feature-performance/</t>
-        </is>
-      </c>
-      <c r="I23" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cl/home-appliances/buying-guide/fridge-freezer/size-volume/</t>
-        </is>
-      </c>
-      <c r="J23" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cl/home-appliances/buying-guide/washing-machine/type/</t>
-        </is>
-      </c>
-      <c r="K23" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cl/home-appliances/buying-guide/washing-machine/feature-performance/</t>
-        </is>
-      </c>
-      <c r="L23" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cl/home-appliances/buying-guide/washing-machine/size-capacity/</t>
-        </is>
-      </c>
-      <c r="M23" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cl/home-appliances/installlation-guide/refrigerators/</t>
-        </is>
-      </c>
-      <c r="N23" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cl/home-appliances/installlation-guide/washing-machine/</t>
-        </is>
-      </c>
+      <c r="H23" s="209" t="n"/>
+      <c r="I23" s="209" t="n"/>
+      <c r="J23" s="209" t="n"/>
+      <c r="K23" s="209" t="n"/>
+      <c r="L23" s="209" t="n"/>
+      <c r="M23" s="209" t="n"/>
+      <c r="N23" s="209" t="n"/>
       <c r="O23" s="0" t="inlineStr"/>
       <c r="P23" s="0" t="inlineStr"/>
       <c r="Q23" s="6" t="inlineStr"/>
@@ -2747,41 +2442,13 @@
           <t>https://www.lg.com/br/home-appliances/buying-guide/fridge-freezer/type</t>
         </is>
       </c>
-      <c r="H24" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/br/home-appliances/buying-guide/fridge-freezer/feature-performance</t>
-        </is>
-      </c>
-      <c r="I24" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/br/home-appliances/buying-guide/fridge-freezer/size-volume</t>
-        </is>
-      </c>
-      <c r="J24" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/br/home-appliances/buying-guide/washing-machine/type</t>
-        </is>
-      </c>
-      <c r="K24" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/br/home-appliances/buying-guide/washing-machine/feature-performance</t>
-        </is>
-      </c>
-      <c r="L24" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/br/home-appliances/buying-guide/washing-machine/size-capacity</t>
-        </is>
-      </c>
-      <c r="M24" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/br/home-appliances/installlation-guide/refrigerators</t>
-        </is>
-      </c>
-      <c r="N24" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/br/home-appliances/installlation-guide/washing-machine/</t>
-        </is>
-      </c>
+      <c r="H24" s="209" t="n"/>
+      <c r="I24" s="209" t="n"/>
+      <c r="J24" s="209" t="n"/>
+      <c r="K24" s="209" t="n"/>
+      <c r="L24" s="209" t="n"/>
+      <c r="M24" s="209" t="n"/>
+      <c r="N24" s="209" t="n"/>
       <c r="O24" s="0" t="inlineStr"/>
       <c r="P24" s="0" t="inlineStr"/>
       <c r="Q24" s="6" t="inlineStr"/>
@@ -2824,41 +2491,13 @@
           <t>https://www.lg.com/sa_en/home-appliances/buying-guide/fridge-freezer/type/</t>
         </is>
       </c>
-      <c r="H25" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa_en/home-appliances/buying-guide/fridge-freezer/feature-performance/</t>
-        </is>
-      </c>
-      <c r="I25" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa_en/home-appliances/buying-guide/fridge-freezer/size-volume/</t>
-        </is>
-      </c>
-      <c r="J25" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa_en/home-appliances/buying-guide/washing-machine/type/</t>
-        </is>
-      </c>
-      <c r="K25" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa_en/home-appliances/buying-guide/washing-machine/feature-performance/</t>
-        </is>
-      </c>
-      <c r="L25" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa_en/home-appliances/buying-guide/washing-machine/size-capacity/</t>
-        </is>
-      </c>
-      <c r="M25" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa_en/home-appliances/installation-guide/fridge-freezer/</t>
-        </is>
-      </c>
-      <c r="N25" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa_en/home-appliances/installation-guide/washing-machine/</t>
-        </is>
-      </c>
+      <c r="H25" s="209" t="n"/>
+      <c r="I25" s="209" t="n"/>
+      <c r="J25" s="209" t="n"/>
+      <c r="K25" s="209" t="n"/>
+      <c r="L25" s="209" t="n"/>
+      <c r="M25" s="209" t="n"/>
+      <c r="N25" s="209" t="n"/>
       <c r="O25" s="0" t="inlineStr"/>
       <c r="P25" s="0" t="inlineStr"/>
       <c r="Q25" s="6" t="inlineStr"/>
@@ -2901,41 +2540,13 @@
           <t>https://www.lg.com/sa/home-appliances/buying-guide/fridge-freezer/type/</t>
         </is>
       </c>
-      <c r="H26" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa/home-appliances/buying-guide/fridge-freezer/feature-performance/</t>
-        </is>
-      </c>
-      <c r="I26" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa/home-appliances/buying-guide/fridge-freezer/size-volume/</t>
-        </is>
-      </c>
-      <c r="J26" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa/home-appliances/buying-guide/washing-machine/type/</t>
-        </is>
-      </c>
-      <c r="K26" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa/home-appliances/buying-guide/washing-machine/feature-performance/</t>
-        </is>
-      </c>
-      <c r="L26" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa/home-appliances/buying-guide/washing-machine/size-capacity/</t>
-        </is>
-      </c>
-      <c r="M26" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa/home-appliances/installation-guide/fridge-freezer/</t>
-        </is>
-      </c>
-      <c r="N26" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa/home-appliances/installation-guide/washing-machine/</t>
-        </is>
-      </c>
+      <c r="H26" s="209" t="n"/>
+      <c r="I26" s="209" t="n"/>
+      <c r="J26" s="209" t="n"/>
+      <c r="K26" s="209" t="n"/>
+      <c r="L26" s="209" t="n"/>
+      <c r="M26" s="209" t="n"/>
+      <c r="N26" s="209" t="n"/>
       <c r="O26" s="0" t="inlineStr"/>
       <c r="P26" s="0" t="inlineStr"/>
       <c r="Q26" s="6" t="inlineStr"/>
@@ -2978,41 +2589,13 @@
           <t>https://www.lg.com/eg_en/home-appliances/buying-guide/fridge-freezer/type/</t>
         </is>
       </c>
-      <c r="H27" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_en/home-appliances/buying-guide/fridge-freezer/feature-performance/</t>
-        </is>
-      </c>
-      <c r="I27" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_en/home-appliances/buying-guide/fridge-freezer/size-volume/</t>
-        </is>
-      </c>
-      <c r="J27" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_en/home-appliances/buying-guide/washing-machine/type/</t>
-        </is>
-      </c>
-      <c r="K27" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_en/home-appliances/buying-guide/washing-machine/feature-performance/</t>
-        </is>
-      </c>
-      <c r="L27" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_en/home-appliances/buying-guide/washing-machine/size-capacity/</t>
-        </is>
-      </c>
-      <c r="M27" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_en/home-appliances/installation-guide/fridge-freezer/</t>
-        </is>
-      </c>
-      <c r="N27" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_en/home-appliances/installation-guide/washing-machine/</t>
-        </is>
-      </c>
+      <c r="H27" s="209" t="n"/>
+      <c r="I27" s="209" t="n"/>
+      <c r="J27" s="209" t="n"/>
+      <c r="K27" s="209" t="n"/>
+      <c r="L27" s="209" t="n"/>
+      <c r="M27" s="209" t="n"/>
+      <c r="N27" s="209" t="n"/>
       <c r="O27" s="0" t="inlineStr"/>
       <c r="P27" s="0" t="inlineStr"/>
       <c r="Q27" s="6" t="inlineStr"/>
@@ -3055,41 +2638,13 @@
           <t>https://www.lg.com/eg_ar/home-appliances/buying-guide/fridge-freezer/type/</t>
         </is>
       </c>
-      <c r="H28" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_ar/home-appliances/buying-guide/fridge-freezer/feature-performance/</t>
-        </is>
-      </c>
-      <c r="I28" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_ar/home-appliances/buying-guide/fridge-freezer/size-volume/</t>
-        </is>
-      </c>
-      <c r="J28" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_ar/home-appliances/buying-guide/washing-machine/type/</t>
-        </is>
-      </c>
-      <c r="K28" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_ar/home-appliances/buying-guide/washing-machine/feature-performance/</t>
-        </is>
-      </c>
-      <c r="L28" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_ar/home-appliances/buying-guide/washing-machine/size-capacity/</t>
-        </is>
-      </c>
-      <c r="M28" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_ar/home-appliances/installation-guide/fridge-freezer/</t>
-        </is>
-      </c>
-      <c r="N28" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_ar/home-appliances/installation-guide/washing-machine/</t>
-        </is>
-      </c>
+      <c r="H28" s="209" t="n"/>
+      <c r="I28" s="209" t="n"/>
+      <c r="J28" s="209" t="n"/>
+      <c r="K28" s="209" t="n"/>
+      <c r="L28" s="209" t="n"/>
+      <c r="M28" s="209" t="n"/>
+      <c r="N28" s="209" t="n"/>
       <c r="O28" s="0" t="inlineStr"/>
       <c r="P28" s="0" t="inlineStr"/>
       <c r="Q28" s="6" t="inlineStr"/>
@@ -3380,178 +2935,66 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3603,6 +3046,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -4118,6 +3562,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -5599,53 +5044,21 @@
       <c r="I6" s="225" t="inlineStr"/>
       <c r="J6" s="224" t="inlineStr"/>
       <c r="K6" s="226" t="inlineStr"/>
-      <c r="L6" s="226" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/appliance-tips-and-guides/</t>
-        </is>
-      </c>
+      <c r="L6" s="226" t="n"/>
       <c r="M6" s="226" t="inlineStr"/>
       <c r="N6" s="226" t="inlineStr"/>
       <c r="O6" s="227" t="inlineStr"/>
       <c r="P6" s="113" t="inlineStr"/>
       <c r="Q6" s="113" t="inlineStr"/>
       <c r="R6" s="226" t="inlineStr"/>
-      <c r="S6" s="228" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa/appliance-tips-and-guides/</t>
-        </is>
-      </c>
-      <c r="T6" s="228" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa_en/appliance-tips-and-guides/</t>
-        </is>
-      </c>
-      <c r="U6" s="228" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_ar/appliance-tips-and-guides/</t>
-        </is>
-      </c>
-      <c r="V6" s="228" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_en/appliance-tips-and-guides/</t>
-        </is>
-      </c>
+      <c r="S6" s="228" t="n"/>
+      <c r="T6" s="228" t="n"/>
+      <c r="U6" s="228" t="n"/>
+      <c r="V6" s="228" t="n"/>
       <c r="W6" s="228" t="inlineStr"/>
-      <c r="X6" s="228" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/co/consejos-y-guias-sobre-electrodomesticos/</t>
-        </is>
-      </c>
-      <c r="Y6" s="228" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/pe/consejos-y-guias-de-electrodomesticos/</t>
-        </is>
-      </c>
-      <c r="Z6" s="228" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cl/consejos-y-guias-de-electrodomesticos/</t>
-        </is>
-      </c>
+      <c r="X6" s="228" t="n"/>
+      <c r="Y6" s="228" t="n"/>
+      <c r="Z6" s="228" t="n"/>
       <c r="AA6" s="228" t="inlineStr"/>
       <c r="AB6" s="228" t="inlineStr"/>
       <c r="AC6" s="228" t="inlineStr"/>
@@ -5656,21 +5069,9 @@
       <c r="AH6" s="55" t="inlineStr"/>
       <c r="AI6" s="55" t="inlineStr"/>
       <c r="AJ6" s="55" t="inlineStr"/>
-      <c r="AK6" s="55" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ee/appliances/tips-and-guides</t>
-        </is>
-      </c>
-      <c r="AL6" s="55" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/lt/appliances/tips-and-guides</t>
-        </is>
-      </c>
-      <c r="AM6" s="55" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/lv/appliances/tips-and-guides</t>
-        </is>
-      </c>
+      <c r="AK6" s="55" t="n"/>
+      <c r="AL6" s="55" t="n"/>
+      <c r="AM6" s="55" t="n"/>
       <c r="AN6" s="55" t="inlineStr"/>
       <c r="AO6" s="55" t="inlineStr"/>
       <c r="AP6" s="55" t="inlineStr"/>
@@ -6270,26 +5671,10 @@
       <c r="P16" s="113" t="inlineStr"/>
       <c r="Q16" s="113" t="inlineStr"/>
       <c r="R16" s="226" t="inlineStr"/>
-      <c r="S16" s="237" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa/appliance-tips-and-guides/refrigerators/refrigerator-size-guide/</t>
-        </is>
-      </c>
-      <c r="T16" s="223" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa_en/appliance-tips-and-guides/refrigerators/refrigerator-size-guide/</t>
-        </is>
-      </c>
-      <c r="U16" s="223" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_ar/lg-story/helpful-guide/refrigerator-size-guide/</t>
-        </is>
-      </c>
-      <c r="V16" s="223" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_en/lg-story/helpful-guide/refrigerator-size-guide/</t>
-        </is>
-      </c>
+      <c r="S16" s="237" t="n"/>
+      <c r="T16" s="223" t="n"/>
+      <c r="U16" s="223" t="n"/>
+      <c r="V16" s="223" t="n"/>
       <c r="W16" s="226" t="inlineStr"/>
       <c r="X16" s="226" t="inlineStr"/>
       <c r="Y16" s="226" t="inlineStr"/>
@@ -6314,40 +5699,25 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AK6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL6" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AM6" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/article/2025/2025-lg-experience-article/ref/article-sa-01-refrigerator_size_guide" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T16" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V16" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/article/2025/2025-lg-experience-article/ref/article-sa-01-refrigerator_size_guide" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6443,6 +5813,7 @@
       <c r="G5" s="127" t="n"/>
     </row>
     <row r="6" ht="40.5" customHeight="1" s="203"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="136" t="inlineStr">
         <is>
@@ -8069,6 +7440,10 @@
       <c r="E3" s="131" t="n"/>
       <c r="F3" s="127" t="n"/>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -8119,16 +7494,16 @@
       </c>
       <c r="D9" s="269" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E9" s="270" t="inlineStr"/>
+          <t>미반영</t>
+        </is>
+      </c>
+      <c r="E9" s="270" t="n"/>
       <c r="F9" s="177" t="n">
         <v>2</v>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: 페이지 라이브·FAQ 콘텐츠 미게시(evo·Hyper), GNB 미노출</t>
+          <t>FAQ 미게시 (evo·Hyper)</t>
         </is>
       </c>
     </row>
@@ -8143,22 +7518,18 @@
           <t>https://www.lg.com/ca_en/monitors/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D10" s="285" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E10" s="270" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+      <c r="D10" s="286" t="inlineStr">
+        <is>
+          <t>부분반영</t>
+        </is>
+      </c>
+      <c r="E10" s="270" t="n"/>
       <c r="F10" s="177" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>GNB: evo Y / Hyper N</t>
+          <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
       </c>
     </row>
@@ -8173,22 +7544,18 @@
           <t>https://www.lg.com/ca_fr/moniteurs/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D11" s="285" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E11" s="270" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+      <c r="D11" s="286" t="inlineStr">
+        <is>
+          <t>부분반영</t>
+        </is>
+      </c>
+      <c r="E11" s="270" t="n"/>
       <c r="F11" s="177" t="n">
         <v>2</v>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>GNB: evo Y / Hyper N</t>
+          <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
       </c>
     </row>
@@ -8205,16 +7572,16 @@
       </c>
       <c r="D12" s="273" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E12" s="274" t="inlineStr"/>
+          <t>미반영</t>
+        </is>
+      </c>
+      <c r="E12" s="274" t="n"/>
       <c r="F12" s="185" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: FAQ 콘텐츠 미게시(evo·Hyper), GNB 노출 중</t>
+          <t>FAQ 미게시 (evo·Hyper)</t>
         </is>
       </c>
     </row>
@@ -8231,16 +7598,16 @@
       </c>
       <c r="D13" s="273" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E13" s="270" t="inlineStr"/>
+          <t>미반영</t>
+        </is>
+      </c>
+      <c r="E13" s="270" t="n"/>
       <c r="F13" s="177" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: evo FAQ 미게시 · Hyper PLP 미개설(404)</t>
+          <t>evo FAQ 미게시 · Hyper 페이지/FAQ 게시 대기</t>
         </is>
       </c>
     </row>
@@ -8257,16 +7624,16 @@
       </c>
       <c r="D14" s="273" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E14" s="270" t="inlineStr"/>
+          <t>미반영</t>
+        </is>
+      </c>
+      <c r="E14" s="270" t="n"/>
       <c r="F14" s="177" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: FAQ 콘텐츠 미게시(evo·Hyper), GNB 노출 중</t>
+          <t>FAQ 미게시 (evo·Hyper)</t>
         </is>
       </c>
     </row>
@@ -8281,22 +7648,18 @@
           <t>https://www.lg.com/it/monitor/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D15" s="247" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E15" s="275" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
+      <c r="D15" s="273" t="inlineStr">
+        <is>
+          <t>미반영</t>
+        </is>
+      </c>
+      <c r="E15" s="275" t="n"/>
       <c r="F15" s="177" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: evo 5문항·Hyper 3문항 라이브, GNB 미노출</t>
+          <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
         </is>
       </c>
     </row>
@@ -8313,16 +7676,16 @@
       </c>
       <c r="D16" s="273" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E16" s="275" t="inlineStr"/>
+          <t>미반영</t>
+        </is>
+      </c>
+      <c r="E16" s="275" t="n"/>
       <c r="F16" s="177" t="n">
         <v>2</v>
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: PLP 미개설(404) — evo·Hyper 모두</t>
+          <t>페이지/FAQ 게시 대기 (evo·Hyper)</t>
         </is>
       </c>
     </row>
@@ -8339,7 +7702,7 @@
       </c>
       <c r="D17" s="247" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>반영</t>
         </is>
       </c>
       <c r="E17" s="270" t="inlineStr">
@@ -8350,11 +7713,7 @@
       <c r="F17" s="177" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="0" t="inlineStr">
-        <is>
-          <t>실측 07/08 확인: 라이브, GNB 노출</t>
-        </is>
-      </c>
+      <c r="G17" s="0" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="267" t="inlineStr">
@@ -8367,22 +7726,18 @@
           <t>https://www.lg.com/se/monitor/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D18" s="247" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E18" s="275" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
+      <c r="D18" s="273" t="inlineStr">
+        <is>
+          <t>미반영</t>
+        </is>
+      </c>
+      <c r="E18" s="275" t="n"/>
       <c r="F18" s="177" t="n">
         <v>2</v>
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>완료 06/22, GNB 미노출</t>
+          <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
         </is>
       </c>
     </row>
@@ -8397,22 +7752,18 @@
           <t>https://www.lg.com/uk/monitors/ultragear-evo/</t>
         </is>
       </c>
-      <c r="D19" s="247" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E19" s="275" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="D19" s="256" t="inlineStr">
+        <is>
+          <t>부분반영</t>
+        </is>
+      </c>
+      <c r="E19" s="275" t="n"/>
       <c r="F19" s="177" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>실측 07/13: evo 5문항·Hyper 라이브, GNB: evo Y / Hyper N</t>
+          <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
       </c>
     </row>
@@ -8945,6 +8296,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -9993,6 +9345,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -10542,6 +9895,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -1763,11 +1763,7 @@
       <c r="F10" s="209" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/appliances/buying-guide/fridge-freezers/type/</t>
-        </is>
-      </c>
+      <c r="G10" s="209" t="n"/>
       <c r="H10" s="209" t="n"/>
       <c r="I10" s="209" t="n"/>
       <c r="J10" s="209" t="n"/>
@@ -1812,11 +1808,7 @@
       <c r="F11" s="209" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/electromenager/guide-d-achat/refrigerateur-congelateur-type/</t>
-        </is>
-      </c>
+      <c r="G11" s="209" t="n"/>
       <c r="H11" s="209" t="n"/>
       <c r="I11" s="209" t="n"/>
       <c r="J11" s="209" t="n"/>
@@ -1906,11 +1898,7 @@
       <c r="F13" s="209" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/elettrodomestici/buying-guide/fridge-freezer-type/</t>
-        </is>
-      </c>
+      <c r="G13" s="209" t="n"/>
       <c r="H13" s="209" t="n"/>
       <c r="I13" s="209" t="n"/>
       <c r="J13" s="209" t="n"/>
@@ -2000,11 +1988,7 @@
       <c r="F15" s="209" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/th/appliances/buying-guide/fridge-freezers/type/</t>
-        </is>
-      </c>
+      <c r="G15" s="209" t="n"/>
       <c r="H15" s="209" t="n"/>
       <c r="I15" s="209" t="n"/>
       <c r="J15" s="209" t="n"/>
@@ -2049,11 +2033,7 @@
       <c r="F16" s="209" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/appliance/buying-guide/kitchen/type/</t>
-        </is>
-      </c>
+      <c r="G16" s="209" t="n"/>
       <c r="H16" s="209" t="n"/>
       <c r="I16" s="209" t="n"/>
       <c r="J16" s="209" t="n"/>
@@ -2098,11 +2078,7 @@
       <c r="F17" s="209" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ph/appliances/buying-guide/fridge-freezers/type/</t>
-        </is>
-      </c>
+      <c r="G17" s="209" t="n"/>
       <c r="H17" s="209" t="n"/>
       <c r="I17" s="209" t="n"/>
       <c r="J17" s="209" t="n"/>
@@ -2147,11 +2123,7 @@
       <c r="F18" s="209" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn/thiet-bi-dien-gia-dung/huong-dan-mua-hang/tu-lanh/loai-tu-lanh/</t>
-        </is>
-      </c>
+      <c r="G18" s="209" t="n"/>
       <c r="H18" s="209" t="n"/>
       <c r="I18" s="209" t="n"/>
       <c r="J18" s="209" t="n"/>
@@ -2196,11 +2168,7 @@
       <c r="F19" s="213" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/appliances/buying-guide/fridge-freezers/type/</t>
-        </is>
-      </c>
+      <c r="G19" s="209" t="n"/>
       <c r="H19" s="209" t="n"/>
       <c r="I19" s="209" t="n"/>
       <c r="J19" s="209" t="n"/>
@@ -2245,11 +2213,7 @@
       <c r="F20" s="209" t="n">
         <v>4</v>
       </c>
-      <c r="G20" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/mx/home-appliances/buying-guide/fridge-freezer/type/</t>
-        </is>
-      </c>
+      <c r="G20" s="209" t="n"/>
       <c r="H20" s="209" t="n"/>
       <c r="I20" s="209" t="n"/>
       <c r="J20" s="209" t="n"/>
@@ -2294,11 +2258,7 @@
       <c r="F21" s="209" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/co/home-appliances/buying-guide/fridge-freezer/type/</t>
-        </is>
-      </c>
+      <c r="G21" s="209" t="n"/>
       <c r="H21" s="209" t="n"/>
       <c r="I21" s="209" t="n"/>
       <c r="J21" s="209" t="n"/>
@@ -2388,11 +2348,7 @@
       <c r="F23" s="209" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cl/home-appliances/buying-guide/fridge-freezer/type/</t>
-        </is>
-      </c>
+      <c r="G23" s="209" t="n"/>
       <c r="H23" s="209" t="n"/>
       <c r="I23" s="209" t="n"/>
       <c r="J23" s="209" t="n"/>
@@ -2437,11 +2393,7 @@
       <c r="F24" s="209" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/br/home-appliances/buying-guide/fridge-freezer/type</t>
-        </is>
-      </c>
+      <c r="G24" s="209" t="n"/>
       <c r="H24" s="209" t="n"/>
       <c r="I24" s="209" t="n"/>
       <c r="J24" s="209" t="n"/>
@@ -2486,11 +2438,7 @@
       <c r="F25" s="209" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa_en/home-appliances/buying-guide/fridge-freezer/type/</t>
-        </is>
-      </c>
+      <c r="G25" s="209" t="n"/>
       <c r="H25" s="209" t="n"/>
       <c r="I25" s="209" t="n"/>
       <c r="J25" s="209" t="n"/>
@@ -2535,11 +2483,7 @@
       <c r="F26" s="209" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa/home-appliances/buying-guide/fridge-freezer/type/</t>
-        </is>
-      </c>
+      <c r="G26" s="209" t="n"/>
       <c r="H26" s="209" t="n"/>
       <c r="I26" s="209" t="n"/>
       <c r="J26" s="209" t="n"/>
@@ -2584,11 +2528,7 @@
       <c r="F27" s="209" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_en/home-appliances/buying-guide/fridge-freezer/type/</t>
-        </is>
-      </c>
+      <c r="G27" s="209" t="n"/>
       <c r="H27" s="209" t="n"/>
       <c r="I27" s="209" t="n"/>
       <c r="J27" s="209" t="n"/>
@@ -2633,11 +2573,7 @@
       <c r="F28" s="209" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="209" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/eg_ar/home-appliances/buying-guide/fridge-freezer/type/</t>
-        </is>
-      </c>
+      <c r="G28" s="209" t="n"/>
       <c r="H28" s="209" t="n"/>
       <c r="I28" s="209" t="n"/>
       <c r="J28" s="209" t="n"/>
@@ -2934,67 +2870,51 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>W16 - CineBeam S PDP Video Update</t>
+          <t>GR26-W16-MS-ITB2C-CineBeam S PDP Video Update</t>
         </is>
       </c>
       <c r="C1" s="3" t="n"/>
@@ -2966,7 +2966,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -3482,7 +3481,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -4696,7 +4694,7 @@
       </c>
       <c r="B1" s="36" t="inlineStr">
         <is>
-          <t>W16 - Copilot+ Filter Creation</t>
+          <t>GR26-W16-MS-IT-PC Copilot+ Filter Creation</t>
         </is>
       </c>
       <c r="C1" s="37" t="n"/>
@@ -5667,7 +5665,7 @@
       </c>
       <c r="B1" s="125" t="inlineStr">
         <is>
-          <t>W16 - Microsoft PDP Gallery Card</t>
+          <t>GR26-W16-MS-IT-PC PDP Gallery Card Addition for JS Global</t>
         </is>
       </c>
       <c r="C1" s="126" t="n"/>
@@ -5733,7 +5731,6 @@
       <c r="G5" s="127" t="n"/>
     </row>
     <row r="6" ht="40.5" customHeight="1" s="203"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="136" t="inlineStr">
         <is>
@@ -6219,7 +6216,7 @@
       </c>
       <c r="B1" s="163" t="inlineStr">
         <is>
-          <t>W17 - GNB Structure</t>
+          <t>GR26-W17-MS-IT-B2C GNB Structure Update 2026 – GP1</t>
         </is>
       </c>
       <c r="C1" s="164" t="n"/>
@@ -7324,7 +7321,7 @@
       </c>
       <c r="B1" s="163" t="inlineStr">
         <is>
-          <t>W18 - FAQ Request (UltraGear PLP)</t>
+          <t>GR26-W18-MS-IT UltraGear evo / Hyper Mini LED PLP FAQ Creation</t>
         </is>
       </c>
       <c r="C1" s="164" t="n"/>
@@ -7360,10 +7357,6 @@
       <c r="E3" s="131" t="n"/>
       <c r="F3" s="127" t="n"/>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -7726,7 +7719,7 @@
       </c>
       <c r="B1" s="163" t="inlineStr">
         <is>
-          <t>W18 - UltraGear OLED FAQ Update</t>
+          <t>GR26-W18-MS-IT UltraGear / OLED Gaming Monitor PLP FAQ Update</t>
         </is>
       </c>
       <c r="C1" s="164" t="n"/>
@@ -8157,7 +8150,7 @@
       </c>
       <c r="B1" s="163" t="inlineStr">
         <is>
-          <t>W22 - UltraGear Buying Guide</t>
+          <t>GR26-W22-MS-IT UltraGear Bying Guide</t>
         </is>
       </c>
       <c r="C1" s="164" t="n"/>
@@ -8216,7 +8209,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -9265,7 +9257,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -9815,7 +9806,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -595,7 +595,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="287">
+  <cellXfs count="289">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1164,6 +1164,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7306,7 +7312,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="34.5" customWidth="1" style="203" min="3" max="3"/>
@@ -7326,8 +7332,8 @@
       </c>
       <c r="C1" s="164" t="n"/>
       <c r="D1" s="164" t="n"/>
-      <c r="E1" s="165" t="n"/>
-      <c r="F1" s="127" t="n"/>
+      <c r="F1" s="165" t="n"/>
+      <c r="G1" s="127" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -7342,8 +7348,8 @@
         </is>
       </c>
       <c r="D2" s="164" t="n"/>
-      <c r="E2" s="165" t="n"/>
-      <c r="F2" s="127" t="n"/>
+      <c r="F2" s="165" t="n"/>
+      <c r="G2" s="127" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="166" t="n"/>
@@ -7354,9 +7360,13 @@
       </c>
       <c r="C3" s="131" t="n"/>
       <c r="D3" s="131" t="n"/>
-      <c r="E3" s="131" t="n"/>
-      <c r="F3" s="127" t="n"/>
-    </row>
+      <c r="F3" s="131" t="n"/>
+      <c r="G3" s="127" t="n"/>
+    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -7380,15 +7390,20 @@
       </c>
       <c r="E8" s="266" t="inlineStr">
         <is>
+          <t>Status 2</t>
+        </is>
+      </c>
+      <c r="F8" s="266" t="inlineStr">
+        <is>
           <t>완료일</t>
         </is>
       </c>
-      <c r="F8" s="266" t="inlineStr">
+      <c r="G8" s="266" t="inlineStr">
         <is>
           <t>Page#</t>
         </is>
       </c>
-      <c r="G8" s="266" t="inlineStr">
+      <c r="H8" s="266" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
@@ -7407,14 +7422,15 @@
       </c>
       <c r="D9" s="269" t="inlineStr">
         <is>
-          <t>미반영</t>
-        </is>
-      </c>
-      <c r="E9" s="270" t="n"/>
-      <c r="F9" s="177" t="n">
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E9" s="287" t="n"/>
+      <c r="F9" s="270" t="n"/>
+      <c r="G9" s="177" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="0" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>FAQ 미게시 (evo·Hyper)</t>
         </is>
@@ -7431,16 +7447,21 @@
           <t>https://www.lg.com/ca_en/monitors/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D10" s="286" t="inlineStr">
-        <is>
-          <t>부분반영</t>
-        </is>
-      </c>
-      <c r="E10" s="270" t="n"/>
-      <c r="F10" s="177" t="n">
+      <c r="D10" s="285" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E10" s="269" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F10" s="270" t="n"/>
+      <c r="G10" s="177" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="0" t="inlineStr">
+      <c r="H10" s="0" t="inlineStr">
         <is>
           <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
@@ -7457,16 +7478,21 @@
           <t>https://www.lg.com/ca_fr/moniteurs/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D11" s="286" t="inlineStr">
-        <is>
-          <t>부분반영</t>
-        </is>
-      </c>
-      <c r="E11" s="270" t="n"/>
-      <c r="F11" s="177" t="n">
+      <c r="D11" s="285" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E11" s="269" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F11" s="270" t="n"/>
+      <c r="G11" s="177" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="0" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
@@ -7485,14 +7511,15 @@
       </c>
       <c r="D12" s="273" t="inlineStr">
         <is>
-          <t>미반영</t>
-        </is>
-      </c>
-      <c r="E12" s="274" t="n"/>
-      <c r="F12" s="185" t="n">
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E12" s="288" t="n"/>
+      <c r="F12" s="274" t="n"/>
+      <c r="G12" s="185" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="0" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>FAQ 미게시 (evo·Hyper)</t>
         </is>
@@ -7511,14 +7538,15 @@
       </c>
       <c r="D13" s="273" t="inlineStr">
         <is>
-          <t>미반영</t>
-        </is>
-      </c>
-      <c r="E13" s="270" t="n"/>
-      <c r="F13" s="177" t="n">
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E13" s="288" t="n"/>
+      <c r="F13" s="270" t="n"/>
+      <c r="G13" s="177" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="0" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>evo FAQ 미게시 · Hyper 페이지/FAQ 게시 대기</t>
         </is>
@@ -7537,14 +7565,15 @@
       </c>
       <c r="D14" s="273" t="inlineStr">
         <is>
-          <t>미반영</t>
-        </is>
-      </c>
-      <c r="E14" s="270" t="n"/>
-      <c r="F14" s="177" t="n">
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E14" s="288" t="n"/>
+      <c r="F14" s="270" t="n"/>
+      <c r="G14" s="177" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="0" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>FAQ 미게시 (evo·Hyper)</t>
         </is>
@@ -7561,16 +7590,21 @@
           <t>https://www.lg.com/it/monitor/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D15" s="273" t="inlineStr">
-        <is>
-          <t>미반영</t>
-        </is>
-      </c>
-      <c r="E15" s="275" t="n"/>
-      <c r="F15" s="177" t="n">
+      <c r="D15" s="247" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E15" s="273" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F15" s="275" t="n"/>
+      <c r="G15" s="177" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="0" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
         </is>
@@ -7589,14 +7623,15 @@
       </c>
       <c r="D16" s="273" t="inlineStr">
         <is>
-          <t>미반영</t>
-        </is>
-      </c>
-      <c r="E16" s="275" t="n"/>
-      <c r="F16" s="177" t="n">
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E16" s="288" t="n"/>
+      <c r="F16" s="275" t="n"/>
+      <c r="G16" s="177" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="0" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>페이지/FAQ 게시 대기 (evo·Hyper)</t>
         </is>
@@ -7615,18 +7650,19 @@
       </c>
       <c r="D17" s="247" t="inlineStr">
         <is>
-          <t>반영</t>
-        </is>
-      </c>
-      <c r="E17" s="270" t="inlineStr">
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E17" s="288" t="n"/>
+      <c r="F17" s="270" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="F17" s="177" t="n">
+      <c r="G17" s="177" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="0" t="n"/>
+      <c r="H17" s="0" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="267" t="inlineStr">
@@ -7639,16 +7675,21 @@
           <t>https://www.lg.com/se/monitor/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D18" s="273" t="inlineStr">
-        <is>
-          <t>미반영</t>
-        </is>
-      </c>
-      <c r="E18" s="275" t="n"/>
-      <c r="F18" s="177" t="n">
+      <c r="D18" s="247" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E18" s="273" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F18" s="275" t="n"/>
+      <c r="G18" s="177" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="0" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
         </is>
@@ -7665,16 +7706,21 @@
           <t>https://www.lg.com/uk/monitors/ultragear-evo/</t>
         </is>
       </c>
-      <c r="D19" s="256" t="inlineStr">
-        <is>
-          <t>부분반영</t>
-        </is>
-      </c>
-      <c r="E19" s="275" t="n"/>
-      <c r="F19" s="177" t="n">
+      <c r="D19" s="247" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E19" s="273" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F19" s="275" t="n"/>
+      <c r="G19" s="177" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="0" t="inlineStr">
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>evo 반영 · Hyper GNB 미노출</t>
         </is>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -7363,10 +7363,6 @@
       <c r="F3" s="131" t="n"/>
       <c r="G3" s="127" t="n"/>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -8211,37 +8207,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>AE_AR : 신규
-BD : 신규
-BE : 신규
-BR : 신규
-CAC : 신규
-CA_EN : 신규
-CA_FR : 신규
-CN : 신규
-CO : 신규
-CP : 신규
-CZ : 신규
-DK : 신규
-EC : 신규
-EE : 신규
-ES : 신규
-FI : 신규
-FR : 신규
-GR : 신규
-HK : 신규
-HK_EN : 신규
-HU : 신규
-ID : 신규
-IL : 신규
-IN : 신규
-IT : 신규
-JP : 신규
-KZ : 신규
-LT : 신규
-LV : 신규
-NL : 신규
-… 외 15건</t>
+          <t>금주 변경 없음</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -9272,24 +9238,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>AU : 신규
-CA_EN : 신규
-CA_FR : 신규
-CN : 신규
-DE : 신규
-FR : 신규
-HK : 신규
-HK_EN : 신규
-IL : 신규
-IT : 신규
-JP : 신규
-NL : 신규
-NZ : 신규
-SA : 신규
-SA_EN : 신규
-SE : 신규
-TW : 신규
-UK : 신규</t>
+          <t>금주 변경 없음</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -14,6 +14,7 @@
     <sheet name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="W28 - AI Upscaling Disclaimer" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4678,6 +4679,1741 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G71"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="166" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="163" t="inlineStr">
+        <is>
+          <t>GR26-W28-IT-PDP-AI-Upscaling-Disclaimer-Update</t>
+        </is>
+      </c>
+      <c r="C1" s="164" t="n"/>
+      <c r="D1" s="164" t="n"/>
+      <c r="E1" s="165" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" s="163" t="inlineStr">
+        <is>
+          <t>금주 신규 등록 · AI Upscaling Disclaimer Update (63 pages / 31 sites)</t>
+        </is>
+      </c>
+      <c r="C2" s="164" t="n"/>
+      <c r="D2" s="164" t="n"/>
+      <c r="E2" s="165" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="166" t="n"/>
+      <c r="B3" s="163" t="n"/>
+      <c r="C3" s="164" t="n"/>
+      <c r="D3" s="164" t="n"/>
+      <c r="E3" s="165" t="n"/>
+    </row>
+    <row r="5">
+      <c r="E5" s="127" t="n"/>
+    </row>
+    <row r="6">
+      <c r="E6" s="127" t="n"/>
+    </row>
+    <row r="7">
+      <c r="E7" s="127" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="283" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B8" s="283" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C8" s="283" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D8" s="283" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E8" s="283" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F8" s="283" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G8" s="283" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" s="203">
+      <c r="B9" s="261" t="inlineStr">
+        <is>
+          <t>AE : AE (en)</t>
+        </is>
+      </c>
+      <c r="C9" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/consumer-monitors/lg-27gm950b-b</t>
+        </is>
+      </c>
+      <c r="D9" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E9" s="123" t="n"/>
+      <c r="F9" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="261" t="inlineStr">
+        <is>
+          <t>AE_AR : AE (ar)</t>
+        </is>
+      </c>
+      <c r="C10" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae_ar/consumer-monitors/lg-27gm950b-b</t>
+        </is>
+      </c>
+      <c r="D10" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E10" s="123" t="n"/>
+      <c r="F10" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="261" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C11" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/monitors/ultragear-gaming/27gm950b/</t>
+        </is>
+      </c>
+      <c r="D11" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E11" s="123" t="n"/>
+      <c r="F11" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="261" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C12" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/gaming/27gm950b-b/</t>
+        </is>
+      </c>
+      <c r="D12" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E12" s="123" t="n"/>
+      <c r="F12" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="261" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C13" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/gaming/27gm950b-b/</t>
+        </is>
+      </c>
+      <c r="D13" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E13" s="123" t="n"/>
+      <c r="F13" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="261" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C14" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-27gm950b-b</t>
+        </is>
+      </c>
+      <c r="D14" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E14" s="123" t="n"/>
+      <c r="F14" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="261" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C15" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/monitore/gaming/27gm950b-b/</t>
+        </is>
+      </c>
+      <c r="D15" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E15" s="123" t="n"/>
+      <c r="F15" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="261" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C16" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/gaming/27gm950b-b/</t>
+        </is>
+      </c>
+      <c r="D16" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E16" s="123" t="n"/>
+      <c r="F16" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="261" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C17" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-27gm950b-b</t>
+        </is>
+      </c>
+      <c r="D17" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E17" s="123" t="n"/>
+      <c r="F17" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="261" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C18" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/gaming/27gm950b-b/</t>
+        </is>
+      </c>
+      <c r="D18" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E18" s="123" t="n"/>
+      <c r="F18" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C19" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/27gm950b-b/</t>
+        </is>
+      </c>
+      <c r="D19" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E19" s="123" t="n"/>
+      <c r="F19" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="261" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C20" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-monitoren/27gm950b-b/</t>
+        </is>
+      </c>
+      <c r="D20" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E20" s="123" t="n"/>
+      <c r="F20" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="261" t="inlineStr">
+        <is>
+          <t>SE : SE (sv)</t>
+        </is>
+      </c>
+      <c r="C21" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/monitor/ultragear-gaming/27gm950b-b/</t>
+        </is>
+      </c>
+      <c r="D21" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E21" s="123" t="n"/>
+      <c r="F21" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="261" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C22" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/gaming-monitor/27gm950b-b/</t>
+        </is>
+      </c>
+      <c r="D22" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E22" s="123" t="n"/>
+      <c r="F22" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>27GM950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="261" t="inlineStr">
+        <is>
+          <t>AE : AE (en)</t>
+        </is>
+      </c>
+      <c r="C23" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/consumer-monitors/lg-39gx950b-b</t>
+        </is>
+      </c>
+      <c r="D23" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E23" s="123" t="n"/>
+      <c r="F23" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="261" t="inlineStr">
+        <is>
+          <t>AE : AE (en)</t>
+        </is>
+      </c>
+      <c r="C24" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/business/monitors/lg-39gx950b-b</t>
+        </is>
+      </c>
+      <c r="D24" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E24" s="123" t="n"/>
+      <c r="F24" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="261" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C25" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/monitors/ultragear-gaming/39gx950b/</t>
+        </is>
+      </c>
+      <c r="D25" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E25" s="123" t="n"/>
+      <c r="F25" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="261" t="inlineStr">
+        <is>
+          <t>BE : BE (nl)</t>
+        </is>
+      </c>
+      <c r="C26" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/monitoren/ultragear-gaming-monitoren/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D26" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E26" s="123" t="n"/>
+      <c r="F26" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="261" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C27" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D27" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E27" s="123" t="n"/>
+      <c r="F27" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="261" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C28" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D28" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E28" s="123" t="n"/>
+      <c r="F28" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="261" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C29" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-39gx950b-b</t>
+        </is>
+      </c>
+      <c r="D29" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E29" s="123" t="n"/>
+      <c r="F29" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="261" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C30" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/monitore/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D30" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E30" s="123" t="n"/>
+      <c r="F30" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="261" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C31" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-39gx950b-b</t>
+        </is>
+      </c>
+      <c r="D31" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E31" s="123" t="n"/>
+      <c r="F31" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="261" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C32" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/monitors/gaming-oled/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D32" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E32" s="123" t="n"/>
+      <c r="F32" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B · SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="261" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C33" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/monitores/monitores-ultragear-evo/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D33" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E33" s="123" t="n"/>
+      <c r="F33" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="261" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C34" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/outlet/outlet-informatica/monitores/39gx950b-b-outlet/</t>
+        </is>
+      </c>
+      <c r="D34" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E34" s="123" t="n"/>
+      <c r="F34" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="261" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C35" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/gaming/39GX950B-B/</t>
+        </is>
+      </c>
+      <c r="D35" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E35" s="123" t="n"/>
+      <c r="F35" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="261" t="inlineStr">
+        <is>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C36" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk/monitors/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D36" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E36" s="123" t="n"/>
+      <c r="F36" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="261" t="inlineStr">
+        <is>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C37" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk_en/monitors/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D37" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E37" s="123" t="n"/>
+      <c r="F37" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="261" t="inlineStr">
+        <is>
+          <t>HU : HU (hu)</t>
+        </is>
+      </c>
+      <c r="C38" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hu/monitorok/ultragear-gaming-oled/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D38" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E38" s="123" t="n"/>
+      <c r="F38" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="261" t="inlineStr">
+        <is>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C39" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitor/gaming/39gx950b/</t>
+        </is>
+      </c>
+      <c r="D39" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E39" s="123" t="n"/>
+      <c r="F39" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="261" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C40" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/ultragear-gaming-oled/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D40" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E40" s="123" t="n"/>
+      <c r="F40" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C41" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D41" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E41" s="123" t="n"/>
+      <c r="F41" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C42" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/39gx950b-bajp/</t>
+        </is>
+      </c>
+      <c r="D42" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E42" s="123" t="n"/>
+      <c r="F42" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="261" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C43" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-monitoren/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D43" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E43" s="123" t="n"/>
+      <c r="F43" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="261" t="inlineStr">
+        <is>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C44" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pe/monitores/gamer/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D44" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E44" s="123" t="n"/>
+      <c r="F44" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="261" t="inlineStr">
+        <is>
+          <t>PL : PL (pl)</t>
+        </is>
+      </c>
+      <c r="C45" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pl/monitory/ultragear-gaming-oled/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D45" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E45" s="123" t="n"/>
+      <c r="F45" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="261" t="inlineStr">
+        <is>
+          <t>SA : SA (ar)</t>
+        </is>
+      </c>
+      <c r="C46" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sa/monitors/ultragear-gaming-oled/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D46" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E46" s="123" t="n"/>
+      <c r="F46" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="261" t="inlineStr">
+        <is>
+          <t>SA_EN : SA (en)</t>
+        </is>
+      </c>
+      <c r="C47" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sa_en/monitors/ultragear-gaming-oled/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D47" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E47" s="123" t="n"/>
+      <c r="F47" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="261" t="inlineStr">
+        <is>
+          <t>SE : SE (sv)</t>
+        </is>
+      </c>
+      <c r="C48" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/monitor/ultragear-gaming-oled/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D48" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E48" s="123" t="n"/>
+      <c r="F48" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="261" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C49" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/consumer-monitors/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D49" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E49" s="123" t="n"/>
+      <c r="F49" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="261" t="inlineStr">
+        <is>
+          <t>TH : TH (th)</t>
+        </is>
+      </c>
+      <c r="C50" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/th/monitors/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D50" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E50" s="123" t="n"/>
+      <c r="F50" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="261" t="inlineStr">
+        <is>
+          <t>TR : TR (tr)</t>
+        </is>
+      </c>
+      <c r="C51" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tr/monitor/ultragear-gaming-oled/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D51" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E51" s="123" t="n"/>
+      <c r="F51" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="261" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C52" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/monitors/ultragear-gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D52" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E52" s="123" t="n"/>
+      <c r="F52" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="261" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C53" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/gaming-monitor/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D53" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E53" s="123" t="n"/>
+      <c r="F53" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="261" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C54" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-32gx870b-b</t>
+        </is>
+      </c>
+      <c r="D54" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E54" s="123" t="n"/>
+      <c r="F54" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="261" t="inlineStr">
+        <is>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C55" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/gaming/32gx870b-b/</t>
+        </is>
+      </c>
+      <c r="D55" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E55" s="123" t="n"/>
+      <c r="F55" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="261" t="inlineStr">
+        <is>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C56" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk/monitors/gaming/32gx870b-b/</t>
+        </is>
+      </c>
+      <c r="D56" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E56" s="123" t="n"/>
+      <c r="F56" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="261" t="inlineStr">
+        <is>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C57" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk_en/monitors/gaming/32gx870b-b/</t>
+        </is>
+      </c>
+      <c r="D57" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E57" s="123" t="n"/>
+      <c r="F57" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C58" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/32gx870b-b/</t>
+        </is>
+      </c>
+      <c r="D58" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E58" s="123" t="n"/>
+      <c r="F58" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C59" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/32gx870b-bajp/</t>
+        </is>
+      </c>
+      <c r="D59" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E59" s="123" t="n"/>
+      <c r="F59" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="261" t="inlineStr">
+        <is>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C60" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pe/monitores/ultragear-gaming-oled/32gx870b-b/</t>
+        </is>
+      </c>
+      <c r="D60" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E60" s="123" t="n"/>
+      <c r="F60" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="261" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C61" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/consumer-monitors/gaming/32gx870b-b/</t>
+        </is>
+      </c>
+      <c r="D61" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E61" s="123" t="n"/>
+      <c r="F61" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="261" t="inlineStr">
+        <is>
+          <t>TR : TR (tr)</t>
+        </is>
+      </c>
+      <c r="C62" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tr/monitor/smart-monitorleri/32gx870b-b/</t>
+        </is>
+      </c>
+      <c r="D62" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E62" s="123" t="n"/>
+      <c r="F62" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="261" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C63" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/gaming/45gx950b/</t>
+        </is>
+      </c>
+      <c r="D63" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E63" s="123" t="n"/>
+      <c r="F63" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="0" t="inlineStr">
+        <is>
+          <t>45GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="261" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C64" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/45gx950b/</t>
+        </is>
+      </c>
+      <c r="D64" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E64" s="123" t="n"/>
+      <c r="F64" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t>45GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="261" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C65" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-45gx950b-b</t>
+        </is>
+      </c>
+      <c r="D65" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E65" s="123" t="n"/>
+      <c r="F65" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
+        <is>
+          <t>45GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="261" t="inlineStr">
+        <is>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C66" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk/monitors/gaming/45gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D66" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E66" s="123" t="n"/>
+      <c r="F66" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="0" t="inlineStr">
+        <is>
+          <t>45GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="261" t="inlineStr">
+        <is>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C67" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk_en/monitors/gaming/45gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D67" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E67" s="123" t="n"/>
+      <c r="F67" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="0" t="inlineStr">
+        <is>
+          <t>45GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C68" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/45gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D68" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E68" s="123" t="n"/>
+      <c r="F68" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="0" t="inlineStr">
+        <is>
+          <t>45GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="261" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C69" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/consumer-monitors/gaming/45gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D69" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E69" s="123" t="n"/>
+      <c r="F69" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="0" t="inlineStr">
+        <is>
+          <t>45GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="261" t="inlineStr">
+        <is>
+          <t>TR : TR (tr)</t>
+        </is>
+      </c>
+      <c r="C70" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tr/monitor/ultragear-gaming-oled/45gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D70" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E70" s="123" t="n"/>
+      <c r="F70" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
+        <is>
+          <t>45GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="261" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C71" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-gaming-ultragear/45gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D71" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E71" s="123" t="n"/>
+      <c r="F71" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="0" t="inlineStr">
+        <is>
+          <t>45GX950B</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -15,6 +15,7 @@
     <sheet name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="W28 - AI Upscaling Disclaimer" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="W28 - UL Verified Eye Comfort" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6414,6 +6415,2157 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G87"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="166" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="163" t="inlineStr">
+        <is>
+          <t>GR26-W28-IT-PDP-UL-Verified-Eye-Comfort-Feature-Upload</t>
+        </is>
+      </c>
+      <c r="C1" s="164" t="n"/>
+      <c r="D1" s="164" t="n"/>
+      <c r="E1" s="165" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" s="163" t="inlineStr">
+        <is>
+          <t>금주 신규 등록 · UL-Verified Eye Comfort Feature Upload (79 pages / 38 sites)</t>
+        </is>
+      </c>
+      <c r="C2" s="164" t="n"/>
+      <c r="D2" s="164" t="n"/>
+      <c r="E2" s="165" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="166" t="n"/>
+      <c r="B3" s="163" t="n"/>
+      <c r="C3" s="164" t="n"/>
+      <c r="D3" s="164" t="n"/>
+      <c r="E3" s="165" t="n"/>
+    </row>
+    <row r="5">
+      <c r="E5" s="127" t="n"/>
+    </row>
+    <row r="6">
+      <c r="E6" s="127" t="n"/>
+    </row>
+    <row r="7">
+      <c r="E7" s="127" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="283" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B8" s="283" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C8" s="283" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D8" s="283" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E8" s="283" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F8" s="283" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G8" s="283" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" s="203">
+      <c r="B9" s="261" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C9" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/monitors/ultragear-gaming/27gx700a-b-aau/</t>
+        </is>
+      </c>
+      <c r="D9" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E9" s="123" t="n"/>
+      <c r="F9" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="261" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C10" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-27gx700a-b</t>
+        </is>
+      </c>
+      <c r="D10" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E10" s="123" t="n"/>
+      <c r="F10" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="261" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C11" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/gaming/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D11" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E11" s="123" t="n"/>
+      <c r="F11" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="261" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C12" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors/gaming-monitors/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D12" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E12" s="123" t="n"/>
+      <c r="F12" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="261" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C13" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D13" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E13" s="123" t="n"/>
+      <c r="F13" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="261" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C14" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs/moniteurs-de-jeu/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D14" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E14" s="123" t="n"/>
+      <c r="F14" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="261" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C15" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-27gx700a-b</t>
+        </is>
+      </c>
+      <c r="D15" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E15" s="123" t="n"/>
+      <c r="F15" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="261" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C16" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/monitore/gaming/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D16" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E16" s="123" t="n"/>
+      <c r="F16" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="261" t="inlineStr">
+        <is>
+          <t>DK : DK (da)</t>
+        </is>
+      </c>
+      <c r="C17" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/skaerme/ultragear-gamerskaerme/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D17" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E17" s="123" t="n"/>
+      <c r="F17" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="261" t="inlineStr">
+        <is>
+          <t>FI : FI (fi)</t>
+        </is>
+      </c>
+      <c r="C18" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fi/naytot/lg-27gx700a-b</t>
+        </is>
+      </c>
+      <c r="D18" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E18" s="123" t="n"/>
+      <c r="F18" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="261" t="inlineStr">
+        <is>
+          <t>GR : GR (el)</t>
+        </is>
+      </c>
+      <c r="C19" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/gr/othones/lg-27gx700a-b</t>
+        </is>
+      </c>
+      <c r="D19" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E19" s="123" t="n"/>
+      <c r="F19" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="261" t="inlineStr">
+        <is>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C20" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk/monitors/gaming/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D20" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E20" s="123" t="n"/>
+      <c r="F20" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="261" t="inlineStr">
+        <is>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C21" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk_en/monitors/gaming/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D21" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E21" s="123" t="n"/>
+      <c r="F21" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="261" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C22" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-27gx700a-b</t>
+        </is>
+      </c>
+      <c r="D22" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E22" s="123" t="n"/>
+      <c r="F22" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="261" t="inlineStr">
+        <is>
+          <t>HU : HU (hu)</t>
+        </is>
+      </c>
+      <c r="C23" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hu/monitorok/ultragear-gaming-monitor/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D23" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E23" s="123" t="n"/>
+      <c r="F23" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="261" t="inlineStr">
+        <is>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C24" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitor/gaming/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D24" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E24" s="123" t="n"/>
+      <c r="F24" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="261" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C25" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-27gx700a-b</t>
+        </is>
+      </c>
+      <c r="D25" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E25" s="123" t="n"/>
+      <c r="F25" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="261" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C26" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/gaming/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D26" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E26" s="123" t="n"/>
+      <c r="F26" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C27" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D27" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E27" s="123" t="n"/>
+      <c r="F27" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="261" t="inlineStr">
+        <is>
+          <t>KZ : KZ (ru)</t>
+        </is>
+      </c>
+      <c r="C28" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/kz/monitors/gaming/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D28" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E28" s="123" t="n"/>
+      <c r="F28" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="261" t="inlineStr">
+        <is>
+          <t>NO : NO (no)</t>
+        </is>
+      </c>
+      <c r="C29" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/no/skjermer/lg-27gx700a-b</t>
+        </is>
+      </c>
+      <c r="D29" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E29" s="123" t="n"/>
+      <c r="F29" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="261" t="inlineStr">
+        <is>
+          <t>PL : PL (pl)</t>
+        </is>
+      </c>
+      <c r="C30" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pl/monitory/ultragear-gaming/27gx700a/</t>
+        </is>
+      </c>
+      <c r="D30" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E30" s="123" t="n"/>
+      <c r="F30" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="261" t="inlineStr">
+        <is>
+          <t>RO : RO (ro)</t>
+        </is>
+      </c>
+      <c r="C31" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ro/monitoare/lg-27gx700a-b</t>
+        </is>
+      </c>
+      <c r="D31" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E31" s="123" t="n"/>
+      <c r="F31" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="261" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C32" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-27gx700a-b</t>
+        </is>
+      </c>
+      <c r="D32" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E32" s="123" t="n"/>
+      <c r="F32" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="261" t="inlineStr">
+        <is>
+          <t>RU : RU (ru)</t>
+        </is>
+      </c>
+      <c r="C33" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/monitors/lg-27gx700a-b</t>
+        </is>
+      </c>
+      <c r="D33" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E33" s="123" t="n"/>
+      <c r="F33" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="261" t="inlineStr">
+        <is>
+          <t>SE : SE (sv)</t>
+        </is>
+      </c>
+      <c r="C34" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/monitor/ultragear-gaming/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D34" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E34" s="123" t="n"/>
+      <c r="F34" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="261" t="inlineStr">
+        <is>
+          <t>TR : TR (tr)</t>
+        </is>
+      </c>
+      <c r="C35" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tr/monitor/oyun-monitorleri/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D35" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E35" s="123" t="n"/>
+      <c r="F35" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="261" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C36" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/gaming/27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D36" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E36" s="123" t="n"/>
+      <c r="F36" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="261" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C37" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/gaming/27gx700a-b-27gx001-pck-uk-c/</t>
+        </is>
+      </c>
+      <c r="D37" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E37" s="123" t="n"/>
+      <c r="F37" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="261" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C38" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/gaming/lg-27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D38" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E38" s="123" t="n"/>
+      <c r="F38" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>27GX700A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="261" t="inlineStr">
+        <is>
+          <t>AE : AE (en)</t>
+        </is>
+      </c>
+      <c r="C39" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/consumer-monitors/lg-27gx790b-b</t>
+        </is>
+      </c>
+      <c r="D39" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E39" s="123" t="n"/>
+      <c r="F39" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="261" t="inlineStr">
+        <is>
+          <t>AE_AR : AE (ar)</t>
+        </is>
+      </c>
+      <c r="C40" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae_ar/consumer-monitors/lg-27gx790b-b</t>
+        </is>
+      </c>
+      <c r="D40" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E40" s="123" t="n"/>
+      <c r="F40" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="261" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C41" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/monitors/ultragear-gaming/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D41" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E41" s="123" t="n"/>
+      <c r="F41" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="261" t="inlineStr">
+        <is>
+          <t>BE_FR : BE (fr)</t>
+        </is>
+      </c>
+      <c r="C42" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/moniteurs/lg-27gx790b-b</t>
+        </is>
+      </c>
+      <c r="D42" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E42" s="123" t="n"/>
+      <c r="F42" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="261" t="inlineStr">
+        <is>
+          <t>BR : BR (pt)</t>
+        </is>
+      </c>
+      <c r="C43" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/br/monitores/monitores-ultragear-oled/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D43" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E43" s="123" t="n"/>
+      <c r="F43" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="261" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C44" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/gaming/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D44" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E44" s="123" t="n"/>
+      <c r="F44" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="261" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C45" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D45" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E45" s="123" t="n"/>
+      <c r="F45" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="261" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C46" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-27gx790b-b</t>
+        </is>
+      </c>
+      <c r="D46" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E46" s="123" t="n"/>
+      <c r="F46" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="261" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C47" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/monitore/gaming/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D47" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E47" s="123" t="n"/>
+      <c r="F47" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="261" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C48" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/monitores/monitores-ultragear-oled-gaming/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D48" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E48" s="123" t="n"/>
+      <c r="F48" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="261" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C49" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/gaming/lg-27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D49" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E49" s="123" t="n"/>
+      <c r="F49" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="261" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C50" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/lg-27gx790b-b-27g411a-bundle/</t>
+        </is>
+      </c>
+      <c r="D50" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E50" s="123" t="n"/>
+      <c r="F50" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="261" t="inlineStr">
+        <is>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C51" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk/monitors/gaming/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D51" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E51" s="123" t="n"/>
+      <c r="F51" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="261" t="inlineStr">
+        <is>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C52" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk_en/monitors/gaming/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D52" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E52" s="123" t="n"/>
+      <c r="F52" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C53" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D53" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E53" s="123" t="n"/>
+      <c r="F53" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="261" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C54" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-oled/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D54" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E54" s="123" t="n"/>
+      <c r="F54" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="261" t="inlineStr">
+        <is>
+          <t>PL : PL (pl)</t>
+        </is>
+      </c>
+      <c r="C55" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pl/monitory/ultragear-gaming/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D55" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E55" s="123" t="n"/>
+      <c r="F55" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="261" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C56" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/consumer-monitors/gaming/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D56" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E56" s="123" t="n"/>
+      <c r="F56" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="261" t="inlineStr">
+        <is>
+          <t>TR : TR (tr)</t>
+        </is>
+      </c>
+      <c r="C57" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tr/monitor/ultragear-gaming-oled/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D57" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E57" s="123" t="n"/>
+      <c r="F57" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="261" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C58" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/gaming/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D58" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E58" s="123" t="n"/>
+      <c r="F58" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="261" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C59" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/gaming/27gx790b-b-27g640a/</t>
+        </is>
+      </c>
+      <c r="D59" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E59" s="123" t="n"/>
+      <c r="F59" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="261" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C60" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-gaming-oled-ultragear-oled/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D60" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E60" s="123" t="n"/>
+      <c r="F60" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="261" t="inlineStr">
+        <is>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C61" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pe/monitores/gamer/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D61" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E61" s="123" t="n"/>
+      <c r="F61" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="261" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C62" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-32gx870b-b</t>
+        </is>
+      </c>
+      <c r="D62" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E62" s="123" t="n"/>
+      <c r="F62" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C63" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/32gx870b-b/</t>
+        </is>
+      </c>
+      <c r="D63" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E63" s="123" t="n"/>
+      <c r="F63" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="261" t="inlineStr">
+        <is>
+          <t>TR : TR (tr)</t>
+        </is>
+      </c>
+      <c r="C64" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tr/monitors/32gx870b-b/</t>
+        </is>
+      </c>
+      <c r="D64" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E64" s="123" t="n"/>
+      <c r="F64" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C65" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/32gx870b-bajp/</t>
+        </is>
+      </c>
+      <c r="D65" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E65" s="123" t="n"/>
+      <c r="F65" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
+        <is>
+          <t>32GX870B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="261" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C66" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/monitors/ultragear-gaming/39gx950b/</t>
+        </is>
+      </c>
+      <c r="D66" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E66" s="123" t="n"/>
+      <c r="F66" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="261" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C67" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D67" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E67" s="123" t="n"/>
+      <c r="F67" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="261" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C68" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D68" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E68" s="123" t="n"/>
+      <c r="F68" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="261" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C69" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-39gx950b-b</t>
+        </is>
+      </c>
+      <c r="D69" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E69" s="123" t="n"/>
+      <c r="F69" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="261" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C70" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/monitore/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D70" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E70" s="123" t="n"/>
+      <c r="F70" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="261" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C71" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/monitores/monitores-ultragear-evo/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D71" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E71" s="123" t="n"/>
+      <c r="F71" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="261" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C72" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/gaming/39GX950B-B/</t>
+        </is>
+      </c>
+      <c r="D72" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E72" s="123" t="n"/>
+      <c r="F72" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="261" t="inlineStr">
+        <is>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C73" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk/monitors/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D73" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E73" s="123" t="n"/>
+      <c r="F73" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="261" t="inlineStr">
+        <is>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C74" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk_en/monitors/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D74" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E74" s="123" t="n"/>
+      <c r="F74" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="261" t="inlineStr">
+        <is>
+          <t>HU : HU (hu)</t>
+        </is>
+      </c>
+      <c r="C75" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hu/monitorok/ultragear-gaming-oled/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D75" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E75" s="123" t="n"/>
+      <c r="F75" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="261" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C76" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/ultragear-gaming-oled/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D76" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E76" s="123" t="n"/>
+      <c r="F76" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C77" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D77" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E77" s="123" t="n"/>
+      <c r="F77" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C78" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/39gx950b-bajp/</t>
+        </is>
+      </c>
+      <c r="D78" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E78" s="123" t="n"/>
+      <c r="F78" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="261" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C79" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-monitoren/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D79" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E79" s="123" t="n"/>
+      <c r="F79" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="261" t="inlineStr">
+        <is>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C80" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pe/monitores/ultragear-gaming-oled/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D80" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E80" s="123" t="n"/>
+      <c r="F80" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="261" t="inlineStr">
+        <is>
+          <t>PL : PL (pl)</t>
+        </is>
+      </c>
+      <c r="C81" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pl/monitory/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D81" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E81" s="123" t="n"/>
+      <c r="F81" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="261" t="inlineStr">
+        <is>
+          <t>SE : SE (sv)</t>
+        </is>
+      </c>
+      <c r="C82" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/monitor/ultragear-gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D82" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E82" s="123" t="n"/>
+      <c r="F82" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="261" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C83" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/consumer-monitors/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D83" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E83" s="123" t="n"/>
+      <c r="F83" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="261" t="inlineStr">
+        <is>
+          <t>TH : TH (th)</t>
+        </is>
+      </c>
+      <c r="C84" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/th/monitors/gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D84" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E84" s="123" t="n"/>
+      <c r="F84" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="261" t="inlineStr">
+        <is>
+          <t>TR : TR (tr)</t>
+        </is>
+      </c>
+      <c r="C85" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tr/monitor/ultragear-gaming-oled/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D85" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E85" s="123" t="n"/>
+      <c r="F85" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="261" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C86" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/monitors/ultragear-gaming/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D86" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E86" s="123" t="n"/>
+      <c r="F86" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="261" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C87" s="261" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/gaming-monitor/39gx950b-b/</t>
+        </is>
+      </c>
+      <c r="D87" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E87" s="123" t="n"/>
+      <c r="F87" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="0" t="inlineStr">
+        <is>
+          <t>39GX950B</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -5158,7 +5158,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>39GX950B</t>
+          <t>39GX950B · Consumer (URL 404 — 재확인 필요)</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>39GX950B</t>
+          <t>39GX950B · Business (URL 404 — 재확인 필요)</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>39GX950B</t>
+          <t>39GX950B · Outlet</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>39GX950B</t>
+          <t>39GX950B (B)</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>39GX950B</t>
+          <t>39GX950B (BAJP)</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>32GX870B</t>
+          <t>32GX870B (B)</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>32GX870B</t>
+          <t>32GX870B (BAJP)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · AI Upscaling Disclaimer Update (63 pages / 31 sites)</t>
+          <t>W29 신규 완료(27GM950B·39GX950B·32GX870B·45GX950B 로케일 다수) · AE 39GX950B(Consumer/Business) URL 404 취소</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="D9" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="E9" s="123" t="n"/>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="D10" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="E10" s="123" t="n"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D11" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E11" s="123" t="n"/>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="D12" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E12" s="123" t="n"/>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="D13" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E13" s="123" t="n"/>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="D14" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E14" s="123" t="n"/>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="D15" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E15" s="123" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="D16" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E16" s="123" t="n"/>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="D17" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E17" s="123" t="n"/>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="D18" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E18" s="123" t="n"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="D19" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E19" s="123" t="n"/>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D20" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E20" s="123" t="n"/>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="D21" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E21" s="123" t="n"/>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="D22" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E22" s="123" t="n"/>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="D23" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="E23" s="123" t="n"/>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="D24" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="E24" s="123" t="n"/>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="D25" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E25" s="123" t="n"/>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="D26" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E26" s="123" t="n"/>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="D27" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E27" s="123" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="D28" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E28" s="123" t="n"/>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="D29" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E29" s="123" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D30" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E30" s="123" t="n"/>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D33" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E33" s="123" t="n"/>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="D34" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E34" s="123" t="n"/>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="D35" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E35" s="123" t="n"/>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D36" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E36" s="123" t="n"/>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D37" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E37" s="123" t="n"/>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="D38" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E38" s="123" t="n"/>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="D39" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E39" s="123" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="D40" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E40" s="123" t="n"/>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="D41" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E41" s="123" t="n"/>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="D42" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E42" s="123" t="n"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="D43" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E43" s="123" t="n"/>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="D44" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E44" s="123" t="n"/>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="D45" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E45" s="123" t="n"/>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="D46" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E46" s="123" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="D47" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E47" s="123" t="n"/>
@@ -5799,7 +5799,7 @@
       </c>
       <c r="D48" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E48" s="123" t="n"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="D49" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E49" s="123" t="n"/>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D50" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E50" s="123" t="n"/>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="D51" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E51" s="123" t="n"/>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="D52" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E52" s="123" t="n"/>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="D53" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E53" s="123" t="n"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="D54" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E54" s="123" t="n"/>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="D55" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E55" s="123" t="n"/>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="D56" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E56" s="123" t="n"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="D57" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E57" s="123" t="n"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="D58" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E58" s="123" t="n"/>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="D59" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E59" s="123" t="n"/>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="D60" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E60" s="123" t="n"/>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="D61" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E61" s="123" t="n"/>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="D62" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E62" s="123" t="n"/>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="D63" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E63" s="123" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="D64" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E64" s="123" t="n"/>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="D65" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E65" s="123" t="n"/>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="D66" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E66" s="123" t="n"/>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="D67" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E67" s="123" t="n"/>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="D68" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E68" s="123" t="n"/>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D69" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E69" s="123" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D70" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E70" s="123" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="D71" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E71" s="123" t="n"/>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · UL-Verified Eye Comfort Feature Upload (79 pages / 38 sites)</t>
+          <t>W29 신규 완료 35건(27GX700A·27GX790B 로케일 다수) · URL 404·에러 2건 취소(27GX790B PE, 32GX870B TR)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="D9" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E9" s="123" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="D11" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E11" s="123" t="n"/>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="D13" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E13" s="123" t="n"/>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="D16" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E16" s="123" t="n"/>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="D17" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E17" s="123" t="n"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D20" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E20" s="123" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="D21" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E21" s="123" t="n"/>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="D23" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E23" s="123" t="n"/>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="D24" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E24" s="123" t="n"/>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D26" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E26" s="123" t="n"/>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="D28" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E28" s="123" t="n"/>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="D30" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E30" s="123" t="n"/>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D34" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E34" s="123" t="n"/>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="D35" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E35" s="123" t="n"/>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D36" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E36" s="123" t="n"/>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="D37" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E37" s="123" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="D38" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E38" s="123" t="n"/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="D41" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E41" s="123" t="n"/>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="D43" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E43" s="123" t="n"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="D44" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E44" s="123" t="n"/>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="D45" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E45" s="123" t="n"/>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D47" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E47" s="123" t="n"/>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="D48" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E48" s="123" t="n"/>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="D49" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E49" s="123" t="n"/>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D50" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E50" s="123" t="n"/>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="D51" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E51" s="123" t="n"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="D52" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E52" s="123" t="n"/>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="D54" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E54" s="123" t="n"/>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="D55" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E55" s="123" t="n"/>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="D56" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E56" s="123" t="n"/>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="D57" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E57" s="123" t="n"/>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D58" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E58" s="123" t="n"/>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="D60" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E60" s="123" t="n"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="D61" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="E61" s="123" t="n"/>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="D64" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="E64" s="123" t="n"/>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="D67" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E67" s="123" t="n"/>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D74" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E74" s="123" t="n"/>
@@ -9577,7 +9577,7 @@
       <c r="B2" s="128" t="inlineStr">
         <is>
           <t>AU : URL 변경
-CN : 작업중 → 법인리뷰</t>
+CN : 법인리뷰 → 완료</t>
         </is>
       </c>
       <c r="C2" s="129" t="n"/>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="D12" s="284" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E12" s="242" t="inlineStr"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -14,8 +14,9 @@
     <sheet name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="W28 - AI Upscaling Disclaimer" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="W28 - UL Verified Eye Comfort" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4683,6 +4684,606 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>GR26-W25-Request to add Copilot+ Hero Banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>금주 신규 등록 · Copilot+ Hero Banner (B2C 완료 10 · 작업중 4 · B2B 작업중 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/ordinateurs-portables/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/laptops</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/laptops/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/notebooks</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/pc-portables/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/laptop/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/laptop-lg-gram/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GLOBAL : GLOBAL (en)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/pcs/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/business/san-pham-tin-hoc/laptop</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/business/computers/laptops/</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/it-products/laptops/</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/business/informatique/pc-portables-professionnels/</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -6415,7 +7016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -4691,586 +4691,586 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>GR26-W25-Request to add Copilot+ Hero Banner</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>이번주 추가</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>금주 신규 등록 · Copilot+ Hero Banner (B2C 완료 10 · 작업중 4 · B2B 작업중 7)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>완료일</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Page#</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/laptops/</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/ordinateurs-portables/</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/laptops</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>IT : IT (it)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>FR : FR (fr)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/fr/pc-portables/</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/laptops/</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/laptop/</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/notebooks</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>VN : VN (vi)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/vn/laptop-lg-gram/</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/laptops/</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>GLOBAL : GLOBAL (en)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/global/business/monitors-pcs/pcs/</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/business/it-products/lg-gram/</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>VN : VN (vi)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/vn/business/san-pham-tin-hoc/laptop</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/business/computers/laptops/</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/business/it-products/laptops/</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>FR : FR (fr)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/fr/business/informatique/pc-portables-professionnels/</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
@@ -5287,7 +5287,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>W29 신규 완료(27GM950B·39GX950B·32GX870B·45GX950B 로케일 다수) · AE 39GX950B(Consumer/Business) URL 404 취소</t>
+          <t>W29 신규 완료(27GM950B·39GX950B·32GX870B·45GX950B) · AE 4건 URL 404 취소 · EE 대상 제외 · ES(SUSPENDED 포함) 완료 — 잔여 작업중 0</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -5948,17 +5948,17 @@
     <row r="31">
       <c r="B31" s="261" t="inlineStr">
         <is>
-          <t>EE : EE (et)</t>
+          <t>ES : ES (es)</t>
         </is>
       </c>
       <c r="C31" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ee/monitorid/lg-39gx950b-b</t>
+          <t>https://www.lg.com/es/monitors/gaming-oled/39gx950b-b/</t>
         </is>
       </c>
       <c r="D31" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E31" s="123" t="n"/>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>39GX950B</t>
+          <t>39GX950B · SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -5979,12 +5979,12 @@
       </c>
       <c r="C32" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es/monitors/gaming-oled/39gx950b-b/</t>
+          <t>https://www.lg.com/es/monitores/monitores-ultragear-evo/39gx950b-b/</t>
         </is>
       </c>
       <c r="D32" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E32" s="123" t="n"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>39GX950B · SUSPENDED</t>
+          <t>39GX950B</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="C33" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es/monitores/monitores-ultragear-evo/39gx950b-b/</t>
+          <t>https://www.lg.com/es/outlet/outlet-informatica/monitores/39gx950b-b-outlet/</t>
         </is>
       </c>
       <c r="D33" s="264" t="inlineStr">
@@ -6019,19 +6019,19 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>39GX950B</t>
+          <t>39GX950B · Outlet</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="261" t="inlineStr">
         <is>
-          <t>ES : ES (es)</t>
+          <t>FR : FR (fr)</t>
         </is>
       </c>
       <c r="C34" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es/outlet/outlet-informatica/monitores/39gx950b-b-outlet/</t>
+          <t>https://www.lg.com/fr/moniteurs/gaming/39GX950B-B/</t>
         </is>
       </c>
       <c r="D34" s="264" t="inlineStr">
@@ -6045,19 +6045,19 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>39GX950B · Outlet</t>
+          <t>39GX950B</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="261" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
+          <t>HK : HK (zh)</t>
         </is>
       </c>
       <c r="C35" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fr/moniteurs/gaming/39GX950B-B/</t>
+          <t>https://www.lg.com/hk/monitors/gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D35" s="264" t="inlineStr">
@@ -6078,12 +6078,12 @@
     <row r="36">
       <c r="B36" s="261" t="inlineStr">
         <is>
-          <t>HK : HK (zh)</t>
+          <t>HK_EN : HK (en)</t>
         </is>
       </c>
       <c r="C36" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk/monitors/gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/hk_en/monitors/gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D36" s="264" t="inlineStr">
@@ -6104,12 +6104,12 @@
     <row r="37">
       <c r="B37" s="261" t="inlineStr">
         <is>
-          <t>HK_EN : HK (en)</t>
+          <t>HU : HU (hu)</t>
         </is>
       </c>
       <c r="C37" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk_en/monitors/gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/hu/monitorok/ultragear-gaming-oled/39gx950b-b/</t>
         </is>
       </c>
       <c r="D37" s="264" t="inlineStr">
@@ -6130,12 +6130,12 @@
     <row r="38">
       <c r="B38" s="261" t="inlineStr">
         <is>
-          <t>HU : HU (hu)</t>
+          <t>ID : ID (in)</t>
         </is>
       </c>
       <c r="C38" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hu/monitorok/ultragear-gaming-oled/39gx950b-b/</t>
+          <t>https://www.lg.com/id/monitor/gaming/39gx950b/</t>
         </is>
       </c>
       <c r="D38" s="264" t="inlineStr">
@@ -6156,12 +6156,12 @@
     <row r="39">
       <c r="B39" s="261" t="inlineStr">
         <is>
-          <t>ID : ID (in)</t>
+          <t>IT : IT (it)</t>
         </is>
       </c>
       <c r="C39" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/id/monitor/gaming/39gx950b/</t>
+          <t>https://www.lg.com/it/monitor/ultragear-gaming-oled/39gx950b-b/</t>
         </is>
       </c>
       <c r="D39" s="264" t="inlineStr">
@@ -6182,12 +6182,12 @@
     <row r="40">
       <c r="B40" s="261" t="inlineStr">
         <is>
-          <t>IT : IT (it)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C40" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/it/monitor/ultragear-gaming-oled/39gx950b-b/</t>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/39gx950b-b/</t>
         </is>
       </c>
       <c r="D40" s="264" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>39GX950B</t>
+          <t>39GX950B (B)</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="C41" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/gaming-monitors/39gx950b-b/</t>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/39gx950b-bajp/</t>
         </is>
       </c>
       <c r="D41" s="264" t="inlineStr">
@@ -6227,19 +6227,19 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>39GX950B (B)</t>
+          <t>39GX950B (BAJP)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="261" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>NL : NL (nl)</t>
         </is>
       </c>
       <c r="C42" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/gaming-monitors/39gx950b-bajp/</t>
+          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-monitoren/39gx950b-b/</t>
         </is>
       </c>
       <c r="D42" s="264" t="inlineStr">
@@ -6253,19 +6253,19 @@
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>39GX950B (BAJP)</t>
+          <t>39GX950B</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="261" t="inlineStr">
         <is>
-          <t>NL : NL (nl)</t>
+          <t>PE : PE (es)</t>
         </is>
       </c>
       <c r="C43" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-monitoren/39gx950b-b/</t>
+          <t>https://www.lg.com/pe/monitores/gamer/39gx950b-b/</t>
         </is>
       </c>
       <c r="D43" s="264" t="inlineStr">
@@ -6286,12 +6286,12 @@
     <row r="44">
       <c r="B44" s="261" t="inlineStr">
         <is>
-          <t>PE : PE (es)</t>
+          <t>PL : PL (pl)</t>
         </is>
       </c>
       <c r="C44" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pe/monitores/gamer/39gx950b-b/</t>
+          <t>https://www.lg.com/pl/monitory/ultragear-gaming-oled/39gx950b-b/</t>
         </is>
       </c>
       <c r="D44" s="264" t="inlineStr">
@@ -6312,12 +6312,12 @@
     <row r="45">
       <c r="B45" s="261" t="inlineStr">
         <is>
-          <t>PL : PL (pl)</t>
+          <t>SA : SA (ar)</t>
         </is>
       </c>
       <c r="C45" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pl/monitory/ultragear-gaming-oled/39gx950b-b/</t>
+          <t>https://www.lg.com/sa/monitors/ultragear-gaming-oled/39gx950b-b/</t>
         </is>
       </c>
       <c r="D45" s="264" t="inlineStr">
@@ -6338,12 +6338,12 @@
     <row r="46">
       <c r="B46" s="261" t="inlineStr">
         <is>
-          <t>SA : SA (ar)</t>
+          <t>SA_EN : SA (en)</t>
         </is>
       </c>
       <c r="C46" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sa/monitors/ultragear-gaming-oled/39gx950b-b/</t>
+          <t>https://www.lg.com/sa_en/monitors/ultragear-gaming-oled/39gx950b-b/</t>
         </is>
       </c>
       <c r="D46" s="264" t="inlineStr">
@@ -6364,12 +6364,12 @@
     <row r="47">
       <c r="B47" s="261" t="inlineStr">
         <is>
-          <t>SA_EN : SA (en)</t>
+          <t>SE : SE (sv)</t>
         </is>
       </c>
       <c r="C47" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sa_en/monitors/ultragear-gaming-oled/39gx950b-b/</t>
+          <t>https://www.lg.com/se/monitor/ultragear-gaming-oled/39gx950b-b/</t>
         </is>
       </c>
       <c r="D47" s="264" t="inlineStr">
@@ -6390,12 +6390,12 @@
     <row r="48">
       <c r="B48" s="261" t="inlineStr">
         <is>
-          <t>SE : SE (sv)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C48" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/se/monitor/ultragear-gaming-oled/39gx950b-b/</t>
+          <t>https://www.lg.com/sg/consumer-monitors/gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D48" s="264" t="inlineStr">
@@ -6416,12 +6416,12 @@
     <row r="49">
       <c r="B49" s="261" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
+          <t>TH : TH (th)</t>
         </is>
       </c>
       <c r="C49" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg/consumer-monitors/gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/th/monitors/gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D49" s="264" t="inlineStr">
@@ -6442,12 +6442,12 @@
     <row r="50">
       <c r="B50" s="261" t="inlineStr">
         <is>
-          <t>TH : TH (th)</t>
+          <t>TR : TR (tr)</t>
         </is>
       </c>
       <c r="C50" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/th/monitors/gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/tr/monitor/ultragear-gaming-oled/39gx950b-b/</t>
         </is>
       </c>
       <c r="D50" s="264" t="inlineStr">
@@ -6468,12 +6468,12 @@
     <row r="51">
       <c r="B51" s="261" t="inlineStr">
         <is>
-          <t>TR : TR (tr)</t>
+          <t>TW : TW (zh)</t>
         </is>
       </c>
       <c r="C51" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tr/monitor/ultragear-gaming-oled/39gx950b-b/</t>
+          <t>https://www.lg.com/tw/monitors/ultragear-gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D51" s="264" t="inlineStr">
@@ -6494,12 +6494,12 @@
     <row r="52">
       <c r="B52" s="261" t="inlineStr">
         <is>
-          <t>TW : TW (zh)</t>
+          <t>UK : GB (en)</t>
         </is>
       </c>
       <c r="C52" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tw/monitors/ultragear-gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/uk/monitors/gaming-monitor/39gx950b-b/</t>
         </is>
       </c>
       <c r="D52" s="264" t="inlineStr">
@@ -6520,12 +6520,12 @@
     <row r="53">
       <c r="B53" s="261" t="inlineStr">
         <is>
-          <t>UK : GB (en)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C53" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/uk/monitors/gaming-monitor/39gx950b-b/</t>
+          <t>https://www.lg.com/cn/monitors/lg-32gx870b-b</t>
         </is>
       </c>
       <c r="D53" s="264" t="inlineStr">
@@ -6539,19 +6539,19 @@
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>39GX950B</t>
+          <t>32GX870B</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="261" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>CO : CO (es)</t>
         </is>
       </c>
       <c r="C54" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-32gx870b-b</t>
+          <t>https://www.lg.com/co/monitores/gaming/32gx870b-b/</t>
         </is>
       </c>
       <c r="D54" s="264" t="inlineStr">
@@ -6572,12 +6572,12 @@
     <row r="55">
       <c r="B55" s="261" t="inlineStr">
         <is>
-          <t>CO : CO (es)</t>
+          <t>HK : HK (zh)</t>
         </is>
       </c>
       <c r="C55" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/co/monitores/gaming/32gx870b-b/</t>
+          <t>https://www.lg.com/hk/monitors/gaming/32gx870b-b/</t>
         </is>
       </c>
       <c r="D55" s="264" t="inlineStr">
@@ -6598,12 +6598,12 @@
     <row r="56">
       <c r="B56" s="261" t="inlineStr">
         <is>
-          <t>HK : HK (zh)</t>
+          <t>HK_EN : HK (en)</t>
         </is>
       </c>
       <c r="C56" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk/monitors/gaming/32gx870b-b/</t>
+          <t>https://www.lg.com/hk_en/monitors/gaming/32gx870b-b/</t>
         </is>
       </c>
       <c r="D56" s="264" t="inlineStr">
@@ -6624,12 +6624,12 @@
     <row r="57">
       <c r="B57" s="261" t="inlineStr">
         <is>
-          <t>HK_EN : HK (en)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C57" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk_en/monitors/gaming/32gx870b-b/</t>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/32gx870b-b/</t>
         </is>
       </c>
       <c r="D57" s="264" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>32GX870B</t>
+          <t>32GX870B (B)</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="C58" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/gaming-monitors/32gx870b-b/</t>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/32gx870b-bajp/</t>
         </is>
       </c>
       <c r="D58" s="264" t="inlineStr">
@@ -6669,19 +6669,19 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>32GX870B (B)</t>
+          <t>32GX870B (BAJP)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="261" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>PE : PE (es)</t>
         </is>
       </c>
       <c r="C59" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/gaming-monitors/32gx870b-bajp/</t>
+          <t>https://www.lg.com/pe/monitores/ultragear-gaming-oled/32gx870b-b/</t>
         </is>
       </c>
       <c r="D59" s="264" t="inlineStr">
@@ -6695,19 +6695,19 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>32GX870B (BAJP)</t>
+          <t>32GX870B</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="261" t="inlineStr">
         <is>
-          <t>PE : PE (es)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C60" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pe/monitores/ultragear-gaming-oled/32gx870b-b/</t>
+          <t>https://www.lg.com/sg/consumer-monitors/gaming/32gx870b-b/</t>
         </is>
       </c>
       <c r="D60" s="264" t="inlineStr">
@@ -6728,12 +6728,12 @@
     <row r="61">
       <c r="B61" s="261" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
+          <t>TR : TR (tr)</t>
         </is>
       </c>
       <c r="C61" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg/consumer-monitors/gaming/32gx870b-b/</t>
+          <t>https://www.lg.com/tr/monitor/smart-monitorleri/32gx870b-b/</t>
         </is>
       </c>
       <c r="D61" s="264" t="inlineStr">
@@ -6754,12 +6754,12 @@
     <row r="62">
       <c r="B62" s="261" t="inlineStr">
         <is>
-          <t>TR : TR (tr)</t>
+          <t>CA_EN : CA (en)</t>
         </is>
       </c>
       <c r="C62" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tr/monitor/smart-monitorleri/32gx870b-b/</t>
+          <t>https://www.lg.com/ca_en/monitors/gaming/45gx950b/</t>
         </is>
       </c>
       <c r="D62" s="264" t="inlineStr">
@@ -6773,19 +6773,19 @@
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>32GX870B</t>
+          <t>45GX950B</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="261" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>CA_FR : CA (fr)</t>
         </is>
       </c>
       <c r="C63" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/monitors/gaming/45gx950b/</t>
+          <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/45gx950b/</t>
         </is>
       </c>
       <c r="D63" s="264" t="inlineStr">
@@ -6806,12 +6806,12 @@
     <row r="64">
       <c r="B64" s="261" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C64" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/45gx950b/</t>
+          <t>https://www.lg.com/cn/monitors/lg-45gx950b-b</t>
         </is>
       </c>
       <c r="D64" s="264" t="inlineStr">
@@ -6832,12 +6832,12 @@
     <row r="65">
       <c r="B65" s="261" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>HK : HK (zh)</t>
         </is>
       </c>
       <c r="C65" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-45gx950b-b</t>
+          <t>https://www.lg.com/hk/monitors/gaming/45gx950b-b/</t>
         </is>
       </c>
       <c r="D65" s="264" t="inlineStr">
@@ -6858,12 +6858,12 @@
     <row r="66">
       <c r="B66" s="261" t="inlineStr">
         <is>
-          <t>HK : HK (zh)</t>
+          <t>HK_EN : HK (en)</t>
         </is>
       </c>
       <c r="C66" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk/monitors/gaming/45gx950b-b/</t>
+          <t>https://www.lg.com/hk_en/monitors/gaming/45gx950b-b/</t>
         </is>
       </c>
       <c r="D66" s="264" t="inlineStr">
@@ -6884,12 +6884,12 @@
     <row r="67">
       <c r="B67" s="261" t="inlineStr">
         <is>
-          <t>HK_EN : HK (en)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C67" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk_en/monitors/gaming/45gx950b-b/</t>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/45gx950b-b/</t>
         </is>
       </c>
       <c r="D67" s="264" t="inlineStr">
@@ -6910,12 +6910,12 @@
     <row r="68">
       <c r="B68" s="261" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C68" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/gaming-monitors/45gx950b-b/</t>
+          <t>https://www.lg.com/sg/consumer-monitors/gaming/45gx950b-b/</t>
         </is>
       </c>
       <c r="D68" s="264" t="inlineStr">
@@ -6936,12 +6936,12 @@
     <row r="69">
       <c r="B69" s="261" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
+          <t>TR : TR (tr)</t>
         </is>
       </c>
       <c r="C69" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg/consumer-monitors/gaming/45gx950b-b/</t>
+          <t>https://www.lg.com/tr/monitor/ultragear-gaming-oled/45gx950b-b/</t>
         </is>
       </c>
       <c r="D69" s="264" t="inlineStr">
@@ -6962,12 +6962,12 @@
     <row r="70">
       <c r="B70" s="261" t="inlineStr">
         <is>
-          <t>TR : TR (tr)</t>
+          <t>VN : VN (vi)</t>
         </is>
       </c>
       <c r="C70" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tr/monitor/ultragear-gaming-oled/45gx950b-b/</t>
+          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-gaming-ultragear/45gx950b-b/</t>
         </is>
       </c>
       <c r="D70" s="264" t="inlineStr">
@@ -6980,32 +6980,6 @@
         <v>1</v>
       </c>
       <c r="G70" s="0" t="inlineStr">
-        <is>
-          <t>45GX950B</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="261" t="inlineStr">
-        <is>
-          <t>VN : VN (vi)</t>
-        </is>
-      </c>
-      <c r="C71" s="261" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-gaming-ultragear/45gx950b-b/</t>
-        </is>
-      </c>
-      <c r="D71" s="264" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E71" s="123" t="n"/>
-      <c r="F71" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="0" t="inlineStr">
         <is>
           <t>45GX950B</t>
         </is>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -10701,7 +10701,8 @@
       <c r="B2" s="163" t="inlineStr">
         <is>
           <t>CZ : 작업중 → 완료
-TR : 법인리뷰 → 작업중</t>
+TR : 법인리뷰 → 작업중
+IN : 법인리뷰 → 완료 (7/16 게시, PTT 확인)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -11241,10 +11242,14 @@
       </c>
       <c r="D29" s="263" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E29" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E29" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
       <c r="F29" s="123" t="n">
         <v>1</v>
       </c>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -6996,7 +6996,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>W29 신규 완료 35건(27GX700A·27GX790B 로케일 다수) · URL 404·에러 2건 취소(27GX790B PE, 32GX870B TR)</t>
+          <t>W30 전건 작업 완료 — 잔여 작업중 0 · 취소 2건(27GX790B PE 404·32GX870B TR 에러) 유지 · CA business 2행 대상 제외(삭제)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -7036,6 +7036,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -7121,7 +7122,7 @@
       </c>
       <c r="D10" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E10" s="123" t="n"/>
@@ -7163,17 +7164,17 @@
     <row r="12">
       <c r="B12" s="261" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>CA_FR : CA (fr)</t>
         </is>
       </c>
       <c r="C12" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/business/monitors/gaming-monitors/27gx700a-b/</t>
+          <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/27gx700a-b/</t>
         </is>
       </c>
       <c r="D12" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E12" s="123" t="n"/>
@@ -7189,12 +7190,12 @@
     <row r="13">
       <c r="B13" s="261" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C13" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/27gx700a-b/</t>
+          <t>https://www.lg.com/cn/monitors/lg-27gx700a-b</t>
         </is>
       </c>
       <c r="D13" s="264" t="inlineStr">
@@ -7215,17 +7216,17 @@
     <row r="14">
       <c r="B14" s="261" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>DE : DE (de)</t>
         </is>
       </c>
       <c r="C14" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/business/moniteurs/moniteurs-de-jeu/27gx700a-b/</t>
+          <t>https://www.lg.com/de/monitore/gaming/27gx700a-b/</t>
         </is>
       </c>
       <c r="D14" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E14" s="123" t="n"/>
@@ -7241,17 +7242,17 @@
     <row r="15">
       <c r="B15" s="261" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>DK : DK (da)</t>
         </is>
       </c>
       <c r="C15" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-27gx700a-b</t>
+          <t>https://www.lg.com/dk/skaerme/ultragear-gamerskaerme/27gx700a-b/</t>
         </is>
       </c>
       <c r="D15" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E15" s="123" t="n"/>
@@ -7267,12 +7268,12 @@
     <row r="16">
       <c r="B16" s="261" t="inlineStr">
         <is>
-          <t>DE : DE (de)</t>
+          <t>FI : FI (fi)</t>
         </is>
       </c>
       <c r="C16" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/de/monitore/gaming/27gx700a-b/</t>
+          <t>https://www.lg.com/fi/naytot/lg-27gx700a-b</t>
         </is>
       </c>
       <c r="D16" s="264" t="inlineStr">
@@ -7293,12 +7294,12 @@
     <row r="17">
       <c r="B17" s="261" t="inlineStr">
         <is>
-          <t>DK : DK (da)</t>
+          <t>GR : GR (el)</t>
         </is>
       </c>
       <c r="C17" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/dk/skaerme/ultragear-gamerskaerme/27gx700a-b/</t>
+          <t>https://www.lg.com/gr/othones/lg-27gx700a-b</t>
         </is>
       </c>
       <c r="D17" s="264" t="inlineStr">
@@ -7319,17 +7320,17 @@
     <row r="18">
       <c r="B18" s="261" t="inlineStr">
         <is>
-          <t>FI : FI (fi)</t>
+          <t>HK : HK (zh)</t>
         </is>
       </c>
       <c r="C18" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fi/naytot/lg-27gx700a-b</t>
+          <t>https://www.lg.com/hk/monitors/gaming/27gx700a-b/</t>
         </is>
       </c>
       <c r="D18" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E18" s="123" t="n"/>
@@ -7345,17 +7346,17 @@
     <row r="19">
       <c r="B19" s="261" t="inlineStr">
         <is>
-          <t>GR : GR (el)</t>
+          <t>HK_EN : HK (en)</t>
         </is>
       </c>
       <c r="C19" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/gr/othones/lg-27gx700a-b</t>
+          <t>https://www.lg.com/hk_en/monitors/gaming/27gx700a-b/</t>
         </is>
       </c>
       <c r="D19" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E19" s="123" t="n"/>
@@ -7371,12 +7372,12 @@
     <row r="20">
       <c r="B20" s="261" t="inlineStr">
         <is>
-          <t>HK : HK (zh)</t>
+          <t>HR : HR (hr)</t>
         </is>
       </c>
       <c r="C20" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk/monitors/gaming/27gx700a-b/</t>
+          <t>https://www.lg.com/hr/monitori/lg-27gx700a-b</t>
         </is>
       </c>
       <c r="D20" s="264" t="inlineStr">
@@ -7397,12 +7398,12 @@
     <row r="21">
       <c r="B21" s="261" t="inlineStr">
         <is>
-          <t>HK_EN : HK (en)</t>
+          <t>HU : HU (hu)</t>
         </is>
       </c>
       <c r="C21" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk_en/monitors/gaming/27gx700a-b/</t>
+          <t>https://www.lg.com/hu/monitorok/ultragear-gaming-monitor/27gx700a-b/</t>
         </is>
       </c>
       <c r="D21" s="264" t="inlineStr">
@@ -7423,17 +7424,17 @@
     <row r="22">
       <c r="B22" s="261" t="inlineStr">
         <is>
-          <t>HR : HR (hr)</t>
+          <t>ID : ID (in)</t>
         </is>
       </c>
       <c r="C22" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hr/monitori/lg-27gx700a-b</t>
+          <t>https://www.lg.com/id/monitor/gaming/27gx700a-b/</t>
         </is>
       </c>
       <c r="D22" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E22" s="123" t="n"/>
@@ -7449,12 +7450,12 @@
     <row r="23">
       <c r="B23" s="261" t="inlineStr">
         <is>
-          <t>HU : HU (hu)</t>
+          <t>IL : IL (iw)</t>
         </is>
       </c>
       <c r="C23" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hu/monitorok/ultragear-gaming-monitor/27gx700a-b/</t>
+          <t>https://www.lg.com/il/monitors/lg-27gx700a-b</t>
         </is>
       </c>
       <c r="D23" s="264" t="inlineStr">
@@ -7475,12 +7476,12 @@
     <row r="24">
       <c r="B24" s="261" t="inlineStr">
         <is>
-          <t>ID : ID (in)</t>
+          <t>IT : IT (it)</t>
         </is>
       </c>
       <c r="C24" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/id/monitor/gaming/27gx700a-b/</t>
+          <t>https://www.lg.com/it/monitor/gaming/27gx700a-b/</t>
         </is>
       </c>
       <c r="D24" s="264" t="inlineStr">
@@ -7501,17 +7502,17 @@
     <row r="25">
       <c r="B25" s="261" t="inlineStr">
         <is>
-          <t>IL : IL (iw)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C25" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/il/monitors/lg-27gx700a-b</t>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/27gx700a-b/</t>
         </is>
       </c>
       <c r="D25" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E25" s="123" t="n"/>
@@ -7527,12 +7528,12 @@
     <row r="26">
       <c r="B26" s="261" t="inlineStr">
         <is>
-          <t>IT : IT (it)</t>
+          <t>KZ : KZ (ru)</t>
         </is>
       </c>
       <c r="C26" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/it/monitor/gaming/27gx700a-b/</t>
+          <t>https://www.lg.com/kz/monitors/gaming/27gx700a-b/</t>
         </is>
       </c>
       <c r="D26" s="264" t="inlineStr">
@@ -7553,17 +7554,17 @@
     <row r="27">
       <c r="B27" s="261" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>NO : NO (no)</t>
         </is>
       </c>
       <c r="C27" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/gaming-monitors/27gx700a-b/</t>
+          <t>https://www.lg.com/no/skjermer/lg-27gx700a-b</t>
         </is>
       </c>
       <c r="D27" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E27" s="123" t="n"/>
@@ -7579,12 +7580,12 @@
     <row r="28">
       <c r="B28" s="261" t="inlineStr">
         <is>
-          <t>KZ : KZ (ru)</t>
+          <t>PL : PL (pl)</t>
         </is>
       </c>
       <c r="C28" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/kz/monitors/gaming/27gx700a-b/</t>
+          <t>https://www.lg.com/pl/monitory/ultragear-gaming/27gx700a/</t>
         </is>
       </c>
       <c r="D28" s="264" t="inlineStr">
@@ -7605,17 +7606,17 @@
     <row r="29">
       <c r="B29" s="261" t="inlineStr">
         <is>
-          <t>NO : NO (no)</t>
+          <t>RO : RO (ro)</t>
         </is>
       </c>
       <c r="C29" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/no/skjermer/lg-27gx700a-b</t>
+          <t>https://www.lg.com/ro/monitoare/lg-27gx700a-b</t>
         </is>
       </c>
       <c r="D29" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E29" s="123" t="n"/>
@@ -7631,12 +7632,12 @@
     <row r="30">
       <c r="B30" s="261" t="inlineStr">
         <is>
-          <t>PL : PL (pl)</t>
+          <t>RS : RS (sr)</t>
         </is>
       </c>
       <c r="C30" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pl/monitory/ultragear-gaming/27gx700a/</t>
+          <t>https://www.lg.com/rs/monitori/lg-27gx700a-b</t>
         </is>
       </c>
       <c r="D30" s="264" t="inlineStr">
@@ -7657,17 +7658,17 @@
     <row r="31">
       <c r="B31" s="261" t="inlineStr">
         <is>
-          <t>RO : RO (ro)</t>
+          <t>RU : RU (ru)</t>
         </is>
       </c>
       <c r="C31" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ro/monitoare/lg-27gx700a-b</t>
+          <t>https://www.lg.com/ru/monitors/lg-27gx700a-b</t>
         </is>
       </c>
       <c r="D31" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E31" s="123" t="n"/>
@@ -7683,17 +7684,17 @@
     <row r="32">
       <c r="B32" s="261" t="inlineStr">
         <is>
-          <t>RS : RS (sr)</t>
+          <t>SE : SE (sv)</t>
         </is>
       </c>
       <c r="C32" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/monitori/lg-27gx700a-b</t>
+          <t>https://www.lg.com/se/monitor/ultragear-gaming/27gx700a-b/</t>
         </is>
       </c>
       <c r="D32" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E32" s="123" t="n"/>
@@ -7709,17 +7710,17 @@
     <row r="33">
       <c r="B33" s="261" t="inlineStr">
         <is>
-          <t>RU : RU (ru)</t>
+          <t>TR : TR (tr)</t>
         </is>
       </c>
       <c r="C33" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ru/monitors/lg-27gx700a-b</t>
+          <t>https://www.lg.com/tr/monitor/oyun-monitorleri/27gx700a-b/</t>
         </is>
       </c>
       <c r="D33" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E33" s="123" t="n"/>
@@ -7735,12 +7736,12 @@
     <row r="34">
       <c r="B34" s="261" t="inlineStr">
         <is>
-          <t>SE : SE (sv)</t>
+          <t>UK : GB (en)</t>
         </is>
       </c>
       <c r="C34" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/se/monitor/ultragear-gaming/27gx700a-b/</t>
+          <t>https://www.lg.com/uk/monitors/gaming/27gx700a-b/</t>
         </is>
       </c>
       <c r="D34" s="264" t="inlineStr">
@@ -7761,12 +7762,12 @@
     <row r="35">
       <c r="B35" s="261" t="inlineStr">
         <is>
-          <t>TR : TR (tr)</t>
+          <t>UK : GB (en)</t>
         </is>
       </c>
       <c r="C35" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tr/monitor/oyun-monitorleri/27gx700a-b/</t>
+          <t>https://www.lg.com/uk/monitors/gaming/27gx700a-b-27gx001-pck-uk-c/</t>
         </is>
       </c>
       <c r="D35" s="264" t="inlineStr">
@@ -7787,12 +7788,12 @@
     <row r="36">
       <c r="B36" s="261" t="inlineStr">
         <is>
-          <t>UK : GB (en)</t>
+          <t>FR : FR (fr)</t>
         </is>
       </c>
       <c r="C36" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/uk/monitors/gaming/27gx700a-b/</t>
+          <t>https://www.lg.com/fr/moniteurs/gaming/lg-27gx700a-b/</t>
         </is>
       </c>
       <c r="D36" s="264" t="inlineStr">
@@ -7813,12 +7814,12 @@
     <row r="37">
       <c r="B37" s="261" t="inlineStr">
         <is>
-          <t>UK : GB (en)</t>
+          <t>AE : AE (en)</t>
         </is>
       </c>
       <c r="C37" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/uk/monitors/gaming/27gx700a-b-27gx001-pck-uk-c/</t>
+          <t>https://www.lg.com/ae/consumer-monitors/lg-27gx790b-b</t>
         </is>
       </c>
       <c r="D37" s="264" t="inlineStr">
@@ -7832,19 +7833,19 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>27GX700A</t>
+          <t>27GX790B</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="261" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
+          <t>AE_AR : AE (ar)</t>
         </is>
       </c>
       <c r="C38" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fr/moniteurs/gaming/lg-27gx700a-b/</t>
+          <t>https://www.lg.com/ae_ar/consumer-monitors/lg-27gx790b-b</t>
         </is>
       </c>
       <c r="D38" s="264" t="inlineStr">
@@ -7858,24 +7859,24 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>27GX700A</t>
+          <t>27GX790B</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="261" t="inlineStr">
         <is>
-          <t>AE : AE (en)</t>
+          <t>AU : AU (en)</t>
         </is>
       </c>
       <c r="C39" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ae/consumer-monitors/lg-27gx790b-b</t>
+          <t>https://www.lg.com/au/monitors/ultragear-gaming/27gx790b-b/</t>
         </is>
       </c>
       <c r="D39" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E39" s="123" t="n"/>
@@ -7891,17 +7892,17 @@
     <row r="40">
       <c r="B40" s="261" t="inlineStr">
         <is>
-          <t>AE_AR : AE (ar)</t>
+          <t>BE_FR : BE (fr)</t>
         </is>
       </c>
       <c r="C40" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ae_ar/consumer-monitors/lg-27gx790b-b</t>
+          <t>https://www.lg.com/be_fr/moniteurs/lg-27gx790b-b</t>
         </is>
       </c>
       <c r="D40" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E40" s="123" t="n"/>
@@ -7917,12 +7918,12 @@
     <row r="41">
       <c r="B41" s="261" t="inlineStr">
         <is>
-          <t>AU : AU (en)</t>
+          <t>BR : BR (pt)</t>
         </is>
       </c>
       <c r="C41" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/au/monitors/ultragear-gaming/27gx790b-b/</t>
+          <t>https://www.lg.com/br/monitores/monitores-ultragear-oled/27gx790b-b/</t>
         </is>
       </c>
       <c r="D41" s="264" t="inlineStr">
@@ -7943,17 +7944,17 @@
     <row r="42">
       <c r="B42" s="261" t="inlineStr">
         <is>
-          <t>BE_FR : BE (fr)</t>
+          <t>CA_EN : CA (en)</t>
         </is>
       </c>
       <c r="C42" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/be_fr/moniteurs/lg-27gx790b-b</t>
+          <t>https://www.lg.com/ca_en/monitors/gaming/27gx790b-b/</t>
         </is>
       </c>
       <c r="D42" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E42" s="123" t="n"/>
@@ -7969,12 +7970,12 @@
     <row r="43">
       <c r="B43" s="261" t="inlineStr">
         <is>
-          <t>BR : BR (pt)</t>
+          <t>CA_FR : CA (fr)</t>
         </is>
       </c>
       <c r="C43" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/br/monitores/monitores-ultragear-oled/27gx790b-b/</t>
+          <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/27gx790b-b/</t>
         </is>
       </c>
       <c r="D43" s="264" t="inlineStr">
@@ -7995,12 +7996,12 @@
     <row r="44">
       <c r="B44" s="261" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C44" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/monitors/gaming/27gx790b-b/</t>
+          <t>https://www.lg.com/cn/monitors/lg-27gx790b-b</t>
         </is>
       </c>
       <c r="D44" s="264" t="inlineStr">
@@ -8021,12 +8022,12 @@
     <row r="45">
       <c r="B45" s="261" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>DE : DE (de)</t>
         </is>
       </c>
       <c r="C45" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/27gx790b-b/</t>
+          <t>https://www.lg.com/de/monitore/gaming/27gx790b-b/</t>
         </is>
       </c>
       <c r="D45" s="264" t="inlineStr">
@@ -8047,17 +8048,17 @@
     <row r="46">
       <c r="B46" s="261" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>ES : ES (es)</t>
         </is>
       </c>
       <c r="C46" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-27gx790b-b</t>
+          <t>https://www.lg.com/es/monitores/monitores-ultragear-oled-gaming/27gx790b-b/</t>
         </is>
       </c>
       <c r="D46" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E46" s="123" t="n"/>
@@ -8073,12 +8074,12 @@
     <row r="47">
       <c r="B47" s="261" t="inlineStr">
         <is>
-          <t>DE : DE (de)</t>
+          <t>FR : FR (fr)</t>
         </is>
       </c>
       <c r="C47" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/de/monitore/gaming/27gx790b-b/</t>
+          <t>https://www.lg.com/fr/moniteurs/gaming/lg-27gx790b-b/</t>
         </is>
       </c>
       <c r="D47" s="264" t="inlineStr">
@@ -8099,12 +8100,12 @@
     <row r="48">
       <c r="B48" s="261" t="inlineStr">
         <is>
-          <t>ES : ES (es)</t>
+          <t>FR : FR (fr)</t>
         </is>
       </c>
       <c r="C48" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es/monitores/monitores-ultragear-oled-gaming/27gx790b-b/</t>
+          <t>https://www.lg.com/fr/moniteurs/lg-27gx790b-b-27g411a-bundle/</t>
         </is>
       </c>
       <c r="D48" s="264" t="inlineStr">
@@ -8125,12 +8126,12 @@
     <row r="49">
       <c r="B49" s="261" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
+          <t>HK : HK (zh)</t>
         </is>
       </c>
       <c r="C49" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fr/moniteurs/gaming/lg-27gx790b-b/</t>
+          <t>https://www.lg.com/hk/monitors/gaming/27gx790b-b/</t>
         </is>
       </c>
       <c r="D49" s="264" t="inlineStr">
@@ -8151,12 +8152,12 @@
     <row r="50">
       <c r="B50" s="261" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
+          <t>HK_EN : HK (en)</t>
         </is>
       </c>
       <c r="C50" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fr/moniteurs/lg-27gx790b-b-27g411a-bundle/</t>
+          <t>https://www.lg.com/hk_en/monitors/gaming/27gx790b-b/</t>
         </is>
       </c>
       <c r="D50" s="264" t="inlineStr">
@@ -8177,12 +8178,12 @@
     <row r="51">
       <c r="B51" s="261" t="inlineStr">
         <is>
-          <t>HK : HK (zh)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C51" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk/monitors/gaming/27gx790b-b/</t>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/27gx790b-b/</t>
         </is>
       </c>
       <c r="D51" s="264" t="inlineStr">
@@ -8203,12 +8204,12 @@
     <row r="52">
       <c r="B52" s="261" t="inlineStr">
         <is>
-          <t>HK_EN : HK (en)</t>
+          <t>NL : NL (nl)</t>
         </is>
       </c>
       <c r="C52" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk_en/monitors/gaming/27gx790b-b/</t>
+          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-oled/27gx790b-b/</t>
         </is>
       </c>
       <c r="D52" s="264" t="inlineStr">
@@ -8229,17 +8230,17 @@
     <row r="53">
       <c r="B53" s="261" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>PL : PL (pl)</t>
         </is>
       </c>
       <c r="C53" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/gaming-monitors/27gx790b-b/</t>
+          <t>https://www.lg.com/pl/monitory/ultragear-gaming/27gx790b-b/</t>
         </is>
       </c>
       <c r="D53" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E53" s="123" t="n"/>
@@ -8255,12 +8256,12 @@
     <row r="54">
       <c r="B54" s="261" t="inlineStr">
         <is>
-          <t>NL : NL (nl)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C54" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-oled/27gx790b-b/</t>
+          <t>https://www.lg.com/sg/consumer-monitors/gaming/27gx790b-b/</t>
         </is>
       </c>
       <c r="D54" s="264" t="inlineStr">
@@ -8281,12 +8282,12 @@
     <row r="55">
       <c r="B55" s="261" t="inlineStr">
         <is>
-          <t>PL : PL (pl)</t>
+          <t>TR : TR (tr)</t>
         </is>
       </c>
       <c r="C55" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pl/monitory/ultragear-gaming/27gx790b-b/</t>
+          <t>https://www.lg.com/tr/monitor/ultragear-gaming-oled/27gx790b-b/</t>
         </is>
       </c>
       <c r="D55" s="264" t="inlineStr">
@@ -8307,12 +8308,12 @@
     <row r="56">
       <c r="B56" s="261" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
+          <t>UK : GB (en)</t>
         </is>
       </c>
       <c r="C56" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg/consumer-monitors/gaming/27gx790b-b/</t>
+          <t>https://www.lg.com/uk/monitors/gaming/27gx790b-b/</t>
         </is>
       </c>
       <c r="D56" s="264" t="inlineStr">
@@ -8333,12 +8334,12 @@
     <row r="57">
       <c r="B57" s="261" t="inlineStr">
         <is>
-          <t>TR : TR (tr)</t>
+          <t>UK : GB (en)</t>
         </is>
       </c>
       <c r="C57" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tr/monitor/ultragear-gaming-oled/27gx790b-b/</t>
+          <t>https://www.lg.com/uk/monitors/gaming/27gx790b-b-27g640a/</t>
         </is>
       </c>
       <c r="D57" s="264" t="inlineStr">
@@ -8359,12 +8360,12 @@
     <row r="58">
       <c r="B58" s="261" t="inlineStr">
         <is>
-          <t>UK : GB (en)</t>
+          <t>VN : VN (vi)</t>
         </is>
       </c>
       <c r="C58" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/uk/monitors/gaming/27gx790b-b/</t>
+          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-gaming-oled-ultragear-oled/27gx790b-b/</t>
         </is>
       </c>
       <c r="D58" s="264" t="inlineStr">
@@ -8385,17 +8386,17 @@
     <row r="59">
       <c r="B59" s="261" t="inlineStr">
         <is>
-          <t>UK : GB (en)</t>
+          <t>PE : PE (es)</t>
         </is>
       </c>
       <c r="C59" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/uk/monitors/gaming/27gx790b-b-27g640a/</t>
+          <t>https://www.lg.com/pe/monitores/gamer/27gx790b-b/</t>
         </is>
       </c>
       <c r="D59" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="E59" s="123" t="n"/>
@@ -8411,12 +8412,12 @@
     <row r="60">
       <c r="B60" s="261" t="inlineStr">
         <is>
-          <t>VN : VN (vi)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C60" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-gaming-oled-ultragear-oled/27gx790b-b/</t>
+          <t>https://www.lg.com/cn/monitors/lg-32gx870b-b</t>
         </is>
       </c>
       <c r="D60" s="264" t="inlineStr">
@@ -8430,24 +8431,24 @@
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>27GX790B</t>
+          <t>32GX870B</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="261" t="inlineStr">
         <is>
-          <t>PE : PE (es)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C61" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pe/monitores/gamer/27gx790b-b/</t>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/32gx870b-b/</t>
         </is>
       </c>
       <c r="D61" s="264" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E61" s="123" t="n"/>
@@ -8456,24 +8457,24 @@
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>27GX790B</t>
+          <t>32GX870B</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="261" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>TR : TR (tr)</t>
         </is>
       </c>
       <c r="C62" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-32gx870b-b</t>
+          <t>https://www.lg.com/tr/monitors/32gx870b-b/</t>
         </is>
       </c>
       <c r="D62" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="E62" s="123" t="n"/>
@@ -8494,12 +8495,12 @@
       </c>
       <c r="C63" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/gaming-monitors/32gx870b-b/</t>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/32gx870b-bajp/</t>
         </is>
       </c>
       <c r="D63" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E63" s="123" t="n"/>
@@ -8515,17 +8516,17 @@
     <row r="64">
       <c r="B64" s="261" t="inlineStr">
         <is>
-          <t>TR : TR (tr)</t>
+          <t>AU : AU (en)</t>
         </is>
       </c>
       <c r="C64" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tr/monitors/32gx870b-b/</t>
+          <t>https://www.lg.com/au/monitors/ultragear-gaming/39gx950b/</t>
         </is>
       </c>
       <c r="D64" s="264" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E64" s="123" t="n"/>
@@ -8534,24 +8535,24 @@
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>32GX870B</t>
+          <t>39GX950B</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="261" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>CA_EN : CA (en)</t>
         </is>
       </c>
       <c r="C65" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/gaming-monitors/32gx870b-bajp/</t>
+          <t>https://www.lg.com/ca_en/monitors/gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D65" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E65" s="123" t="n"/>
@@ -8560,24 +8561,24 @@
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>32GX870B</t>
+          <t>39GX950B</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="261" t="inlineStr">
         <is>
-          <t>AU : AU (en)</t>
+          <t>CA_FR : CA (fr)</t>
         </is>
       </c>
       <c r="C66" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/au/monitors/ultragear-gaming/39gx950b/</t>
+          <t>https://www.lg.com/ca_fr/moniteurs/gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D66" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E66" s="123" t="n"/>
@@ -8593,12 +8594,12 @@
     <row r="67">
       <c r="B67" s="261" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C67" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/monitors/gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/cn/monitors/lg-39gx950b-b</t>
         </is>
       </c>
       <c r="D67" s="264" t="inlineStr">
@@ -8619,17 +8620,17 @@
     <row r="68">
       <c r="B68" s="261" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>DE : DE (de)</t>
         </is>
       </c>
       <c r="C68" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/moniteurs/gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/de/monitore/gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D68" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E68" s="123" t="n"/>
@@ -8645,17 +8646,17 @@
     <row r="69">
       <c r="B69" s="261" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>ES : ES (es)</t>
         </is>
       </c>
       <c r="C69" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-39gx950b-b</t>
+          <t>https://www.lg.com/es/monitores/monitores-ultragear-evo/39gx950b-b/</t>
         </is>
       </c>
       <c r="D69" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E69" s="123" t="n"/>
@@ -8671,17 +8672,17 @@
     <row r="70">
       <c r="B70" s="261" t="inlineStr">
         <is>
-          <t>DE : DE (de)</t>
+          <t>FR : FR (fr)</t>
         </is>
       </c>
       <c r="C70" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/de/monitore/gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/fr/moniteurs/gaming/39GX950B-B/</t>
         </is>
       </c>
       <c r="D70" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E70" s="123" t="n"/>
@@ -8697,17 +8698,17 @@
     <row r="71">
       <c r="B71" s="261" t="inlineStr">
         <is>
-          <t>ES : ES (es)</t>
+          <t>HK : HK (zh)</t>
         </is>
       </c>
       <c r="C71" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es/monitores/monitores-ultragear-evo/39gx950b-b/</t>
+          <t>https://www.lg.com/hk/monitors/gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D71" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E71" s="123" t="n"/>
@@ -8723,17 +8724,17 @@
     <row r="72">
       <c r="B72" s="261" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
+          <t>HK_EN : HK (en)</t>
         </is>
       </c>
       <c r="C72" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fr/moniteurs/gaming/39GX950B-B/</t>
+          <t>https://www.lg.com/hk_en/monitors/gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D72" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E72" s="123" t="n"/>
@@ -8749,17 +8750,17 @@
     <row r="73">
       <c r="B73" s="261" t="inlineStr">
         <is>
-          <t>HK : HK (zh)</t>
+          <t>HU : HU (hu)</t>
         </is>
       </c>
       <c r="C73" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk/monitors/gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/hu/monitorok/ultragear-gaming-oled/39gx950b-b/</t>
         </is>
       </c>
       <c r="D73" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E73" s="123" t="n"/>
@@ -8775,12 +8776,12 @@
     <row r="74">
       <c r="B74" s="261" t="inlineStr">
         <is>
-          <t>HK_EN : HK (en)</t>
+          <t>IT : IT (it)</t>
         </is>
       </c>
       <c r="C74" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk_en/monitors/gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/it/monitor/ultragear-gaming-oled/39gx950b-b/</t>
         </is>
       </c>
       <c r="D74" s="264" t="inlineStr">
@@ -8801,17 +8802,17 @@
     <row r="75">
       <c r="B75" s="261" t="inlineStr">
         <is>
-          <t>HU : HU (hu)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C75" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hu/monitorok/ultragear-gaming-oled/39gx950b-b/</t>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/39gx950b-b/</t>
         </is>
       </c>
       <c r="D75" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E75" s="123" t="n"/>
@@ -8827,17 +8828,17 @@
     <row r="76">
       <c r="B76" s="261" t="inlineStr">
         <is>
-          <t>IT : IT (it)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C76" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/it/monitor/ultragear-gaming-oled/39gx950b-b/</t>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/39gx950b-bajp/</t>
         </is>
       </c>
       <c r="D76" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E76" s="123" t="n"/>
@@ -8853,17 +8854,17 @@
     <row r="77">
       <c r="B77" s="261" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>NL : NL (nl)</t>
         </is>
       </c>
       <c r="C77" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/gaming-monitors/39gx950b-b/</t>
+          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-monitoren/39gx950b-b/</t>
         </is>
       </c>
       <c r="D77" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E77" s="123" t="n"/>
@@ -8879,17 +8880,17 @@
     <row r="78">
       <c r="B78" s="261" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>PE : PE (es)</t>
         </is>
       </c>
       <c r="C78" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/gaming-monitors/39gx950b-bajp/</t>
+          <t>https://www.lg.com/pe/monitores/ultragear-gaming-oled/39gx950b-b/</t>
         </is>
       </c>
       <c r="D78" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E78" s="123" t="n"/>
@@ -8905,17 +8906,17 @@
     <row r="79">
       <c r="B79" s="261" t="inlineStr">
         <is>
-          <t>NL : NL (nl)</t>
+          <t>PL : PL (pl)</t>
         </is>
       </c>
       <c r="C79" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-monitoren/39gx950b-b/</t>
+          <t>https://www.lg.com/pl/monitory/39gx950b-b/</t>
         </is>
       </c>
       <c r="D79" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E79" s="123" t="n"/>
@@ -8931,17 +8932,17 @@
     <row r="80">
       <c r="B80" s="261" t="inlineStr">
         <is>
-          <t>PE : PE (es)</t>
+          <t>SE : SE (sv)</t>
         </is>
       </c>
       <c r="C80" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pe/monitores/ultragear-gaming-oled/39gx950b-b/</t>
+          <t>https://www.lg.com/se/monitor/ultragear-gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D80" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E80" s="123" t="n"/>
@@ -8957,17 +8958,17 @@
     <row r="81">
       <c r="B81" s="261" t="inlineStr">
         <is>
-          <t>PL : PL (pl)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C81" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pl/monitory/39gx950b-b/</t>
+          <t>https://www.lg.com/sg/consumer-monitors/gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D81" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E81" s="123" t="n"/>
@@ -8983,17 +8984,17 @@
     <row r="82">
       <c r="B82" s="261" t="inlineStr">
         <is>
-          <t>SE : SE (sv)</t>
+          <t>TH : TH (th)</t>
         </is>
       </c>
       <c r="C82" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/se/monitor/ultragear-gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/th/monitors/gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D82" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E82" s="123" t="n"/>
@@ -9009,17 +9010,17 @@
     <row r="83">
       <c r="B83" s="261" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
+          <t>TR : TR (tr)</t>
         </is>
       </c>
       <c r="C83" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg/consumer-monitors/gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/tr/monitor/ultragear-gaming-oled/39gx950b-b/</t>
         </is>
       </c>
       <c r="D83" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E83" s="123" t="n"/>
@@ -9035,17 +9036,17 @@
     <row r="84">
       <c r="B84" s="261" t="inlineStr">
         <is>
-          <t>TH : TH (th)</t>
+          <t>TW : TW (zh)</t>
         </is>
       </c>
       <c r="C84" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/th/monitors/gaming/39gx950b-b/</t>
+          <t>https://www.lg.com/tw/monitors/ultragear-gaming/39gx950b-b/</t>
         </is>
       </c>
       <c r="D84" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E84" s="123" t="n"/>
@@ -9061,17 +9062,17 @@
     <row r="85">
       <c r="B85" s="261" t="inlineStr">
         <is>
-          <t>TR : TR (tr)</t>
+          <t>UK : GB (en)</t>
         </is>
       </c>
       <c r="C85" s="261" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tr/monitor/ultragear-gaming-oled/39gx950b-b/</t>
+          <t>https://www.lg.com/uk/monitors/gaming-monitor/39gx950b-b/</t>
         </is>
       </c>
       <c r="D85" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E85" s="123" t="n"/>
@@ -9079,58 +9080,6 @@
         <v>1</v>
       </c>
       <c r="G85" s="0" t="inlineStr">
-        <is>
-          <t>39GX950B</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="261" t="inlineStr">
-        <is>
-          <t>TW : TW (zh)</t>
-        </is>
-      </c>
-      <c r="C86" s="261" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/monitors/ultragear-gaming/39gx950b-b/</t>
-        </is>
-      </c>
-      <c r="D86" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E86" s="123" t="n"/>
-      <c r="F86" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="0" t="inlineStr">
-        <is>
-          <t>39GX950B</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="261" t="inlineStr">
-        <is>
-          <t>UK : GB (en)</t>
-        </is>
-      </c>
-      <c r="C87" s="261" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/monitors/gaming-monitor/39gx950b-b/</t>
-        </is>
-      </c>
-      <c r="D87" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E87" s="123" t="n"/>
-      <c r="F87" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="0" t="inlineStr">
         <is>
           <t>39GX950B</t>
         </is>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -7036,7 +7036,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -10651,7 +10650,8 @@
         <is>
           <t>CZ : 작업중 → 완료
 TR : 법인리뷰 → 작업중
-IN : 법인리뷰 → 완료 (7/16 게시, PTT 확인)</t>
+IN : 법인리뷰 → 완료 (7/16 게시, PTT 확인)
+TR : 작업중 → 완료 (7/23 게시, PTT 확인)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -11617,14 +11617,22 @@
       </c>
       <c r="D48" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E48" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E48" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="F48" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="0" t="inlineStr"/>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>7건 중 6건 게시완료 · 1건 Final Live Check 잔여</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="261" t="inlineStr">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -2946,7 +2946,7 @@
       </c>
       <c r="B1" s="163" t="inlineStr">
         <is>
-          <t>W23 - 52G930B Feature 수정 건</t>
+          <t>GR26-W23 - 52G930B Feature 수정 건</t>
         </is>
       </c>
       <c r="C1" s="164" t="n"/>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="B1" s="163" t="inlineStr">
         <is>
-          <t>W23 - UL인증 feature 삭제 1차</t>
+          <t>GR26-W23 - UL인증 feature 삭제 1차</t>
         </is>
       </c>
       <c r="C1" s="164" t="n"/>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="B1" s="163" t="inlineStr">
         <is>
-          <t>W23 - 27GM950B-B 갤러리 이미지 교체</t>
+          <t>GR26-W23 - 27GM950B-B 갤러리 이미지 교체</t>
         </is>
       </c>
       <c r="C1" s="164" t="n"/>
@@ -14197,7 +14197,7 @@
       </c>
       <c r="B1" s="163" t="inlineStr">
         <is>
-          <t>W23 - 39GX950B 이미지 수정 2차</t>
+          <t>GR26-W23 - 39GX950B 이미지 수정 2차</t>
         </is>
       </c>
       <c r="C1" s="164" t="n"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -11769,7 +11769,8 @@
       <c r="B2" s="163" t="inlineStr">
         <is>
           <t>NL : URL 변경
-SE : URL 변경</t>
+SE : URL 변경
+JP : URL 오기입 정정(uk/ice-solution → jp/monitors/ultragear-evo)</t>
         </is>
       </c>
       <c r="D2" s="164" t="n"/>
@@ -12039,7 +12040,7 @@
       </c>
       <c r="C16" s="268" t="inlineStr">
         <is>
-          <t>https://www.lg.com/uk/ice-solution/</t>
+          <t>https://www.lg.com/jp/monitors/ultragear-evo/</t>
         </is>
       </c>
       <c r="D16" s="273" t="inlineStr">
@@ -12047,7 +12048,11 @@
           <t>법인리뷰</t>
         </is>
       </c>
-      <c r="E16" s="288" t="n"/>
+      <c r="E16" s="288" t="inlineStr">
+        <is>
+          <t>미게시(법인리뷰) · STG 경로 기준</t>
+        </is>
+      </c>
       <c r="F16" s="275" t="n"/>
       <c r="G16" s="177" t="n">
         <v>2</v>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -17,6 +17,10 @@
     <sheet name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="W31 - Windows 11 Landing" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9089,6 +9093,3761 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>GR26-W30-MS-IT Smart Monitor Screen Share 카피 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>금주 신규 등록 · Screen Share 카피/디스클레이머 삭제 · DAM 적재 완료(7/27) 지급 진행 · 대상 4모델(색상 파생 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MX : MX (es)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/mx/monitores/monitores-smart/24u511sb-b/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>24U511SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/monitors/smart-monitors/24u511sb-b/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>24U511SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/smart-monitors/24u511sb-b/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>24U511SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/smart-monitores/24u511sb-b/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>24U511SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AE : AE (en)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://wwwstg.lg.com/ae/consumer-monitors/lg-24u511sb-b</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>24U511SB-B · 페이지 QA review</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BR : BR (pt)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/br/monitores/smart-monitors/24u511sb-b/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>24U511SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MX : MX (es)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/mx/monitores/monitores-smart/27u511sb-w/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>27U511SB-W</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>US : US (en)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/us/monitors/lg-27u511sb-w-smart-monitor</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>27U511SB-W</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/consumer-monitors/smart-monitors/27u511sb-w/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>27U511SB-W</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/monitors/smart-monitors/27u511sb-b/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>27U511SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ID : ID (id)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitor/smart-monitors/27u511sb/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>27U511SB-W</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/smart-monitors/27u511sb-w/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>27U511SB-W</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/smart-monitores/27u511sb-w/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>27U511SB-W</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pe/monitores/fhd-y-qhd/27u511sb-w/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>27U511SB-W</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk_en/monitors/smart-monitors/27u511sb-w/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>27U511SB-W</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk/monitors/smart-monitors/27u511sb-w/</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>27U511SB-W</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AE : AE (en)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://wwwstg.lg.com/ae/consumer-monitors/lg-27u511sb-w</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>27U511SB-W · 페이지 WPL review</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BR : BR (pt)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/br/pt/monitores/smart-monitors/27u511sb-b.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>27U511SB-B · 페이지 New Request</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/jp/ja/monitors/smart-monitors/27u511sb-b.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>27U511SB-B · 페이지 Client Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/monitors/smart-monitors/32u501sb-b/</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>32U501SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ID : ID (id)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitor/smart-monitors/32u501sb/</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>32U501SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/smart-monitors/32u501sb-w/</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>32U501SB-W</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AE : AE (en)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://wwwstg.lg.com/ae/business/monitors/lg-32u501sb-b-ama</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>32U501SB-B · 페이지 In progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/monitors/smart-monitors/32u501sb-b.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>32U501SB-B · 페이지 QA review</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/smart-monitores/32u501sb-b/</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>32U501SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/au/en/monitors/smart-monitors/32U501SB.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>취소</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>32U501SB · 페이지 Cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>US : US (en)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/us/monitors/lg-32u701sb-b-smart-monitor</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>32U701SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/monitores/myview-smart-monitor/32u701sb-b/</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>32U701SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/outlet/outlet-informatica/monitores/32u701sb-b-outlet/</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>32U701SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/monitors/smart-monitors/32u701sb-b/</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>32U701SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TR : TR (tr)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tr/monitor/smart-monitorleri/32u701sb-b/</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>32U701SB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AE : AE (en)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://wwwstg.lg.com/ae/consumer-monitors/lg-32u701sb-b</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>32U701SB-B · 페이지 QA review</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ZA : ZA (en)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/za/en/monitors/smart-monitors/32u701sb.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>32u701sb · 페이지 Client Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BR : BR (pt)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/br/pt/monitores/smart-monitors/32u701sb-b.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>32U701SB-B · 페이지 QA review</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/smart-monitores/32u701sb-b/</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>32U701SB-B</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>GR26-W30-MS-IT UltraGear PLP FAQ 1000Hz 문항 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>금주 신규 등록 · JIRA LGCOMMON-29612 · 1000Hz 제품 문항 3건 추가 · 대상 URL 확정 대기(GR 파일 미수신)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G107"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>GR26-W31-MS-IT gram Secure Lock 컴포넌트 교체</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>예정 · 13개국 대상 · CN은 PDP 라이브이나 기존 Secure Lock 컴포넌트 영역 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/gram/14z90u-g-as67c2/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/gram-pro/16z90u-g-au87c2/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/gram-pro/16z90u-k-aub7c2/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/gram-pro/16z90u-k-aub8c2/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/gram-pro/16z95u-g-as69c2/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>16Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/gram-pro/17z90u-g-au88c2/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/notebooks/gram-pro/16z90u-g-au78gn/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/notebooks/gram-pro/16z90u-k-aub8gn/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/notebooks/gram-pro/17z90u-g-au8bgn/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/laptop-lg-gram/14z90u-g/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/laptop-lg-gram/15u50u-g/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>15U50U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/laptop-lg-gram/16z90u-g-16gb/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/laptop-lg-gram/16z90u-g-32gb/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/laptop-lg-gram/16z95u-g/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>16Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/gram/14z90u-g-au85bn/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/gram/14z90u-g-au88bn/</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/ordenadores/portatiles-para-creadores/14z95u-g-au88bn/</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/gram/14z95u-g-as55bn/</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/gram/14z95u-g-au85bn/</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/laptops/gram/16z90u-k-aub5bn/</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/16z90u-g-au85bn/</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/16z90u-g-au88bn/</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/gram-pro/16z90u-k-aub8bn/</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/14z90u-g-az75a3/</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/14z90u-g-az85a3/</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/14z90u-g-as54a3/</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/14z90u-g-au85a3/</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/14z95u-g-as56a3/</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/14z95u-g-au85a3/</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/14z95u-g-au86a3/</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/14z95u56-16mr70/</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/14z95u85-16mr70/</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/14z95u86-16mr70/</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/15u50u-16mr70/</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>15U50U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/15u50u-g-aa55a3/</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>15U50U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90u-k-azb5a3/</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aua5a3/</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aub5a3/</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aub9a3/</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram-pro/16z95u-16mr70/</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>16Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram-pro/16z95u-g-as55a3/</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>16Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram-pro/16z95u-g-au85a3/</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>16Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/17z90u-g-au85a3/</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/laptops/gram/15u50u-g-aa55an.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>15U50U-G.AA55AN · Erase.Lock -</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/laptops/gram-pro/16z90u-h-au78an.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>16Z90U-H.AU78AN · Erase.Lock -</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/laptops/gram-pro/16z90u-k-aub8an.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>16Z90U-K.AUB8AN · Erase.Lock -</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/laptops/gram-pro/17z90u-g-au78an.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU78AN · Erase.Lock -</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/gram/14z90u-g-as58dn/</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>- · Erase.Lock -</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-gs54j/</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-gs58j/</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-gu85j/</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-vp58j/</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>14Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gs53j/</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gs54j/</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gs55j/</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gu85j/</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gu86j/</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-vp53j/</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-vp55j/</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>14Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-gu85j/</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-gu88j/</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-kub5j/</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-kub9j/</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z95u-gs55j/</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>16Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z95u-gu88j/</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>16Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/17z90u-gu85j/</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/17z90u-gu88j/</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/17z90u-vp55j/</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-gal87c/</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-gal88c/</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb7c/</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb8c/</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb9c/</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-17z90u-al87c/</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-17z90u-gal88c/</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/16z95u-g/</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>16Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/small-medium-business/laptops/16z95u-g/</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>16Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/ordinateurs-portables/16z95u-g/</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>16Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/small-medium-business/ordinateurs-portables/16z95u-g/</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>16Z95U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g78/</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g88/</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/small-medium-business/laptops/all-laptops/17z90u-g78/</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/small-medium-business/laptops/all-laptops/17z90u-g88/</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90u-g78/</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90u-g88/</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ub-h/</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>17Z90UB-H · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/small-medium-business/laptops/all-laptops/17z90ub-h/</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>17Z90UB-H · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90ub-h/</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>17Z90UB-H · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/small-medium-business/computing/purchase-guide/laptops/17z90ub-h/</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>17Z90UB-H · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/ca/en/laptops/all-laptops/17z90ub-h.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>17Z90UR-P · Erase.Lock -</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ur-p/</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>17Z90UR-P · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17Z90ur-p/</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>17Z90UR-P · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/ca/fr/computing/purchase-guide/laptops/17z90ub-h.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>17Z90UR-P · Erase.Lock -</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>15U50U-G · Erase.Lock -</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>15Z95U-G · Erase.Lock -</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>16Z90U-G · Erase.Lock -</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock -</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/16z90u-g-au75ap/</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>16Z90U-G.AU75AP · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/16z90u-g-au88ap/</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>16Z90U-K · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au75ap/</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au78ap/</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au88ap/</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>17Z90U-G · Erase.Lock 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/au/en/laptops/gram-pro/17z90ub-h.html?wcmmode=disabled</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>17Z90UB-H · Erase.Lock -</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>GR26-W31-MS-IT Windows 11 Home Landing Page 업데이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>예정 · 자산 배포 2026-08-09(EN)/2026-09-11(현지화) · 구현 마감 2026-11-15(Jumpstart OEM.com 준수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -9103,936 +9103,936 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>GR26-W30-MS-IT Smart Monitor Screen Share 카피 수정</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>이번주 추가</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>금주 신규 등록 · Screen Share 카피/디스클레이머 삭제 · DAM 적재 완료(7/27) 지급 진행 · 대상 4모델(색상 파생 6)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>완료일</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Page#</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>MX : MX (es)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/mx/monitores/monitores-smart/24u511sb-b/</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>24U511SB-B</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/monitors/smart-monitors/24u511sb-b/</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>24U511SB-B</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/monitors/smart-monitors/24u511sb-b/</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>24U511SB-B</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>CO : CO (es)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/co/monitores/smart-monitores/24u511sb-b/</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>24U511SB-B</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>https://wwwstg.lg.com/ae/consumer-monitors/lg-24u511sb-b</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>24U511SB-B · 페이지 QA review</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>BR : BR (pt)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/br/monitores/smart-monitors/24u511sb-b/</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>24U511SB-B</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>MX : MX (es)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/mx/monitores/monitores-smart/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>27U511SB-W</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>US : US (en)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/us/monitors/lg-27u511sb-w-smart-monitor</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>27U511SB-W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/consumer-monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>27U511SB-W</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/monitors/smart-monitors/27u511sb-b/</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>27U511SB-B</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>ID : ID (id)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/id/monitor/smart-monitors/27u511sb/</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>27U511SB-W</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>27U511SB-W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>CO : CO (es)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/co/monitores/smart-monitores/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>27U511SB-W</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>PE : PE (es)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/pe/monitores/fhd-y-qhd/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>27U511SB-W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>HK_EN : HK (en)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/hk_en/monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>27U511SB-W</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>HK : HK (zh)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/hk/monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>27U511SB-W</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>https://wwwstg.lg.com/ae/consumer-monitors/lg-27u511sb-w</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>27U511SB-W · 페이지 WPL review</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>BR : BR (pt)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/br/pt/monitores/smart-monitors/27u511sb-b.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>27U511SB-B · 페이지 New Request</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/jp/ja/monitors/smart-monitors/27u511sb-b.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>27U511SB-B · 페이지 Client Review</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/monitors/smart-monitors/32u501sb-b/</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>32U501SB-B</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>ID : ID (id)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/id/monitor/smart-monitors/32u501sb/</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>32U501SB-B</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/monitors/smart-monitors/32u501sb-w/</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>32U501SB-W</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>https://wwwstg.lg.com/ae/business/monitors/lg-32u501sb-b-ama</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>32U501SB-B · 페이지 In progress</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/monitors/smart-monitors/32u501sb-b.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>32U501SB-B · 페이지 QA review</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>CO : CO (es)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/co/monitores/smart-monitores/32u501sb-b/</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>32U501SB-B</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/au/en/monitors/smart-monitors/32U501SB.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>취소</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>32U501SB · 페이지 Cancelled</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>US : US (en)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/us/monitors/lg-32u701sb-b-smart-monitor</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>32U701SB-B</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/monitores/myview-smart-monitor/32u701sb-b/</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
         <is>
           <t>32U701SB-B</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/outlet/outlet-informatica/monitores/32u701sb-b-outlet/</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>32U701SB-B</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/monitors/smart-monitors/32u701sb-b/</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
         <is>
           <t>32U701SB-B</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>TR : TR (tr)</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tr/monitor/smart-monitorleri/32u701sb-b/</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
         <is>
           <t>32U701SB-B</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>https://wwwstg.lg.com/ae/consumer-monitors/lg-32u701sb-b</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
         <is>
           <t>32U701SB-B · 페이지 QA review</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>ZA : ZA (en)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/za/en/monitors/smart-monitors/32u701sb.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
         <is>
           <t>32u701sb · 페이지 Client Approved</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>BR : BR (pt)</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/br/pt/monitores/smart-monitors/32u701sb-b.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
         <is>
           <t>32U701SB-B · 페이지 QA review</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>CO : CO (es)</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/co/monitores/smart-monitores/32u701sb-b/</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>32U701SB-B</t>
         </is>
@@ -10049,67 +10049,342 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>GR26-W30-MS-IT UltraGear PLP FAQ 1000Hz 문항 추가</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>이번주 추가</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>금주 신규 등록 · JIRA LGCOMMON-29612 · 1000Hz 제품 문항 3건 추가 · 대상 URL 확정 대기(GR 파일 미수신)</t>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>금주 신규 등록 · JIRA LGCOMMON-29612 · 요청자 Yerim Yeo · Due 2026-08-14 · 기존 UltraGear Gaming PLP 하단 FAQ에 1000Hz 문항 3건 추가 + 각국 번역</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>완료일</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Page#</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/monitors/ultragear-gaming/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CA : CA (en)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/gaming/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CA : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/monitore/gaming/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/monitores/monitores-ultragear-gaming/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/gaming/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/gaming/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-monitoren/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SE : SE (sv)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/monitor/ultragear-gaming/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>UK : UK (en)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/gaming/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
         </is>
       </c>
     </row>
@@ -10128,2641 +10403,2641 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>GR26-W31-MS-IT gram Secure Lock 컴포넌트 교체</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>이번주 추가</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>예정 · 13개국 대상 · CN은 PDP 라이브이나 기존 Secure Lock 컴포넌트 영역 없음</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>완료일</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Page#</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/laptops/gram/14z90u-g-as67c2/</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/laptops/gram-pro/16z90u-g-au87c2/</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/laptops/gram-pro/16z90u-k-aub7c2/</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/laptops/gram-pro/16z90u-k-aub8c2/</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/laptops/gram-pro/16z95u-g-as69c2/</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/laptops/gram-pro/17z90u-g-au88c2/</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-pro/16z90u-g-au78gn/</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-pro/16z90u-k-aub8gn/</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-pro/17z90u-g-au8bgn/</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>VN : VN (vi)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/vn/laptop-lg-gram/14z90u-g/</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>VN : VN (vi)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/vn/laptop-lg-gram/15u50u-g/</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>15U50U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>VN : VN (vi)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/vn/laptop-lg-gram/16z90u-g-16gb/</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>VN : VN (vi)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/vn/laptop-lg-gram/16z90u-g-32gb/</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>VN : VN (vi)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/vn/laptop-lg-gram/16z95u-g/</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/14z90u-g-au85bn/</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/14z90u-g-au88bn/</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/business/informatica/ordenadores/portatiles-para-creadores/14z95u-g-au88bn/</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/14z95u-g-as55bn/</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/14z95u-g-au85bn/</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/laptops/gram/16z90u-k-aub5bn/</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/16z90u-g-au85bn/</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/16z90u-g-au88bn/</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram-pro/16z90u-k-aub8bn/</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/business/it-products/lg-gram/14z90u-g-az75a3/</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/business/it-products/lg-gram/14z90u-g-az85a3/</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram/14z90u-g-as54a3/</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram/14z90u-g-au85a3/</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram/14z95u-g-as56a3/</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram/14z95u-g-au85a3/</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram/14z95u-g-au86a3/</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram/14z95u56-16mr70/</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram/14z95u85-16mr70/</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram/14z95u86-16mr70/</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram/15u50u-16mr70/</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
         <is>
           <t>15U50U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram/15u50u-g-aa55a3/</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>15U50U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90u-k-azb5a3/</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aua5a3/</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aub5a3/</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aub9a3/</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram-pro/16z95u-16mr70/</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="F43" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
         <is>
           <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram-pro/16z95u-g-as55a3/</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
         <is>
           <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram-pro/16z95u-g-au85a3/</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="F45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
         <is>
           <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram/17z90u-g-au85a3/</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="F46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/laptops/gram/15u50u-g-aa55an.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="F47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
         <is>
           <t>15U50U-G.AA55AN · Erase.Lock -</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/laptops/gram-pro/16z90u-h-au78an.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
         <is>
           <t>16Z90U-H.AU78AN · Erase.Lock -</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/laptops/gram-pro/16z90u-k-aub8an.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="F49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K.AUB8AN · Erase.Lock -</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/laptops/gram-pro/17z90u-g-au78an.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="F50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G.AU78AN · Erase.Lock -</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>IT : IT (it)</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/14z90u-g-as58dn/</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr"/>
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
         <is>
           <t>- · Erase.Lock -</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-gs54j/</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="F53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-gs58j/</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-gu85j/</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="F55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-vp58j/</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="F56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gs53j/</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="inlineStr">
+      <c r="F57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gs54j/</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="F58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gs55j/</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="F59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gu85j/</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="F60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gu86j/</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="F61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-vp53j/</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-vp55j/</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="F63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="0" t="inlineStr">
         <is>
           <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-gu85j/</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F64" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-gu88j/</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="F65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-kub5j/</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="F66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-kub9j/</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="F67" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/16z95u-gs55j/</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F68" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="0" t="inlineStr">
         <is>
           <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/16z95u-gu88j/</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="inlineStr">
+      <c r="F69" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="0" t="inlineStr">
         <is>
           <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/17z90u-gu85j/</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F70" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/17z90u-gu88j/</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="F71" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/17z90u-vp55j/</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F72" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/notebooks/lg-16z90u-gal87c/</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 없음</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/notebooks/lg-16z90u-gal88c/</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F74" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 없음</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb7c/</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="F75" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 없음</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb8c/</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F76" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 없음</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb9c/</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F77" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 없음</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/notebooks/lg-17z90u-al87c/</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F78" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 없음</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/notebooks/lg-17z90u-gal88c/</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F79" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 없음</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/laptops/16z95u-g/</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F80" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="0" t="inlineStr">
         <is>
           <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/small-medium-business/laptops/16z95u-g/</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F81" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="0" t="inlineStr">
         <is>
           <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="0" t="inlineStr">
         <is>
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/ordinateurs-portables/16z95u-g/</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F82" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
         <is>
           <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="0" t="inlineStr">
         <is>
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/small-medium-business/ordinateurs-portables/16z95u-g/</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="F83" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="0" t="inlineStr">
         <is>
           <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g78/</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="F84" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g88/</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F85" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/small-medium-business/laptops/all-laptops/17z90u-g78/</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F86" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F86" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/small-medium-business/laptops/all-laptops/17z90u-g88/</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="F87" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="0" t="inlineStr">
         <is>
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90u-g78/</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F88" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="0" t="inlineStr">
         <is>
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90u-g88/</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F89" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ub-h/</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F90" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="0" t="inlineStr">
         <is>
           <t>17Z90UB-H · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/small-medium-business/laptops/all-laptops/17z90ub-h/</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F91" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="0" t="inlineStr">
         <is>
           <t>17Z90UB-H · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="0" t="inlineStr">
         <is>
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90ub-h/</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F92" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="0" t="inlineStr">
         <is>
           <t>17Z90UB-H · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="0" t="inlineStr">
         <is>
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/small-medium-business/computing/purchase-guide/laptops/17z90ub-h/</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="F93" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="0" t="inlineStr">
         <is>
           <t>17Z90UB-H · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/ca/en/laptops/all-laptops/17z90ub-h.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F94" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F94" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="0" t="inlineStr">
         <is>
           <t>17Z90UR-P · Erase.Lock -</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ur-p/</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F95" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F95" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="0" t="inlineStr">
         <is>
           <t>17Z90UR-P · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="0" t="inlineStr">
         <is>
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17Z90ur-p/</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F96" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F96" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="0" t="inlineStr">
         <is>
           <t>17Z90UR-P · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="0" t="inlineStr">
         <is>
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/ca/fr/computing/purchase-guide/laptops/17z90ub-h.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F97" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F97" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="0" t="inlineStr">
         <is>
           <t>17Z90UR-P · Erase.Lock -</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="0" t="inlineStr">
         <is>
           <t>FR : FR (fr)</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr">
+      <c r="C98" s="0" t="inlineStr"/>
+      <c r="D98" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F98" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="F98" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="0" t="inlineStr">
         <is>
           <t>15U50U-G · Erase.Lock -</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="0" t="inlineStr">
         <is>
           <t>FR : FR (fr)</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr">
+      <c r="C99" s="0" t="inlineStr"/>
+      <c r="D99" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F99" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" t="inlineStr">
+      <c r="F99" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="0" t="inlineStr">
         <is>
           <t>15Z95U-G · Erase.Lock -</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="0" t="inlineStr">
         <is>
           <t>FR : FR (fr)</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr">
+      <c r="C100" s="0" t="inlineStr"/>
+      <c r="D100" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F100" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" t="inlineStr">
+      <c r="F100" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="0" t="inlineStr">
         <is>
           <t>16Z90U-G · Erase.Lock -</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="0" t="inlineStr">
         <is>
           <t>FR : FR (fr)</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr">
+      <c r="C101" s="0" t="inlineStr"/>
+      <c r="D101" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F101" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" t="inlineStr">
+      <c r="F101" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock -</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/laptops/gram-pro/16z90u-g-au75ap/</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F102" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="F102" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="0" t="inlineStr">
         <is>
           <t>16Z90U-G.AU75AP · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/laptops/gram-pro/16z90u-g-au88ap/</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F103" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F103" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="0" t="inlineStr">
         <is>
           <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au75ap/</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F104" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" t="inlineStr">
+      <c r="F104" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au78ap/</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F105" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" t="inlineStr">
+      <c r="F105" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au88ap/</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F106" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" t="inlineStr">
+      <c r="F106" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="0" t="inlineStr">
         <is>
           <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="0" t="inlineStr">
         <is>
           <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/au/en/laptops/gram-pro/17z90ub-h.html?wcmmode=disabled</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
-      <c r="F107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" t="inlineStr">
+      <c r="F107" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="0" t="inlineStr">
         <is>
           <t>17Z90UB-H · Erase.Lock -</t>
         </is>
@@ -12783,61 +13058,61 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>GR26-W31-MS-IT Windows 11 Home Landing Page 업데이트</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>이번주 추가</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>예정 · 자산 배포 2026-08-09(EN)/2026-09-11(현지화) · 구현 마감 2026-11-15(Jumpstart OEM.com 준수)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>완료일</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Page#</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -21,6 +21,7 @@
     <sheet name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="W31 - Windows 11 Landing" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="W31 - PDP Gallery Win11 Pro" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10114,275 +10115,275 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/monitors/ultragear-gaming/</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>CA : CA (en)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/monitors/gaming/</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>CA : CA (fr)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/monitore/gaming/</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/monitores/monitores-ultragear-gaming/</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>FR : FR (fr)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/fr/moniteurs/gaming/</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>IT : IT (it)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/monitor/gaming/</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/monitors/gaming-monitors/</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>NL : NL (nl)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/nl/monitoren/ultragear-gaming-monitoren/</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>SE : SE (sv)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/se/monitor/ultragear-gaming/</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>UK : UK (en)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/monitors/gaming/</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>1000Hz 문항 3건 추가 · 현지어 번역 필요</t>
         </is>
@@ -13078,6 +13079,81 @@
       <c r="B2" s="0" t="inlineStr">
         <is>
           <t>예정 · 자산 배포 2026-08-09(EN)/2026-09-11(현지화) · 구현 마감 2026-11-15(Jumpstart OEM.com 준수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>GR26-W31-MS-IT-PC PDP Gallery Card Win11 Pro 영상 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>금주 신규 등록 · W16 PDP Gallery Card 후속 건 · Windows 11 Pro 영상 수정 · 대상 목록 미수신(확인 필요)</t>
         </is>
       </c>
     </row>
@@ -13464,7 +13540,7 @@
       </c>
       <c r="E7" s="223" t="inlineStr">
         <is>
-          <t>6월 12일</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F7" s="224" t="n">
@@ -13526,7 +13602,7 @@
       </c>
       <c r="E8" s="231" t="inlineStr">
         <is>
-          <t>6월 12일</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F8" s="232" t="n">
@@ -13588,7 +13664,7 @@
       </c>
       <c r="E9" s="231" t="inlineStr">
         <is>
-          <t>6월 12일</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F9" s="232" t="n">
@@ -13650,7 +13726,7 @@
       </c>
       <c r="E10" s="231" t="inlineStr">
         <is>
-          <t>6월 12일</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F10" s="225" t="n">
@@ -13712,7 +13788,7 @@
       </c>
       <c r="E11" s="231" t="inlineStr">
         <is>
-          <t>6월 12일</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F11" s="225" t="n">
@@ -13774,7 +13850,7 @@
       </c>
       <c r="E12" s="231" t="inlineStr">
         <is>
-          <t>6월 12일</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F12" s="232" t="n">
@@ -13836,7 +13912,7 @@
       </c>
       <c r="E13" s="234" t="inlineStr">
         <is>
-          <t>6월 12일</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F13" s="232" t="n">
@@ -13898,7 +13974,7 @@
       </c>
       <c r="E14" s="231" t="inlineStr">
         <is>
-          <t>6월 12일</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F14" s="225" t="n">
@@ -13960,7 +14036,7 @@
       </c>
       <c r="E15" s="231" t="inlineStr">
         <is>
-          <t>6월 12일</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F15" s="232" t="n">
@@ -14022,7 +14098,7 @@
       </c>
       <c r="E16" s="228" t="inlineStr">
         <is>
-          <t>6월 12일</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F16" s="225" t="n">
@@ -14267,7 +14343,7 @@
       </c>
       <c r="E10" s="242" t="inlineStr">
         <is>
-          <t>5월 28일</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F10" s="243" t="n">
@@ -14295,7 +14371,7 @@
       </c>
       <c r="E11" s="242" t="inlineStr">
         <is>
-          <t>5월 28일</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F11" s="243" t="n">
@@ -14347,7 +14423,7 @@
       </c>
       <c r="E13" s="242" t="inlineStr">
         <is>
-          <t>5월 28일</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F13" s="253" t="n">
@@ -14375,7 +14451,7 @@
       </c>
       <c r="E14" s="242" t="inlineStr">
         <is>
-          <t>5월 28일</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F14" s="240" t="n">
@@ -14426,10 +14502,14 @@
       </c>
       <c r="D16" s="256" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E16" s="242" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E16" s="242" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
       <c r="F16" s="257" t="n">
         <v>18</v>
       </c>
@@ -14455,7 +14535,7 @@
       </c>
       <c r="E17" s="255" t="inlineStr">
         <is>
-          <t>5월 28일</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F17" s="257" t="n">
@@ -14539,7 +14619,7 @@
       </c>
       <c r="E20" s="242" t="inlineStr">
         <is>
-          <t>5월 28일</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F20" s="257" t="n">
@@ -14972,7 +15052,7 @@
       </c>
       <c r="E18" s="123" t="inlineStr">
         <is>
-          <t>6월 19일</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F18" s="123" t="n">
@@ -16645,7 +16725,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -16671,7 +16751,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>금주 변경 없음</t>
+          <t>PTT 0727 대조 — CP-en 게시 불필요로 대상 제외(취소) · JP-ja 법인리뷰→작업중(번역 문서 미비) · 잔여 작업중 7·법인리뷰 2, PTT상 진척 없음</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -16924,12 +17004,16 @@
       <c r="C18" s="277" t="inlineStr"/>
       <c r="D18" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="E18" s="200" t="inlineStr"/>
       <c r="F18" s="0" t="inlineStr"/>
-      <c r="G18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>CP 페이지 게시 불필요 — PTT 태스크만 종료(2025-11-10, WR2209877YZ)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="261" t="inlineStr">
@@ -17252,12 +17336,16 @@
       <c r="C34" s="277" t="inlineStr"/>
       <c r="D34" s="263" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E34" s="123" t="inlineStr"/>
       <c r="F34" s="0" t="inlineStr"/>
-      <c r="G34" s="0" t="inlineStr"/>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t>번역 문서 미비로 확인요청 중(PTT Request Clarification, 2026-03-30)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="261" t="inlineStr">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -16725,7 +16725,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>PTT 0727 대조 — CP-en 게시 불필요로 대상 제외(취소) · JP-ja 법인리뷰→작업중(번역 문서 미비) · 잔여 작업중 7·법인리뷰 2, PTT상 진척 없음</t>
+          <t>PTT 0727 대조 — JP-ja 법인리뷰→작업중(번역 문서 미비) · CP-en 게시 대상 아님으로 행 삭제 · 잔여 작업중 7·법인리뷰 2, PTT상 진척 없음</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -16998,32 +16998,34 @@
     <row r="18">
       <c r="B18" s="261" t="inlineStr">
         <is>
-          <t>CP-en</t>
-        </is>
-      </c>
-      <c r="C18" s="277" t="inlineStr"/>
-      <c r="D18" s="264" t="inlineStr">
-        <is>
-          <t>취소</t>
-        </is>
-      </c>
-      <c r="E18" s="200" t="inlineStr"/>
-      <c r="F18" s="0" t="inlineStr"/>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t>CP 페이지 게시 불필요 — PTT 태스크만 종료(2025-11-10, WR2209877YZ)</t>
-        </is>
-      </c>
+          <t>CZ-cz</t>
+        </is>
+      </c>
+      <c r="C18" s="277" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D18" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E18" s="123" t="inlineStr"/>
+      <c r="F18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="261" t="inlineStr">
         <is>
-          <t>CZ-cz</t>
+          <t>DK-da</t>
         </is>
       </c>
       <c r="C19" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/dk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D19" s="265" t="inlineStr">
@@ -17040,12 +17042,12 @@
     <row r="20">
       <c r="B20" s="261" t="inlineStr">
         <is>
-          <t>DK-da</t>
+          <t>EC-es</t>
         </is>
       </c>
       <c r="C20" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/dk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/ec/computacion/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D20" s="265" t="inlineStr">
@@ -17062,12 +17064,12 @@
     <row r="21">
       <c r="B21" s="261" t="inlineStr">
         <is>
-          <t>EC-es</t>
+          <t>EE-ee</t>
         </is>
       </c>
       <c r="C21" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ec/computacion/ultragear-buying-guide</t>
+          <t>https://www.lg.com/ee/it-seadmed/buying-guide/ultragear-mangumonitorid</t>
         </is>
       </c>
       <c r="D21" s="265" t="inlineStr">
@@ -17084,12 +17086,12 @@
     <row r="22">
       <c r="B22" s="261" t="inlineStr">
         <is>
-          <t>EE-ee</t>
+          <t>ES-es</t>
         </is>
       </c>
       <c r="C22" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ee/it-seadmed/buying-guide/ultragear-mangumonitorid</t>
+          <t>https://www.lg.com/es/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D22" s="265" t="inlineStr">
@@ -17106,12 +17108,12 @@
     <row r="23">
       <c r="B23" s="261" t="inlineStr">
         <is>
-          <t>ES-es</t>
+          <t>FI-fi</t>
         </is>
       </c>
       <c r="C23" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/fi/it-tuotteet/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D23" s="265" t="inlineStr">
@@ -17128,35 +17130,29 @@
     <row r="24">
       <c r="B24" s="261" t="inlineStr">
         <is>
-          <t>FI-fi</t>
-        </is>
-      </c>
-      <c r="C24" s="277" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fi/it-tuotteet/ultragear-buying-guide</t>
-        </is>
-      </c>
-      <c r="D24" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
+          <t>FR-fr</t>
+        </is>
+      </c>
+      <c r="C24" s="277" t="inlineStr"/>
+      <c r="D24" s="263" t="inlineStr">
+        <is>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E24" s="123" t="inlineStr"/>
-      <c r="F24" s="0" t="n">
-        <v>1</v>
-      </c>
+      <c r="F24" s="0" t="inlineStr"/>
       <c r="G24" s="0" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="261" t="inlineStr">
         <is>
-          <t>FR-fr</t>
+          <t>GR-gr</t>
         </is>
       </c>
       <c r="C25" s="277" t="inlineStr"/>
-      <c r="D25" s="263" t="inlineStr">
-        <is>
-          <t>법인리뷰</t>
+      <c r="D25" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr"/>
@@ -17166,28 +17162,34 @@
     <row r="26">
       <c r="B26" s="261" t="inlineStr">
         <is>
-          <t>GR-gr</t>
-        </is>
-      </c>
-      <c r="C26" s="277" t="inlineStr"/>
-      <c r="D26" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
+          <t>HK-zh</t>
+        </is>
+      </c>
+      <c r="C26" s="277" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D26" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="E26" s="123" t="inlineStr"/>
-      <c r="F26" s="0" t="inlineStr"/>
+      <c r="F26" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="G26" s="0" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="261" t="inlineStr">
         <is>
-          <t>HK-zh</t>
+          <t>HK-en</t>
         </is>
       </c>
       <c r="C27" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/hk_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D27" s="265" t="inlineStr">
@@ -17204,12 +17206,12 @@
     <row r="28">
       <c r="B28" s="261" t="inlineStr">
         <is>
-          <t>HK-en</t>
+          <t>HU-hu</t>
         </is>
       </c>
       <c r="C28" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/hu/microsite-article/ms/it/monitor/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D28" s="265" t="inlineStr">
@@ -17226,12 +17228,12 @@
     <row r="29">
       <c r="B29" s="261" t="inlineStr">
         <is>
-          <t>HU-hu</t>
+          <t>ID-id</t>
         </is>
       </c>
       <c r="C29" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hu/microsite-article/ms/it/monitor/ultragear-buying-guide</t>
+          <t>https://www.lg.com/id/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D29" s="265" t="inlineStr">
@@ -17248,12 +17250,12 @@
     <row r="30">
       <c r="B30" s="261" t="inlineStr">
         <is>
-          <t>ID-id</t>
+          <t>IL-he</t>
         </is>
       </c>
       <c r="C30" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/id/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/il/monitors/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D30" s="265" t="inlineStr">
@@ -17270,12 +17272,12 @@
     <row r="31">
       <c r="B31" s="261" t="inlineStr">
         <is>
-          <t>IL-he</t>
+          <t>IN-en</t>
         </is>
       </c>
       <c r="C31" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/il/monitors/ultragear-buying-guide</t>
+          <t>https://www.lg.com/in/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D31" s="265" t="inlineStr">
@@ -17292,70 +17294,70 @@
     <row r="32">
       <c r="B32" s="261" t="inlineStr">
         <is>
-          <t>IN-en</t>
-        </is>
-      </c>
-      <c r="C32" s="277" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/in/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
-      <c r="D32" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C32" s="277" t="inlineStr"/>
+      <c r="D32" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E32" s="123" t="inlineStr"/>
-      <c r="F32" s="0" t="n">
-        <v>1</v>
-      </c>
+      <c r="F32" s="0" t="inlineStr"/>
       <c r="G32" s="0" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="261" t="inlineStr">
         <is>
-          <t>IT-it</t>
+          <t>JP-ja</t>
         </is>
       </c>
       <c r="C33" s="277" t="inlineStr"/>
-      <c r="D33" s="264" t="inlineStr">
+      <c r="D33" s="263" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr"/>
       <c r="F33" s="0" t="inlineStr"/>
-      <c r="G33" s="0" t="inlineStr"/>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>번역 문서 미비로 확인요청 중(PTT Request Clarification, 2026-03-30)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="261" t="inlineStr">
         <is>
-          <t>JP-ja</t>
-        </is>
-      </c>
-      <c r="C34" s="277" t="inlineStr"/>
-      <c r="D34" s="263" t="inlineStr">
-        <is>
-          <t>작업중</t>
+          <t>KZ-ru</t>
+        </is>
+      </c>
+      <c r="C34" s="277" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/kz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D34" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="E34" s="123" t="inlineStr"/>
-      <c r="F34" s="0" t="inlineStr"/>
-      <c r="G34" s="0" t="inlineStr">
-        <is>
-          <t>번역 문서 미비로 확인요청 중(PTT Request Clarification, 2026-03-30)</t>
-        </is>
-      </c>
+      <c r="F34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="0" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="261" t="inlineStr">
         <is>
-          <t>KZ-ru</t>
+          <t>LT-lt</t>
         </is>
       </c>
       <c r="C35" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/kz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/lt/kompiuterine-technika/buying-guide/ultragear-gaming-monitor</t>
         </is>
       </c>
       <c r="D35" s="265" t="inlineStr">
@@ -17372,12 +17374,12 @@
     <row r="36">
       <c r="B36" s="261" t="inlineStr">
         <is>
-          <t>LT-lt</t>
+          <t>LV-lv</t>
         </is>
       </c>
       <c r="C36" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lt/kompiuterine-technika/buying-guide/ultragear-gaming-monitor</t>
+          <t>https://www.lg.com/lv/datortehnika/buying-guide/ultragear-gaming-monitor</t>
         </is>
       </c>
       <c r="D36" s="265" t="inlineStr">
@@ -17394,12 +17396,12 @@
     <row r="37">
       <c r="B37" s="261" t="inlineStr">
         <is>
-          <t>LV-lv</t>
+          <t>NL-nl</t>
         </is>
       </c>
       <c r="C37" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lv/datortehnika/buying-guide/ultragear-gaming-monitor</t>
+          <t>https://www.lg.com/nl/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D37" s="265" t="inlineStr">
@@ -17416,12 +17418,12 @@
     <row r="38">
       <c r="B38" s="261" t="inlineStr">
         <is>
-          <t>NL-nl</t>
+          <t>NO-no</t>
         </is>
       </c>
       <c r="C38" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nl/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/no/it-produkter/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D38" s="265" t="inlineStr">
@@ -17438,12 +17440,12 @@
     <row r="39">
       <c r="B39" s="261" t="inlineStr">
         <is>
-          <t>NO-no</t>
+          <t>PA-es</t>
         </is>
       </c>
       <c r="C39" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/no/it-produkter/ultragear-buying-guide</t>
+          <t>https://www.lg.com/pa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D39" s="265" t="inlineStr">
@@ -17460,12 +17462,12 @@
     <row r="40">
       <c r="B40" s="261" t="inlineStr">
         <is>
-          <t>PA-es</t>
+          <t>PE-es</t>
         </is>
       </c>
       <c r="C40" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/pe/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D40" s="265" t="inlineStr">
@@ -17482,12 +17484,12 @@
     <row r="41">
       <c r="B41" s="261" t="inlineStr">
         <is>
-          <t>PE-es</t>
+          <t>PH-en</t>
         </is>
       </c>
       <c r="C41" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pe/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/ph/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D41" s="265" t="inlineStr">
@@ -17504,29 +17506,23 @@
     <row r="42">
       <c r="B42" s="261" t="inlineStr">
         <is>
-          <t>PH-en</t>
-        </is>
-      </c>
-      <c r="C42" s="277" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ph/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
-      <c r="D42" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
+          <t>PL-pl</t>
+        </is>
+      </c>
+      <c r="C42" s="277" t="inlineStr"/>
+      <c r="D42" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E42" s="123" t="inlineStr"/>
-      <c r="F42" s="0" t="n">
-        <v>1</v>
-      </c>
+      <c r="F42" s="0" t="inlineStr"/>
       <c r="G42" s="0" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="261" t="inlineStr">
         <is>
-          <t>PL-pl</t>
+          <t>PT-pt</t>
         </is>
       </c>
       <c r="C43" s="277" t="inlineStr"/>
@@ -17542,28 +17538,34 @@
     <row r="44">
       <c r="B44" s="261" t="inlineStr">
         <is>
-          <t>PT-pt</t>
-        </is>
-      </c>
-      <c r="C44" s="277" t="inlineStr"/>
-      <c r="D44" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
+          <t>RS-rs</t>
+        </is>
+      </c>
+      <c r="C44" s="277" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/it-proizvodi/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D44" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="E44" s="123" t="inlineStr"/>
-      <c r="F44" s="0" t="inlineStr"/>
+      <c r="F44" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="G44" s="0" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="261" t="inlineStr">
         <is>
-          <t>RS-rs</t>
+          <t>SA-ar</t>
         </is>
       </c>
       <c r="C45" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/it-proizvodi/ultragear-buying-guide</t>
+          <t>https://www.lg.com/sa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D45" s="265" t="inlineStr">
@@ -17580,12 +17582,12 @@
     <row r="46">
       <c r="B46" s="261" t="inlineStr">
         <is>
-          <t>SA-ar</t>
+          <t>SA-en</t>
         </is>
       </c>
       <c r="C46" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/sa_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D46" s="265" t="inlineStr">
@@ -17602,12 +17604,12 @@
     <row r="47">
       <c r="B47" s="261" t="inlineStr">
         <is>
-          <t>SA-en</t>
+          <t>SE-sv</t>
         </is>
       </c>
       <c r="C47" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sa_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/se/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D47" s="265" t="inlineStr">
@@ -17624,12 +17626,12 @@
     <row r="48">
       <c r="B48" s="261" t="inlineStr">
         <is>
-          <t>SE-sv</t>
+          <t>TH-th</t>
         </is>
       </c>
       <c r="C48" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/se/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/th/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D48" s="265" t="inlineStr">
@@ -17646,12 +17648,12 @@
     <row r="49">
       <c r="B49" s="261" t="inlineStr">
         <is>
-          <t>TH-th</t>
+          <t>TR-tr</t>
         </is>
       </c>
       <c r="C49" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/th/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/tr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D49" s="265" t="inlineStr">
@@ -17668,12 +17670,12 @@
     <row r="50">
       <c r="B50" s="261" t="inlineStr">
         <is>
-          <t>TR-tr</t>
+          <t>TW-zh</t>
         </is>
       </c>
       <c r="C50" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/tw/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D50" s="265" t="inlineStr">
@@ -17690,12 +17692,12 @@
     <row r="51">
       <c r="B51" s="261" t="inlineStr">
         <is>
-          <t>TW-zh</t>
+          <t>UA-uk</t>
         </is>
       </c>
       <c r="C51" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tw/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/ua/it-products/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D51" s="265" t="inlineStr">
@@ -17712,12 +17714,12 @@
     <row r="52">
       <c r="B52" s="261" t="inlineStr">
         <is>
-          <t>UA-uk</t>
+          <t>ZA-en</t>
         </is>
       </c>
       <c r="C52" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ua/it-products/ultragear-buying-guide</t>
+          <t>https://www.lg.com/za/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D52" s="265" t="inlineStr">
@@ -17730,28 +17732,6 @@
         <v>1</v>
       </c>
       <c r="G52" s="0" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="261" t="inlineStr">
-        <is>
-          <t>ZA-en</t>
-        </is>
-      </c>
-      <c r="C53" s="277" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/za/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
-      <c r="D53" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E53" s="123" t="inlineStr"/>
-      <c r="F53" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -16751,7 +16751,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>PTT 0727 대조 — JP-ja 법인리뷰→작업중(번역 문서 미비) · CP-en 게시 대상 아님으로 행 삭제 · 잔여 작업중 7·법인리뷰 2, PTT상 진척 없음</t>
+          <t>PTT 0727 대조 — CP-en 게시 대상 아님으로 행 삭제 · JP-ja 법인리뷰→작업중 · 잔여 작업중 7·법인리뷰 2, PTT상 진척 없음</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -17321,11 +17321,7 @@
       </c>
       <c r="E33" s="123" t="inlineStr"/>
       <c r="F33" s="0" t="inlineStr"/>
-      <c r="G33" s="0" t="inlineStr">
-        <is>
-          <t>번역 문서 미비로 확인요청 중(PTT Request Clarification, 2026-03-30)</t>
-        </is>
-      </c>
+      <c r="G33" s="0" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="261" t="inlineStr">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -14209,8 +14209,7 @@
       </c>
       <c r="B2" s="128" t="inlineStr">
         <is>
-          <t>AU : URL 변경
-CN : 법인리뷰 → 완료</t>
+          <t>대상 리스트 갱신(총 403건) — 구 /business/ 경로 정리로 DE -23·IN -31·SG -17, ES +1 · GLOBAL 반영 완료</t>
         </is>
       </c>
       <c r="C2" s="129" t="n"/>
@@ -14427,7 +14426,7 @@
         </is>
       </c>
       <c r="F13" s="253" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G13" s="244" t="inlineStr"/>
       <c r="H13" s="242" t="inlineStr"/>
@@ -14525,7 +14524,7 @@
       </c>
       <c r="C17" s="244" t="inlineStr">
         <is>
-          <t>https://www.lg.com/in/business/computers/laptops/lg-gram/14z90p-g-ah75a2/</t>
+          <t>https://www.lg.com/in/laptop/gram/14z90r-g-cp54a2/</t>
         </is>
       </c>
       <c r="D17" s="247" t="inlineStr">
@@ -14539,7 +14538,7 @@
         </is>
       </c>
       <c r="F17" s="257" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G17" s="257" t="inlineStr"/>
       <c r="H17" s="257" t="inlineStr"/>
@@ -14623,7 +14622,7 @@
         </is>
       </c>
       <c r="F20" s="257" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="G20" s="257" t="inlineStr"/>
       <c r="H20" s="257" t="inlineStr"/>
@@ -16725,7 +16724,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -9100,7 +9100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · Screen Share 카피/디스클레이머 삭제 · DAM 적재 완료(7/27) 지급 진행 · 대상 4모델(색상 파생 6)</t>
+          <t>라이브 게시 완료 — 대상 17페이지 전건 완료(실측 200 확인) · STG·미게시 행은 대상 제외</t>
         </is>
       </c>
     </row>
@@ -9177,7 +9177,12 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F4" s="0" t="n">
@@ -9202,7 +9207,12 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F5" s="0" t="n">
@@ -9217,17 +9227,22 @@
     <row r="6">
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>CO : CO (es)</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/smart-monitors/24u511sb-b/</t>
+          <t>https://www.lg.com/co/monitores/smart-monitores/24u511sb-b/</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F6" s="0" t="n">
@@ -9242,17 +9257,22 @@
     <row r="7">
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>CO : CO (es)</t>
+          <t>MX : MX (es)</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/co/monitores/smart-monitores/24u511sb-b/</t>
+          <t>https://www.lg.com/mx/monitores/monitores-smart/27u511sb-w/</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F7" s="0" t="n">
@@ -9260,24 +9280,29 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>24U511SB-B</t>
+          <t>27U511SB-W</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>AE : AE (en)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>https://wwwstg.lg.com/ae/consumer-monitors/lg-24u511sb-b</t>
+          <t>https://www.lg.com/sg/consumer-monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F8" s="0" t="n">
@@ -9285,24 +9310,29 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>24U511SB-B · 페이지 QA review</t>
+          <t>27U511SB-W</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>BR : BR (pt)</t>
+          <t>IN : IN (en)</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/br/monitores/smart-monitors/24u511sb-b/</t>
+          <t>https://www.lg.com/in/monitors/smart-monitors/27u511sb-b/</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F9" s="0" t="n">
@@ -9310,24 +9340,29 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>24U511SB-B</t>
+          <t>27U511SB-B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>MX : MX (es)</t>
+          <t>ID : ID (id)</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/mx/monitores/monitores-smart/27u511sb-w/</t>
+          <t>https://www.lg.com/id/monitor/smart-monitors/27u511sb/</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F10" s="0" t="n">
@@ -9342,17 +9377,22 @@
     <row r="11">
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>US : US (en)</t>
+          <t>CO : CO (es)</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/us/monitors/lg-27u511sb-w-smart-monitor</t>
+          <t>https://www.lg.com/co/monitores/smart-monitores/27u511sb-w/</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F11" s="0" t="n">
@@ -9367,17 +9407,22 @@
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
+          <t>PE : PE (es)</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg/consumer-monitors/smart-monitors/27u511sb-w/</t>
+          <t>https://www.lg.com/pe/monitores/fhd-y-qhd/27u511sb-w/</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F12" s="0" t="n">
@@ -9392,17 +9437,22 @@
     <row r="13">
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>IN : IN (en)</t>
+          <t>HK_EN : HK (en)</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/in/monitors/smart-monitors/27u511sb-b/</t>
+          <t>https://www.lg.com/hk_en/monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F13" s="0" t="n">
@@ -9410,24 +9460,29 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>27U511SB-B</t>
+          <t>27U511SB-W</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>ID : ID (id)</t>
+          <t>HK : HK (zh)</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/id/monitor/smart-monitors/27u511sb/</t>
+          <t>https://www.lg.com/hk/monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F14" s="0" t="n">
@@ -9442,17 +9497,22 @@
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>IN : IN (en)</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/smart-monitors/27u511sb-w/</t>
+          <t>https://www.lg.com/in/monitors/smart-monitors/32u501sb-b/</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F15" s="0" t="n">
@@ -9460,24 +9520,29 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>27U511SB-W</t>
+          <t>32U501SB-B</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>CO : CO (es)</t>
+          <t>ID : ID (id)</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/co/monitores/smart-monitores/27u511sb-w/</t>
+          <t>https://www.lg.com/id/monitor/smart-monitors/32u501sb/</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F16" s="0" t="n">
@@ -9485,24 +9550,29 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>27U511SB-W</t>
+          <t>32U501SB-B</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>PE : PE (es)</t>
+          <t>ES : ES (es)</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pe/monitores/fhd-y-qhd/27u511sb-w/</t>
+          <t>https://www.lg.com/es/monitores/myview-smart-monitor/32u701sb-b/</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F17" s="0" t="n">
@@ -9510,24 +9580,29 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>27U511SB-W</t>
+          <t>32U701SB-B</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>HK_EN : HK (en)</t>
+          <t>ES : ES (es)</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk_en/monitors/smart-monitors/27u511sb-w/</t>
+          <t>https://www.lg.com/es/outlet/outlet-informatica/monitores/32u701sb-b-outlet/</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F18" s="0" t="n">
@@ -9535,24 +9610,29 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>27U511SB-W</t>
+          <t>32U701SB-B</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>HK : HK (zh)</t>
+          <t>IN : IN (en)</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk/monitors/smart-monitors/27u511sb-w/</t>
+          <t>https://www.lg.com/in/monitors/smart-monitors/32u701sb-b/</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F19" s="0" t="n">
@@ -9560,480 +9640,35 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>27U511SB-W</t>
+          <t>32U701SB-B</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>AE : AE (en)</t>
+          <t>TR : TR (tr)</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>https://wwwstg.lg.com/ae/consumer-monitors/lg-27u511sb-w</t>
+          <t>https://www.lg.com/tr/monitor/smart-monitorleri/32u701sb-b/</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F20" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="0" t="inlineStr">
-        <is>
-          <t>27U511SB-W · 페이지 WPL review</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t>BR : BR (pt)</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/br/pt/monitores/smart-monitors/27u511sb-b.html?wcmmode=disabled</t>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="0" t="inlineStr">
-        <is>
-          <t>27U511SB-B · 페이지 New Request</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t>JP : JP (ja)</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/jp/ja/monitors/smart-monitors/27u511sb-b.html?wcmmode=disabled</t>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t>27U511SB-B · 페이지 Client Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="0" t="inlineStr">
-        <is>
-          <t>IN : IN (en)</t>
-        </is>
-      </c>
-      <c r="C23" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/in/monitors/smart-monitors/32u501sb-b/</t>
-        </is>
-      </c>
-      <c r="D23" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="0" t="inlineStr">
-        <is>
-          <t>32U501SB-B</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="0" t="inlineStr">
-        <is>
-          <t>ID : ID (id)</t>
-        </is>
-      </c>
-      <c r="C24" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/id/monitor/smart-monitors/32u501sb/</t>
-        </is>
-      </c>
-      <c r="D24" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="0" t="inlineStr">
-        <is>
-          <t>32U501SB-B</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="0" t="inlineStr">
-        <is>
-          <t>JP : JP (ja)</t>
-        </is>
-      </c>
-      <c r="C25" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/jp/monitors/smart-monitors/32u501sb-w/</t>
-        </is>
-      </c>
-      <c r="D25" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F25" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="0" t="inlineStr">
-        <is>
-          <t>32U501SB-W</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="0" t="inlineStr">
-        <is>
-          <t>AE : AE (en)</t>
-        </is>
-      </c>
-      <c r="C26" s="0" t="inlineStr">
-        <is>
-          <t>https://wwwstg.lg.com/ae/business/monitors/lg-32u501sb-b-ama</t>
-        </is>
-      </c>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F26" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="0" t="inlineStr">
-        <is>
-          <t>32U501SB-B · 페이지 In progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="0" t="inlineStr">
-        <is>
-          <t>UK : GB (en)</t>
-        </is>
-      </c>
-      <c r="C27" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/monitors/smart-monitors/32u501sb-b.html?wcmmode=disabled</t>
-        </is>
-      </c>
-      <c r="D27" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F27" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="0" t="inlineStr">
-        <is>
-          <t>32U501SB-B · 페이지 QA review</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="0" t="inlineStr">
-        <is>
-          <t>CO : CO (es)</t>
-        </is>
-      </c>
-      <c r="C28" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/co/monitores/smart-monitores/32u501sb-b/</t>
-        </is>
-      </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t>32U501SB-B</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="0" t="inlineStr">
-        <is>
-          <t>AU : AU (en)</t>
-        </is>
-      </c>
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/au/en/monitors/smart-monitors/32U501SB.html?wcmmode=disabled</t>
-        </is>
-      </c>
-      <c r="D29" s="0" t="inlineStr">
-        <is>
-          <t>취소</t>
-        </is>
-      </c>
-      <c r="F29" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="0" t="inlineStr">
-        <is>
-          <t>32U501SB · 페이지 Cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="0" t="inlineStr">
-        <is>
-          <t>US : US (en)</t>
-        </is>
-      </c>
-      <c r="C30" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/us/monitors/lg-32u701sb-b-smart-monitor</t>
-        </is>
-      </c>
-      <c r="D30" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F30" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="0" t="inlineStr">
-        <is>
-          <t>32U701SB-B</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="0" t="inlineStr">
-        <is>
-          <t>ES : ES (es)</t>
-        </is>
-      </c>
-      <c r="C31" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/es/monitores/myview-smart-monitor/32u701sb-b/</t>
-        </is>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F31" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="0" t="inlineStr">
-        <is>
-          <t>32U701SB-B</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="0" t="inlineStr">
-        <is>
-          <t>ES : ES (es)</t>
-        </is>
-      </c>
-      <c r="C32" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/es/outlet/outlet-informatica/monitores/32u701sb-b-outlet/</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F32" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="0" t="inlineStr">
-        <is>
-          <t>32U701SB-B</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="0" t="inlineStr">
-        <is>
-          <t>IN : IN (en)</t>
-        </is>
-      </c>
-      <c r="C33" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/in/monitors/smart-monitors/32u701sb-b/</t>
-        </is>
-      </c>
-      <c r="D33" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F33" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="0" t="inlineStr">
-        <is>
-          <t>32U701SB-B</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="0" t="inlineStr">
-        <is>
-          <t>TR : TR (tr)</t>
-        </is>
-      </c>
-      <c r="C34" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tr/monitor/smart-monitorleri/32u701sb-b/</t>
-        </is>
-      </c>
-      <c r="D34" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F34" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="0" t="inlineStr">
-        <is>
-          <t>32U701SB-B</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="0" t="inlineStr">
-        <is>
-          <t>AE : AE (en)</t>
-        </is>
-      </c>
-      <c r="C35" s="0" t="inlineStr">
-        <is>
-          <t>https://wwwstg.lg.com/ae/consumer-monitors/lg-32u701sb-b</t>
-        </is>
-      </c>
-      <c r="D35" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="0" t="inlineStr">
-        <is>
-          <t>32U701SB-B · 페이지 QA review</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="0" t="inlineStr">
-        <is>
-          <t>ZA : ZA (en)</t>
-        </is>
-      </c>
-      <c r="C36" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/za/en/monitors/smart-monitors/32u701sb.html?wcmmode=disabled</t>
-        </is>
-      </c>
-      <c r="D36" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F36" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="0" t="inlineStr">
-        <is>
-          <t>32u701sb · 페이지 Client Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="0" t="inlineStr">
-        <is>
-          <t>BR : BR (pt)</t>
-        </is>
-      </c>
-      <c r="C37" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/br/pt/monitores/smart-monitors/32u701sb-b.html?wcmmode=disabled</t>
-        </is>
-      </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="0" t="inlineStr">
-        <is>
-          <t>32U701SB-B · 페이지 QA review</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="0" t="inlineStr">
-        <is>
-          <t>CO : CO (es)</t>
-        </is>
-      </c>
-      <c r="C38" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/co/monitores/smart-monitores/32u701sb-b/</t>
-        </is>
-      </c>
-      <c r="D38" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F38" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>32U701SB-B</t>
         </is>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -9100,7 +9100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9180,7 +9180,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9210,7 +9210,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9240,7 +9240,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9270,7 +9270,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9300,7 +9300,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9330,7 +9330,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9360,7 +9360,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9390,7 +9390,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9420,7 +9420,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9450,7 +9450,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9480,7 +9480,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9510,7 +9510,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9540,7 +9540,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9570,7 +9570,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9600,7 +9600,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9630,7 +9630,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -9660,7 +9660,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -14366,7 +14366,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.13" customWidth="1" style="203" min="1" max="1"/>
@@ -14396,10 +14396,8 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>CZ : 작업중 → 완료
-TR : 법인리뷰 → 작업중
-IN : 법인리뷰 → 완료 (7/16 게시, PTT 확인)
-TR : 작업중 → 완료 (7/23 게시, PTT 확인)</t>
+          <t>IT : 작업중 → 법인리뷰
+SE : 작업중 → 법인리뷰</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -14965,7 +14963,7 @@
       </c>
       <c r="D30" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E30" s="123" t="inlineStr"/>
@@ -15299,7 +15297,7 @@
       </c>
       <c r="D45" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E45" s="123" t="inlineStr"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -14366,7 +14366,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.13" customWidth="1" style="203" min="1" max="1"/>
@@ -16357,7 +16357,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>PTT 0727 대조 — CP-en 게시 대상 아님으로 행 삭제 · JP-ja 법인리뷰→작업중 · 잔여 작업중 7·법인리뷰 2, PTT상 진척 없음</t>
+          <t>FR : 법인리뷰 → 완료 (7/28 게시, 실측 200 확인) · 잔여 작업중 7·법인리뷰 1(CN)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -16765,14 +16765,24 @@
           <t>FR-fr</t>
         </is>
       </c>
-      <c r="C24" s="277" t="inlineStr"/>
+      <c r="C24" s="277" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/ultragear-buying-guide/</t>
+        </is>
+      </c>
       <c r="D24" s="263" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E24" s="123" t="inlineStr"/>
-      <c r="F24" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E24" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="G24" s="0" t="inlineStr"/>
     </row>
     <row r="25">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -16383,7 +16383,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>FR : 법인리뷰 → 완료 (7/28 게시, 실측 200 확인) · 잔여 작업중 7·법인리뷰 1(CN)</t>
+          <t>FR : 법인리뷰 → 완료 (7/24 게시, 실측 200 확인) · 잔여 작업중 7·법인리뷰 1(CN)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="E24" s="123" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F24" s="0" t="n">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -10035,7 +10035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>예정 · 13개국 대상 · CN은 PDP 라이브이나 기존 Secure Lock 컴포넌트 영역 없음</t>
+          <t>타겟 99건 확정(LGE 전달 리스트 기준) — 라이브 92 + STG만 7 · IN(gram 카테고리 없음)·FR(작성중 4) 대상 제외 · CN 7건은 PDP 라이브이나 기존 Secure Lock 영역 없음 · GR EP 품의 중, Jira 등록 예정</t>
         </is>
       </c>
     </row>
@@ -11302,10 +11302,14 @@
     <row r="52">
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>IN : IN (en)</t>
-        </is>
-      </c>
-      <c r="C52" s="0" t="inlineStr"/>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-gs54j/</t>
+        </is>
+      </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -11316,7 +11320,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>- · Erase.Lock -</t>
+          <t>14Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11332,7 @@
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-gs54j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-gs58j/</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -11353,7 +11357,7 @@
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-gs58j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-gu85j/</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -11378,7 +11382,7 @@
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-gu85j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-vp58j/</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -11403,7 +11407,7 @@
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/14z90u-vp58j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gs53j/</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -11416,7 +11420,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>14Z90U-G · Erase.Lock 있음</t>
+          <t>14Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
@@ -11428,7 +11432,7 @@
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gs53j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gs54j/</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -11453,7 +11457,7 @@
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gs54j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gs55j/</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -11478,7 +11482,7 @@
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gs55j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gu85j/</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -11503,7 +11507,7 @@
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gu85j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gu86j/</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -11528,7 +11532,7 @@
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-gu86j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-vp53j/</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -11553,7 +11557,7 @@
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-vp53j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-vp55j/</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -11578,7 +11582,7 @@
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/14z95u-vp55j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-gu85j/</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -11591,7 +11595,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>14Z95U-G · Erase.Lock 있음</t>
+          <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11607,7 @@
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-gu85j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-gu88j/</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -11628,7 +11632,7 @@
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-gu88j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-kub5j/</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -11653,7 +11657,7 @@
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-kub5j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-kub9j/</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -11678,7 +11682,7 @@
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-kub9j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z95u-gs55j/</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -11691,7 +11695,7 @@
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>16Z90U-K · Erase.Lock 있음</t>
+          <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11707,7 @@
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/16z95u-gs55j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z95u-gu88j/</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -11728,7 +11732,7 @@
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/16z95u-gu88j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/17z90u-gu85j/</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -11741,7 +11745,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>16Z95U-G · Erase.Lock 있음</t>
+          <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11757,7 @@
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/17z90u-gu85j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/17z90u-gu88j/</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -11778,7 +11782,7 @@
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/17z90u-gu88j/</t>
+          <t>https://www.lg.com/jp/mobile-pc/gram/17z90u-vp55j/</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -11798,12 +11802,12 @@
     <row r="72">
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/17z90u-vp55j/</t>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-gal87c/</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -11816,7 +11820,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>17Z90U-G · Erase.Lock 있음</t>
+          <t>16Z90U-K · Erase.Lock 없음</t>
         </is>
       </c>
     </row>
@@ -11828,7 +11832,7 @@
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-16z90u-gal87c/</t>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-gal88c/</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -11853,7 +11857,7 @@
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-16z90u-gal88c/</t>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb7c/</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -11878,7 +11882,7 @@
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb7c/</t>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb8c/</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -11903,7 +11907,7 @@
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb8c/</t>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb9c/</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -11928,7 +11932,7 @@
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb9c/</t>
+          <t>https://www.lg.com/cn/notebooks/lg-17z90u-al87c/</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -11941,7 +11945,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>16Z90U-K · Erase.Lock 없음</t>
+          <t>17Z90U-G · Erase.Lock 없음</t>
         </is>
       </c>
     </row>
@@ -11953,7 +11957,7 @@
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-17z90u-al87c/</t>
+          <t>https://www.lg.com/cn/notebooks/lg-17z90u-gal88c/</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
@@ -11973,12 +11977,12 @@
     <row r="79">
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>CA_EN : CA (en)</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-17z90u-gal88c/</t>
+          <t>https://www.lg.com/ca_en/laptops/16z95u-g/</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
@@ -11991,7 +11995,7 @@
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t>17Z90U-G · Erase.Lock 없음</t>
+          <t>16Z95U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12007,7 @@
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/laptops/16z95u-g/</t>
+          <t>https://www.lg.com/ca_en/small-medium-business/laptops/16z95u-g/</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
@@ -12023,12 +12027,12 @@
     <row r="81">
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>CA_FR : CA (fr)</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/small-medium-business/laptops/16z95u-g/</t>
+          <t>https://www.lg.com/ca_fr/ordinateurs-portables/16z95u-g/</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
@@ -12053,7 +12057,7 @@
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/ordinateurs-portables/16z95u-g/</t>
+          <t>https://www.lg.com/ca_fr/small-medium-business/ordinateurs-portables/16z95u-g/</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -12073,12 +12077,12 @@
     <row r="83">
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>CA_EN : CA (en)</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/small-medium-business/ordinateurs-portables/16z95u-g/</t>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g78/</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
@@ -12091,7 +12095,7 @@
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>16Z95U-G · Erase.Lock 있음</t>
+          <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
@@ -12103,7 +12107,7 @@
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g78/</t>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g88/</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
@@ -12128,7 +12132,7 @@
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g88/</t>
+          <t>https://www.lg.com/ca_en/small-medium-business/laptops/all-laptops/17z90u-g78/</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
@@ -12153,7 +12157,7 @@
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/small-medium-business/laptops/all-laptops/17z90u-g78/</t>
+          <t>https://www.lg.com/ca_en/small-medium-business/laptops/all-laptops/17z90u-g88/</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
@@ -12173,12 +12177,12 @@
     <row r="87">
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>CA_FR : CA (fr)</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/small-medium-business/laptops/all-laptops/17z90u-g88/</t>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90u-g78/</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
@@ -12203,7 +12207,7 @@
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90u-g78/</t>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90u-g88/</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
@@ -12223,12 +12227,12 @@
     <row r="89">
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>CA_EN : CA (en)</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90u-g88/</t>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ub-h/</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
@@ -12241,7 +12245,7 @@
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>17Z90U-G · Erase.Lock 있음</t>
+          <t>17Z90UB-H · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
@@ -12253,7 +12257,7 @@
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ub-h/</t>
+          <t>https://www.lg.com/ca_en/small-medium-business/laptops/all-laptops/17z90ub-h/</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
@@ -12273,12 +12277,12 @@
     <row r="91">
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>CA_FR : CA (fr)</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/small-medium-business/laptops/all-laptops/17z90ub-h/</t>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90ub-h/</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
@@ -12303,7 +12307,7 @@
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90ub-h/</t>
+          <t>https://www.lg.com/ca_fr/small-medium-business/computing/purchase-guide/laptops/17z90ub-h/</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
@@ -12323,12 +12327,12 @@
     <row r="93">
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>CA_EN : CA (en)</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/small-medium-business/computing/purchase-guide/laptops/17z90ub-h/</t>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/ca/en/laptops/all-laptops/17z90ub-h.html?wcmmode=disabled</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
@@ -12341,7 +12345,7 @@
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t>17Z90UB-H · Erase.Lock 있음</t>
+          <t>17Z90UR-P · Erase.Lock -</t>
         </is>
       </c>
     </row>
@@ -12353,7 +12357,7 @@
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/ca/en/laptops/all-laptops/17z90ub-h.html?wcmmode=disabled</t>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ur-p/</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
@@ -12366,19 +12370,19 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>17Z90UR-P · Erase.Lock -</t>
+          <t>17Z90UR-P · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>CA_FR : CA (fr)</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ur-p/</t>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17Z90ur-p/</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
@@ -12403,7 +12407,7 @@
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17Z90ur-p/</t>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/ca/fr/computing/purchase-guide/laptops/17z90ub-h.html?wcmmode=disabled</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
@@ -12416,19 +12420,19 @@
       </c>
       <c r="G96" s="0" t="inlineStr">
         <is>
-          <t>17Z90UR-P · Erase.Lock 있음</t>
+          <t>17Z90UR-P · Erase.Lock -</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>AU : AU (en)</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/ca/fr/computing/purchase-guide/laptops/17z90ub-h.html?wcmmode=disabled</t>
+          <t>https://www.lg.com/au/laptops/gram-pro/16z90u-g-au75ap/</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
@@ -12441,17 +12445,21 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>17Z90UR-P · Erase.Lock -</t>
+          <t>16Z90U-G.AU75AP · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
-        </is>
-      </c>
-      <c r="C98" s="0" t="inlineStr"/>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/16z90u-g-au88ap/</t>
+        </is>
+      </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -12462,17 +12470,21 @@
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>15U50U-G · Erase.Lock -</t>
+          <t>16Z90U-K · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
-        </is>
-      </c>
-      <c r="C99" s="0" t="inlineStr"/>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au75ap/</t>
+        </is>
+      </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -12483,17 +12495,21 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>15Z95U-G · Erase.Lock -</t>
+          <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
-        </is>
-      </c>
-      <c r="C100" s="0" t="inlineStr"/>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au78ap/</t>
+        </is>
+      </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -12504,17 +12520,21 @@
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>16Z90U-G · Erase.Lock -</t>
+          <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
-        </is>
-      </c>
-      <c r="C101" s="0" t="inlineStr"/>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au88ap/</t>
+        </is>
+      </c>
       <c r="D101" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -12525,7 +12545,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>17Z90U-G · Erase.Lock -</t>
+          <t>17Z90U-G · Erase.Lock 있음</t>
         </is>
       </c>
     </row>
@@ -12537,7 +12557,7 @@
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>https://www.lg.com/au/laptops/gram-pro/16z90u-g-au75ap/</t>
+          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/au/en/laptops/gram-pro/17z90ub-h.html?wcmmode=disabled</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
@@ -12549,131 +12569,6 @@
         <v>1</v>
       </c>
       <c r="G102" s="0" t="inlineStr">
-        <is>
-          <t>16Z90U-G.AU75AP · Erase.Lock 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="0" t="inlineStr">
-        <is>
-          <t>AU : AU (en)</t>
-        </is>
-      </c>
-      <c r="C103" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/laptops/gram-pro/16z90u-g-au88ap/</t>
-        </is>
-      </c>
-      <c r="D103" s="0" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="F103" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="0" t="inlineStr">
-        <is>
-          <t>16Z90U-K · Erase.Lock 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="0" t="inlineStr">
-        <is>
-          <t>AU : AU (en)</t>
-        </is>
-      </c>
-      <c r="C104" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au75ap/</t>
-        </is>
-      </c>
-      <c r="D104" s="0" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="F104" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" s="0" t="inlineStr">
-        <is>
-          <t>17Z90U-G · Erase.Lock 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="0" t="inlineStr">
-        <is>
-          <t>AU : AU (en)</t>
-        </is>
-      </c>
-      <c r="C105" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au78ap/</t>
-        </is>
-      </c>
-      <c r="D105" s="0" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="F105" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="0" t="inlineStr">
-        <is>
-          <t>17Z90U-G · Erase.Lock 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" s="0" t="inlineStr">
-        <is>
-          <t>AU : AU (en)</t>
-        </is>
-      </c>
-      <c r="C106" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au88ap/</t>
-        </is>
-      </c>
-      <c r="D106" s="0" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="F106" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" s="0" t="inlineStr">
-        <is>
-          <t>17Z90U-G · Erase.Lock 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="0" t="inlineStr">
-        <is>
-          <t>AU : AU (en)</t>
-        </is>
-      </c>
-      <c r="C107" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/au/en/laptops/gram-pro/17z90ub-h.html?wcmmode=disabled</t>
-        </is>
-      </c>
-      <c r="D107" s="0" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="F107" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="0" t="inlineStr">
         <is>
           <t>17Z90UB-H · Erase.Lock -</t>
         </is>
@@ -16357,7 +16252,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -10058,7 +10058,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>타겟 99건 확정(LGE 전달 리스트 기준) — 라이브 92 + STG만 7 · IN(gram 카테고리 없음)·FR(작성중 4) 대상 제외 · CN 7건은 PDP 라이브이나 기존 Secure Lock 영역 없음 · GR EP 품의 중, Jira 등록 예정</t>
+          <t>타겟 99건(LGE 전달 리스트) — 실질 교체 대상 92건 · CN 7건은 PDP 라이브이나 기존 Secure Lock 영역 없어 취소(원본 Erase.Lock 모듈=없음) · 라이브 92 + STG만 7 · IN·FR은 페이지 미존재로 리스트 제외 · GR EP 품의 중, Jira 등록 예정</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="F72" s="0" t="n">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>16Z90U-K · Erase.Lock 없음</t>
+          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
         </is>
       </c>
     </row>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="F73" s="0" t="n">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>16Z90U-K · Erase.Lock 없음</t>
+          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="F74" s="0" t="n">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>16Z90U-K · Erase.Lock 없음</t>
+          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
         </is>
       </c>
     </row>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="F75" s="0" t="n">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>16Z90U-K · Erase.Lock 없음</t>
+          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
         </is>
       </c>
     </row>
@@ -11912,7 +11912,7 @@
       </c>
       <c r="D76" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="F76" s="0" t="n">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>16Z90U-K · Erase.Lock 없음</t>
+          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
         </is>
       </c>
     </row>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="F77" s="0" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>17Z90U-G · Erase.Lock 없음</t>
+          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
         </is>
       </c>
     </row>
@@ -11962,7 +11962,7 @@
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="F78" s="0" t="n">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>17Z90U-G · Erase.Lock 없음</t>
+          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -1540,11 +1540,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/ui</t>
-        </is>
-      </c>
+      <c r="B3" s="10" t="n"/>
       <c r="C3" s="11" t="n"/>
       <c r="D3" s="11" t="n"/>
       <c r="E3" s="12" t="n"/>
@@ -2880,55 +2876,54 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2940,7 +2935,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -2980,6 +2975,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -3455,7 +3451,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3491,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -4692,7 +4689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5292,7 +5289,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -5332,6 +5329,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -7001,7 +6999,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -7041,6 +7039,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -9100,7 +9099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9685,7 +9684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11180,11 +11179,7 @@
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C47" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/laptops/gram/15u50u-g-aa55an.html?wcmmode=disabled</t>
-        </is>
-      </c>
+      <c r="C47" s="0" t="n"/>
       <c r="D47" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -11205,11 +11200,7 @@
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C48" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/laptops/gram-pro/16z90u-h-au78an.html?wcmmode=disabled</t>
-        </is>
-      </c>
+      <c r="C48" s="0" t="n"/>
       <c r="D48" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -11230,11 +11221,7 @@
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C49" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/laptops/gram-pro/16z90u-k-aub8an.html?wcmmode=disabled</t>
-        </is>
-      </c>
+      <c r="C49" s="0" t="n"/>
       <c r="D49" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -11255,11 +11242,7 @@
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C50" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/gb/en/laptops/gram-pro/17z90u-g-au78an.html?wcmmode=disabled</t>
-        </is>
-      </c>
+      <c r="C50" s="0" t="n"/>
       <c r="D50" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -12330,11 +12313,7 @@
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C93" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/ca/en/laptops/all-laptops/17z90ub-h.html?wcmmode=disabled</t>
-        </is>
-      </c>
+      <c r="C93" s="0" t="n"/>
       <c r="D93" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -12405,11 +12384,7 @@
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C96" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/ca/fr/computing/purchase-guide/laptops/17z90ub-h.html?wcmmode=disabled</t>
-        </is>
-      </c>
+      <c r="C96" s="0" t="n"/>
       <c r="D96" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -12555,11 +12530,7 @@
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C102" s="0" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/content/lge/au/en/laptops/gram-pro/17z90ub-h.html?wcmmode=disabled</t>
-        </is>
-      </c>
+      <c r="C102" s="0" t="n"/>
       <c r="D102" s="0" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -12585,7 +12556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12660,7 +12631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13674,25 +13645,15 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/article/2025/2025-lg-experience-article/ref/article-sa-01-refrigerator_size_guide" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13750,11 +13711,7 @@
     </row>
     <row r="3">
       <c r="A3" s="35" t="n"/>
-      <c r="B3" s="130" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/ui</t>
-        </is>
-      </c>
+      <c r="B3" s="130" t="n"/>
       <c r="C3" s="131" t="n"/>
       <c r="D3" s="131" t="n"/>
       <c r="E3" s="132" t="n"/>
@@ -13763,11 +13720,7 @@
     </row>
     <row r="4">
       <c r="A4" s="35" t="n"/>
-      <c r="B4" s="130" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/ui</t>
-        </is>
-      </c>
+      <c r="B4" s="130" t="n"/>
       <c r="C4" s="131" t="n"/>
       <c r="D4" s="131" t="n"/>
       <c r="E4" s="132" t="n"/>
@@ -13776,17 +13729,14 @@
     </row>
     <row r="5">
       <c r="A5" s="35" t="n"/>
-      <c r="B5" s="133" t="inlineStr">
-        <is>
-          <t>https://kor01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fauthor-p86205-e734304.adobeaemcloud.com%2Fui%23%2Faem%2Fassets.html%2Fcontent%2Fdam%2Fmaster-2%2Fhs%2Flgcom%2Flgcom-common%2Farticle%2F2026%2Fcmr&amp;data=05%7C02%7Cjoanna.ryu%40lge.com%7Cf47462a11643436ac07e08de7a8eb1f1%7C5069cde4642a45c08094d0c2dec10be3%7C0%7C0%7C639082950459597401%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=a9NRjuFBdR6yzh7pn8l3w4sfQLCA2HMxO9fzLIOFqYU%3D&amp;reserved=0</t>
-        </is>
-      </c>
+      <c r="B5" s="133" t="n"/>
       <c r="C5" s="134" t="n"/>
       <c r="D5" s="134" t="n"/>
       <c r="E5" s="135" t="n"/>
       <c r="G5" s="127" t="n"/>
     </row>
     <row r="6" ht="40.5" customHeight="1" s="203"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="136" t="inlineStr">
         <is>
@@ -14244,12 +14194,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/reliable-microsite/global" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/reliable-microsite/local" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14261,7 +14208,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.13" customWidth="1" style="203" min="1" max="1"/>
@@ -15420,16 +15367,16 @@
     </row>
     <row r="3">
       <c r="A3" s="166" t="n"/>
-      <c r="B3" s="130" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/ui</t>
-        </is>
-      </c>
+      <c r="B3" s="130" t="n"/>
       <c r="C3" s="131" t="n"/>
       <c r="D3" s="131" t="n"/>
       <c r="F3" s="131" t="n"/>
       <c r="G3" s="127" t="n"/>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -15795,18 +15742,17 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15818,7 +15764,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="22.75" customWidth="1" style="203" min="1" max="1"/>
@@ -15858,11 +15804,7 @@
     </row>
     <row r="3">
       <c r="A3" s="192" t="n"/>
-      <c r="B3" s="193" t="inlineStr">
-        <is>
-          <t>https://author-p86205-e734304.adobeaemcloud.com/ui</t>
-        </is>
-      </c>
+      <c r="B3" s="193" t="n"/>
       <c r="C3" s="194" t="n"/>
       <c r="D3" s="194" t="n"/>
       <c r="E3" s="195" t="n"/>
@@ -16239,9 +16181,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/appliances-faq-hub" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16252,7 +16191,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -16292,6 +16231,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -17277,7 +17217,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -17317,6 +17257,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -17826,7 +17767,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -17866,6 +17807,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -2935,7 +2935,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -2975,7 +2975,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -3451,7 +3450,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -3491,7 +3490,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -4689,7 +4687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5289,7 +5287,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -5329,7 +5327,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -6999,7 +6996,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -7039,7 +7036,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -9099,7 +9095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9684,7 +9680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10034,7 +10030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12556,7 +12552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12631,7 +12627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12654,7 +12650,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · W16 PDP Gallery Card 후속 건 · Windows 11 Pro 영상 수정 · 대상 목록 미수신(확인 필요)</t>
+          <t>전건 완료 — Win11 Pro 영상 수정 79건 · 13개국 · 완료율 100%</t>
         </is>
       </c>
     </row>
@@ -12692,6 +12688,2376 @@
       <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro-2-in-1/16t90sp-g-ap55a/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>16T90SP-G.AP55A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro-2-in-1/16t90sp-g-ap75a/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>16T90SP-G.AP75A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/it-products/laptops/14-inch-lg-gram-laptops/14z90s-v-ap55a8/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>14Z90S-V.AP55A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/it-products/laptops/14-inch-lg-gram-laptops/14z90t-v-ap75a8/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>14Z90T-V.AP75A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/it-products/laptops/16-inch-lg-gram-laptops/16z90s-v-ap55a8/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>16Z90S-V.AP55A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/it-products/laptops/16-inch-lg-gram-laptops/16z90sp-r-ap85a8/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>16Z90SP-R.AP85A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/it-products/laptops/16-inch-lg-gram-laptops/16z90t-v-ap75a8/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>16Z90T-V.AP75A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/it-products/laptops/16-inch-lg-gram-laptops/16z90t-v-ap88a8/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>16Z90T-V.AP88A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/it-products/laptops/16-inch-lg-gram-laptops/16z90tr-e-ap88a8/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>16Z90TR-E.AP88A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/it-products/laptops/17-inch-lg-gram-laptops/17z90t-v-ap75a8/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>17Z90T-V.AP75A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/it-products/laptops/17-inch-lg-gram-laptops/17z90t-v-ap88a8/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>17Z90T-V.AP88A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-14z90ruap55c</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>14Z90RU-G.AP55C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90ruap55c</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>16Z90RU-G.AP55C</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/16t90q-g-ap79g/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>16T90Q-G.AP79G</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/16t90r-g/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>16T90R-G.AP78G</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/16t90sp-k-ap78g/</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>16T90SP-K.AP78G</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/16tb90tp-k-ap78g/</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>16TB90TP-K</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/notebooks/gram-2-in-1/16tb90tp-k-ap78g/</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>16TB90TP-K.AP78G</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/16z90q-g-ap55g/</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>16Z90Q-G.AP55G</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/16z90s-g-ap55g/</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>16Z90S-G.AP55G</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/16z90s-g-ap78g/</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>16Z90S-G.AP78G</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/16z90sp-a-ap7bg/</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>16Z90SP-A.AP7BG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/16zb90r-g-ap75g/</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>16ZB90R-G.AP75G</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/16zb90r-g-ap78g/</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>16ZB90R-G.AP78G</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/16zb90ru-g-ap55g/</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>16ZB90RU-G.AP55G</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/notebooks/gram/16zb90ru-g-ap55g/</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>16ZB90RU-G.AP55G</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/17z90p-g-ap78g/</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>17Z90P-G.AP78G</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/17z90q-g-ap75g/</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>17Z90Q-G.AP75G</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/17z90q-g-ap78g/</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>17Z90Q-G.AP78G</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/17z90q-g-ap79g/</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>17Z90Q-G.AP79G</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/notebooks/gram/17z90r-g-ap7cg/</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>17Z90R-G.AP7CG</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/17z90s-g-ap56g/</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>17Z90S-G.AP56G</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/17z90s-g-ap78g/</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>17Z90S-G.AP78G</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/17z90sp-e-ap7bg/</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>17Z90SP-E.AP7BG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/gram/17zb90r-g-ap78g/</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>17ZB90R-G.AP78G</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/ordenadores/portatiles-ultraligeros/14z90r-v-ap55b/</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>14Z90R-V.AP55B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/gram/14Z90ru-g-ap55b/</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>14Z90RU-G.AP55B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/gram/14z90s-v-ap75b/</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>14Z90S-V.AP75B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/laptops/gram/14z90t-v-ap88b/</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>14Z90T-V.AP88B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/ordenadores/portatiles-ultraligeros/16z90p-g-ap77b/</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>16Z90P-G-AP77B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/gram/16z90ru-g-ap55b/</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>16Z90RU-G.AP55B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/gram/16z90t-v-ap88b/</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>16Z90T-V.AP88B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/gram/17z90t-v-ap88b/</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>17Z90T-V.AP88B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/pc-portables/gram/lg-15u50t-g-ap56f/</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>LG 15U50T-G.AP56F</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/pc-portables/gram/lg-16z90r-g-ap7bf-i7-32go-2to-win-11-pro/</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>LG 16Z90R-G.AP7BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/pc-portables/gram/lg-16z90ru-g-ap55f-i5-16go-512go-win-11-pro/</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>LG 16Z90RU-G.AP55F</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/pc-portables/gram/lg-17z90ru-g-ap55f-i5-16go-512go-win-11-pro/</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>LG 17Z90RU-G.AP55F</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>GLOBAL : GLOBAL (en)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram/14z90r-q/</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>14Z90R-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GLOBAL : GLOBAL (en)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-book/15ub50t/</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>15UB50T</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>GLOBAL : GLOBAL (en)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram/16z90r-q/</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>16Z90R-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GLOBAL : GLOBAL (en)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram/17z90r-q/</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>17Z90R-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/business/computers/laptops/lg-gram/14z980-gap52a2/</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>14Z980-GAP52A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/gram/14z90ru-g-ap55d1/</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>14Z90RU-G.AP55D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/15ub50t-g-ap56d/</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>15UB50T-G</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/gram/16z90ru-g-ap55d1/</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>16Z90RU-G.AP55D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/16z90s-g-ap55d/</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>16Z90S-G.AP55D</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/16z90s-g-ap78d/</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>16Z90S-G.AP78D</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/gram/17z90ru-g/</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>17Z90RU-G</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/gram/17z90s-g/</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>17Z90S-G.AP78D</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z90ru-gp51j/</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>14Z90RU-GP51J</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z90s-vp55j/</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>14Z90S-VP55J</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z90s-vp56j/</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>14Z90S-VP56J</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/14z90t-vp55j/</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>14Z90T-VP55J</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/17z90s-vp55j/</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>17Z90S-VP55J</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/14z90s-v-ap75a3/</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>14Z90S-V.AP75A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/14z90t-g-ap75a3/</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>14Z90T-G.AP75A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/14z90t-g-ap88a3/</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>14Z90T-G.AP88A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/15z90st-v-ap75a3/</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>15Z90ST-V.AP75A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/16t90tp-k-ap88a3/</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>16T90TP-K.AP88A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90s-v-ap75a3/</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>16Z90S-V.AP75A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90s-v-ap78a3/</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>16Z90S-V.AP78A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90s-v-ap88a3/</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>16Z90S-V.AP88A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/gram/14z90r-v-ap56c2/</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>14Z90R-V</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/gram/14z90s-v-ap55c2/</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>14Z90S-V</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/gram/14z90s-v-ap54c2/</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>14Z90S-V</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/gram/14z90t-g-ap55c2/</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>14Z90T-G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/gram/15u50t-g-ap56c2/</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>15U50T-G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/business/san-pham-tin-hoc/laptop/16z90r-c-apl1y/</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>16Z90R-C</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/laptop-lg-gram/16z90s-g-ap76a5/</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>16Z90S-G.AP76A5</t>
         </is>
       </c>
     </row>
@@ -13736,7 +16102,6 @@
       <c r="G5" s="127" t="n"/>
     </row>
     <row r="6" ht="40.5" customHeight="1" s="203"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="136" t="inlineStr">
         <is>
@@ -14208,7 +16573,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.13" customWidth="1" style="203" min="1" max="1"/>
@@ -15373,10 +17738,6 @@
       <c r="F3" s="131" t="n"/>
       <c r="G3" s="127" t="n"/>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -15764,7 +18125,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="22.75" customWidth="1" style="203" min="1" max="1"/>
@@ -16191,7 +18552,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -16231,7 +18592,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -17217,7 +19577,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -17257,7 +19617,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -17767,7 +20126,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -17807,7 +20166,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -12692,2370 +12692,2370 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/laptops/gram-pro-2-in-1/16t90sp-g-ap55a/</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>16T90SP-G.AP55A</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/laptops/gram-pro-2-in-1/16t90sp-g-ap75a/</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>16T90SP-G.AP75A</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/business/it-products/laptops/14-inch-lg-gram-laptops/14z90s-v-ap55a8/</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>14Z90S-V.AP55A8</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/business/it-products/laptops/14-inch-lg-gram-laptops/14z90t-v-ap75a8/</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>14Z90T-V.AP75A8</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/business/it-products/laptops/16-inch-lg-gram-laptops/16z90s-v-ap55a8/</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>16Z90S-V.AP55A8</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/business/it-products/laptops/16-inch-lg-gram-laptops/16z90sp-r-ap85a8/</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>16Z90SP-R.AP85A8</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/business/it-products/laptops/16-inch-lg-gram-laptops/16z90t-v-ap75a8/</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>16Z90T-V.AP75A8</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/business/it-products/laptops/16-inch-lg-gram-laptops/16z90t-v-ap88a8/</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>16Z90T-V.AP88A8</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/business/it-products/laptops/16-inch-lg-gram-laptops/16z90tr-e-ap88a8/</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>16Z90TR-E.AP88A8</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/business/it-products/laptops/17-inch-lg-gram-laptops/17z90t-v-ap75a8/</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>17Z90T-V.AP75A8</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/business/it-products/laptops/17-inch-lg-gram-laptops/17z90t-v-ap88a8/</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>17Z90T-V.AP88A8</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/notebooks/lg-14z90ruap55c</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>14Z90RU-G.AP55C</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/notebooks/lg-16z90ruap55c</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>16Z90RU-G.AP55C</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/16t90q-g-ap79g/</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>16T90Q-G.AP79G</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/16t90r-g/</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>16T90R-G.AP78G</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/16t90sp-k-ap78g/</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>16T90SP-K.AP78G</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/16tb90tp-k-ap78g/</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>16TB90TP-K</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-2-in-1/16tb90tp-k-ap78g/</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>16TB90TP-K.AP78G</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/16z90q-g-ap55g/</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>16Z90Q-G.AP55G</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/16z90s-g-ap55g/</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>16Z90S-G.AP55G</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/16z90s-g-ap78g/</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>16Z90S-G.AP78G</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/16z90sp-a-ap7bg/</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>16Z90SP-A.AP7BG</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/16zb90r-g-ap75g/</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>16ZB90R-G.AP75G</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/16zb90r-g-ap78g/</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>16ZB90R-G.AP78G</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/16zb90ru-g-ap55g/</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>16ZB90RU-G.AP55G</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram/16zb90ru-g-ap55g/</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>16ZB90RU-G.AP55G</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/17z90p-g-ap78g/</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>17Z90P-G.AP78G</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/17z90q-g-ap75g/</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
         <is>
           <t>17Z90Q-G.AP75G</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/17z90q-g-ap78g/</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>17Z90Q-G.AP78G</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/17z90q-g-ap79g/</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
         <is>
           <t>17Z90Q-G.AP79G</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/notebooks/gram/17z90r-g-ap7cg/</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
         <is>
           <t>17Z90R-G.AP7CG</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/17z90s-g-ap56g/</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
         <is>
           <t>17Z90S-G.AP56G</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/17z90s-g-ap78g/</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
         <is>
           <t>17Z90S-G.AP78G</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/17z90sp-e-ap7bg/</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
         <is>
           <t>17Z90SP-E.AP7BG</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/business/gram/17zb90r-g-ap78g/</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>17ZB90R-G.AP78G</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/business/informatica/ordenadores/portatiles-ultraligeros/14z90r-v-ap55b/</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
         <is>
           <t>14Z90R-V.AP55B</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/14Z90ru-g-ap55b/</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
         <is>
           <t>14Z90RU-G.AP55B</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/14z90s-v-ap75b/</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
         <is>
           <t>14Z90S-V.AP75B</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/laptops/gram/14z90t-v-ap88b/</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
         <is>
           <t>14Z90T-V.AP88B</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/business/informatica/ordenadores/portatiles-ultraligeros/16z90p-g-ap77b/</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="F43" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
         <is>
           <t>16Z90P-G-AP77B</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/16z90ru-g-ap55b/</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
         <is>
           <t>16Z90RU-G.AP55B</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/16z90t-v-ap88b/</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="F45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
         <is>
           <t>16Z90T-V.AP88B</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/17z90t-v-ap88b/</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="F46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
         <is>
           <t>17Z90T-V.AP88B</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>FR : FR (fr)</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/fr/pc-portables/gram/lg-15u50t-g-ap56f/</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="F47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
         <is>
           <t>LG 15U50T-G.AP56F</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>FR : FR (fr)</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/fr/pc-portables/gram/lg-16z90r-g-ap7bf-i7-32go-2to-win-11-pro/</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
         <is>
           <t>LG 16Z90R-G.AP7BF</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>FR : FR (fr)</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/fr/pc-portables/gram/lg-16z90ru-g-ap55f-i5-16go-512go-win-11-pro/</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="F49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
         <is>
           <t>LG 16Z90RU-G.AP55F</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>FR : FR (fr)</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/fr/pc-portables/gram/lg-17z90ru-g-ap55f-i5-16go-512go-win-11-pro/</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="F50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
         <is>
           <t>LG 17Z90RU-G.AP55F</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>GLOBAL : GLOBAL (en)</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram/14z90r-q/</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
         <is>
           <t>14Z90R-Q</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>GLOBAL : GLOBAL (en)</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-book/15ub50t/</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
         <is>
           <t>15UB50T</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>GLOBAL : GLOBAL (en)</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram/16z90r-q/</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="F53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
         <is>
           <t>16Z90R-Q</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>GLOBAL : GLOBAL (en)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram/17z90r-q/</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
         <is>
           <t>17Z90R-Q</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/business/computers/laptops/lg-gram/14z980-gap52a2/</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="F55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
         <is>
           <t>14Z980-GAP52A2</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>IT : IT (it)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/14z90ru-g-ap55d1/</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="F56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
         <is>
           <t>14Z90RU-G.AP55D1</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>IT : IT (it)</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/15ub50t-g-ap56d/</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="inlineStr">
+      <c r="F57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
         <is>
           <t>15UB50T-G</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>IT : IT (it)</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/16z90ru-g-ap55d1/</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="F58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
         <is>
           <t>16Z90RU-G.AP55D1</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>IT : IT (it)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/16z90s-g-ap55d/</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="F59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
         <is>
           <t>16Z90S-G.AP55D</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>IT : IT (it)</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/16z90s-g-ap78d/</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="F60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
         <is>
           <t>16Z90S-G.AP78D</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>IT : IT (it)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/17z90ru-g/</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="F61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
         <is>
           <t>17Z90RU-G</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>IT : IT (it)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/17z90s-g/</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
+      <c r="D62" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="0" t="inlineStr">
         <is>
           <t>17Z90S-G.AP78D</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z90ru-gp51j/</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="F63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="0" t="inlineStr">
         <is>
           <t>14Z90RU-GP51J</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z90s-vp55j/</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
+      <c r="D64" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F64" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="0" t="inlineStr">
         <is>
           <t>14Z90S-VP55J</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z90s-vp56j/</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
+      <c r="D65" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E65" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="F65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
         <is>
           <t>14Z90S-VP56J</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/14z90t-vp55j/</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
+      <c r="D66" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="F66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="0" t="inlineStr">
         <is>
           <t>14Z90T-VP55J</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/17z90s-vp55j/</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
+      <c r="D67" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="F67" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="0" t="inlineStr">
         <is>
           <t>17Z90S-VP55J</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/business/it-products/lg-gram/14z90s-v-ap75a3/</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
+      <c r="D68" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F68" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="0" t="inlineStr">
         <is>
           <t>14Z90S-V.AP75A3</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/business/it-products/lg-gram/14z90t-g-ap75a3/</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
+      <c r="D69" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="inlineStr">
+      <c r="F69" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="0" t="inlineStr">
         <is>
           <t>14Z90T-G.AP75A3</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/laptops/gram/14z90t-g-ap88a3/</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
+      <c r="D70" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F70" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
         <is>
           <t>14Z90T-G.AP88A3</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/business/it-products/lg-gram/15z90st-v-ap75a3/</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
+      <c r="D71" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E71" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="F71" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="0" t="inlineStr">
         <is>
           <t>15Z90ST-V.AP75A3</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/business/it-products/lg-gram/16t90tp-k-ap88a3/</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
+      <c r="D72" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F72" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="0" t="inlineStr">
         <is>
           <t>16T90TP-K.AP88A3</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90s-v-ap75a3/</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
+      <c r="D73" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="0" t="inlineStr">
         <is>
           <t>16Z90S-V.AP75A3</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90s-v-ap78a3/</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
+      <c r="D74" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F74" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="0" t="inlineStr">
         <is>
           <t>16Z90S-V.AP78A3</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90s-v-ap88a3/</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
+      <c r="D75" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="F75" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="0" t="inlineStr">
         <is>
           <t>16Z90S-V.AP88A3</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/laptops/gram/14z90r-v-ap56c2/</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
+      <c r="D76" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F76" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="0" t="inlineStr">
         <is>
           <t>14Z90R-V</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/laptops/gram/14z90s-v-ap55c2/</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F77" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="0" t="inlineStr">
         <is>
           <t>14Z90S-V</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/laptops/gram/14z90s-v-ap54c2/</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
+      <c r="D78" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F78" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="0" t="inlineStr">
         <is>
           <t>14Z90S-V</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/laptops/gram/14z90t-g-ap55c2/</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
+      <c r="D79" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F79" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="0" t="inlineStr">
         <is>
           <t>14Z90T-G</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/laptops/gram/15u50t-g-ap56c2/</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
+      <c r="D80" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F80" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="0" t="inlineStr">
         <is>
           <t>15U50T-G</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="0" t="inlineStr">
         <is>
           <t>VN : VN (vi)</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/vn/business/san-pham-tin-hoc/laptop/16z90r-c-apl1y/</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
+      <c r="D81" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F81" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="0" t="inlineStr">
         <is>
           <t>16Z90R-C</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="0" t="inlineStr">
         <is>
           <t>VN : VN (vi)</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/vn/laptop-lg-gram/16z90s-g-ap76a5/</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
+      <c r="D82" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F82" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
         <is>
           <t>16Z90S-G.AP76A5</t>
         </is>
@@ -18347,15 +18347,19 @@
       </c>
       <c r="C13" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es/monitores/monitores-ultragear-gaming/</t>
+          <t>https://www.lg.com/es/monitores/monitores-ultragear-oled-gaming/</t>
         </is>
       </c>
       <c r="D13" s="279" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E13" s="123" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E13" s="123" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
       <c r="F13" s="123" t="n">
         <v>2</v>
       </c>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -18596,6 +18596,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -18721,7 +18722,7 @@
       <c r="C12" s="277" t="inlineStr"/>
       <c r="D12" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E12" s="123" t="inlineStr"/>
@@ -18803,7 +18804,7 @@
       <c r="C16" s="277" t="inlineStr"/>
       <c r="D16" s="263" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E16" s="123" t="inlineStr"/>
@@ -18819,7 +18820,7 @@
       <c r="C17" s="277" t="inlineStr"/>
       <c r="D17" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr"/>
@@ -19141,7 +19142,7 @@
       <c r="C32" s="277" t="inlineStr"/>
       <c r="D32" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E32" s="123" t="inlineStr"/>
@@ -19349,7 +19350,7 @@
       <c r="C42" s="277" t="inlineStr"/>
       <c r="D42" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E42" s="123" t="inlineStr"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -22,6 +22,7 @@
     <sheet name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="W31 - Windows 11 Landing" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="W31 - PDP Gallery Win11 Pro" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="W32 - UltraFine PDP MIC 삭제" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16025,6 +16026,1694 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="203" min="1" max="1"/>
+    <col width="18" customWidth="1" style="203" min="2" max="2"/>
+    <col width="62" customWidth="1" style="203" min="3" max="3"/>
+    <col width="12" customWidth="1" style="203" min="4" max="4"/>
+    <col width="12" customWidth="1" style="203" min="5" max="5"/>
+    <col width="8" customWidth="1" style="203" min="6" max="6"/>
+    <col width="72" customWidth="1" style="203" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>GR26-W32-MS-IT UltraFine PDP MIC 문구 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>금주 신규 등록 · 요청자 Alchan Jung(정알찬 책임) · Due 2026-08-12 · 대상 6모델 × 31개국</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AE : AE (en)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/consumer-monitors/lg-32u700b-b</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CAC : GT (es)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/monitors/lg-27u710b-b</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/uhd-4k-5k/32u700b-b/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/uhd-4k-5k/32u701b-b/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/uhd-4k-et-5k/32u700b-b/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/uhd-4k-et-5k/32u701b-b/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CL : CL (es)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cl/monitores/uhd-4k/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-27u711b-b</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-32u700b-b</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/smart-monitores/27u710b-b/</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/uhd-4k/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/uhd-4k/32u700b-b/</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-27u710b-b</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-27u730b-b</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitor/uhd-4k/27u711b/</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/monitors/uhd-4k-5k/27u710b-b/</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/monitors/uhd-4k-5k/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/27u710b-b/</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/32u700b-b/</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/32u701b-b/</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/32u720b-b/</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>32U720B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LT : LT (lt)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lt/monitoriai/lg-27u710b-b</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LT : LT (lt)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lt/monitoriai/lg-27u730b-b</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LV : LV (lv)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lv/monitori/lg-27u710b-b</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LV : LV (lv)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lv/monitori/lg-27u730b-b</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MX : MX (es)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MX : MX (es)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MY : MY (en)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MY : MY (en)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultrafine-uhd-4k-5k-monitoren/27u710b-b/</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultrafine-uhd-4k-5k-monitoren/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PA : PA (es)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pa/monitores/ultrafine-monitores/27u710b-b/</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pe/monitores/uhd-4k/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PH : PH (en)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ph/monitors/ultra-fine-uhd-4k/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PH : PH (en)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SA : SA (ar)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sa/monitors/uhd-4k-5k/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SA_EN : SA (en)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sa_en/monitors/uhd-4k-5k/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/consumer-monitors/uhd-4k/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/consumer-monitors/uhd-4k/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-do-hoa-ultrafine/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-do-hoa-ultrafine/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ZA : ZA (en)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ZA : ZA (en)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -18596,7 +20285,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -16041,7 +16041,7 @@
     <col width="12" customWidth="1" style="203" min="4" max="4"/>
     <col width="12" customWidth="1" style="203" min="5" max="5"/>
     <col width="8" customWidth="1" style="203" min="6" max="6"/>
-    <col width="72" customWidth="1" style="203" min="7" max="7"/>
+    <col width="86" customWidth="1" style="203" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · 요청자 Alchan Jung(정알찬 책임) · Due 2026-08-12 · 대상 6모델 × 31개국</t>
+          <t>금주 신규 등록 · 요청자 Alchan Jung(정알찬 책임) · Due 2026-08-12 · 대상 6모델 × 31개국 (라이브 URL 36건 실측 200 확인)</t>
         </is>
       </c>
     </row>
@@ -16111,11 +16111,7 @@
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ae/consumer-monitors/lg-32u700b-b</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16127,7 +16123,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시(CMS 라이브 표기였으나 실측 404)</t>
         </is>
       </c>
     </row>
@@ -16451,11 +16447,7 @@
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cn/monitors/lg-32u700b-b</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16467,7 +16459,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시(CMS 라이브 표기였으나 실측 404)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -23,6 +23,7 @@
     <sheet name="W31 - Windows 11 Landing" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="W31 - PDP Gallery Win11 Pro" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="W32 - UltraFine PDP MIC 삭제" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="W31 - Smart Monitor Multi AI" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16045,6 +16046,1686 @@
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>GR26-W32-MS-IT UltraFine PDP MIC 문구 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>금주 신규 등록 · 요청자 Alchan Jung(정알찬 책임) · Due 2026-08-12 · 대상 6모델 × 31개국 (라이브 URL 36건 실측 200 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>AE : AE (en)</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr"/>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시(CMS 라이브 표기였으나 실측 404)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr"/>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr"/>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr"/>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>CAC : GT (es)</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/monitors/lg-27u710b-b</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr"/>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr"/>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/uhd-4k-5k/32u700b-b/</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/uhd-4k-5k/32u701b-b/</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/uhd-4k-et-5k/32u700b-b/</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/uhd-4k-et-5k/32u701b-b/</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>CL : CL (es)</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cl/monitores/uhd-4k/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-27u711b-b</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr"/>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr"/>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시(CMS 라이브 표기였으나 실측 404)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/smart-monitores/27u710b-b/</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/uhd-4k/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/uhd-4k/32u700b-b/</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr"/>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr"/>
+      <c r="F22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr"/>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr"/>
+      <c r="F23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-27u710b-b</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr"/>
+      <c r="F24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-27u730b-b</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr"/>
+      <c r="F25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr"/>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr"/>
+      <c r="F26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr"/>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr"/>
+      <c r="F27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr"/>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr"/>
+      <c r="F28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr"/>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="inlineStr"/>
+      <c r="F29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr"/>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr"/>
+      <c r="F30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr"/>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr"/>
+      <c r="F31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr"/>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr"/>
+      <c r="F32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitor/uhd-4k/27u711b/</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr"/>
+      <c r="F33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr"/>
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E34" s="0" t="inlineStr"/>
+      <c r="F34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/monitors/uhd-4k-5k/27u710b-b/</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr"/>
+      <c r="F35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/monitors/uhd-4k-5k/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr"/>
+      <c r="F36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/27u710b-b/</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr"/>
+      <c r="F37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr"/>
+      <c r="F38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr"/>
+      <c r="F39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/32u700b-b/</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr"/>
+      <c r="F40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/32u701b-b/</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr"/>
+      <c r="F41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/32u720b-b/</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr"/>
+      <c r="F42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t>32U720B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>LT : LT (lt)</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lt/monitoriai/lg-27u710b-b</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr"/>
+      <c r="F43" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>LT : LT (lt)</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lt/monitoriai/lg-27u730b-b</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr"/>
+      <c r="F44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>LV : LV (lv)</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lv/monitori/lg-27u710b-b</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr"/>
+      <c r="F45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>LV : LV (lv)</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lv/monitori/lg-27u730b-b</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr"/>
+      <c r="F46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>MX : MX (es)</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr"/>
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E47" s="0" t="inlineStr"/>
+      <c r="F47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>MX : MX (es)</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr"/>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="inlineStr"/>
+      <c r="F48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>MY : MY (en)</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr"/>
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="inlineStr"/>
+      <c r="F49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>MY : MY (en)</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr"/>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr"/>
+      <c r="F50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultrafine-uhd-4k-5k-monitoren/27u710b-b/</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr"/>
+      <c r="F51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultrafine-uhd-4k-5k-monitoren/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr"/>
+      <c r="F52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>PA : PA (es)</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pa/monitores/ultrafine-monitores/27u710b-b/</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr"/>
+      <c r="F53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr"/>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr"/>
+      <c r="F54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pe/monitores/uhd-4k/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr"/>
+      <c r="F55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr"/>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr"/>
+      <c r="F56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>PH : PH (en)</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ph/monitors/ultra-fine-uhd-4k/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr"/>
+      <c r="F57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>PH : PH (en)</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr"/>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr"/>
+      <c r="F58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>SA : SA (ar)</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sa/monitors/uhd-4k-5k/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr"/>
+      <c r="F59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>SA_EN : SA (en)</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sa_en/monitors/uhd-4k-5k/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr"/>
+      <c r="F60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/consumer-monitors/uhd-4k/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr"/>
+      <c r="F61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/consumer-monitors/uhd-4k/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E62" s="0" t="inlineStr"/>
+      <c r="F62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr"/>
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E63" s="0" t="inlineStr"/>
+      <c r="F63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr"/>
+      <c r="D64" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E64" s="0" t="inlineStr"/>
+      <c r="F64" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr"/>
+      <c r="D65" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E65" s="0" t="inlineStr"/>
+      <c r="F65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-do-hoa-ultrafine/27u711b-b/</t>
+        </is>
+      </c>
+      <c r="D66" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E66" s="0" t="inlineStr"/>
+      <c r="F66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="0" t="inlineStr">
+        <is>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-do-hoa-ultrafine/27u730b-b/</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr"/>
+      <c r="F67" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>ZA : ZA (en)</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr"/>
+      <c r="D68" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E68" s="0" t="inlineStr"/>
+      <c r="F68" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="0" t="inlineStr">
+        <is>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>ZA : ZA (en)</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr"/>
+      <c r="D69" s="0" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E69" s="0" t="inlineStr"/>
+      <c r="F69" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="0" t="inlineStr">
+        <is>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="203" min="1" max="1"/>
+    <col width="18" customWidth="1" style="203" min="2" max="2"/>
+    <col width="62" customWidth="1" style="203" min="3" max="3"/>
+    <col width="12" customWidth="1" style="203" min="4" max="4"/>
+    <col width="12" customWidth="1" style="203" min="5" max="5"/>
+    <col width="8" customWidth="1" style="203" min="6" max="6"/>
+    <col width="96" customWidth="1" style="203" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>Title</t>
@@ -16052,7 +17733,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>GR26-W32-MS-IT UltraFine PDP MIC 문구 삭제</t>
+          <t>GR26-W31-MS-IT Smart Monitor Multi AI 에셋 수정</t>
         </is>
       </c>
     </row>
@@ -16064,7 +17745,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · 요청자 Alchan Jung(정알찬 책임) · Due 2026-08-12 · 대상 6모델 × 31개국 (라이브 URL 36건 실측 200 확인)</t>
+          <t>금주 신규 등록 · 요청자 Yujin Han(한유진 사원) · 요청 2026-07-30 · Due 2026-08-30 · 대상 8모델 × 22개국 (요청서 Target List + CMS/PTT 신규 10건 보강)</t>
         </is>
       </c>
     </row>
@@ -16123,14 +17804,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시(CMS 라이브 표기였으나 실측 404)</t>
+          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>AU : AU (en)</t>
+          <t>AE : AE (en)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -16145,14 +17826,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>AU : AU (en)</t>
+          <t>AE : AE (en)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -16167,14 +17848,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>AU : AU (en)</t>
+          <t>AE : AE (en)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -16189,21 +17870,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>CAC : GT (es)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cac/monitors/lg-27u710b-b</t>
-        </is>
-      </c>
+          <t>AE_AR : AE (ar)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16215,14 +17892,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>AE_AR : AE (ar)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -16237,14 +17914,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>AE_AR : AE (ar)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -16259,21 +17936,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_en/monitors/uhd-4k-5k/32u700b-b/</t>
-        </is>
-      </c>
+          <t>AE_AR : AE (ar)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16285,21 +17958,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_en/monitors/uhd-4k-5k/32u701b-b/</t>
-        </is>
-      </c>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16311,19 +17980,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>BR : BR (pt)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/moniteurs/uhd-4k-et-5k/32u700b-b/</t>
+          <t>https://www.lg.com/br/monitores/smart-monitors/24u511sb-b/</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -16337,19 +18006,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>BR : BR (pt)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/moniteurs/uhd-4k-et-5k/32u701b-b/</t>
+          <t>https://www.lg.com/br/monitores/smart-monitors/27u511sb-b/</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -16363,19 +18032,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>CL : CL (es)</t>
+          <t>BR : BR (pt)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cl/monitores/uhd-4k/27u711b-b/</t>
+          <t>https://www.lg.com/br/monitores/smart-monitors/27u731sb-w/</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -16389,19 +18058,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>BR : BR (pt)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-27u711b-b</t>
+          <t>https://www.lg.com/br/monitores/smart-monitors/32u701sb-b/</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -16415,17 +18084,21 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/smart-monitores/24u511sb-b/</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16437,17 +18110,21 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>CO : CO (es)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/co/monitores/smart-monitores/27u511sb-w/</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16459,7 +18136,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시(CMS 라이브 표기였으나 실측 404)</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -16471,7 +18148,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.lg.com/co/monitores/smart-monitores/27u710b-b/</t>
+          <t>https://www.lg.com/co/monitores/smart-monitores/32u501sb-b/</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -16485,7 +18162,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -16497,7 +18174,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.lg.com/co/monitores/uhd-4k/27u711b-b/</t>
+          <t>https://www.lg.com/co/monitores/smart-monitores/32u701sb-b/</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -16511,21 +18188,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>CO : CO (es)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/co/monitores/uhd-4k/32u700b-b/</t>
-        </is>
-      </c>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16537,7 +18210,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
@@ -16559,7 +18232,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
@@ -16581,19 +18254,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>EE : EE (et)</t>
+          <t>DE : DE (de)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ee/monitorid/lg-27u710b-b</t>
+          <t>https://www.lg.com/de/monitore/smarte-monitore/24u511sb-b/</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -16607,19 +18280,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>EE : EE (et)</t>
+          <t>DE : DE (de)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ee/monitorid/lg-27u730b-b</t>
+          <t>https://www.lg.com/de/monitore/smarte-monitore/27u511sb-b/</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -16633,7 +18306,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
@@ -16643,7 +18316,11 @@
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/outlet/outlet-informatica/monitores/32u701sb-b-outlet/</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16655,17 +18332,21 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk/monitors/smart-monitors/27u511sb-w/</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16677,17 +18358,21 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>HK : HK (zh)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk/monitors/smart-monitors/27u731sb-w/</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16699,17 +18384,21 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>HK : HK (zh)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk_en/monitors/smart-monitors/27u511sb-w/</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16721,17 +18410,21 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>HK : HK (zh)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>HK_EN : HK (en)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk_en/monitors/smart-monitors/27u731sb-w/</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16743,17 +18436,21 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>HK_EN : HK (en)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitor/smart-monitors/27u511sb/</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16765,17 +18462,21 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>HK_EN : HK (en)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitor/smart-monitors/32u501sb/</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16787,7 +18488,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -16799,7 +18500,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.lg.com/id/monitor/uhd-4k/27u711b/</t>
+          <t>https://www.lg.com/id/monitor/smart-monitors/32u721sb-w/</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -16813,17 +18514,21 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>ID : ID (in)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>IN : IN (en)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/monitors/smart-monitors/24u511sb-b/</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -16835,7 +18540,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -16847,7 +18552,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.lg.com/in/monitors/uhd-4k-5k/27u710b-b/</t>
+          <t>https://www.lg.com/in/monitors/smart-monitors/27u511sb-b/</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -16861,7 +18566,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -16873,7 +18578,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.lg.com/in/monitors/uhd-4k-5k/27u730b-b/</t>
+          <t>https://www.lg.com/in/monitors/smart-monitors/27u731sb-w/</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -16887,19 +18592,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>IN : IN (en)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/27u710b-b/</t>
+          <t>https://www.lg.com/in/monitors/smart-monitors/32u501sb-b/</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -16913,19 +18618,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>IN : IN (en)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/27u711b-b/</t>
+          <t>https://www.lg.com/in/monitors/smart-monitors/32u701sb-b/</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -16939,19 +18644,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>IN : IN (en)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/27u730b-b/</t>
+          <t>https://www.lg.com/in/monitors/smart-monitors/32u721sb-w/</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -16965,7 +18670,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -16977,7 +18682,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/32u700b-b/</t>
+          <t>https://www.lg.com/jp/monitors/smart-monitors/24u511sb-b/</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -16991,7 +18696,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -17003,7 +18708,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/32u701b-b/</t>
+          <t>https://www.lg.com/jp/monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -17017,7 +18722,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -17027,11 +18732,7 @@
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/jp/monitors/4k-5k-monitors/32u720b-b/</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -17043,19 +18744,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>32U720B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>LT : LT (lt)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lt/monitoriai/lg-27u710b-b</t>
+          <t>https://www.lg.com/jp/monitors/smart-monitors/32u501sb-w/</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -17069,19 +18770,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>LT : LT (lt)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lt/monitoriai/lg-27u730b-b</t>
+          <t>https://www.lg.com/jp/monitors/smart-monitors/32u721sb-w/</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -17095,19 +18796,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>LV : LV (lv)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lv/monitori/lg-27u710b-b</t>
+          <t>https://www.lg.com/jp/monitors/smart-monitors/34u620sb-b/</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -17121,19 +18822,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>LV : LV (lv)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lv/monitori/lg-27u730b-b</t>
+          <t>https://www.lg.com/jp/monitors/smart-monitors/34u640sb-w/</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -17147,7 +18848,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>34U640SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -17157,7 +18858,11 @@
           <t>MX : MX (es)</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/mx/monitores/monitores-smart/24u511sb-b/</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -17169,7 +18874,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -17179,7 +18884,11 @@
           <t>MX : MX (es)</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/mx/monitores/monitores-smart/27u511sb-w/</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -17191,17 +18900,21 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>MY : MY (en)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>MX : MX (es)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/mx/monitores/monitores-smart/34u620sb-b/</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -17213,17 +18926,21 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>MY : MY (en)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pe/monitores/fhd-y-qhd/27u511sb-w/</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -17235,21 +18952,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>NL : NL (nl)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/nl/monitoren/ultrafine-uhd-4k-5k-monitoren/27u710b-b/</t>
-        </is>
-      </c>
+          <t>SA : SA (ar)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -17261,21 +18974,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>NL : NL (nl)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/nl/monitoren/ultrafine-uhd-4k-5k-monitoren/27u711b-b/</t>
-        </is>
-      </c>
+          <t>SA_EN : SA (en)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -17287,19 +18996,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>PA : PA (es)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pa/monitores/ultrafine-monitores/27u710b-b/</t>
+          <t>https://www.lg.com/sg/consumer-monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -17313,17 +19022,21 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>PE : PE (es)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/consumer-monitors/smart-monitors/32u721sb-w/</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -17335,19 +19048,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>PE : PE (es)</t>
+          <t>TR : TR (tr)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pe/monitores/uhd-4k/27u730b-b/</t>
+          <t>https://www.lg.com/tr/monitor/smart-monitorleri/32u701sb-b/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -17361,14 +19074,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>PE : PE (es)</t>
+          <t>UK : GB (en)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -17383,21 +19096,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>PH : PH (en)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ph/monitors/ultra-fine-uhd-4k/27u711b-b/</t>
-        </is>
-      </c>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -17409,14 +19118,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>PH : PH (en)</t>
+          <t>UK : GB (en)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -17431,21 +19140,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>SA : SA (ar)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa/monitors/uhd-4k-5k/27u730b-b/</t>
-        </is>
-      </c>
+          <t>US : US (en)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -17457,21 +19162,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>SA_EN : SA (en)</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa_en/monitors/uhd-4k-5k/27u730b-b/</t>
-        </is>
-      </c>
+          <t>US : US (en)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -17483,21 +19184,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
+          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sg/consumer-monitors/uhd-4k/27u711b-b/</t>
-        </is>
-      </c>
+          <t>ZA : ZA (en)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -17509,195 +19206,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>SG : SG (en)</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sg/consumer-monitors/uhd-4k/27u730b-b/</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>UK : GB (en)</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>UK : GB (en)</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>UK : GB (en)</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>VN : VN (vi)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-do-hoa-ultrafine/27u711b-b/</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>VN : VN (vi)</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-do-hoa-ultrafine/27u730b-b/</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>ZA : ZA (en)</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>ZA : ZA (en)</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F4" s="0" t="n">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F5" s="0" t="n">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F6" s="0" t="n">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F7" s="0" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F8" s="0" t="n">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F9" s="0" t="n">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F10" s="0" t="n">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F11" s="0" t="n">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F12" s="0" t="n">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F13" s="0" t="n">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F14" s="0" t="n">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F15" s="0" t="n">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F16" s="0" t="n">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F17" s="0" t="n">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F18" s="0" t="n">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F19" s="0" t="n">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F20" s="0" t="n">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F21" s="0" t="n">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F22" s="0" t="n">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F23" s="0" t="n">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F24" s="0" t="n">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F25" s="0" t="n">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F26" s="0" t="n">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F27" s="0" t="n">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F28" s="0" t="n">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F29" s="0" t="n">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F30" s="0" t="n">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F31" s="0" t="n">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F32" s="0" t="n">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F33" s="0" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F34" s="0" t="n">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F35" s="0" t="n">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F36" s="0" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F37" s="0" t="n">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F38" s="0" t="n">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F39" s="0" t="n">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F40" s="0" t="n">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F41" s="0" t="n">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F42" s="0" t="n">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F43" s="0" t="n">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F44" s="0" t="n">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F45" s="0" t="n">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F46" s="0" t="n">
@@ -11180,7 +11180,7 @@
       <c r="C47" s="0" t="n"/>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F47" s="0" t="n">
@@ -11201,7 +11201,7 @@
       <c r="C48" s="0" t="n"/>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F48" s="0" t="n">
@@ -11222,7 +11222,7 @@
       <c r="C49" s="0" t="n"/>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F49" s="0" t="n">
@@ -11243,7 +11243,7 @@
       <c r="C50" s="0" t="n"/>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F50" s="0" t="n">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F51" s="0" t="n">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F52" s="0" t="n">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F53" s="0" t="n">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F54" s="0" t="n">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F55" s="0" t="n">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F56" s="0" t="n">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F57" s="0" t="n">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F58" s="0" t="n">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F59" s="0" t="n">
@@ -11493,7 +11493,7 @@
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F60" s="0" t="n">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F61" s="0" t="n">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F62" s="0" t="n">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="D63" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F63" s="0" t="n">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F64" s="0" t="n">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F65" s="0" t="n">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F66" s="0" t="n">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F67" s="0" t="n">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F68" s="0" t="n">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F69" s="0" t="n">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F70" s="0" t="n">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F71" s="0" t="n">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F79" s="0" t="n">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F80" s="0" t="n">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F81" s="0" t="n">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="D82" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F82" s="0" t="n">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F83" s="0" t="n">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F84" s="0" t="n">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F85" s="0" t="n">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F86" s="0" t="n">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F87" s="0" t="n">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F88" s="0" t="n">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F89" s="0" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F90" s="0" t="n">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F91" s="0" t="n">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F92" s="0" t="n">
@@ -12314,7 +12314,7 @@
       <c r="C93" s="0" t="n"/>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F93" s="0" t="n">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F94" s="0" t="n">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F95" s="0" t="n">
@@ -12385,7 +12385,7 @@
       <c r="C96" s="0" t="n"/>
       <c r="D96" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F96" s="0" t="n">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="D97" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F97" s="0" t="n">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F98" s="0" t="n">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F99" s="0" t="n">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F100" s="0" t="n">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="D101" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F101" s="0" t="n">
@@ -12531,7 +12531,7 @@
       <c r="C102" s="0" t="n"/>
       <c r="D102" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F102" s="0" t="n">
@@ -16115,7 +16115,7 @@
       <c r="C4" s="0" t="inlineStr"/>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr"/>
@@ -16137,7 +16137,7 @@
       <c r="C5" s="0" t="inlineStr"/>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr"/>
@@ -16159,7 +16159,7 @@
       <c r="C6" s="0" t="inlineStr"/>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr"/>
@@ -16181,7 +16181,7 @@
       <c r="C7" s="0" t="inlineStr"/>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr"/>
@@ -16207,7 +16207,7 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr"/>
@@ -16229,7 +16229,7 @@
       <c r="C9" s="0" t="inlineStr"/>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr"/>
@@ -16251,7 +16251,7 @@
       <c r="C10" s="0" t="inlineStr"/>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr"/>
@@ -16277,7 +16277,7 @@
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr"/>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr"/>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr"/>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr"/>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr"/>
@@ -16407,7 +16407,7 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr"/>
@@ -16429,7 +16429,7 @@
       <c r="C17" s="0" t="inlineStr"/>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr"/>
@@ -16451,7 +16451,7 @@
       <c r="C18" s="0" t="inlineStr"/>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr"/>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr"/>
@@ -16503,7 +16503,7 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr"/>
@@ -16529,7 +16529,7 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr"/>
@@ -16551,7 +16551,7 @@
       <c r="C22" s="0" t="inlineStr"/>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr"/>
@@ -16573,7 +16573,7 @@
       <c r="C23" s="0" t="inlineStr"/>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr"/>
@@ -16599,7 +16599,7 @@
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr"/>
@@ -16625,7 +16625,7 @@
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr"/>
@@ -16647,7 +16647,7 @@
       <c r="C26" s="0" t="inlineStr"/>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr"/>
@@ -16669,7 +16669,7 @@
       <c r="C27" s="0" t="inlineStr"/>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr"/>
@@ -16691,7 +16691,7 @@
       <c r="C28" s="0" t="inlineStr"/>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr"/>
@@ -16713,7 +16713,7 @@
       <c r="C29" s="0" t="inlineStr"/>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr"/>
@@ -16735,7 +16735,7 @@
       <c r="C30" s="0" t="inlineStr"/>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr"/>
@@ -16757,7 +16757,7 @@
       <c r="C31" s="0" t="inlineStr"/>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr"/>
@@ -16779,7 +16779,7 @@
       <c r="C32" s="0" t="inlineStr"/>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr"/>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr"/>
@@ -16827,7 +16827,7 @@
       <c r="C34" s="0" t="inlineStr"/>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr"/>
@@ -16853,7 +16853,7 @@
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr"/>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr"/>
@@ -16905,7 +16905,7 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr"/>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E38" s="0" t="inlineStr"/>
@@ -16957,7 +16957,7 @@
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E39" s="0" t="inlineStr"/>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E40" s="0" t="inlineStr"/>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E41" s="0" t="inlineStr"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E42" s="0" t="inlineStr"/>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E43" s="0" t="inlineStr"/>
@@ -17087,7 +17087,7 @@
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E44" s="0" t="inlineStr"/>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E45" s="0" t="inlineStr"/>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E46" s="0" t="inlineStr"/>
@@ -17161,7 +17161,7 @@
       <c r="C47" s="0" t="inlineStr"/>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E47" s="0" t="inlineStr"/>
@@ -17183,7 +17183,7 @@
       <c r="C48" s="0" t="inlineStr"/>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E48" s="0" t="inlineStr"/>
@@ -17205,7 +17205,7 @@
       <c r="C49" s="0" t="inlineStr"/>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E49" s="0" t="inlineStr"/>
@@ -17227,7 +17227,7 @@
       <c r="C50" s="0" t="inlineStr"/>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E50" s="0" t="inlineStr"/>
@@ -17253,7 +17253,7 @@
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E51" s="0" t="inlineStr"/>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E52" s="0" t="inlineStr"/>
@@ -17305,7 +17305,7 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E53" s="0" t="inlineStr"/>
@@ -17327,7 +17327,7 @@
       <c r="C54" s="0" t="inlineStr"/>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E54" s="0" t="inlineStr"/>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E55" s="0" t="inlineStr"/>
@@ -17375,7 +17375,7 @@
       <c r="C56" s="0" t="inlineStr"/>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E56" s="0" t="inlineStr"/>
@@ -17401,7 +17401,7 @@
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E57" s="0" t="inlineStr"/>
@@ -17423,7 +17423,7 @@
       <c r="C58" s="0" t="inlineStr"/>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E58" s="0" t="inlineStr"/>
@@ -17449,7 +17449,7 @@
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E59" s="0" t="inlineStr"/>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E60" s="0" t="inlineStr"/>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E61" s="0" t="inlineStr"/>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E62" s="0" t="inlineStr"/>
@@ -17549,7 +17549,7 @@
       <c r="C63" s="0" t="inlineStr"/>
       <c r="D63" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E63" s="0" t="inlineStr"/>
@@ -17571,7 +17571,7 @@
       <c r="C64" s="0" t="inlineStr"/>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E64" s="0" t="inlineStr"/>
@@ -17593,7 +17593,7 @@
       <c r="C65" s="0" t="inlineStr"/>
       <c r="D65" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E65" s="0" t="inlineStr"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E66" s="0" t="inlineStr"/>
@@ -17645,7 +17645,7 @@
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E67" s="0" t="inlineStr"/>
@@ -17667,7 +17667,7 @@
       <c r="C68" s="0" t="inlineStr"/>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E68" s="0" t="inlineStr"/>
@@ -17689,7 +17689,7 @@
       <c r="C69" s="0" t="inlineStr"/>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E69" s="0" t="inlineStr"/>
@@ -17726,1485 +17726,1485 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>GR26-W31-MS-IT Smart Monitor Multi AI 에셋 수정</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>이번주 추가</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>금주 신규 등록 · 요청자 Yujin Han(한유진 사원) · 요청 2026-07-30 · Due 2026-08-30 · 대상 8모델 × 22개국 (요청서 Target List + CMS/PTT 신규 10건 보강)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Head</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>완료일</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Page#</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr"/>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr"/>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr"/>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr"/>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>AE_AR : AE (ar)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr"/>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>AE_AR : AE (ar)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr"/>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>AE_AR : AE (ar)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr"/>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>AE_AR : AE (ar)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr"/>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr"/>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>BR : BR (pt)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/br/monitores/smart-monitors/24u511sb-b/</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>BR : BR (pt)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/br/monitores/smart-monitors/27u511sb-b/</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>BR : BR (pt)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/br/monitores/smart-monitors/27u731sb-w/</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>BR : BR (pt)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/br/monitores/smart-monitors/32u701sb-b/</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>CO : CO (es)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/co/monitores/smart-monitores/24u511sb-b/</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>CO : CO (es)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/co/monitores/smart-monitores/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>CO : CO (es)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/co/monitores/smart-monitores/32u501sb-b/</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>CO : CO (es)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/co/monitores/smart-monitores/32u701sb-b/</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>CZ : CZ (cs)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr"/>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>CZ : CZ (cs)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr"/>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr"/>
+      <c r="F22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>CZ : CZ (cs)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr"/>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr"/>
+      <c r="F23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/monitore/smarte-monitore/24u511sb-b/</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr"/>
+      <c r="F24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/monitore/smarte-monitore/27u511sb-b/</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr"/>
+      <c r="F25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/outlet/outlet-informatica/monitores/32u701sb-b-outlet/</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr"/>
+      <c r="F26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>HK : HK (zh)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/hk/monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr"/>
+      <c r="F27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>HK : HK (zh)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/hk/monitors/smart-monitors/27u731sb-w/</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr"/>
+      <c r="F28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>HK_EN : HK (en)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/hk_en/monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="inlineStr"/>
+      <c r="F29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>HK_EN : HK (en)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/hk_en/monitors/smart-monitors/27u731sb-w/</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr"/>
+      <c r="F30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>ID : ID (in)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/id/monitor/smart-monitors/27u511sb/</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr"/>
+      <c r="F31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>ID : ID (in)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/id/monitor/smart-monitors/32u501sb/</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr"/>
+      <c r="F32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>ID : ID (in)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/id/monitor/smart-monitors/32u721sb-w/</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr"/>
+      <c r="F33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
         <is>
           <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/monitors/smart-monitors/24u511sb-b/</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E34" s="0" t="inlineStr"/>
+      <c r="F34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
         <is>
           <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/monitors/smart-monitors/27u511sb-b/</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr"/>
+      <c r="F35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/monitors/smart-monitors/27u731sb-w/</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr"/>
+      <c r="F36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
         <is>
           <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/monitors/smart-monitors/32u501sb-b/</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr"/>
+      <c r="F37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
         <is>
           <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/monitors/smart-monitors/32u701sb-b/</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr"/>
+      <c r="F38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>IN : IN (en)</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/in/monitors/smart-monitors/32u721sb-w/</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr"/>
+      <c r="F39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
         <is>
           <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/monitors/smart-monitors/24u511sb-b/</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr"/>
+      <c r="F40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
         <is>
           <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr"/>
+      <c r="F41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr"/>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr"/>
+      <c r="F42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
         <is>
           <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/monitors/smart-monitors/32u501sb-w/</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr"/>
+      <c r="F43" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
         <is>
           <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/monitors/smart-monitors/32u721sb-w/</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr"/>
+      <c r="F44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
         <is>
           <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/monitors/smart-monitors/34u620sb-b/</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr"/>
+      <c r="F45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
         <is>
           <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/monitors/smart-monitors/34u640sb-w/</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr"/>
+      <c r="F46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
         <is>
           <t>34U640SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>MX : MX (es)</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/mx/monitores/monitores-smart/24u511sb-b/</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E47" s="0" t="inlineStr"/>
+      <c r="F47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
         <is>
           <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>MX : MX (es)</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/mx/monitores/monitores-smart/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="inlineStr"/>
+      <c r="F48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>MX : MX (es)</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/mx/monitores/monitores-smart/34u620sb-b/</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="inlineStr"/>
+      <c r="F49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
         <is>
           <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>PE : PE (es)</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/pe/monitores/fhd-y-qhd/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr"/>
+      <c r="F50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>SA : SA (ar)</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr"/>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr"/>
+      <c r="F51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
         <is>
           <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>SA_EN : SA (en)</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr"/>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr"/>
+      <c r="F52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
         <is>
           <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/consumer-monitors/smart-monitors/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr"/>
+      <c r="F53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>SG : SG (en)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sg/consumer-monitors/smart-monitors/32u721sb-w/</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr"/>
+      <c r="F54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
         <is>
           <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>TR : TR (tr)</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tr/monitor/smart-monitorleri/32u701sb-b/</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr"/>
+      <c r="F55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
         <is>
           <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr"/>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr"/>
+      <c r="F56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
         <is>
           <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr"/>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr"/>
+      <c r="F57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
         <is>
           <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr"/>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr"/>
+      <c r="F58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
         <is>
           <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>US : US (en)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr"/>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr"/>
+      <c r="F59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
         <is>
           <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>US : US (en)</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr"/>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr"/>
+      <c r="F60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
         <is>
           <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>ZA : ZA (en)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr"/>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr"/>
+      <c r="F61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
         <is>
           <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -17630,7 +17630,7 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -17630,7 +17630,7 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -19177,11 +19177,7 @@
           <t>AT : AT (de)</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/at/monitore/lg-34wp65c-b/</t>
-        </is>
-      </c>
+      <c r="C7" s="0" t="inlineStr"/>
       <c r="D7" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -19193,7 +19189,7 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>34WP65C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>34WP65C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · STG · 라이브 미게시(실측 404)</t>
         </is>
       </c>
     </row>
@@ -19593,11 +19589,7 @@
           <t>BE_FR : BE (fr)</t>
         </is>
       </c>
-      <c r="C23" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/be_fr/moniteurs/lg-34wp65c-b/</t>
-        </is>
-      </c>
+      <c r="C23" s="0" t="inlineStr"/>
       <c r="D23" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -19609,7 +19601,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>34WP65C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>34WP65C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · STG · 라이브 미게시(실측 404)</t>
         </is>
       </c>
     </row>
@@ -19619,11 +19611,7 @@
           <t>BE_FR : BE (fr)</t>
         </is>
       </c>
-      <c r="C24" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/be_fr/moniteurs/lg-34wp75c-b/</t>
-        </is>
-      </c>
+      <c r="C24" s="0" t="inlineStr"/>
       <c r="D24" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -19635,7 +19623,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>34WP75C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>34WP75C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · STG · 라이브 미게시(실측 404)</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19737,11 @@
           <t>BG : BG (bg)</t>
         </is>
       </c>
-      <c r="C29" s="0" t="inlineStr"/>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-34wp65c-b</t>
+        </is>
+      </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -19761,7 +19753,7 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>34WP65C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 미게시 · CMS/요청서 라이브였으나 실측 카테고리 리다이렉트(soft-404)</t>
+          <t>34WP65C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -20261,11 +20253,7 @@
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C49" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_en/desktop-monitors/lg-34wp65c-b/</t>
-        </is>
-      </c>
+      <c r="C49" s="0" t="inlineStr"/>
       <c r="D49" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -20277,7 +20265,7 @@
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>34WP65C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>34WP65C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · STG · 라이브 미게시(실측 404)</t>
         </is>
       </c>
     </row>
@@ -20651,11 +20639,7 @@
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C64" s="0" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_fr/moniteurs-de-bureau/lg-34wp65c-b/</t>
-        </is>
-      </c>
+      <c r="C64" s="0" t="inlineStr"/>
       <c r="D64" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -20667,7 +20651,7 @@
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>34WP65C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>34WP65C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · STG · 라이브 미게시(실측 404)</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20921,11 @@
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C75" s="0" t="inlineStr"/>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-34wp65c-b</t>
+        </is>
+      </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -20949,7 +20937,7 @@
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>34WP65C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 미게시 · CMS/요청서 라이브였으나 실측 카테고리 리다이렉트(soft-404)</t>
+          <t>34WP65C-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -16036,7 +16036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="203" min="1" max="1"/>
@@ -17470,7 +17470,7 @@
     <row r="59">
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>US : US (en)</t>
+          <t>ZA : ZA (en)</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr"/>
@@ -17484,50 +17484,6 @@
         <v>1</v>
       </c>
       <c r="G59" s="0" t="inlineStr">
-        <is>
-          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="0" t="inlineStr">
-        <is>
-          <t>US : US (en)</t>
-        </is>
-      </c>
-      <c r="C60" s="0" t="inlineStr"/>
-      <c r="D60" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E60" s="0" t="inlineStr"/>
-      <c r="F60" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="0" t="inlineStr">
-        <is>
-          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="0" t="inlineStr">
-        <is>
-          <t>ZA : ZA (en)</t>
-        </is>
-      </c>
-      <c r="C61" s="0" t="inlineStr"/>
-      <c r="D61" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E61" s="0" t="inlineStr"/>
-      <c r="F61" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="0" t="inlineStr">
         <is>
           <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
         </is>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -35,10 +35,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="68">
+  <fonts count="69">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -394,6 +395,13 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -476,7 +484,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border/>
     <border>
       <left style="thin">
@@ -604,11 +612,19 @@
         <color rgb="FF000000"/>
       </left>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="289">
+  <cellXfs count="292">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1184,9 +1200,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -33009,7 +33029,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="34.5" customWidth="1" style="203" min="3" max="3"/>
@@ -33147,9 +33167,11 @@
           <t>GNB 미반영</t>
         </is>
       </c>
-      <c r="F10" s="270" t="n"/>
+      <c r="F10" s="289" t="n">
+        <v>46211</v>
+      </c>
       <c r="G10" s="177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
@@ -33158,109 +33180,123 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="267" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CA : CA (en)</t>
+        </is>
+      </c>
+      <c r="C11" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F11" s="291" t="n">
+        <v>46211</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>evo 반영 · Hyper GNB 미노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="267" t="inlineStr">
         <is>
           <t>CA : CA (fr)</t>
         </is>
       </c>
-      <c r="C11" s="268" t="inlineStr">
+      <c r="C12" s="268" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/moniteurs/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D11" s="285" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E11" s="269" t="inlineStr">
+      <c r="D12" s="285" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E12" s="269" t="inlineStr">
         <is>
           <t>GNB 미반영</t>
         </is>
       </c>
-      <c r="F11" s="270" t="n"/>
-      <c r="G11" s="177" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="0" t="inlineStr">
+      <c r="F12" s="289" t="n">
+        <v>46211</v>
+      </c>
+      <c r="G12" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="271" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CA : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C13" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F13" s="291" t="n">
+        <v>46211</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>evo 반영 · Hyper GNB 미노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="271" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C12" s="272" t="inlineStr">
+      <c r="C14" s="272" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/monitore/hyper-mini-led-ultragear-gaming-monitore/</t>
         </is>
       </c>
-      <c r="D12" s="273" t="inlineStr">
+      <c r="D14" s="273" t="inlineStr">
         <is>
           <t>법인리뷰</t>
         </is>
       </c>
-      <c r="E12" s="288" t="n"/>
-      <c r="F12" s="274" t="n"/>
-      <c r="G12" s="185" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>FAQ 미게시 (evo·Hyper)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="267" t="inlineStr">
-        <is>
-          <t>ES : ES (es)</t>
-        </is>
-      </c>
-      <c r="C13" s="268" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/es/monitores/monitores-ultragear-evo/</t>
-        </is>
-      </c>
-      <c r="D13" s="273" t="inlineStr">
-        <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E13" s="288" t="n"/>
-      <c r="F13" s="270" t="n"/>
-      <c r="G13" s="177" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t>evo FAQ 미게시 · Hyper 페이지/FAQ 게시 대기</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="267" t="inlineStr">
-        <is>
-          <t>FR : FR (fr)</t>
-        </is>
-      </c>
-      <c r="C14" s="268" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/moniteurs/hyper-mini-led-gaming-monitor/</t>
-        </is>
-      </c>
-      <c r="D14" s="273" t="inlineStr">
-        <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
       <c r="E14" s="288" t="n"/>
-      <c r="F14" s="270" t="n"/>
-      <c r="G14" s="177" t="n">
+      <c r="F14" s="274" t="n"/>
+      <c r="G14" s="185" t="n">
         <v>2</v>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -33272,43 +33308,39 @@
     <row r="15">
       <c r="B15" s="267" t="inlineStr">
         <is>
-          <t>IT : IT (it)</t>
+          <t>ES : ES (es)</t>
         </is>
       </c>
       <c r="C15" s="268" t="inlineStr">
         <is>
-          <t>https://www.lg.com/it/monitor/hyper-mini-led-gaming-monitor/</t>
-        </is>
-      </c>
-      <c r="D15" s="247" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E15" s="273" t="inlineStr">
-        <is>
-          <t>GNB 미반영</t>
-        </is>
-      </c>
-      <c r="F15" s="275" t="n"/>
+          <t>https://www.lg.com/es/monitores/monitores-ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D15" s="273" t="inlineStr">
+        <is>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E15" s="288" t="n"/>
+      <c r="F15" s="270" t="n"/>
       <c r="G15" s="177" t="n">
         <v>2</v>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
+          <t>evo FAQ 미게시 · Hyper 페이지/FAQ 게시 대기</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="267" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>FR : FR (fr)</t>
         </is>
       </c>
       <c r="C16" s="268" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp/monitors/ultragear-evo/</t>
+          <t>https://www.lg.com/fr/moniteurs/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
       <c r="D16" s="273" t="inlineStr">
@@ -33316,30 +33348,26 @@
           <t>법인리뷰</t>
         </is>
       </c>
-      <c r="E16" s="288" t="inlineStr">
-        <is>
-          <t>미게시(법인리뷰) · STG 경로 기준</t>
-        </is>
-      </c>
-      <c r="F16" s="275" t="n"/>
+      <c r="E16" s="288" t="n"/>
+      <c r="F16" s="270" t="n"/>
       <c r="G16" s="177" t="n">
         <v>2</v>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>페이지/FAQ 게시 대기 (evo·Hyper)</t>
+          <t>FAQ 미게시 (evo·Hyper)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="267" t="inlineStr">
         <is>
-          <t>NL : NL (nl)</t>
+          <t>IT : IT (it)</t>
         </is>
       </c>
       <c r="C17" s="268" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nl/monitoren/hyper-mini-led-gaming-monitor/</t>
+          <t>https://www.lg.com/it/monitor/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
       <c r="D17" s="247" t="inlineStr">
@@ -33347,43 +33375,47 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E17" s="288" t="n"/>
-      <c r="F17" s="270" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
+      <c r="E17" s="273" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F17" s="275" t="n"/>
       <c r="G17" s="177" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="0" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="267" t="inlineStr">
-        <is>
-          <t>SE : SE (sv)</t>
-        </is>
-      </c>
-      <c r="C18" s="268" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/se/monitor/hyper-mini-led-gaming-monitor/</t>
-        </is>
-      </c>
-      <c r="D18" s="247" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E18" s="273" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C18" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>GNB 미반영</t>
         </is>
       </c>
-      <c r="F18" s="275" t="n"/>
-      <c r="G18" s="177" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="0" t="inlineStr">
+      <c r="F18" s="291" t="n"/>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
         </is>
@@ -33392,22 +33424,22 @@
     <row r="19">
       <c r="B19" s="267" t="inlineStr">
         <is>
-          <t>UK : UK (en)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C19" s="268" t="inlineStr">
         <is>
-          <t>https://www.lg.com/uk/monitors/ultragear-evo/</t>
-        </is>
-      </c>
-      <c r="D19" s="247" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E19" s="273" t="inlineStr">
-        <is>
-          <t>GNB 미반영</t>
+          <t>https://www.lg.com/jp/monitors/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D19" s="273" t="inlineStr">
+        <is>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E19" s="288" t="inlineStr">
+        <is>
+          <t>미게시(법인리뷰) · STG 경로 기준</t>
         </is>
       </c>
       <c r="F19" s="275" t="n"/>
@@ -33415,6 +33447,186 @@
         <v>2</v>
       </c>
       <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>페이지/FAQ 게시 대기 (evo·Hyper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="267" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C20" s="268" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/hyper-mini-led-gaming-monitor/</t>
+        </is>
+      </c>
+      <c r="D20" s="247" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E20" s="288" t="n"/>
+      <c r="F20" s="289" t="n">
+        <v>46218</v>
+      </c>
+      <c r="G20" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="0" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C21" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F21" s="291" t="n">
+        <v>46218</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="267" t="inlineStr">
+        <is>
+          <t>SE : SE (sv)</t>
+        </is>
+      </c>
+      <c r="C22" s="268" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/monitor/hyper-mini-led-gaming-monitor/</t>
+        </is>
+      </c>
+      <c r="D22" s="247" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E22" s="273" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F22" s="275" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G22" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SE : SE (sv)</t>
+        </is>
+      </c>
+      <c r="C23" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/monitor/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F23" s="291" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="267" t="inlineStr">
+        <is>
+          <t>UK : UK (en)</t>
+        </is>
+      </c>
+      <c r="C24" s="268" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D24" s="247" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E24" s="273" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F24" s="275" t="n">
+        <v>46227</v>
+      </c>
+      <c r="G24" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>evo 반영 · Hyper GNB 미노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>UK : UK (en)</t>
+        </is>
+      </c>
+      <c r="C25" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/hyper-mini-led-gaming-monitor/</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F25" s="291" t="n">
+        <v>46227</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
@@ -33425,14 +33637,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33444,7 +33662,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="22.75" customWidth="1" style="203" min="1" max="1"/>
@@ -33560,7 +33778,7 @@
         </is>
       </c>
       <c r="F9" s="123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
@@ -33569,30 +33787,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="261" t="inlineStr">
-        <is>
-          <t>CA : CA (en)</t>
-        </is>
-      </c>
-      <c r="C10" s="277" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_en/monitors/gaming/</t>
-        </is>
-      </c>
-      <c r="D10" s="278" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E10" s="123" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="F10" s="123" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C10" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/monitors/ultragear-gaming-oled/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -33601,12 +33819,12 @@
     <row r="11">
       <c r="B11" s="261" t="inlineStr">
         <is>
-          <t>CA : CA (fr)</t>
+          <t>CA : CA (en)</t>
         </is>
       </c>
       <c r="C11" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/</t>
+          <t>https://www.lg.com/ca_en/monitors/gaming/</t>
         </is>
       </c>
       <c r="D11" s="278" t="inlineStr">
@@ -33614,13 +33832,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E11" s="123" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
+      <c r="E11" s="200" t="n">
+        <v>46212</v>
       </c>
       <c r="F11" s="123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
@@ -33629,30 +33845,28 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="261" t="inlineStr">
-        <is>
-          <t>DE : DE (de)</t>
-        </is>
-      </c>
-      <c r="C12" s="277" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/de/monitore/gaming/</t>
-        </is>
-      </c>
-      <c r="D12" s="278" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E12" s="123" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="F12" s="123" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" s="0" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CA : CA (en)</t>
+        </is>
+      </c>
+      <c r="C12" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/ultragear-gaming-oled/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E12" s="291" t="n">
+        <v>46212</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -33661,68 +33875,68 @@
     <row r="13">
       <c r="B13" s="261" t="inlineStr">
         <is>
-          <t>ES : ES (es)</t>
+          <t>CA : CA (fr)</t>
         </is>
       </c>
       <c r="C13" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es/monitores/monitores-ultragear-oled-gaming/</t>
-        </is>
-      </c>
-      <c r="D13" s="279" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E13" s="123" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
+          <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/</t>
+        </is>
+      </c>
+      <c r="D13" s="278" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E13" s="200" t="n">
+        <v>46212</v>
       </c>
       <c r="F13" s="123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>2026 답변 갱신 미반영 (Gaming·OLED Gaming)</t>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="261" t="inlineStr">
-        <is>
-          <t>FR : FR (fr)</t>
-        </is>
-      </c>
-      <c r="C14" s="277" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/moniteurs/gaming/</t>
-        </is>
-      </c>
-      <c r="D14" s="279" t="inlineStr">
-        <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E14" s="123" t="inlineStr"/>
-      <c r="F14" s="123" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t>2026 답변 갱신 미반영 (Gaming·OLED Gaming)</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CA : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C14" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/ultragear-gaming-oled/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E14" s="291" t="n">
+        <v>46212</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="261" t="inlineStr">
         <is>
-          <t>IT : IT (it)</t>
+          <t>DE : DE (de)</t>
         </is>
       </c>
       <c r="C15" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/it/monitor/gaming/</t>
+          <t>https://www.lg.com/de/monitore/gaming/</t>
         </is>
       </c>
       <c r="D15" s="278" t="inlineStr">
@@ -33736,7 +33950,7 @@
         </is>
       </c>
       <c r="F15" s="123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
@@ -33745,30 +33959,30 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="261" t="inlineStr">
-        <is>
-          <t>JP : JP (ja)</t>
-        </is>
-      </c>
-      <c r="C16" s="277" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/jp/monitors/gaming-monitors/</t>
-        </is>
-      </c>
-      <c r="D16" s="278" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E16" s="123" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C16" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/monitore/ultragear-gaming-oled/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="F16" s="123" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="0" t="inlineStr">
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -33777,94 +33991,390 @@
     <row r="17">
       <c r="B17" s="261" t="inlineStr">
         <is>
-          <t>NL : NL (nl)</t>
+          <t>ES : ES (es)</t>
         </is>
       </c>
       <c r="C17" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-monitoren/</t>
-        </is>
-      </c>
-      <c r="D17" s="278" t="inlineStr">
+          <t>https://www.lg.com/es/monitores/monitores-ultragear-oled-gaming/</t>
+        </is>
+      </c>
+      <c r="D17" s="279" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F17" s="123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
+          <t>2026 답변 갱신 미반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="270" t="inlineStr">
-        <is>
-          <t>SE : SE (sv)</t>
-        </is>
-      </c>
-      <c r="C18" s="277" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/se/monitor/ultragear-gaming/</t>
-        </is>
-      </c>
-      <c r="D18" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E18" s="123" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="F18" s="123" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C18" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/monitores/monitores-ultragear-gaming/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026 답변 갱신 미반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="270" t="inlineStr">
-        <is>
-          <t>UK : UK (en)</t>
+      <c r="B19" s="261" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
         </is>
       </c>
       <c r="C19" s="277" t="inlineStr">
         <is>
-          <t>https://www.lg.com/uk/monitors/gaming/</t>
-        </is>
-      </c>
-      <c r="D19" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E19" s="123" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
+          <t>https://www.lg.com/fr/moniteurs/gaming/</t>
+        </is>
+      </c>
+      <c r="D19" s="279" t="inlineStr">
+        <is>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E19" s="123" t="inlineStr"/>
       <c r="F19" s="123" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
+          <t>2026 답변 갱신 미반영 (Gaming·OLED Gaming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="261" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C20" s="277" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/gaming/</t>
+        </is>
+      </c>
+      <c r="D20" s="278" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E20" s="123" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="F20" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C21" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/ultragear-gaming-oled/</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="261" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C22" s="277" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/gaming-monitors/</t>
+        </is>
+      </c>
+      <c r="D22" s="278" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E22" s="123" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="F22" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C23" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/ultragear-oled-gaming-monitors/</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="261" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C24" s="277" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-monitoren/</t>
+        </is>
+      </c>
+      <c r="D24" s="278" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E24" s="200" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F24" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C25" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultragear-gaming-oled/</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E25" s="291" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="270" t="inlineStr">
+        <is>
+          <t>SE : SE (sv)</t>
+        </is>
+      </c>
+      <c r="C26" s="277" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/monitor/ultragear-gaming/</t>
+        </is>
+      </c>
+      <c r="D26" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E26" s="200" t="n">
+        <v>46195</v>
+      </c>
+      <c r="F26" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SE : SE (sv)</t>
+        </is>
+      </c>
+      <c r="C27" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/monitor/ultragear-gaming-oled/</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E27" s="291" t="n">
+        <v>46195</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="270" t="inlineStr">
+        <is>
+          <t>UK : UK (en)</t>
+        </is>
+      </c>
+      <c r="C28" s="277" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/gaming/</t>
+        </is>
+      </c>
+      <c r="D28" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E28" s="200" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F28" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>UK : UK (en)</t>
+        </is>
+      </c>
+      <c r="C29" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/oled-monitors/</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E29" s="291" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -35,9 +35,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="69">
     <font>
@@ -33029,7 +33028,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="34.5" customWidth="1" style="203" min="3" max="3"/>
@@ -33125,7 +33124,7 @@
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C9" s="268" t="inlineStr">
+      <c r="C9" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/monitors/hyper-mini-led-gaming-monitor/</t>
         </is>
@@ -33138,7 +33137,7 @@
       <c r="E9" s="287" t="n"/>
       <c r="F9" s="270" t="n"/>
       <c r="G9" s="177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
@@ -33147,211 +33146,208 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="267" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C10" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/monitors/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>FAQ 미게시 (evo·Hyper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="267" t="inlineStr">
         <is>
           <t>CA : CA (en)</t>
         </is>
       </c>
-      <c r="C10" s="268" t="inlineStr">
+      <c r="C11" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/monitors/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D10" s="285" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E10" s="269" t="inlineStr">
+      <c r="D11" s="285" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E11" s="269" t="inlineStr">
         <is>
           <t>GNB 미반영</t>
         </is>
       </c>
-      <c r="F10" s="289" t="n">
+      <c r="F11" s="289" t="n">
         <v>46211</v>
       </c>
-      <c r="G10" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
+      <c r="G11" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>CA : CA (en)</t>
         </is>
       </c>
-      <c r="C11" s="290" t="inlineStr">
+      <c r="C12" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/monitors/ultragear-evo/</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>GNB 미반영</t>
         </is>
       </c>
-      <c r="F11" s="291" t="n">
+      <c r="F12" s="291" t="n">
         <v>46211</v>
       </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="267" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="267" t="inlineStr">
         <is>
           <t>CA : CA (fr)</t>
         </is>
       </c>
-      <c r="C12" s="268" t="inlineStr">
+      <c r="C13" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/moniteurs/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D12" s="285" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E12" s="269" t="inlineStr">
+      <c r="D13" s="285" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E13" s="269" t="inlineStr">
         <is>
           <t>GNB 미반영</t>
         </is>
       </c>
-      <c r="F12" s="289" t="n">
+      <c r="F13" s="289" t="n">
         <v>46211</v>
       </c>
-      <c r="G12" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="0" t="inlineStr">
+      <c r="G13" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>CA : CA (fr)</t>
         </is>
       </c>
-      <c r="C13" s="290" t="inlineStr">
+      <c r="C14" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/moniteurs/ultragear-evo/</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>GNB 미반영</t>
         </is>
       </c>
-      <c r="F13" s="291" t="n">
+      <c r="F14" s="291" t="n">
         <v>46211</v>
       </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="G14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="271" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="271" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C14" s="272" t="inlineStr">
+      <c r="C15" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/monitore/hyper-mini-led-ultragear-gaming-monitore/</t>
         </is>
       </c>
-      <c r="D14" s="273" t="inlineStr">
+      <c r="D15" s="273" t="inlineStr">
         <is>
           <t>법인리뷰</t>
         </is>
       </c>
-      <c r="E14" s="288" t="n"/>
-      <c r="F14" s="274" t="n"/>
-      <c r="G14" s="185" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="0" t="inlineStr">
+      <c r="E15" s="288" t="n"/>
+      <c r="F15" s="274" t="n"/>
+      <c r="G15" s="185" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>FAQ 미게시 (evo·Hyper)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="267" t="inlineStr">
-        <is>
-          <t>ES : ES (es)</t>
-        </is>
-      </c>
-      <c r="C15" s="268" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/es/monitores/monitores-ultragear-evo/</t>
-        </is>
-      </c>
-      <c r="D15" s="273" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C16" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/monitore/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>법인리뷰</t>
         </is>
       </c>
-      <c r="E15" s="288" t="n"/>
-      <c r="F15" s="270" t="n"/>
-      <c r="G15" s="177" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="0" t="inlineStr">
-        <is>
-          <t>evo FAQ 미게시 · Hyper 페이지/FAQ 게시 대기</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="267" t="inlineStr">
-        <is>
-          <t>FR : FR (fr)</t>
-        </is>
-      </c>
-      <c r="C16" s="268" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/moniteurs/hyper-mini-led-gaming-monitor/</t>
-        </is>
-      </c>
-      <c r="D16" s="273" t="inlineStr">
-        <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E16" s="288" t="n"/>
-      <c r="F16" s="270" t="n"/>
-      <c r="G16" s="177" t="n">
-        <v>2</v>
+      <c r="F16" s="291" t="n"/>
+      <c r="G16" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
@@ -33362,105 +33358,91 @@
     <row r="17">
       <c r="B17" s="267" t="inlineStr">
         <is>
-          <t>IT : IT (it)</t>
-        </is>
-      </c>
-      <c r="C17" s="268" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/monitor/hyper-mini-led-gaming-monitor/</t>
-        </is>
-      </c>
-      <c r="D17" s="247" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E17" s="273" t="inlineStr">
-        <is>
-          <t>GNB 미반영</t>
-        </is>
-      </c>
-      <c r="F17" s="275" t="n"/>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C17" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/monitores/monitores-ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D17" s="273" t="inlineStr">
+        <is>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E17" s="288" t="n"/>
+      <c r="F17" s="270" t="n"/>
       <c r="G17" s="177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
+          <t>evo FAQ 미게시 · Hyper 페이지/FAQ 게시 대기</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>IT : IT (it)</t>
+      <c r="B18" s="267" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
         </is>
       </c>
       <c r="C18" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/it/monitor/ultragear-evo/</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>GNB 미반영</t>
-        </is>
-      </c>
-      <c r="F18" s="291" t="n"/>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
+          <t>https://www.lg.com/fr/moniteurs/hyper-mini-led-gaming-monitor/</t>
+        </is>
+      </c>
+      <c r="D18" s="273" t="inlineStr">
+        <is>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E18" s="288" t="n"/>
+      <c r="F18" s="270" t="n"/>
+      <c r="G18" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>FAQ 미게시 (evo·Hyper)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="267" t="inlineStr">
-        <is>
-          <t>JP : JP (ja)</t>
-        </is>
-      </c>
-      <c r="C19" s="268" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/jp/monitors/ultragear-evo/</t>
-        </is>
-      </c>
-      <c r="D19" s="273" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C19" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>법인리뷰</t>
         </is>
       </c>
-      <c r="E19" s="288" t="inlineStr">
-        <is>
-          <t>미게시(법인리뷰) · STG 경로 기준</t>
-        </is>
-      </c>
-      <c r="F19" s="275" t="n"/>
-      <c r="G19" s="177" t="n">
-        <v>2</v>
+      <c r="G19" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>페이지/FAQ 게시 대기 (evo·Hyper)</t>
+          <t>FAQ 미게시 (evo·Hyper)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="267" t="inlineStr">
         <is>
-          <t>NL : NL (nl)</t>
-        </is>
-      </c>
-      <c r="C20" s="268" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/nl/monitoren/hyper-mini-led-gaming-monitor/</t>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C20" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
       <c r="D20" s="247" t="inlineStr">
@@ -33468,165 +33450,258 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E20" s="288" t="n"/>
-      <c r="F20" s="289" t="n">
-        <v>46218</v>
-      </c>
+      <c r="E20" s="273" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F20" s="275" t="n"/>
       <c r="G20" s="177" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="0" t="n"/>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>NL : NL (nl)</t>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
         </is>
       </c>
       <c r="C21" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nl/monitoren/ultragear-evo/</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F21" s="291" t="n">
-        <v>46218</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
+          <t>https://www.lg.com/it/monitor/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>GNB 미반영</t>
+        </is>
+      </c>
+      <c r="F21" s="291" t="n"/>
+      <c r="G21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="267" t="inlineStr">
         <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C22" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/monitors/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D22" s="273" t="inlineStr">
+        <is>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E22" s="288" t="inlineStr">
+        <is>
+          <t>미게시(법인리뷰) · STG 경로 기준</t>
+        </is>
+      </c>
+      <c r="F22" s="275" t="n"/>
+      <c r="G22" s="177" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>페이지/FAQ 게시 대기 (evo·Hyper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="267" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C23" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/hyper-mini-led-gaming-monitor/</t>
+        </is>
+      </c>
+      <c r="D23" s="247" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E23" s="288" t="n"/>
+      <c r="F23" s="289" t="n">
+        <v>46218</v>
+      </c>
+      <c r="G23" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="0" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C24" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultragear-evo/</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F24" s="291" t="n">
+        <v>46218</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="267" t="inlineStr">
+        <is>
           <t>SE : SE (sv)</t>
         </is>
       </c>
-      <c r="C22" s="268" t="inlineStr">
+      <c r="C25" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/se/monitor/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D22" s="247" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E22" s="273" t="inlineStr">
+      <c r="D25" s="247" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E25" s="273" t="inlineStr">
         <is>
           <t>GNB 미반영</t>
         </is>
       </c>
-      <c r="F22" s="275" t="n">
+      <c r="F25" s="275" t="n">
         <v>46195</v>
       </c>
-      <c r="G22" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
+      <c r="G25" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>SE : SE (sv)</t>
         </is>
       </c>
-      <c r="C23" s="290" t="inlineStr">
+      <c r="C26" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/se/monitor/ultragear-evo/</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>GNB 미반영</t>
         </is>
       </c>
-      <c r="F23" s="291" t="n">
+      <c r="F26" s="291" t="n">
         <v>46195</v>
       </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="G26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>FAQ 라이브 but GNB 미노출 (evo·Hyper)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="267" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="267" t="inlineStr">
         <is>
           <t>UK : UK (en)</t>
         </is>
       </c>
-      <c r="C24" s="268" t="inlineStr">
+      <c r="C27" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/monitors/ultragear-evo/</t>
         </is>
       </c>
-      <c r="D24" s="247" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E24" s="273" t="inlineStr">
+      <c r="D27" s="247" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E27" s="273" t="inlineStr">
         <is>
           <t>GNB 미반영</t>
         </is>
       </c>
-      <c r="F24" s="275" t="n">
+      <c r="F27" s="275" t="n">
         <v>46227</v>
       </c>
-      <c r="G24" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="0" t="inlineStr">
+      <c r="G27" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>UK : UK (en)</t>
         </is>
       </c>
-      <c r="C25" s="290" t="inlineStr">
+      <c r="C28" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/monitors/hyper-mini-led-gaming-monitor/</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>GNB 미반영</t>
         </is>
       </c>
-      <c r="F25" s="291" t="n">
+      <c r="F28" s="291" t="n">
         <v>46227</v>
       </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="G28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>evo 반영 · Hyper GNB 미노출</t>
         </is>
@@ -33637,20 +33712,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33762,7 +33840,7 @@
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C9" s="277" t="inlineStr">
+      <c r="C9" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/monitors/ultragear-gaming/</t>
         </is>
@@ -33787,7 +33865,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
@@ -33797,20 +33875,20 @@
           <t>https://www.lg.com/au/monitors/ultragear-gaming-oled/</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -33822,7 +33900,7 @@
           <t>CA : CA (en)</t>
         </is>
       </c>
-      <c r="C11" s="277" t="inlineStr">
+      <c r="C11" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/monitors/gaming/</t>
         </is>
@@ -33845,7 +33923,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>CA : CA (en)</t>
         </is>
@@ -33855,7 +33933,7 @@
           <t>https://www.lg.com/ca_en/monitors/ultragear-gaming-oled/</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -33863,10 +33941,10 @@
       <c r="E12" s="291" t="n">
         <v>46212</v>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -33878,7 +33956,7 @@
           <t>CA : CA (fr)</t>
         </is>
       </c>
-      <c r="C13" s="277" t="inlineStr">
+      <c r="C13" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/moniteurs/de-jeu/</t>
         </is>
@@ -33901,7 +33979,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>CA : CA (fr)</t>
         </is>
@@ -33911,7 +33989,7 @@
           <t>https://www.lg.com/ca_fr/moniteurs/ultragear-gaming-oled/</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -33919,10 +33997,10 @@
       <c r="E14" s="291" t="n">
         <v>46212</v>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -33934,7 +34012,7 @@
           <t>DE : DE (de)</t>
         </is>
       </c>
-      <c r="C15" s="277" t="inlineStr">
+      <c r="C15" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/monitore/gaming/</t>
         </is>
@@ -33959,7 +34037,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>DE : DE (de)</t>
         </is>
@@ -33969,20 +34047,20 @@
           <t>https://www.lg.com/de/monitore/ultragear-gaming-oled/</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -33994,7 +34072,7 @@
           <t>ES : ES (es)</t>
         </is>
       </c>
-      <c r="C17" s="277" t="inlineStr">
+      <c r="C17" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/monitores/monitores-ultragear-oled-gaming/</t>
         </is>
@@ -34019,7 +34097,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>ES : ES (es)</t>
         </is>
@@ -34029,20 +34107,20 @@
           <t>https://www.lg.com/es/monitores/monitores-ultragear-gaming/</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>2026 답변 갱신 미반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -34054,7 +34132,7 @@
           <t>FR : FR (fr)</t>
         </is>
       </c>
-      <c r="C19" s="277" t="inlineStr">
+      <c r="C19" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/fr/moniteurs/gaming/</t>
         </is>
@@ -34080,7 +34158,7 @@
           <t>IT : IT (it)</t>
         </is>
       </c>
-      <c r="C20" s="277" t="inlineStr">
+      <c r="C20" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/monitor/gaming/</t>
         </is>
@@ -34105,7 +34183,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>IT : IT (it)</t>
         </is>
@@ -34115,20 +34193,20 @@
           <t>https://www.lg.com/it/monitor/ultragear-gaming-oled/</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -34140,7 +34218,7 @@
           <t>JP : JP (ja)</t>
         </is>
       </c>
-      <c r="C22" s="277" t="inlineStr">
+      <c r="C22" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/monitors/gaming-monitors/</t>
         </is>
@@ -34165,7 +34243,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>JP : JP (ja)</t>
         </is>
@@ -34175,20 +34253,20 @@
           <t>https://www.lg.com/jp/monitors/ultragear-oled-gaming-monitors/</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -34200,7 +34278,7 @@
           <t>NL : NL (nl)</t>
         </is>
       </c>
-      <c r="C24" s="277" t="inlineStr">
+      <c r="C24" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/nl/monitoren/ultragear-gaming-monitoren/</t>
         </is>
@@ -34223,7 +34301,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>NL : NL (nl)</t>
         </is>
@@ -34233,7 +34311,7 @@
           <t>https://www.lg.com/nl/monitoren/ultragear-gaming-oled/</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -34241,10 +34319,10 @@
       <c r="E25" s="291" t="n">
         <v>46209</v>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -34256,7 +34334,7 @@
           <t>SE : SE (sv)</t>
         </is>
       </c>
-      <c r="C26" s="277" t="inlineStr">
+      <c r="C26" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/se/monitor/ultragear-gaming/</t>
         </is>
@@ -34279,7 +34357,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>SE : SE (sv)</t>
         </is>
@@ -34289,7 +34367,7 @@
           <t>https://www.lg.com/se/monitor/ultragear-gaming-oled/</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -34297,10 +34375,10 @@
       <c r="E27" s="291" t="n">
         <v>46195</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -34312,7 +34390,7 @@
           <t>UK : UK (en)</t>
         </is>
       </c>
-      <c r="C28" s="277" t="inlineStr">
+      <c r="C28" s="290" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/monitors/gaming/</t>
         </is>
@@ -34335,7 +34413,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>UK : UK (en)</t>
         </is>
@@ -34345,7 +34423,7 @@
           <t>https://www.lg.com/uk/monitors/oled-monitors/</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -34353,10 +34431,10 @@
       <c r="E29" s="291" t="n">
         <v>46213</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
@@ -34364,16 +34442,27 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -4872,12 +4872,12 @@
       </c>
       <c r="C6" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es/laptops</t>
+          <t>https://www.lg.com/es/portatiles/todos-los-portatiles/</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F6" s="0" t="n">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F7" s="0" t="n">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F18" s="0" t="n">
@@ -33739,10 +33739,12 @@
       </c>
       <c r="D43" s="263" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E43" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E43" s="200" t="n">
+        <v>46246</v>
+      </c>
       <c r="F43" s="123" t="n">
         <v>1</v>
       </c>
@@ -33761,10 +33763,12 @@
       </c>
       <c r="D44" s="263" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E44" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E44" s="200" t="n">
+        <v>46246</v>
+      </c>
       <c r="F44" s="123" t="n">
         <v>1</v>
       </c>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -5127,7 +5127,7 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F16" s="0" t="n">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F20" s="0" t="n">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -5272,12 +5272,12 @@
       </c>
       <c r="C22" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/de/business/</t>
+          <t>https://www.lg.com/de/business/notebooks/gram/</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F22" s="0" t="n">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -5322,12 +5322,12 @@
       </c>
       <c r="C24" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fr/business/informatique/pc-portables-professionnels/</t>
+          <t>https://www.lg.com/fr/business/moniteurs-pcs/laptops/pc-portables-professionnels/</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F24" s="0" t="n">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -19586,7 +19586,7 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr"/>
@@ -19612,7 +19612,7 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr"/>
@@ -19638,7 +19638,7 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr"/>
@@ -19660,7 +19660,7 @@
       <c r="C7" s="0" t="inlineStr"/>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr"/>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr"/>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr"/>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr"/>
@@ -19764,7 +19764,7 @@
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr"/>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr"/>
@@ -19816,7 +19816,7 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr"/>
@@ -19868,7 +19868,7 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr"/>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr"/>
@@ -19920,7 +19920,7 @@
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr"/>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr"/>
@@ -19998,7 +19998,7 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr"/>
@@ -20024,7 +20024,7 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr"/>
@@ -20050,7 +20050,7 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr"/>
@@ -20072,7 +20072,7 @@
       <c r="C23" s="0" t="inlineStr"/>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr"/>
@@ -20094,7 +20094,7 @@
       <c r="C24" s="0" t="inlineStr"/>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr"/>
@@ -20120,7 +20120,7 @@
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr"/>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr"/>
@@ -20172,7 +20172,7 @@
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr"/>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr"/>
@@ -20250,7 +20250,7 @@
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr"/>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr"/>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr"/>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr"/>
@@ -20354,7 +20354,7 @@
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr"/>
@@ -20380,7 +20380,7 @@
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr"/>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr"/>
@@ -20428,7 +20428,7 @@
       <c r="C37" s="0" t="inlineStr"/>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr"/>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E38" s="0" t="inlineStr"/>
@@ -20480,7 +20480,7 @@
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E39" s="0" t="inlineStr"/>
@@ -20506,7 +20506,7 @@
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E40" s="0" t="inlineStr"/>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E41" s="0" t="inlineStr"/>
@@ -20558,7 +20558,7 @@
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E42" s="0" t="inlineStr"/>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E43" s="0" t="inlineStr"/>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E44" s="0" t="inlineStr"/>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E45" s="0" t="inlineStr"/>
@@ -20662,7 +20662,7 @@
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E46" s="0" t="inlineStr"/>
@@ -20688,7 +20688,7 @@
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E47" s="0" t="inlineStr"/>
@@ -20714,7 +20714,7 @@
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E48" s="0" t="inlineStr"/>
@@ -20736,7 +20736,7 @@
       <c r="C49" s="0" t="inlineStr"/>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E49" s="0" t="inlineStr"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E50" s="0" t="inlineStr"/>
@@ -20788,7 +20788,7 @@
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E51" s="0" t="inlineStr"/>
@@ -20814,7 +20814,7 @@
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E52" s="0" t="inlineStr"/>
@@ -20840,7 +20840,7 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E53" s="0" t="inlineStr"/>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E54" s="0" t="inlineStr"/>
@@ -20892,7 +20892,7 @@
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E55" s="0" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E56" s="0" t="inlineStr"/>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E57" s="0" t="inlineStr"/>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E58" s="0" t="inlineStr"/>
@@ -20996,7 +20996,7 @@
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E59" s="0" t="inlineStr"/>
@@ -21022,7 +21022,7 @@
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E60" s="0" t="inlineStr"/>
@@ -21048,7 +21048,7 @@
       </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E61" s="0" t="inlineStr"/>
@@ -21074,7 +21074,7 @@
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E62" s="0" t="inlineStr"/>
@@ -21100,7 +21100,7 @@
       </c>
       <c r="D63" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E63" s="0" t="inlineStr"/>
@@ -21122,7 +21122,7 @@
       <c r="C64" s="0" t="inlineStr"/>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E64" s="0" t="inlineStr"/>
@@ -21148,7 +21148,7 @@
       </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E65" s="0" t="inlineStr"/>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E66" s="0" t="inlineStr"/>
@@ -21200,7 +21200,7 @@
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E67" s="0" t="inlineStr"/>
@@ -21226,7 +21226,7 @@
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E68" s="0" t="inlineStr"/>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E69" s="0" t="inlineStr"/>
@@ -21278,7 +21278,7 @@
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E70" s="0" t="inlineStr"/>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E71" s="0" t="inlineStr"/>
@@ -21330,7 +21330,7 @@
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E72" s="0" t="inlineStr"/>
@@ -21356,7 +21356,7 @@
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E73" s="0" t="inlineStr"/>
@@ -21382,7 +21382,7 @@
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E74" s="0" t="inlineStr"/>
@@ -21408,7 +21408,7 @@
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E75" s="0" t="inlineStr"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="D76" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E76" s="0" t="inlineStr"/>
@@ -21460,7 +21460,7 @@
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E77" s="0" t="inlineStr"/>
@@ -21486,7 +21486,7 @@
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E78" s="0" t="inlineStr"/>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E79" s="0" t="inlineStr"/>
@@ -21538,7 +21538,7 @@
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E80" s="0" t="inlineStr"/>
@@ -21564,7 +21564,7 @@
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E81" s="0" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="D82" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E82" s="0" t="inlineStr"/>
@@ -21616,7 +21616,7 @@
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E83" s="0" t="inlineStr"/>
@@ -21642,7 +21642,7 @@
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E84" s="0" t="inlineStr"/>
@@ -21668,7 +21668,7 @@
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E85" s="0" t="inlineStr"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E86" s="0" t="inlineStr"/>
@@ -21720,7 +21720,7 @@
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E87" s="0" t="inlineStr"/>
@@ -21746,7 +21746,7 @@
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E88" s="0" t="inlineStr"/>
@@ -21772,7 +21772,7 @@
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E89" s="0" t="inlineStr"/>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E90" s="0" t="inlineStr"/>
@@ -21824,7 +21824,7 @@
       </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E91" s="0" t="inlineStr"/>
@@ -21850,7 +21850,7 @@
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E92" s="0" t="inlineStr"/>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E93" s="0" t="inlineStr"/>
@@ -21902,7 +21902,7 @@
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E94" s="0" t="inlineStr"/>
@@ -21928,7 +21928,7 @@
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E95" s="0" t="inlineStr"/>
@@ -21954,7 +21954,7 @@
       </c>
       <c r="D96" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E96" s="0" t="inlineStr"/>
@@ -21980,7 +21980,7 @@
       </c>
       <c r="D97" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E97" s="0" t="inlineStr"/>
@@ -22006,7 +22006,7 @@
       </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E98" s="0" t="inlineStr"/>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E99" s="0" t="inlineStr"/>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E100" s="0" t="inlineStr"/>
@@ -22084,7 +22084,7 @@
       </c>
       <c r="D101" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E101" s="0" t="inlineStr"/>
@@ -22110,7 +22110,7 @@
       </c>
       <c r="D102" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E102" s="0" t="inlineStr"/>
@@ -22136,7 +22136,7 @@
       </c>
       <c r="D103" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E103" s="0" t="inlineStr"/>
@@ -22145,7 +22145,7 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨 · ⚠️ 갤러리 이미지에 어워드 잔존(2026-08-25 실측)</t>
         </is>
       </c>
     </row>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="D104" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E104" s="0" t="inlineStr"/>
@@ -22188,7 +22188,7 @@
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E105" s="0" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="D106" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E106" s="0" t="inlineStr"/>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨 · ⚠️ 갤러리 이미지에 어워드 잔존(2026-08-25 실측)</t>
         </is>
       </c>
     </row>
@@ -22240,7 +22240,7 @@
       </c>
       <c r="D107" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E107" s="0" t="inlineStr"/>
@@ -22266,7 +22266,7 @@
       </c>
       <c r="D108" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E108" s="0" t="inlineStr"/>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="D109" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E109" s="0" t="inlineStr"/>
@@ -22318,7 +22318,7 @@
       </c>
       <c r="D110" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E110" s="0" t="inlineStr"/>
@@ -22344,7 +22344,7 @@
       </c>
       <c r="D111" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E111" s="0" t="inlineStr"/>
@@ -22370,7 +22370,7 @@
       </c>
       <c r="D112" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E112" s="0" t="inlineStr"/>
@@ -22396,7 +22396,7 @@
       </c>
       <c r="D113" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E113" s="0" t="inlineStr"/>
@@ -22422,7 +22422,7 @@
       </c>
       <c r="D114" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E114" s="0" t="inlineStr"/>
@@ -22448,7 +22448,7 @@
       </c>
       <c r="D115" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E115" s="0" t="inlineStr"/>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="D116" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E116" s="0" t="inlineStr"/>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="D117" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E117" s="0" t="inlineStr"/>
@@ -22526,7 +22526,7 @@
       </c>
       <c r="D118" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E118" s="0" t="inlineStr"/>
@@ -22552,7 +22552,7 @@
       </c>
       <c r="D119" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E119" s="0" t="inlineStr"/>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="D120" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E120" s="0" t="inlineStr"/>
@@ -22604,7 +22604,7 @@
       </c>
       <c r="D121" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E121" s="0" t="inlineStr"/>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="D122" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E122" s="0" t="inlineStr"/>
@@ -22656,7 +22656,7 @@
       </c>
       <c r="D123" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E123" s="0" t="inlineStr"/>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="D124" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E124" s="0" t="inlineStr"/>
@@ -22708,7 +22708,7 @@
       </c>
       <c r="D125" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E125" s="0" t="inlineStr"/>
@@ -22734,7 +22734,7 @@
       </c>
       <c r="D126" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E126" s="0" t="inlineStr"/>
@@ -22760,7 +22760,7 @@
       </c>
       <c r="D127" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E127" s="0" t="inlineStr"/>
@@ -22786,7 +22786,7 @@
       </c>
       <c r="D128" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E128" s="0" t="inlineStr"/>
@@ -22812,7 +22812,7 @@
       </c>
       <c r="D129" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E129" s="0" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="D130" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E130" s="0" t="inlineStr"/>
@@ -22864,7 +22864,7 @@
       </c>
       <c r="D131" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E131" s="0" t="inlineStr"/>
@@ -22890,7 +22890,7 @@
       </c>
       <c r="D132" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E132" s="0" t="inlineStr"/>
@@ -22916,7 +22916,7 @@
       </c>
       <c r="D133" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E133" s="0" t="inlineStr"/>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="D134" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E134" s="0" t="inlineStr"/>
@@ -22968,7 +22968,7 @@
       </c>
       <c r="D135" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E135" s="0" t="inlineStr"/>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="D136" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E136" s="0" t="inlineStr"/>
@@ -23020,7 +23020,7 @@
       </c>
       <c r="D137" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E137" s="0" t="inlineStr"/>
@@ -23046,7 +23046,7 @@
       </c>
       <c r="D138" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E138" s="0" t="inlineStr"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="D139" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E139" s="0" t="inlineStr"/>
@@ -23098,7 +23098,7 @@
       </c>
       <c r="D140" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E140" s="0" t="inlineStr"/>
@@ -23124,7 +23124,7 @@
       </c>
       <c r="D141" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E141" s="0" t="inlineStr"/>
@@ -23150,7 +23150,7 @@
       </c>
       <c r="D142" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E142" s="0" t="inlineStr"/>
@@ -23176,7 +23176,7 @@
       </c>
       <c r="D143" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E143" s="0" t="inlineStr"/>
@@ -23202,7 +23202,7 @@
       </c>
       <c r="D144" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E144" s="0" t="inlineStr"/>
@@ -23228,7 +23228,7 @@
       </c>
       <c r="D145" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E145" s="0" t="inlineStr"/>
@@ -23254,7 +23254,7 @@
       </c>
       <c r="D146" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E146" s="0" t="inlineStr"/>
@@ -23280,7 +23280,7 @@
       </c>
       <c r="D147" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E147" s="0" t="inlineStr"/>
@@ -23306,7 +23306,7 @@
       </c>
       <c r="D148" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E148" s="0" t="inlineStr"/>
@@ -23332,7 +23332,7 @@
       </c>
       <c r="D149" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E149" s="0" t="inlineStr"/>
@@ -23358,7 +23358,7 @@
       </c>
       <c r="D150" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E150" s="0" t="inlineStr"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="D151" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E151" s="0" t="inlineStr"/>
@@ -23410,7 +23410,7 @@
       </c>
       <c r="D152" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E152" s="0" t="inlineStr"/>
@@ -23436,7 +23436,7 @@
       </c>
       <c r="D153" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E153" s="0" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="D154" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E154" s="0" t="inlineStr"/>
@@ -23488,7 +23488,7 @@
       </c>
       <c r="D155" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E155" s="0" t="inlineStr"/>
@@ -23514,7 +23514,7 @@
       </c>
       <c r="D156" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E156" s="0" t="inlineStr"/>
@@ -23540,7 +23540,7 @@
       </c>
       <c r="D157" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E157" s="0" t="inlineStr"/>
@@ -23566,7 +23566,7 @@
       </c>
       <c r="D158" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E158" s="0" t="inlineStr"/>
@@ -23592,7 +23592,7 @@
       </c>
       <c r="D159" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E159" s="0" t="inlineStr"/>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="D160" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E160" s="0" t="inlineStr"/>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="D161" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E161" s="0" t="inlineStr"/>
@@ -23670,7 +23670,7 @@
       </c>
       <c r="D162" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E162" s="0" t="inlineStr"/>
@@ -23696,7 +23696,7 @@
       </c>
       <c r="D163" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E163" s="0" t="inlineStr"/>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="D164" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E164" s="0" t="inlineStr"/>
@@ -23748,7 +23748,7 @@
       </c>
       <c r="D165" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E165" s="0" t="inlineStr"/>
@@ -23774,7 +23774,7 @@
       </c>
       <c r="D166" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E166" s="0" t="inlineStr"/>
@@ -23800,7 +23800,7 @@
       </c>
       <c r="D167" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E167" s="0" t="inlineStr"/>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="D168" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E168" s="0" t="inlineStr"/>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="D169" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E169" s="0" t="inlineStr"/>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="D170" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E170" s="0" t="inlineStr"/>
@@ -23904,7 +23904,7 @@
       </c>
       <c r="D171" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E171" s="0" t="inlineStr"/>
@@ -23930,7 +23930,7 @@
       </c>
       <c r="D172" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E172" s="0" t="inlineStr"/>
@@ -23956,7 +23956,7 @@
       </c>
       <c r="D173" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E173" s="0" t="inlineStr"/>
@@ -23982,7 +23982,7 @@
       </c>
       <c r="D174" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E174" s="0" t="inlineStr"/>
@@ -24008,7 +24008,7 @@
       </c>
       <c r="D175" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E175" s="0" t="inlineStr"/>
@@ -24034,7 +24034,7 @@
       </c>
       <c r="D176" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E176" s="0" t="inlineStr"/>
@@ -24060,7 +24060,7 @@
       </c>
       <c r="D177" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E177" s="0" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="D178" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E178" s="0" t="inlineStr"/>
@@ -24112,7 +24112,7 @@
       </c>
       <c r="D179" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E179" s="0" t="inlineStr"/>
@@ -24138,7 +24138,7 @@
       </c>
       <c r="D180" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E180" s="0" t="inlineStr"/>
@@ -24164,7 +24164,7 @@
       </c>
       <c r="D181" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E181" s="0" t="inlineStr"/>
@@ -24190,7 +24190,7 @@
       </c>
       <c r="D182" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E182" s="0" t="inlineStr"/>
@@ -24216,7 +24216,7 @@
       </c>
       <c r="D183" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E183" s="0" t="inlineStr"/>
@@ -24242,7 +24242,7 @@
       </c>
       <c r="D184" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E184" s="0" t="inlineStr"/>
@@ -24268,7 +24268,7 @@
       </c>
       <c r="D185" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E185" s="0" t="inlineStr"/>
@@ -24294,7 +24294,7 @@
       </c>
       <c r="D186" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E186" s="0" t="inlineStr"/>
@@ -24320,7 +24320,7 @@
       </c>
       <c r="D187" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E187" s="0" t="inlineStr"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="D188" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E188" s="0" t="inlineStr"/>
@@ -24372,7 +24372,7 @@
       </c>
       <c r="D189" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E189" s="0" t="inlineStr"/>
@@ -24398,7 +24398,7 @@
       </c>
       <c r="D190" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E190" s="0" t="inlineStr"/>
@@ -24424,7 +24424,7 @@
       </c>
       <c r="D191" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E191" s="0" t="inlineStr"/>
@@ -24450,7 +24450,7 @@
       </c>
       <c r="D192" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E192" s="0" t="inlineStr"/>
@@ -24476,7 +24476,7 @@
       </c>
       <c r="D193" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E193" s="0" t="inlineStr"/>
@@ -24502,7 +24502,7 @@
       </c>
       <c r="D194" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E194" s="0" t="inlineStr"/>
@@ -24528,7 +24528,7 @@
       </c>
       <c r="D195" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E195" s="0" t="inlineStr"/>
@@ -24554,7 +24554,7 @@
       </c>
       <c r="D196" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E196" s="0" t="inlineStr"/>
@@ -24580,7 +24580,7 @@
       </c>
       <c r="D197" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E197" s="0" t="inlineStr"/>
@@ -24606,7 +24606,7 @@
       </c>
       <c r="D198" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E198" s="0" t="inlineStr"/>
@@ -24632,7 +24632,7 @@
       </c>
       <c r="D199" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E199" s="0" t="inlineStr"/>
@@ -24658,7 +24658,7 @@
       </c>
       <c r="D200" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E200" s="0" t="inlineStr"/>
@@ -24684,7 +24684,7 @@
       </c>
       <c r="D201" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E201" s="0" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="D202" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E202" s="0" t="inlineStr"/>
@@ -24736,7 +24736,7 @@
       </c>
       <c r="D203" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E203" s="0" t="inlineStr"/>
@@ -24762,7 +24762,7 @@
       </c>
       <c r="D204" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E204" s="0" t="inlineStr"/>
@@ -24788,7 +24788,7 @@
       </c>
       <c r="D205" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E205" s="0" t="inlineStr"/>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="D206" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E206" s="0" t="inlineStr"/>
@@ -24840,7 +24840,7 @@
       </c>
       <c r="D207" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E207" s="0" t="inlineStr"/>
@@ -24866,7 +24866,7 @@
       </c>
       <c r="D208" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E208" s="0" t="inlineStr"/>
@@ -24892,7 +24892,7 @@
       </c>
       <c r="D209" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E209" s="0" t="inlineStr"/>
@@ -24918,7 +24918,7 @@
       </c>
       <c r="D210" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E210" s="0" t="inlineStr"/>
@@ -24944,7 +24944,7 @@
       </c>
       <c r="D211" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E211" s="0" t="inlineStr"/>
@@ -24970,7 +24970,7 @@
       </c>
       <c r="D212" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E212" s="0" t="inlineStr"/>
@@ -24996,7 +24996,7 @@
       </c>
       <c r="D213" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E213" s="0" t="inlineStr"/>
@@ -25022,7 +25022,7 @@
       </c>
       <c r="D214" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E214" s="0" t="inlineStr"/>
@@ -25048,7 +25048,7 @@
       </c>
       <c r="D215" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E215" s="0" t="inlineStr"/>
@@ -25074,7 +25074,7 @@
       </c>
       <c r="D216" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E216" s="0" t="inlineStr"/>
@@ -25100,7 +25100,7 @@
       </c>
       <c r="D217" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E217" s="0" t="inlineStr"/>
@@ -25126,7 +25126,7 @@
       </c>
       <c r="D218" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E218" s="0" t="inlineStr"/>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="D219" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E219" s="0" t="inlineStr"/>
@@ -25178,7 +25178,7 @@
       </c>
       <c r="D220" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E220" s="0" t="inlineStr"/>
@@ -25204,7 +25204,7 @@
       </c>
       <c r="D221" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E221" s="0" t="inlineStr"/>
@@ -25230,7 +25230,7 @@
       </c>
       <c r="D222" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E222" s="0" t="inlineStr"/>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="D223" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E223" s="0" t="inlineStr"/>
@@ -25282,7 +25282,7 @@
       </c>
       <c r="D224" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E224" s="0" t="inlineStr"/>
@@ -25308,7 +25308,7 @@
       </c>
       <c r="D225" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E225" s="0" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="D226" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E226" s="0" t="inlineStr"/>
@@ -25360,7 +25360,7 @@
       </c>
       <c r="D227" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E227" s="0" t="inlineStr"/>
@@ -25386,7 +25386,7 @@
       </c>
       <c r="D228" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E228" s="0" t="inlineStr"/>
@@ -25412,7 +25412,7 @@
       </c>
       <c r="D229" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E229" s="0" t="inlineStr"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="D230" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E230" s="0" t="inlineStr"/>
@@ -25464,7 +25464,7 @@
       </c>
       <c r="D231" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E231" s="0" t="inlineStr"/>
@@ -25490,7 +25490,7 @@
       </c>
       <c r="D232" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E232" s="0" t="inlineStr"/>
@@ -25516,7 +25516,7 @@
       </c>
       <c r="D233" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E233" s="0" t="inlineStr"/>
@@ -25542,7 +25542,7 @@
       </c>
       <c r="D234" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E234" s="0" t="inlineStr"/>
@@ -25568,7 +25568,7 @@
       </c>
       <c r="D235" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E235" s="0" t="inlineStr"/>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="D236" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E236" s="0" t="inlineStr"/>
@@ -25620,7 +25620,7 @@
       </c>
       <c r="D237" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E237" s="0" t="inlineStr"/>
@@ -25646,7 +25646,7 @@
       </c>
       <c r="D238" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E238" s="0" t="inlineStr"/>
@@ -25672,7 +25672,7 @@
       </c>
       <c r="D239" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E239" s="0" t="inlineStr"/>
@@ -25698,7 +25698,7 @@
       </c>
       <c r="D240" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E240" s="0" t="inlineStr"/>
@@ -25724,7 +25724,7 @@
       </c>
       <c r="D241" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E241" s="0" t="inlineStr"/>
@@ -25750,7 +25750,7 @@
       </c>
       <c r="D242" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E242" s="0" t="inlineStr"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="D243" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E243" s="0" t="inlineStr"/>
@@ -25802,7 +25802,7 @@
       </c>
       <c r="D244" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E244" s="0" t="inlineStr"/>
@@ -25828,7 +25828,7 @@
       </c>
       <c r="D245" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E245" s="0" t="inlineStr"/>
@@ -25854,7 +25854,7 @@
       </c>
       <c r="D246" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E246" s="0" t="inlineStr"/>
@@ -25880,7 +25880,7 @@
       </c>
       <c r="D247" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E247" s="0" t="inlineStr"/>
@@ -25906,7 +25906,7 @@
       </c>
       <c r="D248" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E248" s="0" t="inlineStr"/>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="D249" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E249" s="0" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="D250" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E250" s="0" t="inlineStr"/>
@@ -25984,7 +25984,7 @@
       </c>
       <c r="D251" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E251" s="0" t="inlineStr"/>
@@ -26010,7 +26010,7 @@
       </c>
       <c r="D252" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E252" s="0" t="inlineStr"/>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="D253" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E253" s="0" t="inlineStr"/>
@@ -26062,7 +26062,7 @@
       </c>
       <c r="D254" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E254" s="0" t="inlineStr"/>
@@ -26088,7 +26088,7 @@
       </c>
       <c r="D255" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E255" s="0" t="inlineStr"/>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="D256" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E256" s="0" t="inlineStr"/>
@@ -26140,7 +26140,7 @@
       </c>
       <c r="D257" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E257" s="0" t="inlineStr"/>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="D258" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E258" s="0" t="inlineStr"/>
@@ -26192,7 +26192,7 @@
       </c>
       <c r="D259" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E259" s="0" t="inlineStr"/>
@@ -26218,7 +26218,7 @@
       </c>
       <c r="D260" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E260" s="0" t="inlineStr"/>
@@ -26244,7 +26244,7 @@
       </c>
       <c r="D261" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E261" s="0" t="inlineStr"/>
@@ -26270,7 +26270,7 @@
       </c>
       <c r="D262" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E262" s="0" t="inlineStr"/>
@@ -26296,7 +26296,7 @@
       </c>
       <c r="D263" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E263" s="0" t="inlineStr"/>
@@ -26322,7 +26322,7 @@
       </c>
       <c r="D264" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E264" s="0" t="inlineStr"/>
@@ -26348,7 +26348,7 @@
       </c>
       <c r="D265" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E265" s="0" t="inlineStr"/>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="D266" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E266" s="0" t="inlineStr"/>
@@ -26400,7 +26400,7 @@
       </c>
       <c r="D267" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E267" s="0" t="inlineStr"/>
@@ -26426,7 +26426,7 @@
       </c>
       <c r="D268" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E268" s="0" t="inlineStr"/>
@@ -26452,7 +26452,7 @@
       </c>
       <c r="D269" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E269" s="0" t="inlineStr"/>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="D270" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E270" s="0" t="inlineStr"/>
@@ -26504,7 +26504,7 @@
       </c>
       <c r="D271" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E271" s="0" t="inlineStr"/>
@@ -26530,7 +26530,7 @@
       </c>
       <c r="D272" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E272" s="0" t="inlineStr"/>
@@ -26556,7 +26556,7 @@
       </c>
       <c r="D273" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E273" s="0" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="D274" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E274" s="0" t="inlineStr"/>
@@ -26608,7 +26608,7 @@
       </c>
       <c r="D275" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E275" s="0" t="inlineStr"/>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="D276" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E276" s="0" t="inlineStr"/>
@@ -26660,7 +26660,7 @@
       </c>
       <c r="D277" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E277" s="0" t="inlineStr"/>
@@ -26686,7 +26686,7 @@
       </c>
       <c r="D278" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E278" s="0" t="inlineStr"/>
@@ -26712,7 +26712,7 @@
       </c>
       <c r="D279" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E279" s="0" t="inlineStr"/>
@@ -26738,7 +26738,7 @@
       </c>
       <c r="D280" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E280" s="0" t="inlineStr"/>
@@ -26764,7 +26764,7 @@
       </c>
       <c r="D281" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E281" s="0" t="inlineStr"/>
@@ -26790,7 +26790,7 @@
       </c>
       <c r="D282" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E282" s="0" t="inlineStr"/>
@@ -26816,7 +26816,7 @@
       </c>
       <c r="D283" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E283" s="0" t="inlineStr"/>
@@ -26842,7 +26842,7 @@
       </c>
       <c r="D284" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E284" s="0" t="inlineStr"/>
@@ -26868,7 +26868,7 @@
       </c>
       <c r="D285" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E285" s="0" t="inlineStr"/>
@@ -26894,7 +26894,7 @@
       </c>
       <c r="D286" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E286" s="0" t="inlineStr"/>
@@ -26920,7 +26920,7 @@
       </c>
       <c r="D287" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E287" s="0" t="inlineStr"/>
@@ -26946,7 +26946,7 @@
       </c>
       <c r="D288" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E288" s="0" t="inlineStr"/>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="D289" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E289" s="0" t="inlineStr"/>
@@ -26998,7 +26998,7 @@
       </c>
       <c r="D290" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E290" s="0" t="inlineStr"/>
@@ -27024,7 +27024,7 @@
       </c>
       <c r="D291" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E291" s="0" t="inlineStr"/>
@@ -27050,7 +27050,7 @@
       </c>
       <c r="D292" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E292" s="0" t="inlineStr"/>
@@ -27076,7 +27076,7 @@
       </c>
       <c r="D293" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E293" s="0" t="inlineStr"/>
@@ -27102,7 +27102,7 @@
       </c>
       <c r="D294" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E294" s="0" t="inlineStr"/>
@@ -27128,7 +27128,7 @@
       </c>
       <c r="D295" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E295" s="0" t="inlineStr"/>
@@ -27154,7 +27154,7 @@
       </c>
       <c r="D296" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E296" s="0" t="inlineStr"/>
@@ -27180,7 +27180,7 @@
       </c>
       <c r="D297" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E297" s="0" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="D298" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E298" s="0" t="inlineStr"/>
@@ -27232,7 +27232,7 @@
       </c>
       <c r="D299" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E299" s="0" t="inlineStr"/>
@@ -27258,7 +27258,7 @@
       </c>
       <c r="D300" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E300" s="0" t="inlineStr"/>
@@ -27284,7 +27284,7 @@
       </c>
       <c r="D301" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E301" s="0" t="inlineStr"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="D302" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E302" s="0" t="inlineStr"/>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="D303" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E303" s="0" t="inlineStr"/>
@@ -27362,7 +27362,7 @@
       </c>
       <c r="D304" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E304" s="0" t="inlineStr"/>
@@ -27388,7 +27388,7 @@
       </c>
       <c r="D305" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E305" s="0" t="inlineStr"/>
@@ -27414,7 +27414,7 @@
       </c>
       <c r="D306" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E306" s="0" t="inlineStr"/>
@@ -27440,7 +27440,7 @@
       </c>
       <c r="D307" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E307" s="0" t="inlineStr"/>
@@ -27466,7 +27466,7 @@
       </c>
       <c r="D308" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E308" s="0" t="inlineStr"/>
@@ -27492,7 +27492,7 @@
       </c>
       <c r="D309" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E309" s="0" t="inlineStr"/>
@@ -27518,7 +27518,7 @@
       </c>
       <c r="D310" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E310" s="0" t="inlineStr"/>
@@ -27544,7 +27544,7 @@
       </c>
       <c r="D311" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E311" s="0" t="inlineStr"/>
@@ -27570,7 +27570,7 @@
       </c>
       <c r="D312" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E312" s="0" t="inlineStr"/>
@@ -27596,7 +27596,7 @@
       </c>
       <c r="D313" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E313" s="0" t="inlineStr"/>
@@ -27622,7 +27622,7 @@
       </c>
       <c r="D314" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E314" s="0" t="inlineStr"/>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="D315" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E315" s="0" t="inlineStr"/>
@@ -27674,7 +27674,7 @@
       </c>
       <c r="D316" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E316" s="0" t="inlineStr"/>
@@ -27700,7 +27700,7 @@
       </c>
       <c r="D317" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E317" s="0" t="inlineStr"/>
@@ -27726,7 +27726,7 @@
       </c>
       <c r="D318" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E318" s="0" t="inlineStr"/>
@@ -27752,7 +27752,7 @@
       </c>
       <c r="D319" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E319" s="0" t="inlineStr"/>
@@ -27778,7 +27778,7 @@
       </c>
       <c r="D320" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E320" s="0" t="inlineStr"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -19520,7 +19520,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>GR26-W32-MS-IT 모니터 PDP Digital Trends 2025 Award 삭제</t>
+          <t>GR26-W32-MS-IT Digital Trends 2025 Award 삭제</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -4773,7 +4773,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · Copilot+ Hero Banner (B2C 완료 10 · 작업중 4 · B2B 작업중 7)</t>
+          <t>전건 완료 · Copilot+ Hero Banner (B2C 완료 13 · 취소 1(CN) · B2B 완료 7)</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="F14" s="0" t="n">
@@ -5202,7 +5202,12 @@
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F19" s="0" t="n">
@@ -5252,7 +5257,12 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F21" s="0" t="n">
@@ -5302,7 +5312,12 @@
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F23" s="0" t="n">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -5205,7 +5205,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
@@ -5260,7 +5260,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
@@ -5315,7 +5315,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · JIRA LGCOMMON-29612 · 요청자 Yerim Yeo · Due 2026-08-14 · 기존 UltraGear Gaming PLP 하단 FAQ에 1000Hz 문항 3건 추가 + 각국 번역</t>
+          <t>금주 신규 등록 · JIRA LGCOMMON-29612 · 요청자 Yerim Yeo · Due 2026-08-14 · 기존 UltraGear Gaming PLP 하단 FAQ에 1000Hz 문항 3건 추가 + 각국 번역 · 11개국 작업중 → 법인리뷰</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10020,7 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="F4" s="0" t="n">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="F5" s="0" t="n">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="F6" s="0" t="n">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="F7" s="0" t="n">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="F8" s="0" t="n">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="F9" s="0" t="n">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="F10" s="0" t="n">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="F11" s="0" t="n">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="F12" s="0" t="n">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="F13" s="0" t="n">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="F14" s="0" t="n">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -34777,7 +34777,8 @@
         <is>
           <t>CA_EN : URL 변경
 NL : URL 변경
-SE : URL 변경</t>
+SE : URL 변경
+FR : 법인리뷰 → 완료</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -35145,16 +35146,18 @@
       </c>
       <c r="D19" s="279" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E19" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E19" s="200" t="n">
+        <v>46259</v>
+      </c>
       <c r="F19" s="123" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>2026 답변 갱신 미반영 (Gaming·OLED Gaming)</t>
+          <t>2026 답변 갱신 반영 (Gaming·OLED Gaming)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -12075,7 +12075,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
+          <t>16Z90U-G · Erase.Lock 없음 — 교체 제외(LGE)</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
+          <t>16Z90U-G · Erase.Lock 없음 — 교체 제외(LGE)</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
+          <t>16Z90U-K · Erase.Lock 없음 — 교체 제외(LGE)</t>
         </is>
       </c>
     </row>
@@ -12150,7 +12150,7 @@
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
+          <t>16Z90U-K · Erase.Lock 없음 — 교체 제외(LGE)</t>
         </is>
       </c>
     </row>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
+          <t>16Z90U-K · Erase.Lock 없음 — 교체 제외(LGE)</t>
         </is>
       </c>
     </row>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
+          <t>17Z90U-A · Erase.Lock 없음 — 교체 제외(LGE)</t>
         </is>
       </c>
     </row>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>PDP는 라이브이나 기존 Secure Lock 컴포넌트 영역 없음 — 교체 대상 아님(LGE 확인)</t>
+          <t>17Z90U-G · Erase.Lock 없음 — 교체 제외(LGE)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -34034,7 +34034,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="34.5" customWidth="1" style="203" min="3" max="3"/>
@@ -34067,7 +34067,8 @@
         <is>
           <t>NL : URL 변경
 SE : URL 변경
-JP : URL 오기입 정정(uk/ice-solution → jp/monitors/ultragear-evo)</t>
+JP : URL 오기입 정정(uk/ice-solution → jp/monitors/ultragear-evo)
+AU·DE : 법인리뷰 → 완료 (FILE2 FAQ 실측 반영)</t>
         </is>
       </c>
       <c r="D2" s="164" t="n"/>
@@ -34137,17 +34138,19 @@
       </c>
       <c r="D9" s="269" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E9" s="287" t="n"/>
-      <c r="F9" s="270" t="n"/>
+      <c r="F9" s="289" t="n">
+        <v>46259</v>
+      </c>
       <c r="G9" s="177" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t>FAQ 미게시 (evo·Hyper)</t>
+          <t>FILE2 FAQ 반영 (evo 5Q·Hyper 3Q) · 실측 2026-08-25</t>
         </is>
       </c>
     </row>
@@ -34164,15 +34167,18 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F10" s="291" t="n">
+        <v>46259</v>
       </c>
       <c r="G10" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>FAQ 미게시 (evo·Hyper)</t>
+          <t>FILE2 FAQ 반영 (evo 5Q·Hyper 3Q) · 실측 2026-08-25</t>
         </is>
       </c>
     </row>
@@ -34321,17 +34327,19 @@
       </c>
       <c r="D15" s="273" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E15" s="288" t="n"/>
-      <c r="F15" s="274" t="n"/>
+      <c r="F15" s="274" t="n">
+        <v>46259</v>
+      </c>
       <c r="G15" s="185" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>FAQ 미게시 (evo·Hyper)</t>
+          <t>FILE2 FAQ 반영 (evo 5Q·Hyper 3Q) · 실측 2026-08-25</t>
         </is>
       </c>
     </row>
@@ -34348,16 +34356,18 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="F16" s="291" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F16" s="291" t="n">
+        <v>46259</v>
+      </c>
       <c r="G16" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>FAQ 미게시 (evo·Hyper)</t>
+          <t>FILE2 FAQ 반영 (evo 5Q·Hyper 3Q) · 실측 2026-08-25</t>
         </is>
       </c>
     </row>
@@ -34713,6 +34723,8 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
+    <row r="30"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId1"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -34034,7 +34034,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="34.5" customWidth="1" style="203" min="3" max="3"/>
@@ -34723,8 +34723,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId1"/>
@@ -35521,7 +35519,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>FR : 법인리뷰 → 완료 (7/24 게시, 실측 200 확인) · 잔여 작업중 7·법인리뷰 1(CN)</t>
+          <t>8국 Status 완료(1차) · Remark 2차 수정 예정 · FR(7/24) 포함 전 44국 완료율 100%</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -35535,6 +35533,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -35660,12 +35659,20 @@
       <c r="C12" s="277" t="inlineStr"/>
       <c r="D12" s="264" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E12" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E12" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="F12" s="0" t="inlineStr"/>
-      <c r="G12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>2차 수정 예정(법인리뷰)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="261" t="inlineStr">
@@ -35742,12 +35749,20 @@
       <c r="C16" s="277" t="inlineStr"/>
       <c r="D16" s="263" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E16" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E16" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="F16" s="0" t="inlineStr"/>
-      <c r="G16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>2차 수정 예정(작업중)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="261" t="inlineStr">
@@ -35758,12 +35773,20 @@
       <c r="C17" s="277" t="inlineStr"/>
       <c r="D17" s="264" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E17" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E17" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="F17" s="0" t="inlineStr"/>
-      <c r="G17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>2차 수정 예정(법인리뷰)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="261" t="inlineStr">
@@ -35932,12 +35955,20 @@
       <c r="C25" s="277" t="inlineStr"/>
       <c r="D25" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E25" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E25" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="F25" s="0" t="inlineStr"/>
-      <c r="G25" s="0" t="inlineStr"/>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>2차 수정 예정(작업중)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="261" t="inlineStr">
@@ -36080,12 +36111,20 @@
       <c r="C32" s="277" t="inlineStr"/>
       <c r="D32" s="264" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E32" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E32" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="F32" s="0" t="inlineStr"/>
-      <c r="G32" s="0" t="inlineStr"/>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>2차 수정 예정(법인리뷰)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="261" t="inlineStr">
@@ -36096,12 +36135,20 @@
       <c r="C33" s="277" t="inlineStr"/>
       <c r="D33" s="263" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E33" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E33" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="F33" s="0" t="inlineStr"/>
-      <c r="G33" s="0" t="n"/>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>2차 수정 예정(작업중)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="261" t="inlineStr">
@@ -36288,12 +36335,20 @@
       <c r="C42" s="277" t="inlineStr"/>
       <c r="D42" s="264" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E42" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E42" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="F42" s="0" t="inlineStr"/>
-      <c r="G42" s="0" t="inlineStr"/>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t>2차 수정 예정(법인리뷰)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="261" t="inlineStr">
@@ -36304,12 +36359,20 @@
       <c r="C43" s="277" t="inlineStr"/>
       <c r="D43" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E43" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E43" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="F43" s="0" t="inlineStr"/>
-      <c r="G43" s="0" t="inlineStr"/>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>2차 수정 예정(작업중)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="B44" s="261" t="inlineStr">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -19515,7 +19515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G320"/>
+  <dimension ref="A1:G444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="203" min="1" max="1"/>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · 요청자 Hyerin Shin(신혜린 책임) · 요청 2026-08-06 · Due 2026-08-28 · 라이선스 만료 2026-09-01 · 33모델 × 44개국 (라이브 314건 실측: 404 0 · soft-404 2 · 경로이동 2 반영)</t>
+          <t>PTT 추적 반영(2026-08-27) · 완료 409 · 작업중 32 · 상태변경 0 · URL갱신 4 · 신규 124</t>
         </is>
       </c>
     </row>
@@ -21730,7 +21730,7 @@
       </c>
       <c r="C87" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz/monitory/ultragear-gaming/27gx790a-b/</t>
+          <t>https://www.lg.com/cz/monitory/sety-s-monitorem/27gx790a-b-27gx001/</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="C88" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz/monitory/ultragear-gaming/32gx850a-b/</t>
+          <t>https://www.lg.com/cz/monitory/sety-s-monitorem/32gx850a-b-32gx001/</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="C91" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz/monitory/ultragear-gaming/39gx90sa-w/</t>
+          <t>https://www.lg.com/cz/monitory/sety-s-monitorem/39gx90sa-w-39gx001/</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="C103" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/de/monitore/uhd-4k-5k/32u990a-s/</t>
+          <t>https://www.lg.com/de/monitore/monitor-bundles/32u990a-s-32u9001/</t>
         </is>
       </c>
       <c r="D103" s="0" t="inlineStr">
@@ -22160,7 +22160,7 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨 · ⚠️ 갤러리 이미지에 어워드 잔존(2026-08-25 실측)</t>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -27803,6 +27803,3106 @@
       <c r="G320" s="0" t="inlineStr">
         <is>
           <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>BR : BR (pt)</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/br/monitores/monitores-full-hd-qhd/24u411b-b/</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F321" t="n">
+        <v>1</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/full-hd/24u411b-b-acc/</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>1</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/pleine-hd/24u411b-b-acc/</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F323" t="n">
+        <v>1</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/smart/24u411b-b/</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F324" t="n">
+        <v>1</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>PE : PE (es)</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pe/monitores/fhd-y-qhd/24u411b-b/</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F325" t="n">
+        <v>1</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-27g850a-b/</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>1</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-27g850a-b/</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F327" t="n">
+        <v>1</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-27g850a-b/</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F328" t="n">
+        <v>1</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>FI : FI (fi)</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fi/naytot/lg-27g850a-b/</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>1</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-27g850a-b/</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>1</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>LT : LT (lt)</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lt/monitoriai/lg-27g850a-b/</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F331" t="n">
+        <v>1</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>LV : LV (lv)</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lv/monitori/lg-27g850a-b/</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F332" t="n">
+        <v>1</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>NO : NO (no)</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/no/skjermer/lg-27g850a-b/</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>1</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>RO : RO (ro)</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ro/monitoare/lg-27g850a-b/</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F334" t="n">
+        <v>1</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-27g850a-b/</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F335" t="n">
+        <v>1</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>RU : RU (ru)</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/monitors/lg-27g850a-b/</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F336" t="n">
+        <v>1</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>1</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>1</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>1</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>1</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F341" t="n">
+        <v>1</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>RU : RU (ru)</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/monitors/lg-27gx700a-b/</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F342" t="n">
+        <v>1</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-27gx790a-b/</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F343" t="n">
+        <v>1</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>GT : GT (es)</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/monitors/lg-27gx790a-b/</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F344" t="n">
+        <v>1</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-27gx790a-b/</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F345" t="n">
+        <v>1</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>EC : EC (es)</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ec/monitores/lg-27gx790a-b/</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F346" t="n">
+        <v>1</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-27gx790a-b/</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F347" t="n">
+        <v>1</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-27gx790a-b/</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F348" t="n">
+        <v>1</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-27gx790a-b/</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F349" t="n">
+        <v>1</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>LT : LT (lt)</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lt/monitoriai/lg-27gx790a-b/</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F350" t="n">
+        <v>1</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>LV : LV (lv)</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lv/monitori/lg-27gx790a-b/</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F351" t="n">
+        <v>1</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-27gx790a-b/</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F352" t="n">
+        <v>1</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>RU : RU (ru)</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/monitors/lg-27gx790a-b/</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F353" t="n">
+        <v>1</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>SK : SK (sk)</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sk/monitory/lg-27gx790a-b/</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F354" t="n">
+        <v>1</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F355" t="n">
+        <v>1</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F356" t="n">
+        <v>1</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/promotions/ultragear-gaming-monitory/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>1</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F358" t="n">
+        <v>1</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitor/gaming/27gx790b/</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F359" t="n">
+        <v>1</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>27GX790-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F360" t="n">
+        <v>1</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F361" t="n">
+        <v>1</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/monitors/ultragear-gaming/27gx790b-b/</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F362" t="n">
+        <v>1</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/monitors/full-hd-qhd/27u411b-b/</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F363" t="n">
+        <v>1</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>27U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/ultrafine-uhd-4k-monitory/27u511sb-b/</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F364" t="n">
+        <v>1</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>27U511SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/ultrafine-uhd-4k-monitory/27u511sb-w/</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F365" t="n">
+        <v>1</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>27U511SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/professional-monitor/27u731sb-w/</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F366" t="n">
+        <v>1</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>27U731SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-do-hoa-ultrafine/27u731sb-w/</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F367" t="n">
+        <v>1</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>27U731SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-32gx850a-b/</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F368" t="n">
+        <v>1</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>GT : GT (es)</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/monitors/lg-32gx850a-b/</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F369" t="n">
+        <v>1</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-32gx850a-b/</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F370" t="n">
+        <v>1</v>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>SK : SK (sk)</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sk/monitory/lg-32gx850a-b/</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>1</v>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitor/fhd-qhd/32u401b-b/</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F372" t="n">
+        <v>1</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>32U401B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/monitors/smart-monitors/32u701sb-b-acc/</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>1</v>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>32U701SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/moniteurs/smart/32u701sb-b-acc/</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F374" t="n">
+        <v>1</v>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>32U701SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/smart/32u701sb-b/</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>1</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>32U701SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>1</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>BR : BR (pt)</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/br/business/monitores/monitores-produtos/monitores-ultrawide/32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>1</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>GT : GT (es)</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/monitors/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>1</v>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>1</v>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>EC : EC (es)</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ec/monitores/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>1</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>1</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>1</v>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>RU : RU (ru)</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/monitors/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>1</v>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>AE : AE (en)</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/consumer-monitors/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>1</v>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>AE_AR : AE (ar)</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae_ar/consumer-monitors/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>1</v>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/monitors/ultrafine-uhd-4k-5k/32u990a-s-aau/</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>1</v>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>BR : BR (pt)</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/br/monitores/monitores-uhd-4k/32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>1</v>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>GT : GT (es)</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/monitors/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>1</v>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>1</v>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>DK : DK (da)</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/skaerme/ultrafine-uhd-4k-og-5k-skaerme/32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>1</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>EC : EC (es)</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ec/monitores/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>1</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>FI : FI (fi)</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fi/naytot/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>1</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/uhd-4k-5k/lg-32u990a-s-moniteur-bureautique/</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>1</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>GR : GR (el)</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/gr/othones/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>1</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>1</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>HU : HU (hu)</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hu/monitorok/ultrafine-uhd-4k-es-5k-monitor/32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>1</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitors/32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>1</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>1</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>MX : MX (es)</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/mx/monitores/todos-los-monitores/32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>1</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultrafine-uhd-4k-5k-monitoren/32U990A-S/</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F400" t="n">
+        <v>1</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>RO : RO (ro)</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ro/monitoare/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>1</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F402" t="n">
+        <v>1</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>SE : SE (sv)</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/monitors/uhd-4k-5k/32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
+        <v>1</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>SK : SK (sk)</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sk/monitory/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F404" t="n">
+        <v>1</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-34u601b-b/</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>1</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/monitores/monitores-ultrawide/34u601b-b/</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F406" t="n">
+        <v>1</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/ultrawide/34u601b-b-aeuq/</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>1</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>BR : BR (pt)</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/br/monitores/monitores-ultrawide/34u620b-b/</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F408" t="n">
+        <v>1</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>34U620B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-34u620b-b/</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>1</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>34U620B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/ultrawide-sirokouhle-monitory/34u640b-b/</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>1</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>34U640B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/smart/34u640sb-w/</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>1</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>34U640SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-39gx90sa-w/</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>1</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-39gx90sa-w/</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F413" t="n">
+        <v>1</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-39gx90sa-w/</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F414" t="n">
+        <v>1</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/gaming/lg-39gx90sa-w-moniteur-ultragear/</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F415" t="n">
+        <v>1</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-39gx90sa-w/</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F416" t="n">
+        <v>1</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-39gx90sa-w/</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F417" t="n">
+        <v>1</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>BE_FR : BE (fr)</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/moniteurs/moniteurs-ultrafine/40U990A-W/</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F418" t="n">
+        <v>1</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F419" t="n">
+        <v>1</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F420" t="n">
+        <v>1</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>GR : GR (el)</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/gr/othones/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F421" t="n">
+        <v>1</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F422" t="n">
+        <v>1</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>LT : LT (lt)</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lt/monitoriai/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F423" t="n">
+        <v>1</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>LV : LV (lv)</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lv/monitori/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F424" t="n">
+        <v>1</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>RU : RU (ru)</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/monitors/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F425" t="n">
+        <v>1</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>SK : SK (sk)</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sk/monitory/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F426" t="n">
+        <v>1</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-45gx90sa-b/</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F427" t="n">
+        <v>1</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-45gx90sa-b/</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F428" t="n">
+        <v>1</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-45gx90sa-b/</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F429" t="n">
+        <v>1</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-45gx90sa-b/</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F430" t="n">
+        <v>1</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F431" t="n">
+        <v>1</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>GT : GT (es)</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/monitors/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F432" t="n">
+        <v>1</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F433" t="n">
+        <v>1</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>EC : EC (es)</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ec/monitores/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F434" t="n">
+        <v>1</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F435" t="n">
+        <v>1</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F436" t="n">
+        <v>1</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>1</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>SK : SK (sk)</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sk/monitory/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F438" t="n">
+        <v>1</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-49u950a-w/</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F439" t="n">
+        <v>1</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-49u950a-w/</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F440" t="n">
+        <v>1</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>GR : GR (el)</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/gr/othones/lg-49u950a-w/</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F441" t="n">
+        <v>1</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-49u950a-w/</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F442" t="n">
+        <v>1</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-49u950a-w/</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F443" t="n">
+        <v>1</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>SK : SK (sk)</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sk/monitory/lg-49u950a-w/</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F444" t="n">
+        <v>1</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
@@ -35533,7 +38633,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -19547,7 +19547,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>PTT 추적 반영(2026-08-27) · 완료 409 · 작업중 32 · 상태변경 0 · URL갱신 4 · 신규 124</t>
+          <t>PTT 추적 2차 반영(2026-08-27) · 완료 427 · 작업중 14 · 상태변경 18 · URL갱신 0 · 미매칭 0</t>
         </is>
       </c>
     </row>
@@ -27807,3102 +27807,3102 @@
       </c>
     </row>
     <row r="321">
-      <c r="B321" t="inlineStr">
+      <c r="B321" s="0" t="inlineStr">
         <is>
           <t>BR : BR (pt)</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
+      <c r="C321" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/br/monitores/monitores-full-hd-qhd/24u411b-b/</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F321" t="n">
-        <v>1</v>
-      </c>
-      <c r="G321" t="inlineStr">
+      <c r="D321" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F321" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G321" s="0" t="inlineStr">
         <is>
           <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="B322" t="inlineStr">
+      <c r="B322" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr">
+      <c r="C322" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/monitors/full-hd/24u411b-b-acc/</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr">
+      <c r="D322" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F322" t="n">
-        <v>1</v>
-      </c>
-      <c r="G322" t="inlineStr">
+      <c r="F322" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G322" s="0" t="inlineStr">
         <is>
           <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="B323" t="inlineStr">
+      <c r="B323" s="0" t="inlineStr">
         <is>
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr">
+      <c r="C323" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/moniteurs/pleine-hd/24u411b-b-acc/</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr">
+      <c r="D323" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F323" t="n">
-        <v>1</v>
-      </c>
-      <c r="G323" t="inlineStr">
+      <c r="F323" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G323" s="0" t="inlineStr">
         <is>
           <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="B324" t="inlineStr">
+      <c r="B324" s="0" t="inlineStr">
         <is>
           <t>CZ : CZ (cs)</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr">
+      <c r="C324" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cz/monitory/smart/24u411b-b/</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr">
+      <c r="D324" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F324" t="n">
-        <v>1</v>
-      </c>
-      <c r="G324" t="inlineStr">
+      <c r="F324" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G324" s="0" t="inlineStr">
         <is>
           <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="B325" t="inlineStr">
+      <c r="B325" s="0" t="inlineStr">
         <is>
           <t>PE : PE (es)</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
+      <c r="C325" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/pe/monitores/fhd-y-qhd/24u411b-b/</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F325" t="n">
-        <v>1</v>
-      </c>
-      <c r="G325" t="inlineStr">
+      <c r="D325" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F325" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G325" s="0" t="inlineStr">
         <is>
           <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="326">
-      <c r="B326" t="inlineStr">
+      <c r="B326" s="0" t="inlineStr">
         <is>
           <t>BG : BG (bg)</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
+      <c r="C326" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/bg/monitori/lg-27g850a-b/</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F326" t="n">
-        <v>1</v>
-      </c>
-      <c r="G326" t="inlineStr">
+      <c r="D326" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F326" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G326" s="0" t="inlineStr">
         <is>
           <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="B327" t="inlineStr">
+      <c r="B327" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr">
+      <c r="C327" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/monitors/lg-27g850a-b/</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F327" t="n">
-        <v>1</v>
-      </c>
-      <c r="G327" t="inlineStr">
+      <c r="D327" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F327" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G327" s="0" t="inlineStr">
         <is>
           <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="328">
-      <c r="B328" t="inlineStr">
+      <c r="B328" s="0" t="inlineStr">
         <is>
           <t>EE : EE (et)</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr">
+      <c r="C328" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ee/monitorid/lg-27g850a-b/</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F328" t="n">
-        <v>1</v>
-      </c>
-      <c r="G328" t="inlineStr">
+      <c r="D328" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F328" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G328" s="0" t="inlineStr">
         <is>
           <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="329">
-      <c r="B329" t="inlineStr">
+      <c r="B329" s="0" t="inlineStr">
         <is>
           <t>FI : FI (fi)</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
+      <c r="C329" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/fi/naytot/lg-27g850a-b/</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F329" t="n">
-        <v>1</v>
-      </c>
-      <c r="G329" t="inlineStr">
+      <c r="D329" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F329" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G329" s="0" t="inlineStr">
         <is>
           <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="B330" t="inlineStr">
+      <c r="B330" s="0" t="inlineStr">
         <is>
           <t>HR : HR (hr)</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
+      <c r="C330" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/hr/monitori/lg-27g850a-b/</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F330" t="n">
-        <v>1</v>
-      </c>
-      <c r="G330" t="inlineStr">
+      <c r="D330" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F330" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G330" s="0" t="inlineStr">
         <is>
           <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="B331" t="inlineStr">
+      <c r="B331" s="0" t="inlineStr">
         <is>
           <t>LT : LT (lt)</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr">
+      <c r="C331" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/lt/monitoriai/lg-27g850a-b/</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F331" t="n">
-        <v>1</v>
-      </c>
-      <c r="G331" t="inlineStr">
+      <c r="D331" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F331" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G331" s="0" t="inlineStr">
         <is>
           <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="B332" t="inlineStr">
+      <c r="B332" s="0" t="inlineStr">
         <is>
           <t>LV : LV (lv)</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr">
+      <c r="C332" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/lv/monitori/lg-27g850a-b/</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F332" t="n">
-        <v>1</v>
-      </c>
-      <c r="G332" t="inlineStr">
+      <c r="D332" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F332" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G332" s="0" t="inlineStr">
         <is>
           <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="B333" t="inlineStr">
+      <c r="B333" s="0" t="inlineStr">
         <is>
           <t>NO : NO (no)</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr">
+      <c r="C333" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/no/skjermer/lg-27g850a-b/</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F333" t="n">
-        <v>1</v>
-      </c>
-      <c r="G333" t="inlineStr">
+      <c r="D333" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F333" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G333" s="0" t="inlineStr">
         <is>
           <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="B334" t="inlineStr">
+      <c r="B334" s="0" t="inlineStr">
         <is>
           <t>RO : RO (ro)</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr">
+      <c r="C334" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ro/monitoare/lg-27g850a-b/</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F334" t="n">
-        <v>1</v>
-      </c>
-      <c r="G334" t="inlineStr">
+      <c r="D334" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F334" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G334" s="0" t="inlineStr">
         <is>
           <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="B335" t="inlineStr">
+      <c r="B335" s="0" t="inlineStr">
         <is>
           <t>RS : RS (sr)</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr">
+      <c r="C335" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/rs/monitori/lg-27g850a-b/</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F335" t="n">
-        <v>1</v>
-      </c>
-      <c r="G335" t="inlineStr">
+      <c r="D335" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F335" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G335" s="0" t="inlineStr">
         <is>
           <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="B336" t="inlineStr">
+      <c r="B336" s="0" t="inlineStr">
         <is>
           <t>RU : RU (ru)</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
+      <c r="C336" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ru/monitors/lg-27g850a-b/</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F336" t="n">
-        <v>1</v>
-      </c>
-      <c r="G336" t="inlineStr">
+      <c r="D336" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F336" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G336" s="0" t="inlineStr">
         <is>
           <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="B337" t="inlineStr">
+      <c r="B337" s="0" t="inlineStr">
         <is>
           <t>BG : BG (bg)</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
+      <c r="C337" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/bg/monitori/lg-27gx700a-b/</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F337" t="n">
-        <v>1</v>
-      </c>
-      <c r="G337" t="inlineStr">
+      <c r="D337" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F337" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G337" s="0" t="inlineStr">
         <is>
           <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="B338" t="inlineStr">
+      <c r="B338" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr">
+      <c r="C338" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/monitors/lg-27gx700a-b/</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F338" t="n">
-        <v>1</v>
-      </c>
-      <c r="G338" t="inlineStr">
+      <c r="D338" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F338" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G338" s="0" t="inlineStr">
         <is>
           <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="339">
-      <c r="B339" t="inlineStr">
+      <c r="B339" s="0" t="inlineStr">
         <is>
           <t>HR : HR (hr)</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr">
+      <c r="C339" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/hr/monitori/lg-27gx700a-b/</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F339" t="n">
-        <v>1</v>
-      </c>
-      <c r="G339" t="inlineStr">
+      <c r="D339" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F339" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G339" s="0" t="inlineStr">
         <is>
           <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="340">
-      <c r="B340" t="inlineStr">
+      <c r="B340" s="0" t="inlineStr">
         <is>
           <t>IL : IL (iw)</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr">
+      <c r="C340" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/il/monitors/lg-27gx700a-b/</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F340" t="n">
-        <v>1</v>
-      </c>
-      <c r="G340" t="inlineStr">
+      <c r="D340" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F340" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G340" s="0" t="inlineStr">
         <is>
           <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="341">
-      <c r="B341" t="inlineStr">
+      <c r="B341" s="0" t="inlineStr">
         <is>
           <t>RS : RS (sr)</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr">
+      <c r="C341" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/rs/monitori/lg-27gx700a-b/</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F341" t="n">
-        <v>1</v>
-      </c>
-      <c r="G341" t="inlineStr">
+      <c r="D341" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F341" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G341" s="0" t="inlineStr">
         <is>
           <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="342">
-      <c r="B342" t="inlineStr">
+      <c r="B342" s="0" t="inlineStr">
         <is>
           <t>RU : RU (ru)</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr">
+      <c r="C342" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ru/monitors/lg-27gx700a-b/</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F342" t="n">
-        <v>1</v>
-      </c>
-      <c r="G342" t="inlineStr">
+      <c r="D342" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F342" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G342" s="0" t="inlineStr">
         <is>
           <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="B343" t="inlineStr">
+      <c r="B343" s="0" t="inlineStr">
         <is>
           <t>BG : BG (bg)</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr">
+      <c r="C343" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/bg/monitori/lg-27gx790a-b/</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F343" t="n">
-        <v>1</v>
-      </c>
-      <c r="G343" t="inlineStr">
+      <c r="D343" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F343" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G343" s="0" t="inlineStr">
         <is>
           <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="B344" t="inlineStr">
+      <c r="B344" s="0" t="inlineStr">
         <is>
           <t>GT : GT (es)</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr">
+      <c r="C344" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cac/monitors/lg-27gx790a-b/</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F344" t="n">
-        <v>1</v>
-      </c>
-      <c r="G344" t="inlineStr">
+      <c r="D344" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F344" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G344" s="0" t="inlineStr">
         <is>
           <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="B345" t="inlineStr">
+      <c r="B345" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr">
+      <c r="C345" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/monitors/lg-27gx790a-b/</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F345" t="n">
-        <v>1</v>
-      </c>
-      <c r="G345" t="inlineStr">
+      <c r="D345" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F345" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G345" s="0" t="inlineStr">
         <is>
           <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="B346" t="inlineStr">
+      <c r="B346" s="0" t="inlineStr">
         <is>
           <t>EC : EC (es)</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr">
+      <c r="C346" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ec/monitores/lg-27gx790a-b/</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F346" t="n">
-        <v>1</v>
-      </c>
-      <c r="G346" t="inlineStr">
+      <c r="D346" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F346" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G346" s="0" t="inlineStr">
         <is>
           <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="B347" t="inlineStr">
+      <c r="B347" s="0" t="inlineStr">
         <is>
           <t>EE : EE (et)</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr">
+      <c r="C347" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ee/monitorid/lg-27gx790a-b/</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F347" t="n">
-        <v>1</v>
-      </c>
-      <c r="G347" t="inlineStr">
+      <c r="D347" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F347" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G347" s="0" t="inlineStr">
         <is>
           <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="348">
-      <c r="B348" t="inlineStr">
+      <c r="B348" s="0" t="inlineStr">
         <is>
           <t>HR : HR (hr)</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr">
+      <c r="C348" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/hr/monitori/lg-27gx790a-b/</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F348" t="n">
-        <v>1</v>
-      </c>
-      <c r="G348" t="inlineStr">
+      <c r="D348" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F348" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G348" s="0" t="inlineStr">
         <is>
           <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="349">
-      <c r="B349" t="inlineStr">
+      <c r="B349" s="0" t="inlineStr">
         <is>
           <t>IL : IL (iw)</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr">
+      <c r="C349" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/il/monitors/lg-27gx790a-b/</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F349" t="n">
-        <v>1</v>
-      </c>
-      <c r="G349" t="inlineStr">
+      <c r="D349" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F349" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G349" s="0" t="inlineStr">
         <is>
           <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="B350" t="inlineStr">
+      <c r="B350" s="0" t="inlineStr">
         <is>
           <t>LT : LT (lt)</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr">
+      <c r="C350" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/lt/monitoriai/lg-27gx790a-b/</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F350" t="n">
-        <v>1</v>
-      </c>
-      <c r="G350" t="inlineStr">
+      <c r="D350" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F350" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G350" s="0" t="inlineStr">
         <is>
           <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="B351" t="inlineStr">
+      <c r="B351" s="0" t="inlineStr">
         <is>
           <t>LV : LV (lv)</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr">
+      <c r="C351" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/lv/monitori/lg-27gx790a-b/</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F351" t="n">
-        <v>1</v>
-      </c>
-      <c r="G351" t="inlineStr">
+      <c r="D351" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F351" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G351" s="0" t="inlineStr">
         <is>
           <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="352">
-      <c r="B352" t="inlineStr">
+      <c r="B352" s="0" t="inlineStr">
         <is>
           <t>RS : RS (sr)</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
+      <c r="C352" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/rs/monitori/lg-27gx790a-b/</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F352" t="n">
-        <v>1</v>
-      </c>
-      <c r="G352" t="inlineStr">
+      <c r="D352" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F352" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G352" s="0" t="inlineStr">
         <is>
           <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="353">
-      <c r="B353" t="inlineStr">
+      <c r="B353" s="0" t="inlineStr">
         <is>
           <t>RU : RU (ru)</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
+      <c r="C353" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ru/monitors/lg-27gx790a-b/</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F353" t="n">
-        <v>1</v>
-      </c>
-      <c r="G353" t="inlineStr">
+      <c r="D353" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F353" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G353" s="0" t="inlineStr">
         <is>
           <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="354">
-      <c r="B354" t="inlineStr">
+      <c r="B354" s="0" t="inlineStr">
         <is>
           <t>SK : SK (sk)</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
+      <c r="C354" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sk/monitory/lg-27gx790a-b/</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F354" t="n">
-        <v>1</v>
-      </c>
-      <c r="G354" t="inlineStr">
+      <c r="D354" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F354" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G354" s="0" t="inlineStr">
         <is>
           <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="355">
-      <c r="B355" t="inlineStr">
+      <c r="B355" s="0" t="inlineStr">
         <is>
           <t>BG : BG (bg)</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
+      <c r="C355" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/bg/monitori/lg-27gx790b-b/</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F355" t="n">
-        <v>1</v>
-      </c>
-      <c r="G355" t="inlineStr">
+      <c r="D355" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F355" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G355" s="0" t="inlineStr">
         <is>
           <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="356">
-      <c r="B356" t="inlineStr">
+      <c r="B356" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
+      <c r="C356" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/monitors/lg-27gx790b-b/</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F356" t="n">
-        <v>1</v>
-      </c>
-      <c r="G356" t="inlineStr">
+      <c r="D356" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F356" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G356" s="0" t="inlineStr">
         <is>
           <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="357">
-      <c r="B357" t="inlineStr">
+      <c r="B357" s="0" t="inlineStr">
         <is>
           <t>CZ : CZ (cs)</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr">
+      <c r="C357" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cz/promotions/ultragear-gaming-monitory/27gx790b-b/</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
+      <c r="D357" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F357" t="n">
-        <v>1</v>
-      </c>
-      <c r="G357" t="inlineStr">
+      <c r="F357" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G357" s="0" t="inlineStr">
         <is>
           <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="B358" t="inlineStr">
+      <c r="B358" s="0" t="inlineStr">
         <is>
           <t>HR : HR (hr)</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr">
+      <c r="C358" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/hr/monitori/lg-27gx790b-b/</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F358" t="n">
-        <v>1</v>
-      </c>
-      <c r="G358" t="inlineStr">
+      <c r="D358" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F358" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G358" s="0" t="inlineStr">
         <is>
           <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="359">
-      <c r="B359" t="inlineStr">
+      <c r="B359" s="0" t="inlineStr">
         <is>
           <t>ID : ID (in)</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr">
+      <c r="C359" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/id/monitor/gaming/27gx790b/</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F359" t="n">
-        <v>1</v>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>27GX790-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+      <c r="D359" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F359" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G359" s="0" t="inlineStr">
+        <is>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="360">
-      <c r="B360" t="inlineStr">
+      <c r="B360" s="0" t="inlineStr">
         <is>
           <t>IL : IL (iw)</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr">
+      <c r="C360" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/il/monitors/lg-27gx790b-b/</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F360" t="n">
-        <v>1</v>
-      </c>
-      <c r="G360" t="inlineStr">
+      <c r="D360" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F360" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G360" s="0" t="inlineStr">
         <is>
           <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="361">
-      <c r="B361" t="inlineStr">
+      <c r="B361" s="0" t="inlineStr">
         <is>
           <t>RS : RS (sr)</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
+      <c r="C361" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/rs/monitori/lg-27gx790b-b/</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F361" t="n">
-        <v>1</v>
-      </c>
-      <c r="G361" t="inlineStr">
+      <c r="D361" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F361" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G361" s="0" t="inlineStr">
         <is>
           <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="362">
-      <c r="B362" t="inlineStr">
+      <c r="B362" s="0" t="inlineStr">
         <is>
           <t>TW : TW (zh)</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr">
+      <c r="C362" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/tw/monitors/ultragear-gaming/27gx790b-b/</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr">
+      <c r="D362" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F362" t="n">
-        <v>1</v>
-      </c>
-      <c r="G362" t="inlineStr">
+      <c r="F362" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G362" s="0" t="inlineStr">
         <is>
           <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="B363" t="inlineStr">
+      <c r="B363" s="0" t="inlineStr">
         <is>
           <t>AU : AU (en)</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr">
+      <c r="C363" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/monitors/full-hd-qhd/27u411b-b/</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F363" t="n">
-        <v>1</v>
-      </c>
-      <c r="G363" t="inlineStr">
+      <c r="D363" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F363" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G363" s="0" t="inlineStr">
         <is>
           <t>27U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="364">
-      <c r="B364" t="inlineStr">
+      <c r="B364" s="0" t="inlineStr">
         <is>
           <t>CZ : CZ (cs)</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr">
+      <c r="C364" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cz/monitory/ultrafine-uhd-4k-monitory/27u511sb-b/</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr">
+      <c r="D364" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F364" t="n">
-        <v>1</v>
-      </c>
-      <c r="G364" t="inlineStr">
+      <c r="F364" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G364" s="0" t="inlineStr">
         <is>
           <t>27U511SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
     <row r="365">
-      <c r="B365" t="inlineStr">
+      <c r="B365" s="0" t="inlineStr">
         <is>
           <t>CZ : CZ (cs)</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr">
+      <c r="C365" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cz/monitory/ultrafine-uhd-4k-monitory/27u511sb-w/</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr">
+      <c r="D365" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F365" t="n">
-        <v>1</v>
-      </c>
-      <c r="G365" t="inlineStr">
+      <c r="F365" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G365" s="0" t="inlineStr">
         <is>
           <t>27U511SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
     <row r="366">
-      <c r="B366" t="inlineStr">
+      <c r="B366" s="0" t="inlineStr">
         <is>
           <t>CZ : CZ (cs)</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C366" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cz/monitory/professional-monitor/27u731sb-w/</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
+      <c r="D366" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F366" t="n">
-        <v>1</v>
-      </c>
-      <c r="G366" t="inlineStr">
+      <c r="F366" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G366" s="0" t="inlineStr">
         <is>
           <t>27U731SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
     <row r="367">
-      <c r="B367" t="inlineStr">
+      <c r="B367" s="0" t="inlineStr">
         <is>
           <t>VN : VN (vi)</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
+      <c r="C367" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-do-hoa-ultrafine/27u731sb-w/</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr">
+      <c r="D367" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F367" t="n">
-        <v>1</v>
-      </c>
-      <c r="G367" t="inlineStr">
+      <c r="F367" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G367" s="0" t="inlineStr">
         <is>
           <t>27U731SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
     <row r="368">
-      <c r="B368" t="inlineStr">
+      <c r="B368" s="0" t="inlineStr">
         <is>
           <t>BG : BG (bg)</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr">
+      <c r="C368" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/bg/monitori/lg-32gx850a-b/</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F368" t="n">
-        <v>1</v>
-      </c>
-      <c r="G368" t="inlineStr">
+      <c r="D368" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F368" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G368" s="0" t="inlineStr">
         <is>
           <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="B369" t="inlineStr">
+      <c r="B369" s="0" t="inlineStr">
         <is>
           <t>GT : GT (es)</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr">
+      <c r="C369" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cac/monitors/lg-32gx850a-b/</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F369" t="n">
-        <v>1</v>
-      </c>
-      <c r="G369" t="inlineStr">
+      <c r="D369" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F369" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G369" s="0" t="inlineStr">
         <is>
           <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="B370" t="inlineStr">
+      <c r="B370" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr">
+      <c r="C370" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cn/monitors/lg-32gx850a-b/</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F370" t="n">
-        <v>1</v>
-      </c>
-      <c r="G370" t="inlineStr">
+      <c r="D370" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F370" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G370" s="0" t="inlineStr">
         <is>
           <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="371">
-      <c r="B371" t="inlineStr">
+      <c r="B371" s="0" t="inlineStr">
         <is>
           <t>SK : SK (sk)</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr">
+      <c r="C371" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sk/monitory/lg-32gx850a-b/</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F371" t="n">
-        <v>1</v>
-      </c>
-      <c r="G371" t="inlineStr">
+      <c r="D371" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F371" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G371" s="0" t="inlineStr">
         <is>
           <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="372">
-      <c r="B372" t="inlineStr">
+      <c r="B372" s="0" t="inlineStr">
         <is>
           <t>ID : ID (in)</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr">
+      <c r="C372" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/id/monitor/fhd-qhd/32u401b-b/</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F372" t="n">
-        <v>1</v>
-      </c>
-      <c r="G372" t="inlineStr">
+      <c r="D372" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F372" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G372" s="0" t="inlineStr">
         <is>
           <t>32U401B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="373">
-      <c r="B373" t="inlineStr">
+      <c r="B373" s="0" t="inlineStr">
         <is>
           <t>CA_EN : CA (en)</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr">
+      <c r="C373" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/monitors/smart-monitors/32u701sb-b-acc/</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
+      <c r="D373" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F373" t="n">
-        <v>1</v>
-      </c>
-      <c r="G373" t="inlineStr">
+      <c r="F373" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G373" s="0" t="inlineStr">
         <is>
           <t>32U701SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
     <row r="374">
-      <c r="B374" t="inlineStr">
+      <c r="B374" s="0" t="inlineStr">
         <is>
           <t>CA_FR : CA (fr)</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr">
+      <c r="C374" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_fr/moniteurs/smart/32u701sb-b-acc/</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr">
+      <c r="D374" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F374" t="n">
-        <v>1</v>
-      </c>
-      <c r="G374" t="inlineStr">
+      <c r="F374" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G374" s="0" t="inlineStr">
         <is>
           <t>32U701SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
     <row r="375">
-      <c r="B375" t="inlineStr">
+      <c r="B375" s="0" t="inlineStr">
         <is>
           <t>CZ : CZ (cs)</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr">
+      <c r="C375" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/cz/monitory/smart/32u701sb-b/</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr">
+      <c r="D375" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F375" t="n">
-        <v>1</v>
-      </c>
-      <c r="G375" t="inlineStr">
+      <c r="F375" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G375" s="0" t="inlineStr">
         <is>
           <t>32U701SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
         </is>
       </c>
     </row>
     <row r="376">
-      <c r="B376" t="inlineStr">
+      <c r="B376" s="0" t="inlineStr">
         <is>
           <t>BG : BG (bg)</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr">
+      <c r="C376" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/bg/monitori/lg-32u889sa-w/</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F376" t="n">
-        <v>1</v>
-      </c>
-      <c r="G376" t="inlineStr">
+      <c r="D376" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F376" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G376" s="0" t="inlineStr">
         <is>
           <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="B377" t="inlineStr">
+      <c r="B377" s="0" t="inlineStr">
         <is>
           <t>BR : BR (pt)</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr">
+      <c r="C377" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/br/business/monitores/monitores-produtos/monitores-ultrawide/32u889sa-w/</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr">
+      <c r="D377" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F377" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G377" s="0" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" s="0" t="inlineStr">
+        <is>
+          <t>GT : GT (es)</t>
+        </is>
+      </c>
+      <c r="C378" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/monitors/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D378" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F378" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G378" s="0" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" s="0" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C379" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D379" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F379" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G379" s="0" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" s="0" t="inlineStr">
+        <is>
+          <t>EC : EC (es)</t>
+        </is>
+      </c>
+      <c r="C380" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ec/monitores/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D380" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F380" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G380" s="0" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" s="0" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C381" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D381" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F381" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G381" s="0" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" s="0" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C382" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D382" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F382" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G382" s="0" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" s="0" t="inlineStr">
+        <is>
+          <t>RU : RU (ru)</t>
+        </is>
+      </c>
+      <c r="C383" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/monitors/lg-32u889sa-w/</t>
+        </is>
+      </c>
+      <c r="D383" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F383" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G383" s="0" t="inlineStr">
+        <is>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" s="0" t="inlineStr">
+        <is>
+          <t>AE : AE (en)</t>
+        </is>
+      </c>
+      <c r="C384" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/consumer-monitors/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D384" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F384" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G384" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" s="0" t="inlineStr">
+        <is>
+          <t>AE_AR : AE (ar)</t>
+        </is>
+      </c>
+      <c r="C385" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae_ar/consumer-monitors/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D385" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F385" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G385" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" s="0" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C386" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/monitors/ultrafine-uhd-4k-5k/32u990a-s-aau/</t>
+        </is>
+      </c>
+      <c r="D386" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F386" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G386" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" s="0" t="inlineStr">
+        <is>
+          <t>BR : BR (pt)</t>
+        </is>
+      </c>
+      <c r="C387" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/br/monitores/monitores-uhd-4k/32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D387" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F387" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G387" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" s="0" t="inlineStr">
+        <is>
+          <t>GT : GT (es)</t>
+        </is>
+      </c>
+      <c r="C388" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/monitors/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D388" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F388" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G388" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" s="0" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C389" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D389" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F389" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G389" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" s="0" t="inlineStr">
+        <is>
+          <t>DK : DK (da)</t>
+        </is>
+      </c>
+      <c r="C390" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/skaerme/ultrafine-uhd-4k-og-5k-skaerme/32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D390" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F390" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G390" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" s="0" t="inlineStr">
+        <is>
+          <t>EC : EC (es)</t>
+        </is>
+      </c>
+      <c r="C391" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ec/monitores/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D391" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F391" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G391" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" s="0" t="inlineStr">
+        <is>
+          <t>FI : FI (fi)</t>
+        </is>
+      </c>
+      <c r="C392" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fi/naytot/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D392" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F392" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G392" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" s="0" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C393" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/uhd-4k-5k/lg-32u990a-s-moniteur-bureautique/</t>
+        </is>
+      </c>
+      <c r="D393" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F393" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G393" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" s="0" t="inlineStr">
+        <is>
+          <t>GR : GR (el)</t>
+        </is>
+      </c>
+      <c r="C394" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/gr/othones/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D394" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F394" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G394" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" s="0" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C395" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D395" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F395" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G395" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" s="0" t="inlineStr">
+        <is>
+          <t>HU : HU (hu)</t>
+        </is>
+      </c>
+      <c r="C396" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hu/monitorok/ultrafine-uhd-4k-es-5k-monitor/32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D396" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F396" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G396" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" s="0" t="inlineStr">
+        <is>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C397" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitors/32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D397" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F397" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G397" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" s="0" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C398" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D398" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F398" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G398" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" s="0" t="inlineStr">
+        <is>
+          <t>MX : MX (es)</t>
+        </is>
+      </c>
+      <c r="C399" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/mx/monitores/todos-los-monitores/32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D399" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F399" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G399" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" s="0" t="inlineStr">
+        <is>
+          <t>NL : NL (nl)</t>
+        </is>
+      </c>
+      <c r="C400" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/monitoren/ultrafine-uhd-4k-5k-monitoren/32U990A-S/</t>
+        </is>
+      </c>
+      <c r="D400" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F400" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G400" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" s="0" t="inlineStr">
+        <is>
+          <t>RO : RO (ro)</t>
+        </is>
+      </c>
+      <c r="C401" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ro/monitoare/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D401" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F401" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G401" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" s="0" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C402" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D402" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F402" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G402" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" s="0" t="inlineStr">
+        <is>
+          <t>SE : SE (sv)</t>
+        </is>
+      </c>
+      <c r="C403" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/monitors/uhd-4k-5k/32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D403" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F403" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G403" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" s="0" t="inlineStr">
+        <is>
+          <t>SK : SK (sk)</t>
+        </is>
+      </c>
+      <c r="C404" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sk/monitory/lg-32u990a-s/</t>
+        </is>
+      </c>
+      <c r="D404" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F404" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G404" s="0" t="inlineStr">
+        <is>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" s="0" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C405" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-34u601b-b/</t>
+        </is>
+      </c>
+      <c r="D405" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F405" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G405" s="0" t="inlineStr">
+        <is>
+          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" s="0" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C406" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/monitores/monitores-ultrawide/34u601b-b/</t>
+        </is>
+      </c>
+      <c r="D406" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F406" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G406" s="0" t="inlineStr">
+        <is>
+          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" s="0" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C407" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/ultrawide/34u601b-b-aeuq/</t>
+        </is>
+      </c>
+      <c r="D407" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F407" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G407" s="0" t="inlineStr">
+        <is>
+          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" s="0" t="inlineStr">
+        <is>
+          <t>BR : BR (pt)</t>
+        </is>
+      </c>
+      <c r="C408" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/br/monitores/monitores-ultrawide/34u620b-b/</t>
+        </is>
+      </c>
+      <c r="D408" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F408" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G408" s="0" t="inlineStr">
+        <is>
+          <t>34U620B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" s="0" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C409" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-34u620b-b/</t>
+        </is>
+      </c>
+      <c r="D409" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F409" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G409" s="0" t="inlineStr">
+        <is>
+          <t>34U620B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" s="0" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C410" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/ultrawide-sirokouhle-monitory/34u640b-b/</t>
+        </is>
+      </c>
+      <c r="D410" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
         </is>
       </c>
-      <c r="F377" t="n">
-        <v>1</v>
-      </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="B378" t="inlineStr">
+      <c r="F410" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G410" s="0" t="inlineStr">
+        <is>
+          <t>34U640B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" s="0" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C411" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/smart/34u640sb-w/</t>
+        </is>
+      </c>
+      <c r="D411" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="F411" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G411" s="0" t="inlineStr">
+        <is>
+          <t>34U640SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" s="0" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C412" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-39gx90sa-w/</t>
+        </is>
+      </c>
+      <c r="D412" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F412" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G412" s="0" t="inlineStr">
+        <is>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" s="0" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C413" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-39gx90sa-w/</t>
+        </is>
+      </c>
+      <c r="D413" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F413" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G413" s="0" t="inlineStr">
+        <is>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" s="0" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C414" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-39gx90sa-w/</t>
+        </is>
+      </c>
+      <c r="D414" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F414" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G414" s="0" t="inlineStr">
+        <is>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" s="0" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C415" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/gaming/lg-39gx90sa-w-moniteur-ultragear/</t>
+        </is>
+      </c>
+      <c r="D415" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F415" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G415" s="0" t="inlineStr">
+        <is>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" s="0" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C416" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-39gx90sa-w/</t>
+        </is>
+      </c>
+      <c r="D416" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F416" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G416" s="0" t="inlineStr">
+        <is>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" s="0" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C417" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-39gx90sa-w/</t>
+        </is>
+      </c>
+      <c r="D417" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F417" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G417" s="0" t="inlineStr">
+        <is>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" s="0" t="inlineStr">
+        <is>
+          <t>BE_FR : BE (fr)</t>
+        </is>
+      </c>
+      <c r="C418" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/moniteurs/moniteurs-ultrafine/40U990A-W/</t>
+        </is>
+      </c>
+      <c r="D418" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F418" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G418" s="0" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" s="0" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C419" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D419" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F419" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G419" s="0" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" s="0" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C420" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D420" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F420" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G420" s="0" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" s="0" t="inlineStr">
+        <is>
+          <t>GR : GR (el)</t>
+        </is>
+      </c>
+      <c r="C421" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/gr/othones/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D421" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F421" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G421" s="0" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" s="0" t="inlineStr">
+        <is>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C422" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D422" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F422" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G422" s="0" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" s="0" t="inlineStr">
+        <is>
+          <t>LT : LT (lt)</t>
+        </is>
+      </c>
+      <c r="C423" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lt/monitoriai/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D423" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F423" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G423" s="0" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" s="0" t="inlineStr">
+        <is>
+          <t>LV : LV (lv)</t>
+        </is>
+      </c>
+      <c r="C424" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lv/monitori/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D424" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F424" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G424" s="0" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" s="0" t="inlineStr">
+        <is>
+          <t>RU : RU (ru)</t>
+        </is>
+      </c>
+      <c r="C425" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/monitors/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D425" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F425" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G425" s="0" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" s="0" t="inlineStr">
+        <is>
+          <t>SK : SK (sk)</t>
+        </is>
+      </c>
+      <c r="C426" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sk/monitory/lg-40u990a-w/</t>
+        </is>
+      </c>
+      <c r="D426" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F426" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G426" s="0" t="inlineStr">
+        <is>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" s="0" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C427" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-45gx90sa-b/</t>
+        </is>
+      </c>
+      <c r="D427" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F427" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G427" s="0" t="inlineStr">
+        <is>
+          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" s="0" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C428" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-45gx90sa-b/</t>
+        </is>
+      </c>
+      <c r="D428" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F428" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G428" s="0" t="inlineStr">
+        <is>
+          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" s="0" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C429" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-45gx90sa-b/</t>
+        </is>
+      </c>
+      <c r="D429" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F429" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G429" s="0" t="inlineStr">
+        <is>
+          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" s="0" t="inlineStr">
+        <is>
+          <t>RS : RS (sr)</t>
+        </is>
+      </c>
+      <c r="C430" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-45gx90sa-b/</t>
+        </is>
+      </c>
+      <c r="D430" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F430" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G430" s="0" t="inlineStr">
+        <is>
+          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" s="0" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C431" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D431" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F431" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G431" s="0" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" s="0" t="inlineStr">
         <is>
           <t>GT : GT (es)</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cac/monitors/lg-32u889sa-w/</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F378" t="n">
-        <v>1</v>
-      </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="B379" t="inlineStr">
+      <c r="C432" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/monitors/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D432" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F432" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G432" s="0" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" s="0" t="inlineStr">
         <is>
           <t>CN : CN (zh)</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cn/monitors/lg-32u889sa-w/</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F379" t="n">
-        <v>1</v>
-      </c>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="B380" t="inlineStr">
+      <c r="C433" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/monitors/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D433" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F433" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G433" s="0" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" s="0" t="inlineStr">
         <is>
           <t>EC : EC (es)</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ec/monitores/lg-32u889sa-w/</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F380" t="n">
-        <v>1</v>
-      </c>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="B381" t="inlineStr">
+      <c r="C434" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ec/monitores/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D434" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F434" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G434" s="0" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" s="0" t="inlineStr">
+        <is>
+          <t>HR : HR (hr)</t>
+        </is>
+      </c>
+      <c r="C435" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hr/monitori/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D435" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F435" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G435" s="0" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" s="0" t="inlineStr">
         <is>
           <t>IL : IL (iw)</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/il/monitors/lg-32u889sa-w/</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F381" t="n">
-        <v>1</v>
-      </c>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="B382" t="inlineStr">
+      <c r="C436" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D436" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F436" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G436" s="0" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" s="0" t="inlineStr">
         <is>
           <t>RS : RS (sr)</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/rs/monitori/lg-32u889sa-w/</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F382" t="n">
-        <v>1</v>
-      </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>RU : RU (ru)</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ru/monitors/lg-32u889sa-w/</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F383" t="n">
-        <v>1</v>
-      </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>AE : AE (en)</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ae/consumer-monitors/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F384" t="n">
-        <v>1</v>
-      </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>AE_AR : AE (ar)</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ae_ar/consumer-monitors/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F385" t="n">
-        <v>1</v>
-      </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>AU : AU (en)</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/monitors/ultrafine-uhd-4k-5k/32u990a-s-aau/</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F386" t="n">
-        <v>1</v>
-      </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>BR : BR (pt)</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/br/monitores/monitores-uhd-4k/32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F387" t="n">
-        <v>1</v>
-      </c>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>GT : GT (es)</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cac/monitors/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F388" t="n">
-        <v>1</v>
-      </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>CN : CN (zh)</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cn/monitors/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F389" t="n">
-        <v>1</v>
-      </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>DK : DK (da)</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/dk/skaerme/ultrafine-uhd-4k-og-5k-skaerme/32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F390" t="n">
-        <v>1</v>
-      </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>EC : EC (es)</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ec/monitores/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F391" t="n">
-        <v>1</v>
-      </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>FI : FI (fi)</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fi/naytot/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F392" t="n">
-        <v>1</v>
-      </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>FR : FR (fr)</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/moniteurs/uhd-4k-5k/lg-32u990a-s-moniteur-bureautique/</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F393" t="n">
-        <v>1</v>
-      </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="B394" t="inlineStr">
+      <c r="C437" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D437" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F437" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G437" s="0" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" s="0" t="inlineStr">
+        <is>
+          <t>SK : SK (sk)</t>
+        </is>
+      </c>
+      <c r="C438" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sk/monitory/lg-45gx950a-b/</t>
+        </is>
+      </c>
+      <c r="D438" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F438" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G438" s="0" t="inlineStr">
+        <is>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" s="0" t="inlineStr">
+        <is>
+          <t>BG : BG (bg)</t>
+        </is>
+      </c>
+      <c r="C439" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bg/monitori/lg-49u950a-w/</t>
+        </is>
+      </c>
+      <c r="D439" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F439" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G439" s="0" t="inlineStr">
+        <is>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" s="0" t="inlineStr">
+        <is>
+          <t>EE : EE (et)</t>
+        </is>
+      </c>
+      <c r="C440" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/monitorid/lg-49u950a-w/</t>
+        </is>
+      </c>
+      <c r="D440" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F440" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G440" s="0" t="inlineStr">
+        <is>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" s="0" t="inlineStr">
         <is>
           <t>GR : GR (el)</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/gr/othones/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F394" t="n">
-        <v>1</v>
-      </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>HR : HR (hr)</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/hr/monitori/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F395" t="n">
-        <v>1</v>
-      </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>HU : HU (hu)</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/hu/monitorok/ultrafine-uhd-4k-es-5k-monitor/32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F396" t="n">
-        <v>1</v>
-      </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>ID : ID (in)</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/id/monitors/32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F397" t="n">
-        <v>1</v>
-      </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="B398" t="inlineStr">
+      <c r="C441" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/gr/othones/lg-49u950a-w/</t>
+        </is>
+      </c>
+      <c r="D441" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F441" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G441" s="0" t="inlineStr">
+        <is>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" s="0" t="inlineStr">
         <is>
           <t>IL : IL (iw)</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/il/monitors/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F398" t="n">
-        <v>1</v>
-      </c>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>MX : MX (es)</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/mx/monitores/todos-los-monitores/32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F399" t="n">
-        <v>1</v>
-      </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>NL : NL (nl)</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/nl/monitoren/ultrafine-uhd-4k-5k-monitoren/32U990A-S/</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F400" t="n">
-        <v>1</v>
-      </c>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>RO : RO (ro)</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ro/monitoare/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F401" t="n">
-        <v>1</v>
-      </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="B402" t="inlineStr">
+      <c r="C442" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-49u950a-w/</t>
+        </is>
+      </c>
+      <c r="D442" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F442" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G442" s="0" t="inlineStr">
+        <is>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" s="0" t="inlineStr">
         <is>
           <t>RS : RS (sr)</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/rs/monitori/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F402" t="n">
-        <v>1</v>
-      </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>SE : SE (sv)</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/se/monitors/uhd-4k-5k/32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F403" t="n">
-        <v>1</v>
-      </c>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="B404" t="inlineStr">
+      <c r="C443" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/monitori/lg-49u950a-w/</t>
+        </is>
+      </c>
+      <c r="D443" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F443" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G443" s="0" t="inlineStr">
+        <is>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" s="0" t="inlineStr">
         <is>
           <t>SK : SK (sk)</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sk/monitory/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F404" t="n">
-        <v>1</v>
-      </c>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>CN : CN (zh)</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cn/monitors/lg-34u601b-b/</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F405" t="n">
-        <v>1</v>
-      </c>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>ES : ES (es)</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/es/monitores/monitores-ultrawide/34u601b-b/</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F406" t="n">
-        <v>1</v>
-      </c>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>IT : IT (it)</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/monitor/ultrawide/34u601b-b-aeuq/</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F407" t="n">
-        <v>1</v>
-      </c>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>BR : BR (pt)</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/br/monitores/monitores-ultrawide/34u620b-b/</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F408" t="n">
-        <v>1</v>
-      </c>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>34U620B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>RS : RS (sr)</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/rs/monitori/lg-34u620b-b/</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F409" t="n">
-        <v>1</v>
-      </c>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>34U620B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>CZ : CZ (cs)</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cz/monitory/ultrawide-sirokouhle-monitory/34u640b-b/</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F410" t="n">
-        <v>1</v>
-      </c>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>34U640B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>CZ : CZ (cs)</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cz/monitory/smart/34u640sb-w/</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F411" t="n">
-        <v>1</v>
-      </c>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>34U640SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>BG : BG (bg)</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/bg/monitori/lg-39gx90sa-w/</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F412" t="n">
-        <v>1</v>
-      </c>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>CN : CN (zh)</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cn/monitors/lg-39gx90sa-w/</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F413" t="n">
-        <v>1</v>
-      </c>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>EE : EE (et)</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ee/monitorid/lg-39gx90sa-w/</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F414" t="n">
-        <v>1</v>
-      </c>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>FR : FR (fr)</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/moniteurs/gaming/lg-39gx90sa-w-moniteur-ultragear/</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F415" t="n">
-        <v>1</v>
-      </c>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>HR : HR (hr)</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/hr/monitori/lg-39gx90sa-w/</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F416" t="n">
-        <v>1</v>
-      </c>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>RS : RS (sr)</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/rs/monitori/lg-39gx90sa-w/</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F417" t="n">
-        <v>1</v>
-      </c>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>BE_FR : BE (fr)</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/be_fr/moniteurs/moniteurs-ultrafine/40U990A-W/</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F418" t="n">
-        <v>1</v>
-      </c>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>CN : CN (zh)</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cn/monitors/lg-40u990a-w/</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F419" t="n">
-        <v>1</v>
-      </c>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>EE : EE (et)</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ee/monitorid/lg-40u990a-w/</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F420" t="n">
-        <v>1</v>
-      </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>GR : GR (el)</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/gr/othones/lg-40u990a-w/</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F421" t="n">
-        <v>1</v>
-      </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>IL : IL (iw)</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/il/monitors/lg-40u990a-w/</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F422" t="n">
-        <v>1</v>
-      </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>LT : LT (lt)</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/lt/monitoriai/lg-40u990a-w/</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F423" t="n">
-        <v>1</v>
-      </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>LV : LV (lv)</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/lv/monitori/lg-40u990a-w/</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F424" t="n">
-        <v>1</v>
-      </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>RU : RU (ru)</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ru/monitors/lg-40u990a-w/</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F425" t="n">
-        <v>1</v>
-      </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>SK : SK (sk)</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sk/monitory/lg-40u990a-w/</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F426" t="n">
-        <v>1</v>
-      </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>BG : BG (bg)</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/bg/monitori/lg-45gx90sa-b/</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F427" t="n">
-        <v>1</v>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>CN : CN (zh)</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cn/monitors/lg-45gx90sa-b/</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F428" t="n">
-        <v>1</v>
-      </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>HR : HR (hr)</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/hr/monitori/lg-45gx90sa-b/</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F429" t="n">
-        <v>1</v>
-      </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>RS : RS (sr)</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/rs/monitori/lg-45gx90sa-b/</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="F430" t="n">
-        <v>1</v>
-      </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>BG : BG (bg)</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/bg/monitori/lg-45gx950a-b/</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F431" t="n">
-        <v>1</v>
-      </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>GT : GT (es)</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cac/monitors/lg-45gx950a-b/</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F432" t="n">
-        <v>1</v>
-      </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>CN : CN (zh)</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cn/monitors/lg-45gx950a-b/</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F433" t="n">
-        <v>1</v>
-      </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>EC : EC (es)</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ec/monitores/lg-45gx950a-b/</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F434" t="n">
-        <v>1</v>
-      </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>HR : HR (hr)</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/hr/monitori/lg-45gx950a-b/</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F435" t="n">
-        <v>1</v>
-      </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>IL : IL (iw)</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/il/monitors/lg-45gx950a-b/</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F436" t="n">
-        <v>1</v>
-      </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>RS : RS (sr)</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/rs/monitori/lg-45gx950a-b/</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F437" t="n">
-        <v>1</v>
-      </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>SK : SK (sk)</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sk/monitory/lg-45gx950a-b/</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F438" t="n">
-        <v>1</v>
-      </c>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>BG : BG (bg)</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/bg/monitori/lg-49u950a-w/</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F439" t="n">
-        <v>1</v>
-      </c>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>EE : EE (et)</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ee/monitorid/lg-49u950a-w/</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F440" t="n">
-        <v>1</v>
-      </c>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>GR : GR (el)</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/gr/othones/lg-49u950a-w/</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F441" t="n">
-        <v>1</v>
-      </c>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>IL : IL (iw)</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/il/monitors/lg-49u950a-w/</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F442" t="n">
-        <v>1</v>
-      </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>RS : RS (sr)</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/rs/monitori/lg-49u950a-w/</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F443" t="n">
-        <v>1</v>
-      </c>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>SK : SK (sk)</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
+      <c r="C444" s="0" t="inlineStr">
         <is>
           <t>https://www.lg.com/sk/monitory/lg-49u950a-w/</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F444" t="n">
-        <v>1</v>
-      </c>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+      <c r="D444" s="0" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="F444" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G444" s="0" t="inlineStr">
+        <is>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -10818,7 +10818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13762,50 +13762,6 @@
       <c r="G112" s="0" t="inlineStr">
         <is>
           <t>14Z90U-G-AU74A3 · Erase.Lock 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115">
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/notebook/gram-pro/17z90u-g-au78dn/</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/notebook/gram/15u50u-g-ar53dn/</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/notebook/gram-pro/17z90ub-h-au79dn/</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/16z90u-kub4j/</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/17z90ub-hu9cj/</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sg/laptops/gram/14z90u-g-au74a3/</t>
         </is>
       </c>
     </row>
@@ -13911,12 +13867,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId106"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -20651,7 +20651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G451"/>
+  <dimension ref="A1:G444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="203" min="1" max="1"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>PTT 갤러리/PDP 추적(2026-08-27) · 완료 428 · 작업중 20 · 갤러리체크 34 · 어워드외 6</t>
+          <t>완료 일괄(2026-08-31) · 지정 URL 7건 삭제 · 완료 441</t>
         </is>
       </c>
     </row>
@@ -20740,7 +20740,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E4" s="0" t="inlineStr"/>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F4" s="0" t="n">
         <v>1</v>
       </c>
@@ -20766,7 +20770,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E5" s="0" t="inlineStr"/>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F5" s="0" t="n">
         <v>1</v>
       </c>
@@ -20792,7 +20800,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E6" s="0" t="inlineStr"/>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F6" s="0" t="n">
         <v>1</v>
       </c>
@@ -20814,7 +20826,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E7" s="0" t="inlineStr"/>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F7" s="0" t="n">
         <v>1</v>
       </c>
@@ -20900,7 +20916,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E10" s="0" t="inlineStr"/>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F10" s="0" t="n">
         <v>1</v>
       </c>
@@ -20956,7 +20976,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E12" s="0" t="inlineStr"/>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F12" s="0" t="n">
         <v>1</v>
       </c>
@@ -20982,7 +21006,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E13" s="0" t="inlineStr"/>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F13" s="0" t="n">
         <v>1</v>
       </c>
@@ -21008,7 +21036,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E14" s="0" t="inlineStr"/>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F14" s="0" t="n">
         <v>1</v>
       </c>
@@ -21034,7 +21066,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E15" s="0" t="inlineStr"/>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F15" s="0" t="n">
         <v>1</v>
       </c>
@@ -21060,7 +21096,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E16" s="0" t="inlineStr"/>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F16" s="0" t="n">
         <v>1</v>
       </c>
@@ -21086,7 +21126,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E17" s="0" t="inlineStr"/>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F17" s="0" t="n">
         <v>1</v>
       </c>
@@ -21112,7 +21156,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E18" s="0" t="inlineStr"/>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F18" s="0" t="n">
         <v>1</v>
       </c>
@@ -21138,7 +21186,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E19" s="0" t="inlineStr"/>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F19" s="0" t="n">
         <v>1</v>
       </c>
@@ -21164,7 +21216,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E20" s="0" t="inlineStr"/>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F20" s="0" t="n">
         <v>1</v>
       </c>
@@ -21190,7 +21246,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E21" s="0" t="inlineStr"/>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F21" s="0" t="n">
         <v>1</v>
       </c>
@@ -21216,7 +21276,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E22" s="0" t="inlineStr"/>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F22" s="0" t="n">
         <v>1</v>
       </c>
@@ -21238,7 +21302,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E23" s="0" t="inlineStr"/>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F23" s="0" t="n">
         <v>1</v>
       </c>
@@ -21260,7 +21328,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E24" s="0" t="inlineStr"/>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F24" s="0" t="n">
         <v>1</v>
       </c>
@@ -21286,7 +21358,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E25" s="0" t="inlineStr"/>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F25" s="0" t="n">
         <v>1</v>
       </c>
@@ -21312,7 +21388,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E26" s="0" t="inlineStr"/>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F26" s="0" t="n">
         <v>1</v>
       </c>
@@ -21338,7 +21418,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E27" s="0" t="inlineStr"/>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F27" s="0" t="n">
         <v>1</v>
       </c>
@@ -21364,7 +21448,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E28" s="0" t="inlineStr"/>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F28" s="0" t="n">
         <v>1</v>
       </c>
@@ -21390,7 +21478,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E29" s="0" t="inlineStr"/>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F29" s="0" t="n">
         <v>1</v>
       </c>
@@ -21416,7 +21508,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E30" s="0" t="inlineStr"/>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F30" s="0" t="n">
         <v>1</v>
       </c>
@@ -21532,7 +21628,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E34" s="0" t="inlineStr"/>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F34" s="0" t="n">
         <v>1</v>
       </c>
@@ -21614,7 +21714,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E37" s="0" t="inlineStr"/>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F37" s="0" t="n">
         <v>1</v>
       </c>
@@ -21880,7 +21984,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E46" s="0" t="inlineStr"/>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F46" s="0" t="n">
         <v>1</v>
       </c>
@@ -21962,7 +22070,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E49" s="0" t="inlineStr"/>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F49" s="0" t="n">
         <v>1</v>
       </c>
@@ -22348,7 +22460,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E62" s="0" t="inlineStr"/>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F62" s="0" t="n">
         <v>1</v>
       </c>
@@ -22400,7 +22516,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E64" s="0" t="inlineStr"/>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F64" s="0" t="n">
         <v>1</v>
       </c>
@@ -22726,7 +22846,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E75" s="0" t="inlineStr"/>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F75" s="0" t="n">
         <v>1</v>
       </c>
@@ -22812,7 +22936,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E78" s="0" t="inlineStr"/>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F78" s="0" t="n">
         <v>1</v>
       </c>
@@ -22838,7 +22966,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E79" s="0" t="inlineStr"/>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F79" s="0" t="n">
         <v>1</v>
       </c>
@@ -22954,7 +23086,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E83" s="0" t="inlineStr"/>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F83" s="0" t="n">
         <v>1</v>
       </c>
@@ -23070,7 +23206,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E87" s="0" t="inlineStr"/>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F87" s="0" t="n">
         <v>1</v>
       </c>
@@ -23096,7 +23236,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E88" s="0" t="inlineStr"/>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F88" s="0" t="n">
         <v>1</v>
       </c>
@@ -23182,7 +23326,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E91" s="0" t="inlineStr"/>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F91" s="0" t="n">
         <v>1</v>
       </c>
@@ -23268,7 +23416,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E94" s="0" t="inlineStr"/>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F94" s="0" t="n">
         <v>1</v>
       </c>
@@ -23324,7 +23476,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E96" s="0" t="inlineStr"/>
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F96" s="0" t="n">
         <v>1</v>
       </c>
@@ -23380,7 +23536,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E98" s="0" t="inlineStr"/>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F98" s="0" t="n">
         <v>1</v>
       </c>
@@ -23406,7 +23566,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E99" s="0" t="inlineStr"/>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F99" s="0" t="n">
         <v>1</v>
       </c>
@@ -23522,7 +23686,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E103" s="0" t="inlineStr"/>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F103" s="0" t="n">
         <v>1</v>
       </c>
@@ -23548,7 +23716,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E104" s="0" t="inlineStr"/>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F104" s="0" t="n">
         <v>1</v>
       </c>
@@ -23844,7 +24016,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E114" s="0" t="inlineStr"/>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F114" s="0" t="n">
         <v>1</v>
       </c>
@@ -23870,7 +24046,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E115" s="0" t="inlineStr"/>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F115" s="0" t="n">
         <v>1</v>
       </c>
@@ -23896,7 +24076,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E116" s="0" t="inlineStr"/>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F116" s="0" t="n">
         <v>1</v>
       </c>
@@ -23922,7 +24106,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E117" s="0" t="inlineStr"/>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F117" s="0" t="n">
         <v>1</v>
       </c>
@@ -23948,7 +24136,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E118" s="0" t="inlineStr"/>
+      <c r="E118" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F118" s="0" t="n">
         <v>1</v>
       </c>
@@ -23974,7 +24166,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E119" s="0" t="inlineStr"/>
+      <c r="E119" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F119" s="0" t="n">
         <v>1</v>
       </c>
@@ -24000,7 +24196,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E120" s="0" t="inlineStr"/>
+      <c r="E120" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F120" s="0" t="n">
         <v>1</v>
       </c>
@@ -24026,7 +24226,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E121" s="0" t="inlineStr"/>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F121" s="0" t="n">
         <v>1</v>
       </c>
@@ -24082,7 +24286,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E123" s="0" t="inlineStr"/>
+      <c r="E123" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F123" s="0" t="n">
         <v>1</v>
       </c>
@@ -24288,7 +24496,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E130" s="0" t="inlineStr"/>
+      <c r="E130" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F130" s="0" t="n">
         <v>1</v>
       </c>
@@ -24524,7 +24736,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E138" s="0" t="inlineStr"/>
+      <c r="E138" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F138" s="0" t="n">
         <v>1</v>
       </c>
@@ -24850,7 +25066,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E149" s="0" t="inlineStr"/>
+      <c r="E149" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F149" s="0" t="n">
         <v>1</v>
       </c>
@@ -25116,7 +25336,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E158" s="0" t="inlineStr"/>
+      <c r="E158" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F158" s="0" t="n">
         <v>1</v>
       </c>
@@ -25772,7 +25996,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E180" s="0" t="inlineStr"/>
+      <c r="E180" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F180" s="0" t="n">
         <v>1</v>
       </c>
@@ -25828,7 +26056,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E182" s="0" t="inlineStr"/>
+      <c r="E182" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F182" s="0" t="n">
         <v>1</v>
       </c>
@@ -25854,7 +26086,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E183" s="0" t="inlineStr"/>
+      <c r="E183" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F183" s="0" t="n">
         <v>1</v>
       </c>
@@ -25880,7 +26116,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E184" s="0" t="inlineStr"/>
+      <c r="E184" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F184" s="0" t="n">
         <v>1</v>
       </c>
@@ -25966,7 +26206,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E187" s="0" t="inlineStr"/>
+      <c r="E187" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F187" s="0" t="n">
         <v>1</v>
       </c>
@@ -26022,7 +26266,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E189" s="0" t="inlineStr"/>
+      <c r="E189" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F189" s="0" t="n">
         <v>1</v>
       </c>
@@ -26198,7 +26446,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E195" s="0" t="inlineStr"/>
+      <c r="E195" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F195" s="0" t="n">
         <v>1</v>
       </c>
@@ -26224,7 +26476,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E196" s="0" t="inlineStr"/>
+      <c r="E196" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F196" s="0" t="n">
         <v>1</v>
       </c>
@@ -26280,7 +26536,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E198" s="0" t="inlineStr"/>
+      <c r="E198" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F198" s="0" t="n">
         <v>1</v>
       </c>
@@ -26306,7 +26566,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E199" s="0" t="inlineStr"/>
+      <c r="E199" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F199" s="0" t="n">
         <v>1</v>
       </c>
@@ -26452,7 +26716,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E204" s="0" t="inlineStr"/>
+      <c r="E204" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F204" s="0" t="n">
         <v>1</v>
       </c>
@@ -26658,7 +26926,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E211" s="0" t="inlineStr"/>
+      <c r="E211" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F211" s="0" t="n">
         <v>1</v>
       </c>
@@ -27614,7 +27886,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E243" s="0" t="inlineStr"/>
+      <c r="E243" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F243" s="0" t="n">
         <v>1</v>
       </c>
@@ -28360,7 +28636,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E268" s="0" t="inlineStr"/>
+      <c r="E268" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F268" s="0" t="n">
         <v>1</v>
       </c>
@@ -28386,7 +28666,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E269" s="0" t="inlineStr"/>
+      <c r="E269" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F269" s="0" t="n">
         <v>1</v>
       </c>
@@ -28472,7 +28756,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E272" s="0" t="inlineStr"/>
+      <c r="E272" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F272" s="0" t="n">
         <v>1</v>
       </c>
@@ -28708,7 +28996,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E280" s="0" t="inlineStr"/>
+      <c r="E280" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F280" s="0" t="n">
         <v>1</v>
       </c>
@@ -28734,7 +29026,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E281" s="0" t="inlineStr"/>
+      <c r="E281" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F281" s="0" t="n">
         <v>1</v>
       </c>
@@ -29060,7 +29356,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E292" s="0" t="inlineStr"/>
+      <c r="E292" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F292" s="0" t="n">
         <v>1</v>
       </c>
@@ -29386,7 +29686,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E303" s="0" t="inlineStr"/>
+      <c r="E303" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F303" s="0" t="n">
         <v>1</v>
       </c>
@@ -29412,7 +29716,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E304" s="0" t="inlineStr"/>
+      <c r="E304" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="F304" s="0" t="n">
         <v>1</v>
       </c>
@@ -29918,6 +30226,11 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="E321" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="F321" s="0" t="n">
         <v>1</v>
       </c>
@@ -29930,17 +30243,22 @@
     <row r="322">
       <c r="B322" s="0" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>CZ : CZ (cs)</t>
         </is>
       </c>
       <c r="C322" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/monitors/full-hd/24u411b-b-acc/</t>
+          <t>https://www.lg.com/cz/monitory/smart/24u411b-b/</t>
         </is>
       </c>
       <c r="D322" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E322" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F322" s="0" t="n">
@@ -29948,24 +30266,29 @@
       </c>
       <c r="G322" s="0" t="inlineStr">
         <is>
-          <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01)</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="B323" s="0" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>PE : PE (es)</t>
         </is>
       </c>
       <c r="C323" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/moniteurs/pleine-hd/24u411b-b-acc/</t>
+          <t>https://www.lg.com/pe/monitores/fhd-y-qhd/24u411b-b/</t>
         </is>
       </c>
       <c r="D323" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E323" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F323" s="0" t="n">
@@ -29973,24 +30296,29 @@
       </c>
       <c r="G323" s="0" t="inlineStr">
         <is>
-          <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="B324" s="0" t="inlineStr">
         <is>
-          <t>CZ : CZ (cs)</t>
+          <t>BG : BG (bg)</t>
         </is>
       </c>
       <c r="C324" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz/monitory/smart/24u411b-b/</t>
+          <t>https://www.lg.com/bg/monitori/lg-27g850a-b/</t>
         </is>
       </c>
       <c r="D324" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E324" s="0" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F324" s="0" t="n">
@@ -29998,19 +30326,19 @@
       </c>
       <c r="G324" s="0" t="inlineStr">
         <is>
-          <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="B325" s="0" t="inlineStr">
         <is>
-          <t>PE : PE (es)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C325" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pe/monitores/fhd-y-qhd/24u411b-b/</t>
+          <t>https://www.lg.com/cn/monitors/lg-27g850a-b/</t>
         </is>
       </c>
       <c r="D325" s="0" t="inlineStr">
@@ -30018,24 +30346,29 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="E325" s="0" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
       <c r="F325" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G325" s="0" t="inlineStr">
         <is>
-          <t>24U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="B326" s="0" t="inlineStr">
         <is>
-          <t>BG : BG (bg)</t>
+          <t>EE : EE (et)</t>
         </is>
       </c>
       <c r="C326" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/bg/monitori/lg-27g850a-b/</t>
+          <t>https://www.lg.com/ee/monitorid/lg-27g850a-b/</t>
         </is>
       </c>
       <c r="D326" s="0" t="inlineStr">
@@ -30045,7 +30378,7 @@
       </c>
       <c r="E326" s="0" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="F326" s="0" t="n">
@@ -30060,12 +30393,12 @@
     <row r="327">
       <c r="B327" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>FI : FI (fi)</t>
         </is>
       </c>
       <c r="C327" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-27g850a-b/</t>
+          <t>https://www.lg.com/fi/naytot/lg-27g850a-b/</t>
         </is>
       </c>
       <c r="D327" s="0" t="inlineStr">
@@ -30075,7 +30408,7 @@
       </c>
       <c r="E327" s="0" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F327" s="0" t="n">
@@ -30090,12 +30423,12 @@
     <row r="328">
       <c r="B328" s="0" t="inlineStr">
         <is>
-          <t>EE : EE (et)</t>
+          <t>HR : HR (hr)</t>
         </is>
       </c>
       <c r="C328" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ee/monitorid/lg-27g850a-b/</t>
+          <t>https://www.lg.com/hr/monitori/lg-27g850a-b/</t>
         </is>
       </c>
       <c r="D328" s="0" t="inlineStr">
@@ -30105,7 +30438,7 @@
       </c>
       <c r="E328" s="0" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F328" s="0" t="n">
@@ -30120,12 +30453,12 @@
     <row r="329">
       <c r="B329" s="0" t="inlineStr">
         <is>
-          <t>FI : FI (fi)</t>
+          <t>LT : LT (lt)</t>
         </is>
       </c>
       <c r="C329" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fi/naytot/lg-27g850a-b/</t>
+          <t>https://www.lg.com/lt/monitoriai/lg-27g850a-b/</t>
         </is>
       </c>
       <c r="D329" s="0" t="inlineStr">
@@ -30135,7 +30468,7 @@
       </c>
       <c r="E329" s="0" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="F329" s="0" t="n">
@@ -30150,12 +30483,12 @@
     <row r="330">
       <c r="B330" s="0" t="inlineStr">
         <is>
-          <t>HR : HR (hr)</t>
+          <t>LV : LV (lv)</t>
         </is>
       </c>
       <c r="C330" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hr/monitori/lg-27g850a-b/</t>
+          <t>https://www.lg.com/lv/monitori/lg-27g850a-b/</t>
         </is>
       </c>
       <c r="D330" s="0" t="inlineStr">
@@ -30165,7 +30498,7 @@
       </c>
       <c r="E330" s="0" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="F330" s="0" t="n">
@@ -30180,12 +30513,12 @@
     <row r="331">
       <c r="B331" s="0" t="inlineStr">
         <is>
-          <t>LT : LT (lt)</t>
+          <t>NO : NO (no)</t>
         </is>
       </c>
       <c r="C331" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lt/monitoriai/lg-27g850a-b/</t>
+          <t>https://www.lg.com/no/skjermer/lg-27g850a-b/</t>
         </is>
       </c>
       <c r="D331" s="0" t="inlineStr">
@@ -30195,7 +30528,7 @@
       </c>
       <c r="E331" s="0" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F331" s="0" t="n">
@@ -30210,12 +30543,12 @@
     <row r="332">
       <c r="B332" s="0" t="inlineStr">
         <is>
-          <t>LV : LV (lv)</t>
+          <t>RO : RO (ro)</t>
         </is>
       </c>
       <c r="C332" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lv/monitori/lg-27g850a-b/</t>
+          <t>https://www.lg.com/ro/monitoare/lg-27g850a-b/</t>
         </is>
       </c>
       <c r="D332" s="0" t="inlineStr">
@@ -30225,7 +30558,7 @@
       </c>
       <c r="E332" s="0" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="F332" s="0" t="n">
@@ -30240,12 +30573,12 @@
     <row r="333">
       <c r="B333" s="0" t="inlineStr">
         <is>
-          <t>NO : NO (no)</t>
+          <t>RS : RS (sr)</t>
         </is>
       </c>
       <c r="C333" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/no/skjermer/lg-27g850a-b/</t>
+          <t>https://www.lg.com/rs/monitori/lg-27g850a-b/</t>
         </is>
       </c>
       <c r="D333" s="0" t="inlineStr">
@@ -30255,7 +30588,7 @@
       </c>
       <c r="E333" s="0" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="F333" s="0" t="n">
@@ -30270,12 +30603,12 @@
     <row r="334">
       <c r="B334" s="0" t="inlineStr">
         <is>
-          <t>RO : RO (ro)</t>
+          <t>RU : RU (ru)</t>
         </is>
       </c>
       <c r="C334" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ro/monitoare/lg-27g850a-b/</t>
+          <t>https://www.lg.com/ru/monitors/lg-27g850a-b/</t>
         </is>
       </c>
       <c r="D334" s="0" t="inlineStr">
@@ -30285,7 +30618,7 @@
       </c>
       <c r="E334" s="0" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="F334" s="0" t="n">
@@ -30300,12 +30633,12 @@
     <row r="335">
       <c r="B335" s="0" t="inlineStr">
         <is>
-          <t>RS : RS (sr)</t>
+          <t>BG : BG (bg)</t>
         </is>
       </c>
       <c r="C335" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/monitori/lg-27g850a-b/</t>
+          <t>https://www.lg.com/bg/monitori/lg-27gx700a-b/</t>
         </is>
       </c>
       <c r="D335" s="0" t="inlineStr">
@@ -30315,7 +30648,7 @@
       </c>
       <c r="E335" s="0" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F335" s="0" t="n">
@@ -30323,19 +30656,19 @@
       </c>
       <c r="G335" s="0" t="inlineStr">
         <is>
-          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="B336" s="0" t="inlineStr">
         <is>
-          <t>RU : RU (ru)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C336" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ru/monitors/lg-27g850a-b/</t>
+          <t>https://www.lg.com/cn/monitors/lg-27gx700a-b/</t>
         </is>
       </c>
       <c r="D336" s="0" t="inlineStr">
@@ -30345,7 +30678,7 @@
       </c>
       <c r="E336" s="0" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="F336" s="0" t="n">
@@ -30353,19 +30686,19 @@
       </c>
       <c r="G336" s="0" t="inlineStr">
         <is>
-          <t>27G850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="B337" s="0" t="inlineStr">
         <is>
-          <t>BG : BG (bg)</t>
+          <t>HR : HR (hr)</t>
         </is>
       </c>
       <c r="C337" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/bg/monitori/lg-27gx700a-b/</t>
+          <t>https://www.lg.com/hr/monitori/lg-27gx700a-b/</t>
         </is>
       </c>
       <c r="D337" s="0" t="inlineStr">
@@ -30375,7 +30708,7 @@
       </c>
       <c r="E337" s="0" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="F337" s="0" t="n">
@@ -30390,12 +30723,12 @@
     <row r="338">
       <c r="B338" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>IL : IL (iw)</t>
         </is>
       </c>
       <c r="C338" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-27gx700a-b/</t>
+          <t>https://www.lg.com/il/monitors/lg-27gx700a-b/</t>
         </is>
       </c>
       <c r="D338" s="0" t="inlineStr">
@@ -30405,7 +30738,7 @@
       </c>
       <c r="E338" s="0" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F338" s="0" t="n">
@@ -30420,12 +30753,12 @@
     <row r="339">
       <c r="B339" s="0" t="inlineStr">
         <is>
-          <t>HR : HR (hr)</t>
+          <t>RS : RS (sr)</t>
         </is>
       </c>
       <c r="C339" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hr/monitori/lg-27gx700a-b/</t>
+          <t>https://www.lg.com/rs/monitori/lg-27gx700a-b/</t>
         </is>
       </c>
       <c r="D339" s="0" t="inlineStr">
@@ -30435,7 +30768,7 @@
       </c>
       <c r="E339" s="0" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F339" s="0" t="n">
@@ -30450,12 +30783,12 @@
     <row r="340">
       <c r="B340" s="0" t="inlineStr">
         <is>
-          <t>IL : IL (iw)</t>
+          <t>RU : RU (ru)</t>
         </is>
       </c>
       <c r="C340" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/il/monitors/lg-27gx700a-b/</t>
+          <t>https://www.lg.com/ru/monitors/lg-27gx700a-b/</t>
         </is>
       </c>
       <c r="D340" s="0" t="inlineStr">
@@ -30465,7 +30798,7 @@
       </c>
       <c r="E340" s="0" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="F340" s="0" t="n">
@@ -30480,12 +30813,12 @@
     <row r="341">
       <c r="B341" s="0" t="inlineStr">
         <is>
-          <t>RS : RS (sr)</t>
+          <t>BG : BG (bg)</t>
         </is>
       </c>
       <c r="C341" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/monitori/lg-27gx700a-b/</t>
+          <t>https://www.lg.com/bg/monitori/lg-27gx790a-b/</t>
         </is>
       </c>
       <c r="D341" s="0" t="inlineStr">
@@ -30495,7 +30828,7 @@
       </c>
       <c r="E341" s="0" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F341" s="0" t="n">
@@ -30503,19 +30836,19 @@
       </c>
       <c r="G341" s="0" t="inlineStr">
         <is>
-          <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="B342" s="0" t="inlineStr">
         <is>
-          <t>RU : RU (ru)</t>
+          <t>GT : GT (es)</t>
         </is>
       </c>
       <c r="C342" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ru/monitors/lg-27gx700a-b/</t>
+          <t>https://www.lg.com/cac/monitors/lg-27gx790a-b/</t>
         </is>
       </c>
       <c r="D342" s="0" t="inlineStr">
@@ -30525,7 +30858,7 @@
       </c>
       <c r="E342" s="0" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="F342" s="0" t="n">
@@ -30533,19 +30866,19 @@
       </c>
       <c r="G342" s="0" t="inlineStr">
         <is>
-          <t>27GX700A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="B343" s="0" t="inlineStr">
         <is>
-          <t>BG : BG (bg)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C343" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/bg/monitori/lg-27gx790a-b/</t>
+          <t>https://www.lg.com/cn/monitors/lg-27gx790a-b/</t>
         </is>
       </c>
       <c r="D343" s="0" t="inlineStr">
@@ -30555,7 +30888,7 @@
       </c>
       <c r="E343" s="0" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="F343" s="0" t="n">
@@ -30570,12 +30903,12 @@
     <row r="344">
       <c r="B344" s="0" t="inlineStr">
         <is>
-          <t>GT : GT (es)</t>
+          <t>EC : EC (es)</t>
         </is>
       </c>
       <c r="C344" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cac/monitors/lg-27gx790a-b/</t>
+          <t>https://www.lg.com/ec/monitores/lg-27gx790a-b/</t>
         </is>
       </c>
       <c r="D344" s="0" t="inlineStr">
@@ -30600,12 +30933,12 @@
     <row r="345">
       <c r="B345" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>EE : EE (et)</t>
         </is>
       </c>
       <c r="C345" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-27gx790a-b/</t>
+          <t>https://www.lg.com/ee/monitorid/lg-27gx790a-b/</t>
         </is>
       </c>
       <c r="D345" s="0" t="inlineStr">
@@ -30615,7 +30948,7 @@
       </c>
       <c r="E345" s="0" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="F345" s="0" t="n">
@@ -30630,12 +30963,12 @@
     <row r="346">
       <c r="B346" s="0" t="inlineStr">
         <is>
-          <t>EC : EC (es)</t>
+          <t>HR : HR (hr)</t>
         </is>
       </c>
       <c r="C346" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ec/monitores/lg-27gx790a-b/</t>
+          <t>https://www.lg.com/hr/monitori/lg-27gx790a-b/</t>
         </is>
       </c>
       <c r="D346" s="0" t="inlineStr">
@@ -30645,7 +30978,7 @@
       </c>
       <c r="E346" s="0" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F346" s="0" t="n">
@@ -30660,12 +30993,12 @@
     <row r="347">
       <c r="B347" s="0" t="inlineStr">
         <is>
-          <t>EE : EE (et)</t>
+          <t>IL : IL (iw)</t>
         </is>
       </c>
       <c r="C347" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ee/monitorid/lg-27gx790a-b/</t>
+          <t>https://www.lg.com/il/monitors/lg-27gx790a-b/</t>
         </is>
       </c>
       <c r="D347" s="0" t="inlineStr">
@@ -30675,7 +31008,7 @@
       </c>
       <c r="E347" s="0" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="F347" s="0" t="n">
@@ -30690,12 +31023,12 @@
     <row r="348">
       <c r="B348" s="0" t="inlineStr">
         <is>
-          <t>HR : HR (hr)</t>
+          <t>LT : LT (lt)</t>
         </is>
       </c>
       <c r="C348" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hr/monitori/lg-27gx790a-b/</t>
+          <t>https://www.lg.com/lt/monitoriai/lg-27gx790a-b/</t>
         </is>
       </c>
       <c r="D348" s="0" t="inlineStr">
@@ -30705,7 +31038,7 @@
       </c>
       <c r="E348" s="0" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="F348" s="0" t="n">
@@ -30720,12 +31053,12 @@
     <row r="349">
       <c r="B349" s="0" t="inlineStr">
         <is>
-          <t>IL : IL (iw)</t>
+          <t>LV : LV (lv)</t>
         </is>
       </c>
       <c r="C349" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/il/monitors/lg-27gx790a-b/</t>
+          <t>https://www.lg.com/lv/monitori/lg-27gx790a-b/</t>
         </is>
       </c>
       <c r="D349" s="0" t="inlineStr">
@@ -30735,7 +31068,7 @@
       </c>
       <c r="E349" s="0" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="F349" s="0" t="n">
@@ -30750,12 +31083,12 @@
     <row r="350">
       <c r="B350" s="0" t="inlineStr">
         <is>
-          <t>LT : LT (lt)</t>
+          <t>RS : RS (sr)</t>
         </is>
       </c>
       <c r="C350" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lt/monitoriai/lg-27gx790a-b/</t>
+          <t>https://www.lg.com/rs/monitori/lg-27gx790a-b/</t>
         </is>
       </c>
       <c r="D350" s="0" t="inlineStr">
@@ -30765,7 +31098,7 @@
       </c>
       <c r="E350" s="0" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="F350" s="0" t="n">
@@ -30780,12 +31113,12 @@
     <row r="351">
       <c r="B351" s="0" t="inlineStr">
         <is>
-          <t>LV : LV (lv)</t>
+          <t>RU : RU (ru)</t>
         </is>
       </c>
       <c r="C351" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lv/monitori/lg-27gx790a-b/</t>
+          <t>https://www.lg.com/ru/monitors/lg-27gx790a-b/</t>
         </is>
       </c>
       <c r="D351" s="0" t="inlineStr">
@@ -30795,7 +31128,7 @@
       </c>
       <c r="E351" s="0" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="F351" s="0" t="n">
@@ -30810,12 +31143,12 @@
     <row r="352">
       <c r="B352" s="0" t="inlineStr">
         <is>
-          <t>RS : RS (sr)</t>
+          <t>SK : SK (sk)</t>
         </is>
       </c>
       <c r="C352" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/monitori/lg-27gx790a-b/</t>
+          <t>https://www.lg.com/sk/monitory/lg-27gx790a-b/</t>
         </is>
       </c>
       <c r="D352" s="0" t="inlineStr">
@@ -30825,7 +31158,7 @@
       </c>
       <c r="E352" s="0" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F352" s="0" t="n">
@@ -30840,12 +31173,12 @@
     <row r="353">
       <c r="B353" s="0" t="inlineStr">
         <is>
-          <t>RU : RU (ru)</t>
+          <t>BG : BG (bg)</t>
         </is>
       </c>
       <c r="C353" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ru/monitors/lg-27gx790a-b/</t>
+          <t>https://www.lg.com/bg/monitori/lg-27gx790b-b/</t>
         </is>
       </c>
       <c r="D353" s="0" t="inlineStr">
@@ -30855,7 +31188,7 @@
       </c>
       <c r="E353" s="0" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F353" s="0" t="n">
@@ -30863,19 +31196,19 @@
       </c>
       <c r="G353" s="0" t="inlineStr">
         <is>
-          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="B354" s="0" t="inlineStr">
         <is>
-          <t>SK : SK (sk)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C354" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sk/monitory/lg-27gx790a-b/</t>
+          <t>https://www.lg.com/cn/monitors/lg-27gx790b-b/</t>
         </is>
       </c>
       <c r="D354" s="0" t="inlineStr">
@@ -30885,7 +31218,7 @@
       </c>
       <c r="E354" s="0" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="F354" s="0" t="n">
@@ -30893,19 +31226,19 @@
       </c>
       <c r="G354" s="0" t="inlineStr">
         <is>
-          <t>27GX790A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="B355" s="0" t="inlineStr">
         <is>
-          <t>BG : BG (bg)</t>
+          <t>CZ : CZ (cs)</t>
         </is>
       </c>
       <c r="C355" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/bg/monitori/lg-27gx790b-b/</t>
+          <t>https://www.lg.com/cz/promotions/ultragear-gaming-monitory/27gx790b-b/</t>
         </is>
       </c>
       <c r="D355" s="0" t="inlineStr">
@@ -30913,24 +31246,29 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="E355" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
       <c r="F355" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G355" s="0" t="inlineStr">
         <is>
-          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01)</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="B356" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>HR : HR (hr)</t>
         </is>
       </c>
       <c r="C356" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-27gx790b-b/</t>
+          <t>https://www.lg.com/hr/monitori/lg-27gx790b-b/</t>
         </is>
       </c>
       <c r="D356" s="0" t="inlineStr">
@@ -30940,7 +31278,7 @@
       </c>
       <c r="E356" s="0" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F356" s="0" t="n">
@@ -30955,17 +31293,22 @@
     <row r="357">
       <c r="B357" s="0" t="inlineStr">
         <is>
-          <t>CZ : CZ (cs)</t>
+          <t>ID : ID (in)</t>
         </is>
       </c>
       <c r="C357" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz/promotions/ultragear-gaming-monitory/27gx790b-b/</t>
+          <t>https://www.lg.com/id/monitor/gaming/27gx790b/</t>
         </is>
       </c>
       <c r="D357" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E357" s="0" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F357" s="0" t="n">
@@ -30973,24 +31316,29 @@
       </c>
       <c r="G357" s="0" t="inlineStr">
         <is>
-          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="B358" s="0" t="inlineStr">
         <is>
-          <t>HR : HR (hr)</t>
+          <t>IL : IL (iw)</t>
         </is>
       </c>
       <c r="C358" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hr/monitori/lg-27gx790b-b/</t>
+          <t>https://www.lg.com/il/monitors/lg-27gx790b-b/</t>
         </is>
       </c>
       <c r="D358" s="0" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="E358" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="F358" s="0" t="n">
@@ -31005,12 +31353,12 @@
     <row r="359">
       <c r="B359" s="0" t="inlineStr">
         <is>
-          <t>ID : ID (in)</t>
+          <t>RS : RS (sr)</t>
         </is>
       </c>
       <c r="C359" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/id/monitor/gaming/27gx790b/</t>
+          <t>https://www.lg.com/rs/monitori/lg-27gx790b-b/</t>
         </is>
       </c>
       <c r="D359" s="0" t="inlineStr">
@@ -31020,7 +31368,7 @@
       </c>
       <c r="E359" s="0" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F359" s="0" t="n">
@@ -31035,12 +31383,12 @@
     <row r="360">
       <c r="B360" s="0" t="inlineStr">
         <is>
-          <t>IL : IL (iw)</t>
+          <t>TW : TW (zh)</t>
         </is>
       </c>
       <c r="C360" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/il/monitors/lg-27gx790b-b/</t>
+          <t>https://www.lg.com/tw/monitors/ultragear-gaming/27gx790b-b/</t>
         </is>
       </c>
       <c r="D360" s="0" t="inlineStr">
@@ -31050,7 +31398,7 @@
       </c>
       <c r="E360" s="0" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F360" s="0" t="n">
@@ -31058,19 +31406,19 @@
       </c>
       <c r="G360" s="0" t="inlineStr">
         <is>
-          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="B361" s="0" t="inlineStr">
         <is>
-          <t>RS : RS (sr)</t>
+          <t>AU : AU (en)</t>
         </is>
       </c>
       <c r="C361" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/monitori/lg-27gx790b-b/</t>
+          <t>https://www.lg.com/au/monitors/full-hd-qhd/27u411b-b/</t>
         </is>
       </c>
       <c r="D361" s="0" t="inlineStr">
@@ -31078,29 +31426,39 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="E361" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F361" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G361" s="0" t="inlineStr">
         <is>
-          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>27U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="B362" s="0" t="inlineStr">
         <is>
-          <t>TW : TW (zh)</t>
+          <t>CZ : CZ (cs)</t>
         </is>
       </c>
       <c r="C362" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tw/monitors/ultragear-gaming/27gx790b-b/</t>
+          <t>https://www.lg.com/cz/monitory/professional-monitor/27u731sb-w/</t>
         </is>
       </c>
       <c r="D362" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E362" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F362" s="0" t="n">
@@ -31108,19 +31466,19 @@
       </c>
       <c r="G362" s="0" t="inlineStr">
         <is>
-          <t>27GX790B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>27U731SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01)</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="B363" s="0" t="inlineStr">
         <is>
-          <t>AU : AU (en)</t>
+          <t>BG : BG (bg)</t>
         </is>
       </c>
       <c r="C363" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/au/monitors/full-hd-qhd/27u411b-b/</t>
+          <t>https://www.lg.com/bg/monitori/lg-32gx850a-b/</t>
         </is>
       </c>
       <c r="D363" s="0" t="inlineStr">
@@ -31128,29 +31486,39 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="E363" s="0" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
       <c r="F363" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G363" s="0" t="inlineStr">
         <is>
-          <t>27U411B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="B364" s="0" t="inlineStr">
         <is>
-          <t>CZ : CZ (cs)</t>
+          <t>GT : GT (es)</t>
         </is>
       </c>
       <c r="C364" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz/monitory/ultrafine-uhd-4k-monitory/27u511sb-b/</t>
+          <t>https://www.lg.com/cac/monitors/lg-32gx850a-b/</t>
         </is>
       </c>
       <c r="D364" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E364" s="0" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="F364" s="0" t="n">
@@ -31158,24 +31526,29 @@
       </c>
       <c r="G364" s="0" t="inlineStr">
         <is>
-          <t>27U511SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="B365" s="0" t="inlineStr">
         <is>
-          <t>CZ : CZ (cs)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C365" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz/monitory/ultrafine-uhd-4k-monitory/27u511sb-w/</t>
+          <t>https://www.lg.com/cn/monitors/lg-32gx850a-b/</t>
         </is>
       </c>
       <c r="D365" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E365" s="0" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F365" s="0" t="n">
@@ -31183,24 +31556,29 @@
       </c>
       <c r="G365" s="0" t="inlineStr">
         <is>
-          <t>27U511SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="B366" s="0" t="inlineStr">
         <is>
-          <t>CZ : CZ (cs)</t>
+          <t>SK : SK (sk)</t>
         </is>
       </c>
       <c r="C366" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz/monitory/professional-monitor/27u731sb-w/</t>
+          <t>https://www.lg.com/sk/monitory/lg-32gx850a-b/</t>
         </is>
       </c>
       <c r="D366" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E366" s="0" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="F366" s="0" t="n">
@@ -31208,24 +31586,29 @@
       </c>
       <c r="G366" s="0" t="inlineStr">
         <is>
-          <t>27U731SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="B367" s="0" t="inlineStr">
         <is>
-          <t>VN : VN (vi)</t>
+          <t>ID : ID (in)</t>
         </is>
       </c>
       <c r="C367" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/vn/man-hinh-may-tinh/man-hinh-do-hoa-ultrafine/27u731sb-w/</t>
+          <t>https://www.lg.com/id/monitor/fhd-qhd/32u401b-b/</t>
         </is>
       </c>
       <c r="D367" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E367" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F367" s="0" t="n">
@@ -31233,19 +31616,19 @@
       </c>
       <c r="G367" s="0" t="inlineStr">
         <is>
-          <t>27U731SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>32U401B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="B368" s="0" t="inlineStr">
         <is>
-          <t>BG : BG (bg)</t>
+          <t>CZ : CZ (cs)</t>
         </is>
       </c>
       <c r="C368" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/bg/monitori/lg-32gx850a-b/</t>
+          <t>https://www.lg.com/cz/monitory/smart/32u701sb-b/</t>
         </is>
       </c>
       <c r="D368" s="0" t="inlineStr">
@@ -31255,7 +31638,7 @@
       </c>
       <c r="E368" s="0" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F368" s="0" t="n">
@@ -31263,19 +31646,19 @@
       </c>
       <c r="G368" s="0" t="inlineStr">
         <is>
-          <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U701SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01)</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="B369" s="0" t="inlineStr">
         <is>
-          <t>GT : GT (es)</t>
+          <t>BG : BG (bg)</t>
         </is>
       </c>
       <c r="C369" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cac/monitors/lg-32gx850a-b/</t>
+          <t>https://www.lg.com/bg/monitori/lg-32u889sa-w/</t>
         </is>
       </c>
       <c r="D369" s="0" t="inlineStr">
@@ -31285,7 +31668,7 @@
       </c>
       <c r="E369" s="0" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F369" s="0" t="n">
@@ -31293,19 +31676,19 @@
       </c>
       <c r="G369" s="0" t="inlineStr">
         <is>
-          <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="B370" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>BR : BR (pt)</t>
         </is>
       </c>
       <c r="C370" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-32gx850a-b/</t>
+          <t>https://www.lg.com/br/business/monitores/monitores-produtos/monitores-ultrawide/32u889sa-w/</t>
         </is>
       </c>
       <c r="D370" s="0" t="inlineStr">
@@ -31315,7 +31698,7 @@
       </c>
       <c r="E370" s="0" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="F370" s="0" t="n">
@@ -31323,19 +31706,19 @@
       </c>
       <c r="G370" s="0" t="inlineStr">
         <is>
-          <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="B371" s="0" t="inlineStr">
         <is>
-          <t>SK : SK (sk)</t>
+          <t>GT : GT (es)</t>
         </is>
       </c>
       <c r="C371" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sk/monitory/lg-32gx850a-b/</t>
+          <t>https://www.lg.com/cac/monitors/lg-32u889sa-w/</t>
         </is>
       </c>
       <c r="D371" s="0" t="inlineStr">
@@ -31353,19 +31736,19 @@
       </c>
       <c r="G371" s="0" t="inlineStr">
         <is>
-          <t>32GX850A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="B372" s="0" t="inlineStr">
         <is>
-          <t>ID : ID (in)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C372" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/id/monitor/fhd-qhd/32u401b-b/</t>
+          <t>https://www.lg.com/cn/monitors/lg-32u889sa-w/</t>
         </is>
       </c>
       <c r="D372" s="0" t="inlineStr">
@@ -31375,7 +31758,7 @@
       </c>
       <c r="E372" s="0" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="F372" s="0" t="n">
@@ -31383,24 +31766,29 @@
       </c>
       <c r="G372" s="0" t="inlineStr">
         <is>
-          <t>32U401B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="B373" s="0" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>EC : EC (es)</t>
         </is>
       </c>
       <c r="C373" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/monitors/smart-monitors/32u701sb-b-acc/</t>
+          <t>https://www.lg.com/ec/monitores/lg-32u889sa-w/</t>
         </is>
       </c>
       <c r="D373" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E373" s="0" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F373" s="0" t="n">
@@ -31408,24 +31796,29 @@
       </c>
       <c r="G373" s="0" t="inlineStr">
         <is>
-          <t>32U701SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="B374" s="0" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>IL : IL (iw)</t>
         </is>
       </c>
       <c r="C374" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/moniteurs/smart/32u701sb-b-acc/</t>
+          <t>https://www.lg.com/il/monitors/lg-32u889sa-w/</t>
         </is>
       </c>
       <c r="D374" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E374" s="0" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F374" s="0" t="n">
@@ -31433,24 +31826,29 @@
       </c>
       <c r="G374" s="0" t="inlineStr">
         <is>
-          <t>32U701SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="B375" s="0" t="inlineStr">
         <is>
-          <t>CZ : CZ (cs)</t>
+          <t>RS : RS (sr)</t>
         </is>
       </c>
       <c r="C375" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz/monitory/smart/32u701sb-b/</t>
+          <t>https://www.lg.com/rs/monitori/lg-32u889sa-w/</t>
         </is>
       </c>
       <c r="D375" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E375" s="0" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="F375" s="0" t="n">
@@ -31458,19 +31856,19 @@
       </c>
       <c r="G375" s="0" t="inlineStr">
         <is>
-          <t>32U701SB-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="B376" s="0" t="inlineStr">
         <is>
-          <t>BG : BG (bg)</t>
+          <t>RU : RU (ru)</t>
         </is>
       </c>
       <c r="C376" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/bg/monitori/lg-32u889sa-w/</t>
+          <t>https://www.lg.com/ru/monitors/lg-32u889sa-w/</t>
         </is>
       </c>
       <c r="D376" s="0" t="inlineStr">
@@ -31480,7 +31878,7 @@
       </c>
       <c r="E376" s="0" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="F376" s="0" t="n">
@@ -31495,12 +31893,12 @@
     <row r="377">
       <c r="B377" s="0" t="inlineStr">
         <is>
-          <t>BR : BR (pt)</t>
+          <t>AE : AE (en)</t>
         </is>
       </c>
       <c r="C377" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/br/business/monitores/monitores-produtos/monitores-ultrawide/32u889sa-w/</t>
+          <t>https://www.lg.com/ae/consumer-monitors/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D377" s="0" t="inlineStr">
@@ -31510,7 +31908,7 @@
       </c>
       <c r="E377" s="0" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="F377" s="0" t="n">
@@ -31518,19 +31916,19 @@
       </c>
       <c r="G377" s="0" t="inlineStr">
         <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="B378" s="0" t="inlineStr">
         <is>
-          <t>GT : GT (es)</t>
+          <t>AE_AR : AE (ar)</t>
         </is>
       </c>
       <c r="C378" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cac/monitors/lg-32u889sa-w/</t>
+          <t>https://www.lg.com/ae_ar/consumer-monitors/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D378" s="0" t="inlineStr">
@@ -31540,7 +31938,7 @@
       </c>
       <c r="E378" s="0" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F378" s="0" t="n">
@@ -31548,19 +31946,19 @@
       </c>
       <c r="G378" s="0" t="inlineStr">
         <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="B379" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>AU : AU (en)</t>
         </is>
       </c>
       <c r="C379" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-32u889sa-w/</t>
+          <t>https://www.lg.com/au/monitors/ultrafine-uhd-4k-5k/32u990a-s-aau/</t>
         </is>
       </c>
       <c r="D379" s="0" t="inlineStr">
@@ -31570,7 +31968,7 @@
       </c>
       <c r="E379" s="0" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F379" s="0" t="n">
@@ -31578,19 +31976,19 @@
       </c>
       <c r="G379" s="0" t="inlineStr">
         <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="B380" s="0" t="inlineStr">
         <is>
-          <t>EC : EC (es)</t>
+          <t>BR : BR (pt)</t>
         </is>
       </c>
       <c r="C380" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ec/monitores/lg-32u889sa-w/</t>
+          <t>https://www.lg.com/br/monitores/monitores-uhd-4k/32u990a-s/</t>
         </is>
       </c>
       <c r="D380" s="0" t="inlineStr">
@@ -31600,7 +31998,7 @@
       </c>
       <c r="E380" s="0" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F380" s="0" t="n">
@@ -31608,19 +32006,19 @@
       </c>
       <c r="G380" s="0" t="inlineStr">
         <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="B381" s="0" t="inlineStr">
         <is>
-          <t>IL : IL (iw)</t>
+          <t>GT : GT (es)</t>
         </is>
       </c>
       <c r="C381" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/il/monitors/lg-32u889sa-w/</t>
+          <t>https://www.lg.com/cac/monitors/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D381" s="0" t="inlineStr">
@@ -31630,7 +32028,7 @@
       </c>
       <c r="E381" s="0" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="F381" s="0" t="n">
@@ -31638,19 +32036,19 @@
       </c>
       <c r="G381" s="0" t="inlineStr">
         <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="B382" s="0" t="inlineStr">
         <is>
-          <t>RS : RS (sr)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C382" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/monitori/lg-32u889sa-w/</t>
+          <t>https://www.lg.com/cn/monitors/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D382" s="0" t="inlineStr">
@@ -31660,7 +32058,7 @@
       </c>
       <c r="E382" s="0" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="F382" s="0" t="n">
@@ -31668,19 +32066,19 @@
       </c>
       <c r="G382" s="0" t="inlineStr">
         <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="B383" s="0" t="inlineStr">
         <is>
-          <t>RU : RU (ru)</t>
+          <t>DK : DK (da)</t>
         </is>
       </c>
       <c r="C383" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ru/monitors/lg-32u889sa-w/</t>
+          <t>https://www.lg.com/dk/skaerme/ultrafine-uhd-4k-og-5k-skaerme/32u990a-s/</t>
         </is>
       </c>
       <c r="D383" s="0" t="inlineStr">
@@ -31690,7 +32088,7 @@
       </c>
       <c r="E383" s="0" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="F383" s="0" t="n">
@@ -31698,19 +32096,19 @@
       </c>
       <c r="G383" s="0" t="inlineStr">
         <is>
-          <t>32U889SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="B384" s="0" t="inlineStr">
         <is>
-          <t>AE : AE (en)</t>
+          <t>EC : EC (es)</t>
         </is>
       </c>
       <c r="C384" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ae/consumer-monitors/lg-32u990a-s/</t>
+          <t>https://www.lg.com/ec/monitores/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D384" s="0" t="inlineStr">
@@ -31720,7 +32118,7 @@
       </c>
       <c r="E384" s="0" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="F384" s="0" t="n">
@@ -31735,12 +32133,12 @@
     <row r="385">
       <c r="B385" s="0" t="inlineStr">
         <is>
-          <t>AE_AR : AE (ar)</t>
+          <t>FI : FI (fi)</t>
         </is>
       </c>
       <c r="C385" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ae_ar/consumer-monitors/lg-32u990a-s/</t>
+          <t>https://www.lg.com/fi/naytot/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D385" s="0" t="inlineStr">
@@ -31750,7 +32148,7 @@
       </c>
       <c r="E385" s="0" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="F385" s="0" t="n">
@@ -31765,12 +32163,12 @@
     <row r="386">
       <c r="B386" s="0" t="inlineStr">
         <is>
-          <t>AU : AU (en)</t>
+          <t>FR : FR (fr)</t>
         </is>
       </c>
       <c r="C386" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/au/monitors/ultrafine-uhd-4k-5k/32u990a-s-aau/</t>
+          <t>https://www.lg.com/fr/moniteurs/uhd-4k-5k/lg-32u990a-s-moniteur-bureautique/</t>
         </is>
       </c>
       <c r="D386" s="0" t="inlineStr">
@@ -31780,7 +32178,7 @@
       </c>
       <c r="E386" s="0" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="F386" s="0" t="n">
@@ -31795,12 +32193,12 @@
     <row r="387">
       <c r="B387" s="0" t="inlineStr">
         <is>
-          <t>BR : BR (pt)</t>
+          <t>GR : GR (el)</t>
         </is>
       </c>
       <c r="C387" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/br/monitores/monitores-uhd-4k/32u990a-s/</t>
+          <t>https://www.lg.com/gr/othones/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D387" s="0" t="inlineStr">
@@ -31810,7 +32208,7 @@
       </c>
       <c r="E387" s="0" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F387" s="0" t="n">
@@ -31825,12 +32223,12 @@
     <row r="388">
       <c r="B388" s="0" t="inlineStr">
         <is>
-          <t>GT : GT (es)</t>
+          <t>HR : HR (hr)</t>
         </is>
       </c>
       <c r="C388" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cac/monitors/lg-32u990a-s/</t>
+          <t>https://www.lg.com/hr/monitori/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D388" s="0" t="inlineStr">
@@ -31840,7 +32238,7 @@
       </c>
       <c r="E388" s="0" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F388" s="0" t="n">
@@ -31855,12 +32253,12 @@
     <row r="389">
       <c r="B389" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>HU : HU (hu)</t>
         </is>
       </c>
       <c r="C389" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-32u990a-s/</t>
+          <t>https://www.lg.com/hu/monitorok/ultrafine-uhd-4k-es-5k-monitor/32u990a-s/</t>
         </is>
       </c>
       <c r="D389" s="0" t="inlineStr">
@@ -31870,7 +32268,7 @@
       </c>
       <c r="E389" s="0" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F389" s="0" t="n">
@@ -31885,12 +32283,12 @@
     <row r="390">
       <c r="B390" s="0" t="inlineStr">
         <is>
-          <t>DK : DK (da)</t>
+          <t>ID : ID (in)</t>
         </is>
       </c>
       <c r="C390" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/dk/skaerme/ultrafine-uhd-4k-og-5k-skaerme/32u990a-s/</t>
+          <t>https://www.lg.com/id/monitors/32u990a-s/</t>
         </is>
       </c>
       <c r="D390" s="0" t="inlineStr">
@@ -31900,7 +32298,7 @@
       </c>
       <c r="E390" s="0" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F390" s="0" t="n">
@@ -31915,12 +32313,12 @@
     <row r="391">
       <c r="B391" s="0" t="inlineStr">
         <is>
-          <t>EC : EC (es)</t>
+          <t>IL : IL (iw)</t>
         </is>
       </c>
       <c r="C391" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ec/monitores/lg-32u990a-s/</t>
+          <t>https://www.lg.com/il/monitors/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D391" s="0" t="inlineStr">
@@ -31930,7 +32328,7 @@
       </c>
       <c r="E391" s="0" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F391" s="0" t="n">
@@ -31945,12 +32343,12 @@
     <row r="392">
       <c r="B392" s="0" t="inlineStr">
         <is>
-          <t>FI : FI (fi)</t>
+          <t>MX : MX (es)</t>
         </is>
       </c>
       <c r="C392" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fi/naytot/lg-32u990a-s/</t>
+          <t>https://www.lg.com/mx/monitores/todos-los-monitores/32u990a-s/</t>
         </is>
       </c>
       <c r="D392" s="0" t="inlineStr">
@@ -31960,7 +32358,7 @@
       </c>
       <c r="E392" s="0" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F392" s="0" t="n">
@@ -31975,12 +32373,12 @@
     <row r="393">
       <c r="B393" s="0" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
+          <t>NL : NL (nl)</t>
         </is>
       </c>
       <c r="C393" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fr/moniteurs/uhd-4k-5k/lg-32u990a-s-moniteur-bureautique/</t>
+          <t>https://www.lg.com/nl/monitoren/ultrafine-uhd-4k-5k-monitoren/32U990A-S/</t>
         </is>
       </c>
       <c r="D393" s="0" t="inlineStr">
@@ -31990,7 +32388,7 @@
       </c>
       <c r="E393" s="0" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F393" s="0" t="n">
@@ -32005,12 +32403,12 @@
     <row r="394">
       <c r="B394" s="0" t="inlineStr">
         <is>
-          <t>GR : GR (el)</t>
+          <t>RO : RO (ro)</t>
         </is>
       </c>
       <c r="C394" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/gr/othones/lg-32u990a-s/</t>
+          <t>https://www.lg.com/ro/monitoare/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D394" s="0" t="inlineStr">
@@ -32020,7 +32418,7 @@
       </c>
       <c r="E394" s="0" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="F394" s="0" t="n">
@@ -32035,12 +32433,12 @@
     <row r="395">
       <c r="B395" s="0" t="inlineStr">
         <is>
-          <t>HR : HR (hr)</t>
+          <t>RS : RS (sr)</t>
         </is>
       </c>
       <c r="C395" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hr/monitori/lg-32u990a-s/</t>
+          <t>https://www.lg.com/rs/monitori/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D395" s="0" t="inlineStr">
@@ -32050,7 +32448,7 @@
       </c>
       <c r="E395" s="0" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="F395" s="0" t="n">
@@ -32065,17 +32463,22 @@
     <row r="396">
       <c r="B396" s="0" t="inlineStr">
         <is>
-          <t>HU : HU (hu)</t>
+          <t>SE : SE (sv)</t>
         </is>
       </c>
       <c r="C396" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hu/monitorok/ultrafine-uhd-4k-es-5k-monitor/32u990a-s/</t>
+          <t>https://www.lg.com/se/monitors/uhd-4k-5k/32u990a-s/</t>
         </is>
       </c>
       <c r="D396" s="0" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="E396" s="0" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="F396" s="0" t="n">
@@ -32090,12 +32493,12 @@
     <row r="397">
       <c r="B397" s="0" t="inlineStr">
         <is>
-          <t>ID : ID (in)</t>
+          <t>SK : SK (sk)</t>
         </is>
       </c>
       <c r="C397" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/id/monitors/32u990a-s/</t>
+          <t>https://www.lg.com/sk/monitory/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D397" s="0" t="inlineStr">
@@ -32105,7 +32508,7 @@
       </c>
       <c r="E397" s="0" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="F397" s="0" t="n">
@@ -32120,12 +32523,12 @@
     <row r="398">
       <c r="B398" s="0" t="inlineStr">
         <is>
-          <t>IL : IL (iw)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C398" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/il/monitors/lg-32u990a-s/</t>
+          <t>https://www.lg.com/cn/monitors/lg-34u601b-b/</t>
         </is>
       </c>
       <c r="D398" s="0" t="inlineStr">
@@ -32135,7 +32538,7 @@
       </c>
       <c r="E398" s="0" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F398" s="0" t="n">
@@ -32143,19 +32546,19 @@
       </c>
       <c r="G398" s="0" t="inlineStr">
         <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="B399" s="0" t="inlineStr">
         <is>
-          <t>MX : MX (es)</t>
+          <t>ES : ES (es)</t>
         </is>
       </c>
       <c r="C399" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/mx/monitores/todos-los-monitores/32u990a-s/</t>
+          <t>https://www.lg.com/es/monitores/monitores-ultrawide/34u601b-b/</t>
         </is>
       </c>
       <c r="D399" s="0" t="inlineStr">
@@ -32163,24 +32566,29 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="E399" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="F399" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G399" s="0" t="inlineStr">
         <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="B400" s="0" t="inlineStr">
         <is>
-          <t>NL : NL (nl)</t>
+          <t>IT : IT (it)</t>
         </is>
       </c>
       <c r="C400" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nl/monitoren/ultrafine-uhd-4k-5k-monitoren/32U990A-S/</t>
+          <t>https://www.lg.com/it/monitor/ultrawide/34u601b-b-aeuq/</t>
         </is>
       </c>
       <c r="D400" s="0" t="inlineStr">
@@ -32190,7 +32598,7 @@
       </c>
       <c r="E400" s="0" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F400" s="0" t="n">
@@ -32198,19 +32606,19 @@
       </c>
       <c r="G400" s="0" t="inlineStr">
         <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="B401" s="0" t="inlineStr">
         <is>
-          <t>RO : RO (ro)</t>
+          <t>BR : BR (pt)</t>
         </is>
       </c>
       <c r="C401" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ro/monitoare/lg-32u990a-s/</t>
+          <t>https://www.lg.com/br/monitores/monitores-ultrawide/34u620b-b/</t>
         </is>
       </c>
       <c r="D401" s="0" t="inlineStr">
@@ -32220,7 +32628,7 @@
       </c>
       <c r="E401" s="0" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F401" s="0" t="n">
@@ -32228,7 +32636,7 @@
       </c>
       <c r="G401" s="0" t="inlineStr">
         <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>34U620B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -32240,7 +32648,7 @@
       </c>
       <c r="C402" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/monitori/lg-32u990a-s/</t>
+          <t>https://www.lg.com/rs/monitori/lg-34u620b-b/</t>
         </is>
       </c>
       <c r="D402" s="0" t="inlineStr">
@@ -32250,7 +32658,7 @@
       </c>
       <c r="E402" s="0" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F402" s="0" t="n">
@@ -32258,19 +32666,19 @@
       </c>
       <c r="G402" s="0" t="inlineStr">
         <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>34U620B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="B403" s="0" t="inlineStr">
         <is>
-          <t>SE : SE (sv)</t>
+          <t>CZ : CZ (cs)</t>
         </is>
       </c>
       <c r="C403" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/se/monitors/uhd-4k-5k/32u990a-s/</t>
+          <t>https://www.lg.com/cz/monitory/ultrawide-sirokouhle-monitory/34u640b-b/</t>
         </is>
       </c>
       <c r="D403" s="0" t="inlineStr">
@@ -32280,7 +32688,7 @@
       </c>
       <c r="E403" s="0" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F403" s="0" t="n">
@@ -32288,19 +32696,19 @@
       </c>
       <c r="G403" s="0" t="inlineStr">
         <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>34U640B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01)</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="B404" s="0" t="inlineStr">
         <is>
-          <t>SK : SK (sk)</t>
+          <t>CZ : CZ (cs)</t>
         </is>
       </c>
       <c r="C404" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sk/monitory/lg-32u990a-s/</t>
+          <t>https://www.lg.com/cz/monitory/smart/34u640sb-w/</t>
         </is>
       </c>
       <c r="D404" s="0" t="inlineStr">
@@ -32310,7 +32718,7 @@
       </c>
       <c r="E404" s="0" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F404" s="0" t="n">
@@ -32318,19 +32726,19 @@
       </c>
       <c r="G404" s="0" t="inlineStr">
         <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>34U640SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01)</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="B405" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>BG : BG (bg)</t>
         </is>
       </c>
       <c r="C405" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-34u601b-b/</t>
+          <t>https://www.lg.com/bg/monitori/lg-39gx90sa-w/</t>
         </is>
       </c>
       <c r="D405" s="0" t="inlineStr">
@@ -32340,7 +32748,7 @@
       </c>
       <c r="E405" s="0" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F405" s="0" t="n">
@@ -32348,19 +32756,19 @@
       </c>
       <c r="G405" s="0" t="inlineStr">
         <is>
-          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="B406" s="0" t="inlineStr">
         <is>
-          <t>ES : ES (es)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C406" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es/monitores/monitores-ultrawide/34u601b-b/</t>
+          <t>https://www.lg.com/cn/monitors/lg-39gx90sa-w/</t>
         </is>
       </c>
       <c r="D406" s="0" t="inlineStr">
@@ -32368,24 +32776,29 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="E406" s="0" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
       <c r="F406" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G406" s="0" t="inlineStr">
         <is>
-          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="B407" s="0" t="inlineStr">
         <is>
-          <t>IT : IT (it)</t>
+          <t>EE : EE (et)</t>
         </is>
       </c>
       <c r="C407" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/it/monitor/ultrawide/34u601b-b-aeuq/</t>
+          <t>https://www.lg.com/ee/monitorid/lg-39gx90sa-w/</t>
         </is>
       </c>
       <c r="D407" s="0" t="inlineStr">
@@ -32393,24 +32806,29 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="E407" s="0" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
       <c r="F407" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G407" s="0" t="inlineStr">
         <is>
-          <t>34U601B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="B408" s="0" t="inlineStr">
         <is>
-          <t>BR : BR (pt)</t>
+          <t>FR : FR (fr)</t>
         </is>
       </c>
       <c r="C408" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/br/monitores/monitores-ultrawide/34u620b-b/</t>
+          <t>https://www.lg.com/fr/moniteurs/gaming/lg-39gx90sa-w-moniteur-ultragear/</t>
         </is>
       </c>
       <c r="D408" s="0" t="inlineStr">
@@ -32420,7 +32838,7 @@
       </c>
       <c r="E408" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="F408" s="0" t="n">
@@ -32428,19 +32846,19 @@
       </c>
       <c r="G408" s="0" t="inlineStr">
         <is>
-          <t>34U620B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="B409" s="0" t="inlineStr">
         <is>
-          <t>RS : RS (sr)</t>
+          <t>HR : HR (hr)</t>
         </is>
       </c>
       <c r="C409" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/monitori/lg-34u620b-b/</t>
+          <t>https://www.lg.com/hr/monitori/lg-39gx90sa-w/</t>
         </is>
       </c>
       <c r="D409" s="0" t="inlineStr">
@@ -32448,29 +32866,39 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="E409" s="0" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
       <c r="F409" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G409" s="0" t="inlineStr">
         <is>
-          <t>34U620B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="B410" s="0" t="inlineStr">
         <is>
-          <t>CZ : CZ (cs)</t>
+          <t>RS : RS (sr)</t>
         </is>
       </c>
       <c r="C410" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz/monitory/ultrawide-sirokouhle-monitory/34u640b-b/</t>
+          <t>https://www.lg.com/rs/monitori/lg-39gx90sa-w/</t>
         </is>
       </c>
       <c r="D410" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E410" s="0" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="F410" s="0" t="n">
@@ -32478,24 +32906,29 @@
       </c>
       <c r="G410" s="0" t="inlineStr">
         <is>
-          <t>34U640B-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="B411" s="0" t="inlineStr">
         <is>
-          <t>CZ : CZ (cs)</t>
+          <t>BE_FR : BE (fr)</t>
         </is>
       </c>
       <c r="C411" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz/monitory/smart/34u640sb-w/</t>
+          <t>https://www.lg.com/be_fr/moniteurs/moniteurs-ultrafine/40U990A-W/</t>
         </is>
       </c>
       <c r="D411" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E411" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F411" s="0" t="n">
@@ -32503,19 +32936,19 @@
       </c>
       <c r="G411" s="0" t="inlineStr">
         <is>
-          <t>34U640SB-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 작업중(PTT 추적)</t>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="B412" s="0" t="inlineStr">
         <is>
-          <t>BG : BG (bg)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C412" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/bg/monitori/lg-39gx90sa-w/</t>
+          <t>https://www.lg.com/cn/monitors/lg-40u990a-w/</t>
         </is>
       </c>
       <c r="D412" s="0" t="inlineStr">
@@ -32525,7 +32958,7 @@
       </c>
       <c r="E412" s="0" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="F412" s="0" t="n">
@@ -32533,19 +32966,19 @@
       </c>
       <c r="G412" s="0" t="inlineStr">
         <is>
-          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="B413" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>EE : EE (et)</t>
         </is>
       </c>
       <c r="C413" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-39gx90sa-w/</t>
+          <t>https://www.lg.com/ee/monitorid/lg-40u990a-w/</t>
         </is>
       </c>
       <c r="D413" s="0" t="inlineStr">
@@ -32555,7 +32988,7 @@
       </c>
       <c r="E413" s="0" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="F413" s="0" t="n">
@@ -32563,19 +32996,19 @@
       </c>
       <c r="G413" s="0" t="inlineStr">
         <is>
-          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="B414" s="0" t="inlineStr">
         <is>
-          <t>EE : EE (et)</t>
+          <t>GR : GR (el)</t>
         </is>
       </c>
       <c r="C414" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ee/monitorid/lg-39gx90sa-w/</t>
+          <t>https://www.lg.com/gr/othones/lg-40u990a-w/</t>
         </is>
       </c>
       <c r="D414" s="0" t="inlineStr">
@@ -32585,7 +33018,7 @@
       </c>
       <c r="E414" s="0" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F414" s="0" t="n">
@@ -32593,19 +33026,19 @@
       </c>
       <c r="G414" s="0" t="inlineStr">
         <is>
-          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="B415" s="0" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
+          <t>IL : IL (iw)</t>
         </is>
       </c>
       <c r="C415" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fr/moniteurs/gaming/lg-39gx90sa-w-moniteur-ultragear/</t>
+          <t>https://www.lg.com/il/monitors/lg-40u990a-w/</t>
         </is>
       </c>
       <c r="D415" s="0" t="inlineStr">
@@ -32615,7 +33048,7 @@
       </c>
       <c r="E415" s="0" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F415" s="0" t="n">
@@ -32623,19 +33056,19 @@
       </c>
       <c r="G415" s="0" t="inlineStr">
         <is>
-          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="B416" s="0" t="inlineStr">
         <is>
-          <t>HR : HR (hr)</t>
+          <t>LT : LT (lt)</t>
         </is>
       </c>
       <c r="C416" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hr/monitori/lg-39gx90sa-w/</t>
+          <t>https://www.lg.com/lt/monitoriai/lg-40u990a-w/</t>
         </is>
       </c>
       <c r="D416" s="0" t="inlineStr">
@@ -32645,7 +33078,7 @@
       </c>
       <c r="E416" s="0" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="F416" s="0" t="n">
@@ -32653,19 +33086,19 @@
       </c>
       <c r="G416" s="0" t="inlineStr">
         <is>
-          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="B417" s="0" t="inlineStr">
         <is>
-          <t>RS : RS (sr)</t>
+          <t>LV : LV (lv)</t>
         </is>
       </c>
       <c r="C417" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/monitori/lg-39gx90sa-w/</t>
+          <t>https://www.lg.com/lv/monitori/lg-40u990a-w/</t>
         </is>
       </c>
       <c r="D417" s="0" t="inlineStr">
@@ -32675,7 +33108,7 @@
       </c>
       <c r="E417" s="0" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="F417" s="0" t="n">
@@ -32683,24 +33116,29 @@
       </c>
       <c r="G417" s="0" t="inlineStr">
         <is>
-          <t>39GX90SA-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="B418" s="0" t="inlineStr">
         <is>
-          <t>BE_FR : BE (fr)</t>
+          <t>RU : RU (ru)</t>
         </is>
       </c>
       <c r="C418" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/be_fr/moniteurs/moniteurs-ultrafine/40U990A-W/</t>
+          <t>https://www.lg.com/ru/monitors/lg-40u990a-w/</t>
         </is>
       </c>
       <c r="D418" s="0" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="E418" s="0" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="F418" s="0" t="n">
@@ -32715,12 +33153,12 @@
     <row r="419">
       <c r="B419" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>SK : SK (sk)</t>
         </is>
       </c>
       <c r="C419" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-40u990a-w/</t>
+          <t>https://www.lg.com/sk/monitory/lg-40u990a-w/</t>
         </is>
       </c>
       <c r="D419" s="0" t="inlineStr">
@@ -32730,7 +33168,7 @@
       </c>
       <c r="E419" s="0" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="F419" s="0" t="n">
@@ -32745,12 +33183,12 @@
     <row r="420">
       <c r="B420" s="0" t="inlineStr">
         <is>
-          <t>EE : EE (et)</t>
+          <t>BG : BG (bg)</t>
         </is>
       </c>
       <c r="C420" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ee/monitorid/lg-40u990a-w/</t>
+          <t>https://www.lg.com/bg/monitori/lg-45gx90sa-b/</t>
         </is>
       </c>
       <c r="D420" s="0" t="inlineStr">
@@ -32760,7 +33198,7 @@
       </c>
       <c r="E420" s="0" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F420" s="0" t="n">
@@ -32768,19 +33206,19 @@
       </c>
       <c r="G420" s="0" t="inlineStr">
         <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="B421" s="0" t="inlineStr">
         <is>
-          <t>GR : GR (el)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C421" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/gr/othones/lg-40u990a-w/</t>
+          <t>https://www.lg.com/cn/monitors/lg-45gx90sa-b/</t>
         </is>
       </c>
       <c r="D421" s="0" t="inlineStr">
@@ -32790,7 +33228,7 @@
       </c>
       <c r="E421" s="0" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F421" s="0" t="n">
@@ -32798,19 +33236,19 @@
       </c>
       <c r="G421" s="0" t="inlineStr">
         <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="B422" s="0" t="inlineStr">
         <is>
-          <t>IL : IL (iw)</t>
+          <t>HR : HR (hr)</t>
         </is>
       </c>
       <c r="C422" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/il/monitors/lg-40u990a-w/</t>
+          <t>https://www.lg.com/hr/monitori/lg-45gx90sa-b/</t>
         </is>
       </c>
       <c r="D422" s="0" t="inlineStr">
@@ -32820,7 +33258,7 @@
       </c>
       <c r="E422" s="0" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F422" s="0" t="n">
@@ -32828,19 +33266,19 @@
       </c>
       <c r="G422" s="0" t="inlineStr">
         <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="B423" s="0" t="inlineStr">
         <is>
-          <t>LT : LT (lt)</t>
+          <t>RS : RS (sr)</t>
         </is>
       </c>
       <c r="C423" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lt/monitoriai/lg-40u990a-w/</t>
+          <t>https://www.lg.com/rs/monitori/lg-45gx90sa-b/</t>
         </is>
       </c>
       <c r="D423" s="0" t="inlineStr">
@@ -32850,7 +33288,7 @@
       </c>
       <c r="E423" s="0" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="F423" s="0" t="n">
@@ -32858,19 +33296,19 @@
       </c>
       <c r="G423" s="0" t="inlineStr">
         <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="B424" s="0" t="inlineStr">
         <is>
-          <t>LV : LV (lv)</t>
+          <t>BG : BG (bg)</t>
         </is>
       </c>
       <c r="C424" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lv/monitori/lg-40u990a-w/</t>
+          <t>https://www.lg.com/bg/monitori/lg-45gx950a-b/</t>
         </is>
       </c>
       <c r="D424" s="0" t="inlineStr">
@@ -32880,7 +33318,7 @@
       </c>
       <c r="E424" s="0" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="F424" s="0" t="n">
@@ -32888,19 +33326,19 @@
       </c>
       <c r="G424" s="0" t="inlineStr">
         <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="B425" s="0" t="inlineStr">
         <is>
-          <t>RU : RU (ru)</t>
+          <t>GT : GT (es)</t>
         </is>
       </c>
       <c r="C425" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ru/monitors/lg-40u990a-w/</t>
+          <t>https://www.lg.com/cac/monitors/lg-45gx950a-b/</t>
         </is>
       </c>
       <c r="D425" s="0" t="inlineStr">
@@ -32910,7 +33348,7 @@
       </c>
       <c r="E425" s="0" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F425" s="0" t="n">
@@ -32918,19 +33356,19 @@
       </c>
       <c r="G425" s="0" t="inlineStr">
         <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="B426" s="0" t="inlineStr">
         <is>
-          <t>SK : SK (sk)</t>
+          <t>CN : CN (zh)</t>
         </is>
       </c>
       <c r="C426" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sk/monitory/lg-40u990a-w/</t>
+          <t>https://www.lg.com/cn/monitors/lg-45gx950a-b/</t>
         </is>
       </c>
       <c r="D426" s="0" t="inlineStr">
@@ -32940,7 +33378,7 @@
       </c>
       <c r="E426" s="0" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="F426" s="0" t="n">
@@ -32948,19 +33386,19 @@
       </c>
       <c r="G426" s="0" t="inlineStr">
         <is>
-          <t>40U990A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="B427" s="0" t="inlineStr">
         <is>
-          <t>BG : BG (bg)</t>
+          <t>EC : EC (es)</t>
         </is>
       </c>
       <c r="C427" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/bg/monitori/lg-45gx90sa-b/</t>
+          <t>https://www.lg.com/ec/monitores/lg-45gx950a-b/</t>
         </is>
       </c>
       <c r="D427" s="0" t="inlineStr">
@@ -32970,7 +33408,7 @@
       </c>
       <c r="E427" s="0" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F427" s="0" t="n">
@@ -32978,19 +33416,19 @@
       </c>
       <c r="G427" s="0" t="inlineStr">
         <is>
-          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="B428" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>HR : HR (hr)</t>
         </is>
       </c>
       <c r="C428" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-45gx90sa-b/</t>
+          <t>https://www.lg.com/hr/monitori/lg-45gx950a-b/</t>
         </is>
       </c>
       <c r="D428" s="0" t="inlineStr">
@@ -33000,7 +33438,7 @@
       </c>
       <c r="E428" s="0" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="F428" s="0" t="n">
@@ -33008,19 +33446,19 @@
       </c>
       <c r="G428" s="0" t="inlineStr">
         <is>
-          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="B429" s="0" t="inlineStr">
         <is>
-          <t>HR : HR (hr)</t>
+          <t>IL : IL (iw)</t>
         </is>
       </c>
       <c r="C429" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hr/monitori/lg-45gx90sa-b/</t>
+          <t>https://www.lg.com/il/monitors/lg-45gx950a-b/</t>
         </is>
       </c>
       <c r="D429" s="0" t="inlineStr">
@@ -33030,7 +33468,7 @@
       </c>
       <c r="E429" s="0" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="F429" s="0" t="n">
@@ -33038,7 +33476,7 @@
       </c>
       <c r="G429" s="0" t="inlineStr">
         <is>
-          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -33050,7 +33488,7 @@
       </c>
       <c r="C430" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/monitori/lg-45gx90sa-b/</t>
+          <t>https://www.lg.com/rs/monitori/lg-45gx950a-b/</t>
         </is>
       </c>
       <c r="D430" s="0" t="inlineStr">
@@ -33060,7 +33498,7 @@
       </c>
       <c r="E430" s="0" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F430" s="0" t="n">
@@ -33068,19 +33506,19 @@
       </c>
       <c r="G430" s="0" t="inlineStr">
         <is>
-          <t>45GX90SA-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="B431" s="0" t="inlineStr">
         <is>
-          <t>BG : BG (bg)</t>
+          <t>SK : SK (sk)</t>
         </is>
       </c>
       <c r="C431" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/bg/monitori/lg-45gx950a-b/</t>
+          <t>https://www.lg.com/sk/monitory/lg-45gx950a-b/</t>
         </is>
       </c>
       <c r="D431" s="0" t="inlineStr">
@@ -33090,7 +33528,7 @@
       </c>
       <c r="E431" s="0" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="F431" s="0" t="n">
@@ -33105,12 +33543,12 @@
     <row r="432">
       <c r="B432" s="0" t="inlineStr">
         <is>
-          <t>GT : GT (es)</t>
+          <t>BG : BG (bg)</t>
         </is>
       </c>
       <c r="C432" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cac/monitors/lg-45gx950a-b/</t>
+          <t>https://www.lg.com/bg/monitori/lg-49u950a-w/</t>
         </is>
       </c>
       <c r="D432" s="0" t="inlineStr">
@@ -33120,7 +33558,7 @@
       </c>
       <c r="E432" s="0" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="F432" s="0" t="n">
@@ -33128,19 +33566,19 @@
       </c>
       <c r="G432" s="0" t="inlineStr">
         <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="B433" s="0" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>EE : EE (et)</t>
         </is>
       </c>
       <c r="C433" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/monitors/lg-45gx950a-b/</t>
+          <t>https://www.lg.com/ee/monitorid/lg-49u950a-w/</t>
         </is>
       </c>
       <c r="D433" s="0" t="inlineStr">
@@ -33150,7 +33588,7 @@
       </c>
       <c r="E433" s="0" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="F433" s="0" t="n">
@@ -33158,19 +33596,19 @@
       </c>
       <c r="G433" s="0" t="inlineStr">
         <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="B434" s="0" t="inlineStr">
         <is>
-          <t>EC : EC (es)</t>
+          <t>GR : GR (el)</t>
         </is>
       </c>
       <c r="C434" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ec/monitores/lg-45gx950a-b/</t>
+          <t>https://www.lg.com/gr/othones/lg-49u950a-w/</t>
         </is>
       </c>
       <c r="D434" s="0" t="inlineStr">
@@ -33180,7 +33618,7 @@
       </c>
       <c r="E434" s="0" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F434" s="0" t="n">
@@ -33188,19 +33626,19 @@
       </c>
       <c r="G434" s="0" t="inlineStr">
         <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="B435" s="0" t="inlineStr">
         <is>
-          <t>HR : HR (hr)</t>
+          <t>IL : IL (iw)</t>
         </is>
       </c>
       <c r="C435" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hr/monitori/lg-45gx950a-b/</t>
+          <t>https://www.lg.com/il/monitors/lg-49u950a-w/</t>
         </is>
       </c>
       <c r="D435" s="0" t="inlineStr">
@@ -33210,7 +33648,7 @@
       </c>
       <c r="E435" s="0" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="F435" s="0" t="n">
@@ -33218,19 +33656,19 @@
       </c>
       <c r="G435" s="0" t="inlineStr">
         <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="B436" s="0" t="inlineStr">
         <is>
-          <t>IL : IL (iw)</t>
+          <t>RS : RS (sr)</t>
         </is>
       </c>
       <c r="C436" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/il/monitors/lg-45gx950a-b/</t>
+          <t>https://www.lg.com/rs/monitori/lg-49u950a-w/</t>
         </is>
       </c>
       <c r="D436" s="0" t="inlineStr">
@@ -33240,7 +33678,7 @@
       </c>
       <c r="E436" s="0" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F436" s="0" t="n">
@@ -33248,19 +33686,19 @@
       </c>
       <c r="G436" s="0" t="inlineStr">
         <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="B437" s="0" t="inlineStr">
         <is>
-          <t>RS : RS (sr)</t>
+          <t>SK : SK (sk)</t>
         </is>
       </c>
       <c r="C437" s="294" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/monitori/lg-45gx950a-b/</t>
+          <t>https://www.lg.com/sk/monitory/lg-49u950a-w/</t>
         </is>
       </c>
       <c r="D437" s="0" t="inlineStr">
@@ -33270,7 +33708,7 @@
       </c>
       <c r="E437" s="0" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F437" s="0" t="n">
@@ -33278,19 +33716,19 @@
       </c>
       <c r="G437" s="0" t="inlineStr">
         <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="B438" s="0" t="inlineStr">
         <is>
-          <t>SK : SK (sk)</t>
-        </is>
-      </c>
-      <c r="C438" s="294" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sk/monitory/lg-45gx950a-b/</t>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C438" s="292" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/monitore/uhd-4k-5k/32u990a-s</t>
         </is>
       </c>
       <c r="D438" s="0" t="inlineStr">
@@ -33300,7 +33738,7 @@
       </c>
       <c r="E438" s="0" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="F438" s="0" t="n">
@@ -33308,19 +33746,19 @@
       </c>
       <c r="G438" s="0" t="inlineStr">
         <is>
-          <t>45GX950A-B · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨 · 갤러리/PDP 체크</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="B439" s="0" t="inlineStr">
         <is>
-          <t>BG : BG (bg)</t>
-        </is>
-      </c>
-      <c r="C439" s="294" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/bg/monitori/lg-49u950a-w/</t>
+          <t>BR : BR (pt)</t>
+        </is>
+      </c>
+      <c r="C439" s="292" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/br/monitores/monitores-uhd-4k/32u990a-s/</t>
         </is>
       </c>
       <c r="D439" s="0" t="inlineStr">
@@ -33330,7 +33768,7 @@
       </c>
       <c r="E439" s="0" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F439" s="0" t="n">
@@ -33338,19 +33776,19 @@
       </c>
       <c r="G439" s="0" t="inlineStr">
         <is>
-          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · 갤러리/PDP 이미지 수정 (어워드 외)</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="B440" s="0" t="inlineStr">
         <is>
-          <t>EE : EE (et)</t>
-        </is>
-      </c>
-      <c r="C440" s="294" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ee/monitorid/lg-49u950a-w/</t>
+          <t>FI : FI (fi)</t>
+        </is>
+      </c>
+      <c r="C440" s="292" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fi/naytot/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D440" s="0" t="inlineStr">
@@ -33360,7 +33798,7 @@
       </c>
       <c r="E440" s="0" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F440" s="0" t="n">
@@ -33368,7 +33806,7 @@
       </c>
       <c r="G440" s="0" t="inlineStr">
         <is>
-          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · 갤러리/PDP 이미지 수정 (어워드 외)</t>
         </is>
       </c>
     </row>
@@ -33378,9 +33816,9 @@
           <t>GR : GR (el)</t>
         </is>
       </c>
-      <c r="C441" s="294" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/gr/othones/lg-49u950a-w/</t>
+      <c r="C441" s="292" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/gr/othones/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D441" s="0" t="inlineStr">
@@ -33390,7 +33828,7 @@
       </c>
       <c r="E441" s="0" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F441" s="0" t="n">
@@ -33398,19 +33836,19 @@
       </c>
       <c r="G441" s="0" t="inlineStr">
         <is>
-          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · 갤러리/PDP 이미지 수정 (어워드 외)</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="B442" s="0" t="inlineStr">
         <is>
-          <t>IL : IL (iw)</t>
-        </is>
-      </c>
-      <c r="C442" s="294" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/il/monitors/lg-49u950a-w/</t>
+          <t>ID : ID (in)</t>
+        </is>
+      </c>
+      <c r="C442" s="292" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/monitors/32u990a-s/</t>
         </is>
       </c>
       <c r="D442" s="0" t="inlineStr">
@@ -33420,7 +33858,7 @@
       </c>
       <c r="E442" s="0" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F442" s="0" t="n">
@@ -33428,19 +33866,19 @@
       </c>
       <c r="G442" s="0" t="inlineStr">
         <is>
-          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · 갤러리/PDP 이미지 수정 (어워드 외)</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="B443" s="0" t="inlineStr">
         <is>
-          <t>RS : RS (sr)</t>
-        </is>
-      </c>
-      <c r="C443" s="294" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/rs/monitori/lg-49u950a-w/</t>
+          <t>IL : IL (iw)</t>
+        </is>
+      </c>
+      <c r="C443" s="292" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/lg-32u990a-s/</t>
         </is>
       </c>
       <c r="D443" s="0" t="inlineStr">
@@ -33450,7 +33888,7 @@
       </c>
       <c r="E443" s="0" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F443" s="0" t="n">
@@ -33458,19 +33896,19 @@
       </c>
       <c r="G443" s="0" t="inlineStr">
         <is>
-          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
+          <t>32U990A-S · 갤러리/PDP 이미지 수정 (어워드 외)</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="B444" s="0" t="inlineStr">
         <is>
-          <t>SK : SK (sk)</t>
-        </is>
-      </c>
-      <c r="C444" s="294" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sk/monitory/lg-49u950a-w/</t>
+          <t>MX : MX (es)</t>
+        </is>
+      </c>
+      <c r="C444" s="292" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/mx/monitores/todos-los-monitores/32u990a-s/</t>
         </is>
       </c>
       <c r="D444" s="0" t="inlineStr">
@@ -33480,193 +33918,13 @@
       </c>
       <c r="E444" s="0" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F444" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G444" s="0" t="inlineStr">
-        <is>
-          <t>49U950A-W · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="B445" s="0" t="inlineStr">
-        <is>
-          <t>GLOBAL</t>
-        </is>
-      </c>
-      <c r="C445" s="292" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/de/monitore/uhd-4k-5k/32u990a-s</t>
-        </is>
-      </c>
-      <c r="D445" s="0" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E445" s="0" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="F445" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G445" s="0" t="inlineStr">
-        <is>
-          <t>32U990A-S · Digital Trends 2025 Best Monitor Award 로고·quote 삭제 (라이선스 만료 2026-09-01) · 라이브 게시됨 · 갤러리/PDP 체크</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="B446" s="0" t="inlineStr">
-        <is>
-          <t>BR : BR (pt)</t>
-        </is>
-      </c>
-      <c r="C446" s="292" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/br/monitores/monitores-uhd-4k/32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D446" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F446" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G446" s="0" t="inlineStr">
-        <is>
-          <t>32U990A-S · 갤러리/PDP 이미지 수정 (어워드 외)</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="B447" s="0" t="inlineStr">
-        <is>
-          <t>FI : FI (fi)</t>
-        </is>
-      </c>
-      <c r="C447" s="292" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fi/naytot/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D447" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F447" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G447" s="0" t="inlineStr">
-        <is>
-          <t>32U990A-S · 갤러리/PDP 이미지 수정 (어워드 외)</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="B448" s="0" t="inlineStr">
-        <is>
-          <t>GR : GR (el)</t>
-        </is>
-      </c>
-      <c r="C448" s="292" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/gr/othones/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D448" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F448" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G448" s="0" t="inlineStr">
-        <is>
-          <t>32U990A-S · 갤러리/PDP 이미지 수정 (어워드 외)</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="B449" s="0" t="inlineStr">
-        <is>
-          <t>ID : ID (in)</t>
-        </is>
-      </c>
-      <c r="C449" s="292" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/id/monitors/32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D449" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F449" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G449" s="0" t="inlineStr">
-        <is>
-          <t>32U990A-S · 갤러리/PDP 이미지 수정 (어워드 외)</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="B450" s="0" t="inlineStr">
-        <is>
-          <t>IL : IL (iw)</t>
-        </is>
-      </c>
-      <c r="C450" s="292" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/il/monitors/lg-32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D450" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F450" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G450" s="0" t="inlineStr">
-        <is>
-          <t>32U990A-S · 갤러리/PDP 이미지 수정 (어워드 외)</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="B451" s="0" t="inlineStr">
-        <is>
-          <t>MX : MX (es)</t>
-        </is>
-      </c>
-      <c r="C451" s="292" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/mx/monitores/todos-los-monitores/32u990a-s/</t>
-        </is>
-      </c>
-      <c r="D451" s="0" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="F451" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G451" s="0" t="inlineStr">
         <is>
           <t>32U990A-S · 갤러리/PDP 이미지 수정 (어워드 외)</t>
         </is>
@@ -33986,136 +34244,122 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId310"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId311"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C321" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C358" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C364" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C365" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C367" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C368" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C369" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C371" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C373" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C374" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C378" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C389" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C395" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C398" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C415" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C423" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C424" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C429" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C433" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C434" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C438" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C441" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C445" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C446" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C447" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C448" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C449" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C450" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C451" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C358" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C368" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C369" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C371" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C378" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C389" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C395" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C398" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C415" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C423" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C424" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C429" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C433" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C434" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C438" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C441" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId428"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -10841,7 +10841,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>URL 동기화(2026-08-28) · GLOBAL 제외 · 사이트 기준 완료 6/11 (55%) · 완료 6국 · 법인리뷰 4국 · 작업중 1국 · 취소 1국 · 행 완료 34 · 법인리뷰 46 · 작업중 22 · 취소 7</t>
+          <t>완료 일괄(2026-09-01) · 사이트 기준 완료 11/11 (100%) · 완료 102 · 취소 7</t>
         </is>
       </c>
     </row>
@@ -10895,7 +10895,12 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F4" s="0" t="n">
@@ -10920,7 +10925,12 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F5" s="0" t="n">
@@ -10945,7 +10955,12 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F6" s="0" t="n">
@@ -10970,7 +10985,12 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F7" s="0" t="n">
@@ -10995,7 +11015,12 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F8" s="0" t="n">
@@ -11020,7 +11045,12 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F9" s="0" t="n">
@@ -11555,7 +11585,12 @@
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F27" s="0" t="n">
@@ -11580,7 +11615,12 @@
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F28" s="0" t="n">
@@ -11605,7 +11645,12 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F29" s="0" t="n">
@@ -11630,7 +11675,12 @@
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F30" s="0" t="n">
@@ -11655,7 +11705,12 @@
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F31" s="0" t="n">
@@ -11680,7 +11735,12 @@
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F32" s="0" t="n">
@@ -11705,7 +11765,12 @@
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F33" s="0" t="n">
@@ -11730,7 +11795,12 @@
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F34" s="0" t="n">
@@ -11755,7 +11825,12 @@
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F35" s="0" t="n">
@@ -11780,7 +11855,12 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F36" s="0" t="n">
@@ -11805,7 +11885,12 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F37" s="0" t="n">
@@ -11830,7 +11915,12 @@
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F38" s="0" t="n">
@@ -11855,7 +11945,12 @@
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F39" s="0" t="n">
@@ -11880,7 +11975,12 @@
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F40" s="0" t="n">
@@ -11905,7 +12005,12 @@
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F41" s="0" t="n">
@@ -11930,7 +12035,12 @@
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F42" s="0" t="n">
@@ -11955,7 +12065,12 @@
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F43" s="0" t="n">
@@ -11980,7 +12095,12 @@
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F44" s="0" t="n">
@@ -12005,7 +12125,12 @@
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F45" s="0" t="n">
@@ -12030,7 +12155,12 @@
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F46" s="0" t="n">
@@ -12205,7 +12335,12 @@
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F52" s="0" t="n">
@@ -12230,7 +12365,12 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F53" s="0" t="n">
@@ -12255,7 +12395,12 @@
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F54" s="0" t="n">
@@ -12280,7 +12425,12 @@
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F55" s="0" t="n">
@@ -12305,7 +12455,12 @@
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F56" s="0" t="n">
@@ -12330,7 +12485,12 @@
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F57" s="0" t="n">
@@ -12355,7 +12515,12 @@
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F58" s="0" t="n">
@@ -12380,7 +12545,12 @@
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F59" s="0" t="n">
@@ -12405,7 +12575,12 @@
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F60" s="0" t="n">
@@ -12430,7 +12605,12 @@
       </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F61" s="0" t="n">
@@ -12455,7 +12635,12 @@
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F62" s="0" t="n">
@@ -12480,7 +12665,12 @@
       </c>
       <c r="D63" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F63" s="0" t="n">
@@ -12505,7 +12695,12 @@
       </c>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F64" s="0" t="n">
@@ -12530,7 +12725,12 @@
       </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E65" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F65" s="0" t="n">
@@ -12555,7 +12755,12 @@
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F66" s="0" t="n">
@@ -12580,7 +12785,12 @@
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F67" s="0" t="n">
@@ -12605,7 +12815,12 @@
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F68" s="0" t="n">
@@ -12630,7 +12845,12 @@
       </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F69" s="0" t="n">
@@ -12655,7 +12875,12 @@
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F70" s="0" t="n">
@@ -12680,7 +12905,12 @@
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E71" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F71" s="0" t="n">
@@ -12880,7 +13110,12 @@
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F79" s="0" t="n">
@@ -12905,7 +13140,12 @@
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F80" s="0" t="n">
@@ -12930,7 +13170,12 @@
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F81" s="0" t="n">
@@ -12955,7 +13200,12 @@
       </c>
       <c r="D82" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F82" s="0" t="n">
@@ -12980,7 +13230,12 @@
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F83" s="0" t="n">
@@ -13005,7 +13260,12 @@
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F84" s="0" t="n">
@@ -13030,7 +13290,12 @@
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F85" s="0" t="n">
@@ -13055,7 +13320,12 @@
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F86" s="0" t="n">
@@ -13080,7 +13350,12 @@
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F87" s="0" t="n">
@@ -13105,7 +13380,12 @@
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F88" s="0" t="n">
@@ -13130,7 +13410,12 @@
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F89" s="0" t="n">
@@ -13155,7 +13440,12 @@
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F90" s="0" t="n">
@@ -13180,7 +13470,12 @@
       </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F91" s="0" t="n">
@@ -13205,7 +13500,12 @@
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F92" s="0" t="n">
@@ -13226,7 +13526,12 @@
       <c r="C93" s="0" t="n"/>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F93" s="0" t="n">
@@ -13251,7 +13556,12 @@
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F94" s="0" t="n">
@@ -13276,7 +13586,12 @@
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F95" s="0" t="n">
@@ -13297,7 +13612,12 @@
       <c r="C96" s="0" t="n"/>
       <c r="D96" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F96" s="0" t="n">
@@ -13498,7 +13818,12 @@
       </c>
       <c r="D103" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F103" s="0" t="n">
@@ -13703,7 +14028,12 @@
       </c>
       <c r="D110" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F110" s="0" t="n">
@@ -13728,7 +14058,12 @@
       </c>
       <c r="D111" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F111" s="0" t="n">
@@ -13753,7 +14088,12 @@
       </c>
       <c r="D112" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F112" s="0" t="n">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · JIRA LGCOMMON-29612 · 요청자 Yerim Yeo · Due 2026-08-14 · 기존 UltraGear Gaming PLP 하단 FAQ에 1000Hz 문항 3건 추가 + 각국 번역 · 11개국 작업중 → 법인리뷰</t>
+          <t>완료 일괄(2026-09-02) · 11 Sites / 11 Pages 100% · 완료 11</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,12 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F4" s="0" t="n">
@@ -10557,7 +10562,12 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F5" s="0" t="n">
@@ -10582,7 +10592,12 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F6" s="0" t="n">
@@ -10607,7 +10622,12 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F7" s="0" t="n">
@@ -10632,7 +10652,12 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F8" s="0" t="n">
@@ -10657,7 +10682,12 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F9" s="0" t="n">
@@ -10682,7 +10712,12 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F10" s="0" t="n">
@@ -10707,7 +10742,12 @@
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F11" s="0" t="n">
@@ -10732,7 +10772,12 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F12" s="0" t="n">
@@ -10757,7 +10802,12 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F13" s="0" t="n">
@@ -10782,7 +10832,12 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F14" s="0" t="n">
@@ -11888,7 +11943,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
@@ -11918,7 +11973,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
@@ -12338,7 +12393,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="0" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -13143,7 +13198,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="0" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
@@ -13203,7 +13258,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" s="0" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
@@ -13293,7 +13348,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="0" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
@@ -13323,7 +13378,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" s="0" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -13443,7 +13498,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" s="0" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
@@ -13503,7 +13558,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E92" s="0" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
@@ -13529,7 +13584,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" s="0" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
@@ -13615,7 +13670,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="0" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -41041,10 +41041,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>NL : URL 변경
-SE : URL 변경
-JP : URL 오기입 정정(uk/ice-solution → jp/monitors/ultragear-evo)
-AU·DE : 법인리뷰 → 완료 (FILE2 FAQ 실측 반영)</t>
+          <t>JP 완료(2026-09-02) · 사이트 8/10 (80%) · 완료 17 · 법인리뷰 3 · 작업중 0</t>
         </is>
       </c>
       <c r="D2" s="164" t="n"/>
@@ -41059,6 +41056,10 @@
       <c r="F3" s="131" t="n"/>
       <c r="G3" s="127" t="n"/>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -41501,7 +41502,7 @@
       </c>
       <c r="D22" s="273" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E22" s="288" t="inlineStr">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -41056,10 +41056,6 @@
       <c r="F3" s="131" t="n"/>
       <c r="G3" s="127" t="n"/>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -41507,12 +41503,14 @@
       </c>
       <c r="E22" s="288" t="inlineStr">
         <is>
-          <t>미게시(법인리뷰) · STG 경로 기준</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F22" s="275" t="n"/>
-      <c r="G22" s="177" t="n">
-        <v>2</v>
+      <c r="G22" s="177" t="inlineStr">
+        <is>
+          <t>2 · 미게시(법인리뷰) · STG 경로 기준</t>
+        </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -41506,10 +41506,12 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F22" s="275" t="n"/>
+      <c r="F22" s="275" t="n">
+        <v>2</v>
+      </c>
       <c r="G22" s="177" t="inlineStr">
         <is>
-          <t>2 · 미게시(법인리뷰) · STG 경로 기준</t>
+          <t>미게시(법인리뷰) · STG 경로 기준</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -17834,7 +17834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="203" min="1" max="1"/>
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · 요청자 Yujin Han(한유진 사원) · 요청 2026-07-30 · Due 2026-08-30 · 대상 8모델 × 22개국 (요청서 Target List + CMS/PTT 신규 10건 보강)</t>
+          <t>타겟 보강(2026-09-03) · URL 채움 12 · 신규 행 1 · 행 57 · URL 50 · 사이트 21 · 작업중 57</t>
         </is>
       </c>
     </row>
@@ -17913,7 +17913,11 @@
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr"/>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/consumer-monitors/lg-24u511sb-b</t>
+        </is>
+      </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -17935,7 +17939,11 @@
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr"/>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/consumer-monitors/lg-27u511sb-w</t>
+        </is>
+      </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -17957,7 +17965,11 @@
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr"/>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/consumer-monitors/lg-32u501sb-b</t>
+        </is>
+      </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -17979,7 +17991,11 @@
           <t>AE : AE (en)</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr"/>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/consumer-monitors/lg-32u701sb-b</t>
+        </is>
+      </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -18001,7 +18017,11 @@
           <t>AE_AR : AE (ar)</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr"/>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae_ar/consumer-monitors/lg-24u511sb-b</t>
+        </is>
+      </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -18023,7 +18043,11 @@
           <t>AE_AR : AE (ar)</t>
         </is>
       </c>
-      <c r="C9" s="0" t="inlineStr"/>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae_ar/consumer-monitors/lg-27u511sb-w</t>
+        </is>
+      </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -18045,7 +18069,11 @@
           <t>AE_AR : AE (ar)</t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr"/>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae_ar/consumer-monitors/lg-32u501sb-b</t>
+        </is>
+      </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -18319,7 +18347,11 @@
           <t>CZ : CZ (cs)</t>
         </is>
       </c>
-      <c r="C21" s="0" t="inlineStr"/>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/smart/24u511sb-b/</t>
+        </is>
+      </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -18341,7 +18373,11 @@
           <t>CZ : CZ (cs)</t>
         </is>
       </c>
-      <c r="C22" s="0" t="inlineStr"/>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/ultrafine-uhd-4k-monitory/27u511sb-w/</t>
+        </is>
+      </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -18353,7 +18389,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규 · White</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18399,11 @@
           <t>CZ : CZ (cs)</t>
         </is>
       </c>
-      <c r="C23" s="0" t="inlineStr"/>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/smart/32u721sb-w/</t>
+        </is>
+      </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -19227,7 +19267,11 @@
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C57" s="0" t="inlineStr"/>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/smart-monitors/32u501sb-b/</t>
+        </is>
+      </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -19249,7 +19293,11 @@
           <t>UK : GB (en)</t>
         </is>
       </c>
-      <c r="C58" s="0" t="inlineStr"/>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/monitors/ultrawide/32u721sb-w/</t>
+        </is>
+      </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
           <t>작업중</t>
@@ -19284,6 +19332,32 @@
       <c r="G59" s="0" t="inlineStr">
         <is>
           <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>CZ : CZ (cs)</t>
+        </is>
+      </c>
+      <c r="C60" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/monitory/ultrafine-uhd-4k-monitory/27u511sb-b/</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="n"/>
+      <c r="F60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
+        <is>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 타겟 보강(2026-09-03) · Black</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>타겟 보강(2026-09-03) · URL 채움 12 · 신규 행 1 · 행 57 · URL 50 · 사이트 21 · 작업중 57</t>
+          <t>진행 업데이트(2026-09-07) · 사이트 완료 5/21 (24%) · 완료 16 · 작업중 41</t>
         </is>
       </c>
     </row>
@@ -18354,10 +18354,14 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="F21" s="0" t="n">
         <v>1</v>
       </c>
@@ -18432,10 +18436,14 @@
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E24" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
       <c r="F24" s="0" t="n">
         <v>1</v>
       </c>
@@ -18562,10 +18570,14 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E29" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
       <c r="F29" s="0" t="n">
         <v>1</v>
       </c>
@@ -18588,10 +18600,14 @@
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E30" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="F30" s="0" t="n">
         <v>1</v>
       </c>
@@ -18692,10 +18708,14 @@
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E34" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="F34" s="0" t="n">
         <v>1</v>
       </c>
@@ -18718,10 +18738,14 @@
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E35" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
       <c r="F35" s="0" t="n">
         <v>1</v>
       </c>
@@ -18744,10 +18768,14 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E36" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
       <c r="F36" s="0" t="n">
         <v>1</v>
       </c>
@@ -18770,10 +18798,14 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E37" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="F37" s="0" t="n">
         <v>1</v>
       </c>
@@ -18796,10 +18828,14 @@
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E38" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="F38" s="0" t="n">
         <v>1</v>
       </c>
@@ -18822,10 +18858,14 @@
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E39" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
       <c r="F39" s="0" t="n">
         <v>1</v>
       </c>
@@ -19104,10 +19144,14 @@
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E50" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
       <c r="F50" s="0" t="n">
         <v>1</v>
       </c>
@@ -19174,10 +19218,14 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E53" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="F53" s="0" t="n">
         <v>1</v>
       </c>
@@ -19200,10 +19248,14 @@
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E54" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="F54" s="0" t="n">
         <v>1</v>
       </c>
@@ -19226,10 +19278,14 @@
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E55" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
       <c r="F55" s="0" t="n">
         <v>1</v>
       </c>
@@ -19274,10 +19330,14 @@
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E57" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
       <c r="F57" s="0" t="n">
         <v>1</v>
       </c>
@@ -19300,10 +19360,14 @@
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E58" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="F58" s="0" t="n">
         <v>1</v>
       </c>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -18359,7 +18359,7 @@
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F21" s="0" t="n">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F24" s="0" t="n">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F29" s="0" t="n">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F30" s="0" t="n">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F34" s="0" t="n">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F35" s="0" t="n">
@@ -18773,7 +18773,7 @@
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F36" s="0" t="n">
@@ -18803,7 +18803,7 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F37" s="0" t="n">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F38" s="0" t="n">
@@ -18863,7 +18863,7 @@
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F39" s="0" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F50" s="0" t="n">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F53" s="0" t="n">
@@ -19253,7 +19253,7 @@
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F54" s="0" t="n">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F55" s="0" t="n">
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F57" s="0" t="n">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F58" s="0" t="n">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -18359,7 +18359,7 @@
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F21" s="0" t="n">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F24" s="0" t="n">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F29" s="0" t="n">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F30" s="0" t="n">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F34" s="0" t="n">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F35" s="0" t="n">
@@ -18773,7 +18773,7 @@
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F36" s="0" t="n">
@@ -18803,7 +18803,7 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F37" s="0" t="n">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F38" s="0" t="n">
@@ -18863,7 +18863,7 @@
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F39" s="0" t="n">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F50" s="0" t="n">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F53" s="0" t="n">
@@ -19253,7 +19253,7 @@
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F54" s="0" t="n">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F55" s="0" t="n">
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F57" s="0" t="n">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F58" s="0" t="n">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -17829,7 +17829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>진행 업데이트(2026-09-07) · 사이트 완료 5/21 (24%) · 완료 16 · 작업중 41</t>
+          <t>진행 업데이트(2026-09-07) · 사이트 완료 8/21 (38%) · 완료 24 · 작업중 33</t>
         </is>
       </c>
     </row>
@@ -18466,7 +18466,7 @@
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr"/>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr"/>
@@ -18630,7 +18630,7 @@
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr"/>
@@ -18656,7 +18656,7 @@
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr"/>
@@ -18682,7 +18682,7 @@
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr"/>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E47" s="0" t="inlineStr"/>
@@ -19092,7 +19092,7 @@
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E48" s="0" t="inlineStr"/>
@@ -19427,43 +19427,43 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId37"/>
+    <hyperlink ref="C13" r:id="rId1"/>
+    <hyperlink ref="C14" r:id="rId2"/>
+    <hyperlink ref="C15" r:id="rId3"/>
+    <hyperlink ref="C16" r:id="rId4"/>
+    <hyperlink ref="C17" r:id="rId5"/>
+    <hyperlink ref="C18" r:id="rId6"/>
+    <hyperlink ref="C19" r:id="rId7"/>
+    <hyperlink ref="C20" r:id="rId8"/>
+    <hyperlink ref="C24" r:id="rId9"/>
+    <hyperlink ref="C25" r:id="rId10"/>
+    <hyperlink ref="C26" r:id="rId11"/>
+    <hyperlink ref="C27" r:id="rId12"/>
+    <hyperlink ref="C28" r:id="rId13"/>
+    <hyperlink ref="C29" r:id="rId14"/>
+    <hyperlink ref="C30" r:id="rId15"/>
+    <hyperlink ref="C31" r:id="rId16"/>
+    <hyperlink ref="C32" r:id="rId17"/>
+    <hyperlink ref="C33" r:id="rId18"/>
+    <hyperlink ref="C34" r:id="rId19"/>
+    <hyperlink ref="C35" r:id="rId20"/>
+    <hyperlink ref="C36" r:id="rId21"/>
+    <hyperlink ref="C37" r:id="rId22"/>
+    <hyperlink ref="C38" r:id="rId23"/>
+    <hyperlink ref="C39" r:id="rId24"/>
+    <hyperlink ref="C40" r:id="rId25"/>
+    <hyperlink ref="C41" r:id="rId26"/>
+    <hyperlink ref="C43" r:id="rId27"/>
+    <hyperlink ref="C44" r:id="rId28"/>
+    <hyperlink ref="C45" r:id="rId29"/>
+    <hyperlink ref="C46" r:id="rId30"/>
+    <hyperlink ref="C47" r:id="rId31"/>
+    <hyperlink ref="C48" r:id="rId32"/>
+    <hyperlink ref="C49" r:id="rId33"/>
+    <hyperlink ref="C50" r:id="rId34"/>
+    <hyperlink ref="C53" r:id="rId35"/>
+    <hyperlink ref="C54" r:id="rId36"/>
+    <hyperlink ref="C55" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -17829,7 +17829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>진행 업데이트(2026-09-07) · 사이트 완료 8/21 (38%) · 완료 24 · 작업중 33</t>
+          <t>진행 업데이트(2026-09-07) · 사이트 완료 9/21 (43%) · 완료 25 · 작업중 32</t>
         </is>
       </c>
     </row>
@@ -19069,7 +19069,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E47" s="0" t="inlineStr"/>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="F47" s="0" t="n">
         <v>1</v>
       </c>
@@ -19095,7 +19099,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E48" s="0" t="inlineStr"/>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="F48" s="0" t="n">
         <v>1</v>
       </c>
@@ -19118,10 +19126,14 @@
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E49" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="F49" s="0" t="n">
         <v>1</v>
       </c>
@@ -19427,43 +19439,43 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C13" r:id="rId1"/>
-    <hyperlink ref="C14" r:id="rId2"/>
-    <hyperlink ref="C15" r:id="rId3"/>
-    <hyperlink ref="C16" r:id="rId4"/>
-    <hyperlink ref="C17" r:id="rId5"/>
-    <hyperlink ref="C18" r:id="rId6"/>
-    <hyperlink ref="C19" r:id="rId7"/>
-    <hyperlink ref="C20" r:id="rId8"/>
-    <hyperlink ref="C24" r:id="rId9"/>
-    <hyperlink ref="C25" r:id="rId10"/>
-    <hyperlink ref="C26" r:id="rId11"/>
-    <hyperlink ref="C27" r:id="rId12"/>
-    <hyperlink ref="C28" r:id="rId13"/>
-    <hyperlink ref="C29" r:id="rId14"/>
-    <hyperlink ref="C30" r:id="rId15"/>
-    <hyperlink ref="C31" r:id="rId16"/>
-    <hyperlink ref="C32" r:id="rId17"/>
-    <hyperlink ref="C33" r:id="rId18"/>
-    <hyperlink ref="C34" r:id="rId19"/>
-    <hyperlink ref="C35" r:id="rId20"/>
-    <hyperlink ref="C36" r:id="rId21"/>
-    <hyperlink ref="C37" r:id="rId22"/>
-    <hyperlink ref="C38" r:id="rId23"/>
-    <hyperlink ref="C39" r:id="rId24"/>
-    <hyperlink ref="C40" r:id="rId25"/>
-    <hyperlink ref="C41" r:id="rId26"/>
-    <hyperlink ref="C43" r:id="rId27"/>
-    <hyperlink ref="C44" r:id="rId28"/>
-    <hyperlink ref="C45" r:id="rId29"/>
-    <hyperlink ref="C46" r:id="rId30"/>
-    <hyperlink ref="C47" r:id="rId31"/>
-    <hyperlink ref="C48" r:id="rId32"/>
-    <hyperlink ref="C49" r:id="rId33"/>
-    <hyperlink ref="C50" r:id="rId34"/>
-    <hyperlink ref="C53" r:id="rId35"/>
-    <hyperlink ref="C54" r:id="rId36"/>
-    <hyperlink ref="C55" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -41191,7 +41191,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>JP 완료(2026-09-02) · 사이트 8/10 (80%) · 완료 17 · 법인리뷰 3 · 작업중 0</t>
+          <t>ES 완료(2026-09-11) · 사이트 9/10 (90%) · 완료 18 · 법인리뷰 2 · 작업중 0</t>
         </is>
       </c>
       <c r="D2" s="164" t="n"/>
@@ -41507,17 +41507,21 @@
       </c>
       <c r="D17" s="273" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E17" s="288" t="n"/>
-      <c r="F17" s="270" t="n"/>
+      <c r="F17" s="270" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="G17" s="177" t="n">
         <v>2</v>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>evo FAQ 미게시 · Hyper 페이지/FAQ 게시 대기</t>
+          <t>evo·Hyper FAQ 게시 완료</t>
         </is>
       </c>
     </row>
@@ -41651,22 +41655,18 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E22" s="288" t="inlineStr">
+      <c r="E22" s="288" t="n"/>
+      <c r="F22" s="275" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F22" s="275" t="n">
+      <c r="G22" s="177" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="177" t="inlineStr">
-        <is>
-          <t>미게시(법인리뷰) · STG 경로 기준</t>
-        </is>
-      </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>페이지/FAQ 게시 대기 (evo·Hyper)</t>
+          <t>evo·Hyper FAQ 게시 완료</t>
         </is>
       </c>
     </row>
